--- a/SKTC_CpZr_Capacity_RawData_Calculation_2026_2028.xlsx
+++ b/SKTC_CpZr_Capacity_RawData_Calculation_2026_2028.xlsx
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2030" uniqueCount="1053">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2031" uniqueCount="1057">
   <si>
     <r>
       <rPr>
@@ -7849,6 +7849,184 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2028 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 수정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· 2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하반기 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">1,120 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">아님</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">사용자 수정 지시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2026-10-01)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">용기</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">/</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">연 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">10,080 kg</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
@@ -8548,6 +8726,65 @@
   <si>
     <r>
       <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">840 kg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가정 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(2027 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">하반기 수준과 다름</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
         <b val="true"/>
         <sz val="9"/>
         <color rgb="FF000000"/>
@@ -8751,7 +8988,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">49,120 kg</t>
+      <t xml:space="preserve">45,760 kg</t>
     </r>
   </si>
   <si>
@@ -8871,7 +9108,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">= 49,120 kg</t>
+      <t xml:space="preserve">= 45,760 kg</t>
     </r>
   </si>
   <si>
@@ -21329,7 +21566,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">톤 기준</t>
+      <t xml:space="preserve">톤 기준 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이지켐 월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">840 kg </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">가정</t>
     </r>
   </si>
   <si>
@@ -22582,20 +22857,29 @@
       <rPr>
         <sz val="9"/>
         <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.92</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">톤 부족 방향</t>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">기본 시나리오 — 방향은 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">E</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">열</t>
     </r>
   </si>
   <si>
@@ -22668,25 +22952,7 @@
     </r>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1.08</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">톤 여유 방향 — 미확정</t>
-    </r>
+    <t xml:space="preserve">검토안 — 미확정</t>
   </si>
   <si>
     <r>
@@ -24041,18 +24307,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">기준 시 −</t>
-    </r>
-    <r>
-      <rPr>
-        <i val="true"/>
-        <sz val="9"/>
-        <color rgb="FF7F7F7F"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">1,920</t>
+      <t xml:space="preserve">균등 환산 기준</t>
     </r>
   </si>
   <si>
@@ -27953,11 +28208,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="74199575"/>
-        <c:axId val="66549688"/>
+        <c:axId val="96233383"/>
+        <c:axId val="20192760"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="74199575"/>
+        <c:axId val="96233383"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -27989,7 +28244,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="66549688"/>
+        <c:crossAx val="20192760"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -27997,7 +28252,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="66549688"/>
+        <c:axId val="20192760"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -28039,7 +28294,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="74199575"/>
+        <c:crossAx val="96233383"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -28358,40 +28613,40 @@
                   <c:v>4093.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="24">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="25">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="26">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="27">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="28">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="29">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="30">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="31">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="32">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="33">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="34">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
                 <c:pt idx="35">
-                  <c:v>4093.33333333333</c:v>
+                  <c:v>3813.33333333333</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -28684,11 +28939,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="49729966"/>
-        <c:axId val="2452718"/>
+        <c:axId val="83994883"/>
+        <c:axId val="32617448"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="49729966"/>
+        <c:axId val="83994883"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -28720,7 +28975,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2452718"/>
+        <c:crossAx val="32617448"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -28728,7 +28983,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="2452718"/>
+        <c:axId val="32617448"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -28770,7 +29025,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="49729966"/>
+        <c:crossAx val="83994883"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -31477,25 +31732,27 @@
         <v>307</v>
       </c>
       <c r="B121" s="31" t="n">
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="C121" s="9" t="s">
         <v>292</v>
       </c>
       <c r="D121" s="9" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="E121" s="13" t="s">
         <v>111</v>
       </c>
       <c r="F121" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="G121" s="9"/>
+        <v>309</v>
+      </c>
+      <c r="G121" s="9" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="122" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A122" s="13" t="s">
-        <v>308</v>
+        <v>311</v>
       </c>
       <c r="B122" s="31" t="n">
         <v>300</v>
@@ -31516,57 +31773,57 @@
     </row>
     <row r="124" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A124" s="32" t="s">
-        <v>309</v>
+        <v>312</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="11" t="s">
-        <v>310</v>
+        <v>313</v>
       </c>
       <c r="B125" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C125" s="33" t="s">
-        <v>312</v>
+        <v>315</v>
       </c>
       <c r="D125" s="33" t="s">
-        <v>313</v>
+        <v>316</v>
       </c>
       <c r="E125" s="33" t="s">
-        <v>314</v>
+        <v>317</v>
       </c>
       <c r="F125" s="33" t="s">
-        <v>315</v>
+        <v>318</v>
       </c>
       <c r="G125" s="33" t="s">
-        <v>316</v>
+        <v>319</v>
       </c>
       <c r="H125" s="33" t="s">
-        <v>317</v>
+        <v>320</v>
       </c>
       <c r="I125" s="33" t="s">
-        <v>318</v>
+        <v>321</v>
       </c>
       <c r="J125" s="33" t="s">
-        <v>319</v>
+        <v>322</v>
       </c>
       <c r="K125" s="33" t="s">
-        <v>320</v>
+        <v>323</v>
       </c>
       <c r="L125" s="33" t="s">
-        <v>321</v>
+        <v>324</v>
       </c>
       <c r="M125" s="33" t="s">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="N125" s="33" t="s">
-        <v>323</v>
+        <v>326</v>
       </c>
       <c r="O125" s="11" t="s">
-        <v>324</v>
+        <v>327</v>
       </c>
       <c r="P125" s="11" t="s">
-        <v>325</v>
+        <v>328</v>
       </c>
       <c r="Q125" s="11" t="s">
         <v>15</v>
@@ -31577,7 +31834,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B126" s="16" t="n">
         <v>2026</v>
@@ -31623,7 +31880,7 @@
         <v>16980</v>
       </c>
       <c r="P126" s="13" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q126" s="13" t="s">
         <v>22</v>
@@ -31632,7 +31889,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B127" s="16" t="n">
         <v>2026</v>
@@ -31654,13 +31911,13 @@
         <v>미제시</v>
       </c>
       <c r="P127" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q127" s="13" t="s">
         <v>22</v>
       </c>
       <c r="R127" s="13" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31711,13 +31968,13 @@
         <v>2240</v>
       </c>
       <c r="P128" s="13" t="s">
-        <v>327</v>
+        <v>330</v>
       </c>
       <c r="Q128" s="13" t="s">
         <v>22</v>
       </c>
       <c r="R128" s="9" t="s">
-        <v>331</v>
+        <v>334</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31744,18 +32001,18 @@
         <v>미제시</v>
       </c>
       <c r="P129" s="13" t="s">
-        <v>329</v>
+        <v>332</v>
       </c>
       <c r="Q129" s="13" t="s">
         <v>22</v>
       </c>
       <c r="R129" s="13" t="s">
-        <v>330</v>
+        <v>333</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A130" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B130" s="16" t="n">
         <v>2027</v>
@@ -31819,12 +32076,12 @@
         <v>22</v>
       </c>
       <c r="R130" s="9" t="s">
-        <v>332</v>
+        <v>335</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A131" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B131" s="16" t="n">
         <v>2027</v>
@@ -31888,7 +32145,7 @@
         <v>22</v>
       </c>
       <c r="R131" s="9" t="s">
-        <v>333</v>
+        <v>336</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -31957,7 +32214,7 @@
         <v>22</v>
       </c>
       <c r="R132" s="9" t="s">
-        <v>334</v>
+        <v>337</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32026,12 +32283,12 @@
         <v>22</v>
       </c>
       <c r="R133" s="13" t="s">
-        <v>335</v>
+        <v>338</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="13" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="B134" s="16" t="n">
         <v>2028</v>
@@ -32100,7 +32357,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A135" s="9" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="B135" s="16" t="n">
         <v>2028</v>
@@ -32176,64 +32433,64 @@
       </c>
       <c r="C136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="D136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="E136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="G136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="H136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="I136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="J136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="K136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="L136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="M136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="N136" s="37" t="n">
         <f aca="false">01_Inputs!$B$121</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="O136" s="35" t="n">
         <f aca="false">IF(COUNT(C136:N136)=0,"미제시",SUM(C136:N136))</f>
-        <v>13440</v>
+        <v>10080</v>
       </c>
       <c r="P136" s="13" t="s">
         <v>111</v>
       </c>
       <c r="Q136" s="13" t="s">
-        <v>22</v>
-      </c>
-      <c r="R136" s="9" t="s">
-        <v>304</v>
+        <v>309</v>
+      </c>
+      <c r="R136" s="13" t="s">
+        <v>339</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32307,7 +32564,7 @@
     </row>
     <row r="138" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A138" s="38" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="B138" s="16" t="n">
         <v>2026</v>
@@ -32365,18 +32622,18 @@
         <v>19220</v>
       </c>
       <c r="P138" s="13" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q138" s="13" t="s">
         <v>35</v>
       </c>
       <c r="R138" s="9" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A139" s="38" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B139" s="16" t="n">
         <v>2027</v>
@@ -32434,87 +32691,87 @@
         <v>43400</v>
       </c>
       <c r="P139" s="13" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q139" s="13" t="s">
         <v>35</v>
       </c>
       <c r="R139" s="13" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A140" s="38" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B140" s="16" t="n">
         <v>2028</v>
       </c>
       <c r="C140" s="35" t="n">
         <f aca="false">N(C134)+N(C135)+N(C136)+N(C137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="D140" s="35" t="n">
         <f aca="false">N(D134)+N(D135)+N(D136)+N(D137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="E140" s="35" t="n">
         <f aca="false">N(E134)+N(E135)+N(E136)+N(E137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="F140" s="35" t="n">
         <f aca="false">N(F134)+N(F135)+N(F136)+N(F137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="G140" s="35" t="n">
         <f aca="false">N(G134)+N(G135)+N(G136)+N(G137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H140" s="35" t="n">
         <f aca="false">N(H134)+N(H135)+N(H136)+N(H137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="I140" s="35" t="n">
         <f aca="false">N(I134)+N(I135)+N(I136)+N(I137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="J140" s="35" t="n">
         <f aca="false">N(J134)+N(J135)+N(J136)+N(J137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="K140" s="35" t="n">
         <f aca="false">N(K134)+N(K135)+N(K136)+N(K137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="L140" s="35" t="n">
         <f aca="false">N(L134)+N(L135)+N(L136)+N(L137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="M140" s="35" t="n">
         <f aca="false">N(M134)+N(M135)+N(M136)+N(M137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="N140" s="35" t="n">
         <f aca="false">N(N134)+N(N135)+N(N136)+N(N137)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="O140" s="35" t="n">
         <f aca="false">SUM(C140:N140)</f>
-        <v>49120</v>
+        <v>45760</v>
       </c>
       <c r="P140" s="13" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="Q140" s="13" t="s">
         <v>35</v>
       </c>
       <c r="R140" s="13" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A141" s="13" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="O141" s="39" t="str">
         <f aca="false">IF(ABS(O138-19220)&lt;0.001,"일치","불일치")</f>
@@ -32523,7 +32780,7 @@
     </row>
     <row r="142" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A142" s="13" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="O142" s="39" t="str">
         <f aca="false">IF(ABS(O139-43400)&lt;0.001,"일치","불일치")</f>
@@ -32532,10 +32789,10 @@
     </row>
     <row r="143" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A143" s="13" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="O143" s="39" t="str">
-        <f aca="false">IF(ABS(O140-49120)&lt;0.001,"일치","불일치")</f>
+        <f aca="false">IF(ABS(O140-45760)&lt;0.001,"일치","불일치")</f>
         <v>일치</v>
       </c>
     </row>
@@ -32600,12 +32857,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32654,82 +32911,82 @@
     </row>
     <row r="5" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="33" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="D5" s="33" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="O5" s="41" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="P5" s="41" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="Q5" s="41" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="R5" s="41" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="S5" s="41" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="T5" s="41" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="U5" s="41" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="V5" s="41" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="W5" s="41" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="X5" s="41" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="Y5" s="41" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="Z5" s="41" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -32737,10 +32994,10 @@
         <v>1</v>
       </c>
       <c r="B6" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C6" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D6" s="3" t="n">
         <v>37</v>
@@ -32751,14 +33008,14 @@
       <c r="F6" s="5"/>
       <c r="G6" s="5"/>
       <c r="H6" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I6" s="42" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J6" s="5"/>
       <c r="K6" s="3" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="L6" s="3" t="n">
         <v>23</v>
@@ -32809,10 +33066,10 @@
         <v>2</v>
       </c>
       <c r="B7" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C7" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D7" s="3" t="n">
         <v>38</v>
@@ -32823,14 +33080,14 @@
       <c r="F7" s="5"/>
       <c r="G7" s="5"/>
       <c r="H7" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I7" s="42" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="J7" s="5"/>
       <c r="K7" s="3" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="L7" s="3" t="n">
         <v>26</v>
@@ -32896,10 +33153,10 @@
         <v>3</v>
       </c>
       <c r="B8" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C8" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D8" s="3" t="n">
         <v>39</v>
@@ -32910,10 +33167,10 @@
       <c r="F8" s="5"/>
       <c r="G8" s="5"/>
       <c r="H8" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I8" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J8" s="5"/>
       <c r="K8" s="3" t="s">
@@ -32983,10 +33240,10 @@
         <v>4</v>
       </c>
       <c r="B9" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D9" s="3" t="n">
         <v>40</v>
@@ -32997,14 +33254,14 @@
       <c r="F9" s="5"/>
       <c r="G9" s="5"/>
       <c r="H9" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I9" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J9" s="5"/>
       <c r="K9" s="3" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="L9" s="3" t="n">
         <v>5</v>
@@ -33070,10 +33327,10 @@
         <v>5</v>
       </c>
       <c r="B10" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D10" s="3" t="n">
         <v>41</v>
@@ -33084,14 +33341,14 @@
       <c r="F10" s="5"/>
       <c r="G10" s="5"/>
       <c r="H10" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I10" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J10" s="5"/>
       <c r="K10" s="3" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="L10" s="3" t="n">
         <v>8</v>
@@ -33157,10 +33414,10 @@
         <v>6</v>
       </c>
       <c r="B11" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D11" s="3" t="n">
         <v>42</v>
@@ -33171,14 +33428,14 @@
       <c r="F11" s="5"/>
       <c r="G11" s="5"/>
       <c r="H11" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I11" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J11" s="5"/>
       <c r="K11" s="3" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="L11" s="3" t="n">
         <v>11</v>
@@ -33244,10 +33501,10 @@
         <v>7</v>
       </c>
       <c r="B12" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D12" s="3" t="n">
         <v>43</v>
@@ -33258,14 +33515,14 @@
       <c r="F12" s="5"/>
       <c r="G12" s="5"/>
       <c r="H12" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I12" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J12" s="5"/>
       <c r="K12" s="3" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="L12" s="3" t="n">
         <v>14</v>
@@ -33331,10 +33588,10 @@
         <v>8</v>
       </c>
       <c r="B13" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>44</v>
@@ -33345,14 +33602,14 @@
       <c r="F13" s="5"/>
       <c r="G13" s="5"/>
       <c r="H13" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I13" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J13" s="5"/>
       <c r="K13" s="3" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="L13" s="3" t="n">
         <v>17</v>
@@ -33418,10 +33675,10 @@
         <v>9</v>
       </c>
       <c r="B14" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C14" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D14" s="3" t="n">
         <v>45</v>
@@ -33432,14 +33689,14 @@
       <c r="F14" s="5"/>
       <c r="G14" s="5"/>
       <c r="H14" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I14" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J14" s="5"/>
       <c r="K14" s="3" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="L14" s="3" t="n">
         <v>20</v>
@@ -33505,10 +33762,10 @@
         <v>10</v>
       </c>
       <c r="B15" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C15" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D15" s="3" t="n">
         <v>46</v>
@@ -33519,14 +33776,14 @@
       <c r="F15" s="5"/>
       <c r="G15" s="5"/>
       <c r="H15" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I15" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J15" s="5"/>
       <c r="K15" s="3" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="L15" s="3" t="n">
         <v>23</v>
@@ -33592,10 +33849,10 @@
         <v>11</v>
       </c>
       <c r="B16" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D16" s="3" t="n">
         <v>47</v>
@@ -33606,14 +33863,14 @@
       <c r="F16" s="5"/>
       <c r="G16" s="5"/>
       <c r="H16" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I16" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J16" s="5"/>
       <c r="K16" s="3" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="L16" s="3" t="n">
         <v>25</v>
@@ -33679,10 +33936,10 @@
         <v>12</v>
       </c>
       <c r="B17" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D17" s="3" t="n">
         <v>48</v>
@@ -33693,14 +33950,14 @@
       <c r="F17" s="5"/>
       <c r="G17" s="5"/>
       <c r="H17" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I17" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J17" s="5"/>
       <c r="K17" s="3" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="L17" s="3" t="n">
         <v>27</v>
@@ -33766,10 +34023,10 @@
         <v>13</v>
       </c>
       <c r="B18" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D18" s="3" t="n">
         <v>49</v>
@@ -33780,14 +34037,14 @@
       <c r="F18" s="5"/>
       <c r="G18" s="5"/>
       <c r="H18" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I18" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J18" s="5"/>
       <c r="K18" s="3" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="L18" s="3" t="n">
         <v>28</v>
@@ -33853,10 +34110,10 @@
         <v>14</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D19" s="3" t="n">
         <v>50</v>
@@ -33867,14 +34124,14 @@
       <c r="F19" s="5"/>
       <c r="G19" s="5"/>
       <c r="H19" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I19" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J19" s="5"/>
       <c r="K19" s="3" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="L19" s="3" t="n">
         <v>1</v>
@@ -33940,10 +34197,10 @@
         <v>15</v>
       </c>
       <c r="B20" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D20" s="3" t="n">
         <v>51</v>
@@ -33954,14 +34211,14 @@
       <c r="F20" s="5"/>
       <c r="G20" s="5"/>
       <c r="H20" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I20" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J20" s="5"/>
       <c r="K20" s="3" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="L20" s="3" t="n">
         <v>3</v>
@@ -34027,10 +34284,10 @@
         <v>16</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C21" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D21" s="3" t="n">
         <v>52</v>
@@ -34041,14 +34298,14 @@
       <c r="F21" s="5"/>
       <c r="G21" s="5"/>
       <c r="H21" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I21" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J21" s="5"/>
       <c r="K21" s="3" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="L21" s="3" t="n">
         <v>6</v>
@@ -34114,10 +34371,10 @@
         <v>17</v>
       </c>
       <c r="B22" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C22" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D22" s="3" t="n">
         <v>53</v>
@@ -34128,14 +34385,14 @@
       <c r="F22" s="5"/>
       <c r="G22" s="5"/>
       <c r="H22" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I22" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J22" s="5"/>
       <c r="K22" s="3" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="L22" s="3" t="n">
         <v>8</v>
@@ -34201,10 +34458,10 @@
         <v>18</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C23" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D23" s="3" t="n">
         <v>54</v>
@@ -34215,14 +34472,14 @@
       <c r="F23" s="5"/>
       <c r="G23" s="5"/>
       <c r="H23" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I23" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J23" s="5"/>
       <c r="K23" s="3" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="L23" s="3" t="n">
         <v>11</v>
@@ -34288,10 +34545,10 @@
         <v>19</v>
       </c>
       <c r="B24" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C24" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D24" s="3" t="n">
         <v>55</v>
@@ -34302,14 +34559,14 @@
       <c r="F24" s="5"/>
       <c r="G24" s="5"/>
       <c r="H24" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I24" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J24" s="5"/>
       <c r="K24" s="3" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="L24" s="3" t="n">
         <v>14</v>
@@ -34375,10 +34632,10 @@
         <v>20</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C25" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D25" s="3" t="n">
         <v>56</v>
@@ -34389,14 +34646,14 @@
       <c r="F25" s="5"/>
       <c r="G25" s="5"/>
       <c r="H25" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I25" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J25" s="5"/>
       <c r="K25" s="3" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="L25" s="3" t="n">
         <v>17</v>
@@ -34462,10 +34719,10 @@
         <v>21</v>
       </c>
       <c r="B26" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C26" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D26" s="3" t="n">
         <v>57</v>
@@ -34476,14 +34733,14 @@
       <c r="F26" s="5"/>
       <c r="G26" s="5"/>
       <c r="H26" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I26" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J26" s="5"/>
       <c r="K26" s="3" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="L26" s="3" t="n">
         <v>20</v>
@@ -34549,10 +34806,10 @@
         <v>22</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C27" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D27" s="3" t="n">
         <v>58</v>
@@ -34563,14 +34820,14 @@
       <c r="F27" s="5"/>
       <c r="G27" s="5"/>
       <c r="H27" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I27" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J27" s="5"/>
       <c r="K27" s="3" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="L27" s="3" t="n">
         <v>23</v>
@@ -34636,10 +34893,10 @@
         <v>23</v>
       </c>
       <c r="B28" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C28" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D28" s="3" t="n">
         <v>59</v>
@@ -34650,14 +34907,14 @@
       <c r="F28" s="5"/>
       <c r="G28" s="5"/>
       <c r="H28" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I28" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J28" s="5"/>
       <c r="K28" s="3" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="L28" s="3" t="n">
         <v>26</v>
@@ -34723,10 +34980,10 @@
         <v>24</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C29" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D29" s="3" t="n">
         <v>60</v>
@@ -34737,14 +34994,14 @@
       <c r="F29" s="5"/>
       <c r="G29" s="5"/>
       <c r="H29" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I29" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J29" s="5"/>
       <c r="K29" s="3" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="L29" s="3" t="n">
         <v>29</v>
@@ -34810,10 +35067,10 @@
         <v>25</v>
       </c>
       <c r="B30" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C30" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D30" s="3" t="n">
         <v>61</v>
@@ -34824,14 +35081,14 @@
       <c r="F30" s="5"/>
       <c r="G30" s="5"/>
       <c r="H30" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I30" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J30" s="5"/>
       <c r="K30" s="3" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="L30" s="3" t="n">
         <v>1</v>
@@ -34897,10 +35154,10 @@
         <v>26</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C31" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D31" s="3" t="n">
         <v>62</v>
@@ -34911,14 +35168,14 @@
       <c r="F31" s="5"/>
       <c r="G31" s="5"/>
       <c r="H31" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I31" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J31" s="5"/>
       <c r="K31" s="3" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="L31" s="3" t="n">
         <v>4</v>
@@ -34984,10 +35241,10 @@
         <v>27</v>
       </c>
       <c r="B32" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D32" s="3" t="n">
         <v>63</v>
@@ -34998,14 +35255,14 @@
       <c r="F32" s="5"/>
       <c r="G32" s="5"/>
       <c r="H32" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I32" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J32" s="5"/>
       <c r="K32" s="3" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="L32" s="3" t="n">
         <v>7</v>
@@ -35071,10 +35328,10 @@
         <v>28</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C33" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D33" s="3" t="n">
         <v>64</v>
@@ -35085,14 +35342,14 @@
       <c r="F33" s="5"/>
       <c r="G33" s="5"/>
       <c r="H33" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I33" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J33" s="5"/>
       <c r="K33" s="3" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="L33" s="3" t="n">
         <v>10</v>
@@ -35158,10 +35415,10 @@
         <v>29</v>
       </c>
       <c r="B34" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C34" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D34" s="3" t="n">
         <v>65</v>
@@ -35172,14 +35429,14 @@
       <c r="F34" s="5"/>
       <c r="G34" s="5"/>
       <c r="H34" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I34" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J34" s="5"/>
       <c r="K34" s="3" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="L34" s="3" t="n">
         <v>13</v>
@@ -35245,10 +35502,10 @@
         <v>30</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C35" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D35" s="3" t="n">
         <v>66</v>
@@ -35259,14 +35516,14 @@
       <c r="F35" s="5"/>
       <c r="G35" s="5"/>
       <c r="H35" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I35" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J35" s="5"/>
       <c r="K35" s="3" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="L35" s="3" t="n">
         <v>16</v>
@@ -35332,10 +35589,10 @@
         <v>31</v>
       </c>
       <c r="B36" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C36" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D36" s="3" t="n">
         <v>67</v>
@@ -35346,14 +35603,14 @@
       <c r="F36" s="5"/>
       <c r="G36" s="5"/>
       <c r="H36" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I36" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J36" s="5"/>
       <c r="K36" s="3" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="L36" s="3" t="n">
         <v>19</v>
@@ -35419,10 +35676,10 @@
         <v>32</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C37" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D37" s="3" t="n">
         <v>68</v>
@@ -35433,14 +35690,14 @@
       <c r="F37" s="5"/>
       <c r="G37" s="5"/>
       <c r="H37" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I37" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J37" s="5"/>
       <c r="K37" s="3" t="s">
-        <v>409</v>
+        <v>413</v>
       </c>
       <c r="L37" s="3" t="n">
         <v>22</v>
@@ -35506,10 +35763,10 @@
         <v>33</v>
       </c>
       <c r="B38" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C38" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D38" s="3" t="n">
         <v>69</v>
@@ -35520,14 +35777,14 @@
       <c r="F38" s="5"/>
       <c r="G38" s="5"/>
       <c r="H38" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I38" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J38" s="5"/>
       <c r="K38" s="3" t="s">
-        <v>410</v>
+        <v>414</v>
       </c>
       <c r="L38" s="3" t="n">
         <v>25</v>
@@ -35593,10 +35850,10 @@
         <v>34</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D39" s="3" t="n">
         <v>70</v>
@@ -35607,14 +35864,14 @@
       <c r="F39" s="5"/>
       <c r="G39" s="5"/>
       <c r="H39" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I39" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J39" s="5"/>
       <c r="K39" s="3" t="s">
-        <v>411</v>
+        <v>415</v>
       </c>
       <c r="L39" s="3" t="n">
         <v>28</v>
@@ -35680,10 +35937,10 @@
         <v>35</v>
       </c>
       <c r="B40" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C40" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D40" s="3" t="n">
         <v>71</v>
@@ -35694,14 +35951,14 @@
       <c r="F40" s="5"/>
       <c r="G40" s="5"/>
       <c r="H40" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I40" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J40" s="5"/>
       <c r="K40" s="3" t="s">
-        <v>412</v>
+        <v>416</v>
       </c>
       <c r="L40" s="3" t="n">
         <v>31</v>
@@ -35767,10 +36024,10 @@
         <v>36</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C41" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D41" s="3" t="n">
         <v>72</v>
@@ -35781,14 +36038,14 @@
       <c r="F41" s="5"/>
       <c r="G41" s="5"/>
       <c r="H41" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I41" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J41" s="5"/>
       <c r="K41" s="3" t="s">
-        <v>413</v>
+        <v>417</v>
       </c>
       <c r="L41" s="3" t="n">
         <v>3</v>
@@ -35854,10 +36111,10 @@
         <v>37</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C42" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D42" s="3" t="n">
         <v>73</v>
@@ -35868,14 +36125,14 @@
       <c r="F42" s="5"/>
       <c r="G42" s="5"/>
       <c r="H42" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I42" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J42" s="5"/>
       <c r="K42" s="3" t="s">
-        <v>414</v>
+        <v>418</v>
       </c>
       <c r="L42" s="3" t="n">
         <v>5</v>
@@ -35941,10 +36198,10 @@
         <v>38</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C43" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D43" s="3" t="n">
         <v>74</v>
@@ -35955,14 +36212,14 @@
       <c r="F43" s="5"/>
       <c r="G43" s="5"/>
       <c r="H43" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I43" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J43" s="5"/>
       <c r="K43" s="3" t="s">
-        <v>415</v>
+        <v>419</v>
       </c>
       <c r="L43" s="3" t="n">
         <v>7</v>
@@ -36028,10 +36285,10 @@
         <v>39</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C44" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D44" s="3" t="n">
         <v>75</v>
@@ -36042,14 +36299,14 @@
       <c r="F44" s="5"/>
       <c r="G44" s="5"/>
       <c r="H44" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I44" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J44" s="5"/>
       <c r="K44" s="3" t="s">
-        <v>416</v>
+        <v>420</v>
       </c>
       <c r="L44" s="3" t="n">
         <v>9</v>
@@ -36115,10 +36372,10 @@
         <v>40</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C45" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D45" s="3" t="n">
         <v>76</v>
@@ -36129,14 +36386,14 @@
       <c r="F45" s="5"/>
       <c r="G45" s="5"/>
       <c r="H45" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I45" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J45" s="5"/>
       <c r="K45" s="3" t="s">
-        <v>417</v>
+        <v>421</v>
       </c>
       <c r="L45" s="3" t="n">
         <v>11</v>
@@ -36202,10 +36459,10 @@
         <v>41</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C46" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D46" s="3" t="n">
         <v>77</v>
@@ -36216,14 +36473,14 @@
       <c r="F46" s="5"/>
       <c r="G46" s="5"/>
       <c r="H46" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I46" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J46" s="5"/>
       <c r="K46" s="3" t="s">
-        <v>418</v>
+        <v>422</v>
       </c>
       <c r="L46" s="3" t="n">
         <v>14</v>
@@ -36289,10 +36546,10 @@
         <v>42</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C47" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D47" s="3" t="n">
         <v>78</v>
@@ -36303,14 +36560,14 @@
       <c r="F47" s="5"/>
       <c r="G47" s="5"/>
       <c r="H47" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I47" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J47" s="5"/>
       <c r="K47" s="3" t="s">
-        <v>419</v>
+        <v>423</v>
       </c>
       <c r="L47" s="3" t="n">
         <v>19</v>
@@ -36376,10 +36633,10 @@
         <v>43</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C48" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D48" s="3" t="n">
         <v>79</v>
@@ -36390,14 +36647,14 @@
       <c r="F48" s="5"/>
       <c r="G48" s="5"/>
       <c r="H48" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I48" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J48" s="5"/>
       <c r="K48" s="3" t="s">
-        <v>420</v>
+        <v>424</v>
       </c>
       <c r="L48" s="3" t="n">
         <v>23</v>
@@ -36463,10 +36720,10 @@
         <v>44</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C49" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D49" s="3" t="n">
         <v>80</v>
@@ -36477,14 +36734,14 @@
       <c r="F49" s="5"/>
       <c r="G49" s="5"/>
       <c r="H49" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I49" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J49" s="5"/>
       <c r="K49" s="3" t="s">
-        <v>421</v>
+        <v>425</v>
       </c>
       <c r="L49" s="3" t="n">
         <v>26</v>
@@ -36550,10 +36807,10 @@
         <v>45</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C50" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D50" s="3" t="n">
         <v>81</v>
@@ -36564,14 +36821,14 @@
       <c r="F50" s="5"/>
       <c r="G50" s="5"/>
       <c r="H50" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I50" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J50" s="5"/>
       <c r="K50" s="3" t="s">
-        <v>422</v>
+        <v>426</v>
       </c>
       <c r="L50" s="3" t="n">
         <v>28</v>
@@ -36637,10 +36894,10 @@
         <v>46</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C51" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D51" s="3" t="n">
         <v>82</v>
@@ -36651,14 +36908,14 @@
       <c r="F51" s="5"/>
       <c r="G51" s="5"/>
       <c r="H51" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I51" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J51" s="5"/>
       <c r="K51" s="3" t="s">
-        <v>423</v>
+        <v>427</v>
       </c>
       <c r="L51" s="3" t="n">
         <v>1</v>
@@ -36724,10 +36981,10 @@
         <v>47</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C52" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D52" s="3" t="n">
         <v>83</v>
@@ -36738,14 +36995,14 @@
       <c r="F52" s="5"/>
       <c r="G52" s="5"/>
       <c r="H52" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I52" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J52" s="5"/>
       <c r="K52" s="3" t="s">
-        <v>424</v>
+        <v>428</v>
       </c>
       <c r="L52" s="3" t="n">
         <v>4</v>
@@ -36811,10 +37068,10 @@
         <v>48</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C53" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>84</v>
@@ -36825,14 +37082,14 @@
       <c r="F53" s="5"/>
       <c r="G53" s="5"/>
       <c r="H53" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I53" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J53" s="5"/>
       <c r="K53" s="3" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="L53" s="3" t="n">
         <v>7</v>
@@ -36898,10 +37155,10 @@
         <v>49</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C54" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D54" s="3" t="n">
         <v>85</v>
@@ -36912,14 +37169,14 @@
       <c r="F54" s="5"/>
       <c r="G54" s="5"/>
       <c r="H54" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I54" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J54" s="5"/>
       <c r="K54" s="3" t="s">
-        <v>426</v>
+        <v>430</v>
       </c>
       <c r="L54" s="3" t="n">
         <v>10</v>
@@ -36985,10 +37242,10 @@
         <v>50</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C55" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D55" s="3" t="n">
         <v>86</v>
@@ -36999,14 +37256,14 @@
       <c r="F55" s="5"/>
       <c r="G55" s="5"/>
       <c r="H55" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I55" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J55" s="5"/>
       <c r="K55" s="3" t="s">
-        <v>427</v>
+        <v>431</v>
       </c>
       <c r="L55" s="3" t="n">
         <v>12</v>
@@ -37072,10 +37329,10 @@
         <v>51</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C56" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D56" s="3" t="n">
         <v>87</v>
@@ -37086,14 +37343,14 @@
       <c r="F56" s="5"/>
       <c r="G56" s="5"/>
       <c r="H56" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I56" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J56" s="5"/>
       <c r="K56" s="3" t="s">
-        <v>428</v>
+        <v>432</v>
       </c>
       <c r="L56" s="3" t="n">
         <v>15</v>
@@ -37159,10 +37416,10 @@
         <v>52</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D57" s="3" t="n">
         <v>88</v>
@@ -37173,14 +37430,14 @@
       <c r="F57" s="5"/>
       <c r="G57" s="5"/>
       <c r="H57" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I57" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J57" s="5"/>
       <c r="K57" s="3" t="s">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="L57" s="3" t="n">
         <v>18</v>
@@ -37246,10 +37503,10 @@
         <v>53</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D58" s="3" t="n">
         <v>89</v>
@@ -37260,14 +37517,14 @@
       <c r="F58" s="5"/>
       <c r="G58" s="5"/>
       <c r="H58" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I58" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J58" s="5"/>
       <c r="K58" s="3" t="s">
-        <v>430</v>
+        <v>434</v>
       </c>
       <c r="L58" s="3" t="n">
         <v>20</v>
@@ -37333,10 +37590,10 @@
         <v>54</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D59" s="3" t="n">
         <v>90</v>
@@ -37347,14 +37604,14 @@
       <c r="F59" s="5"/>
       <c r="G59" s="5"/>
       <c r="H59" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I59" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J59" s="5"/>
       <c r="K59" s="3" t="s">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="L59" s="3" t="n">
         <v>23</v>
@@ -37420,10 +37677,10 @@
         <v>55</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D60" s="3" t="n">
         <v>91</v>
@@ -37434,14 +37691,14 @@
       <c r="F60" s="5"/>
       <c r="G60" s="5"/>
       <c r="H60" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I60" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J60" s="5"/>
       <c r="K60" s="3" t="s">
-        <v>432</v>
+        <v>436</v>
       </c>
       <c r="L60" s="3" t="n">
         <v>26</v>
@@ -37507,10 +37764,10 @@
         <v>56</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="D61" s="3" t="n">
         <v>92</v>
@@ -37521,10 +37778,10 @@
       <c r="F61" s="5"/>
       <c r="G61" s="5"/>
       <c r="H61" s="13" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="I61" s="42" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="J61" s="5"/>
       <c r="K61" s="3" t="s">
@@ -37591,72 +37848,72 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="32" t="s">
-        <v>433</v>
+        <v>437</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="39.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="11" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>434</v>
+        <v>438</v>
       </c>
       <c r="C64" s="11" t="s">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="D64" s="11" t="s">
-        <v>436</v>
+        <v>440</v>
       </c>
       <c r="E64" s="11" t="s">
-        <v>437</v>
+        <v>441</v>
       </c>
       <c r="F64" s="11" t="s">
-        <v>438</v>
+        <v>442</v>
       </c>
       <c r="G64" s="33" t="s">
-        <v>439</v>
+        <v>443</v>
       </c>
       <c r="H64" s="11" t="s">
-        <v>440</v>
+        <v>444</v>
       </c>
       <c r="I64" s="11" t="s">
-        <v>441</v>
+        <v>445</v>
       </c>
       <c r="J64" s="11" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="K64" s="11" t="s">
-        <v>443</v>
+        <v>447</v>
       </c>
       <c r="L64" s="11" t="s">
-        <v>444</v>
+        <v>448</v>
       </c>
       <c r="M64" s="11" t="s">
-        <v>445</v>
+        <v>449</v>
       </c>
       <c r="N64" s="11" t="s">
-        <v>446</v>
+        <v>450</v>
       </c>
       <c r="O64" s="33" t="s">
-        <v>447</v>
+        <v>451</v>
       </c>
       <c r="P64" s="33" t="s">
-        <v>448</v>
+        <v>452</v>
       </c>
       <c r="Q64" s="33" t="s">
-        <v>449</v>
+        <v>453</v>
       </c>
       <c r="R64" s="33" t="s">
-        <v>450</v>
+        <v>454</v>
       </c>
       <c r="S64" s="33" t="s">
-        <v>451</v>
+        <v>455</v>
       </c>
       <c r="T64" s="33" t="s">
-        <v>452</v>
+        <v>456</v>
       </c>
       <c r="U64" s="11" t="s">
-        <v>453</v>
+        <v>457</v>
       </c>
       <c r="V64" s="11" t="s">
         <v>16</v>
@@ -37664,7 +37921,7 @@
     </row>
     <row r="65" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>454</v>
+        <v>458</v>
       </c>
       <c r="B65" s="9" t="str">
         <f aca="false">"#"&amp;_xlfn.MINIFS($D$6:$D$61,$O$6:$O$61,5)&amp;"~#"&amp;_xlfn.MAXIFS($D$6:$D$61,$O$6:$O$61,5)</f>
@@ -37744,12 +38001,12 @@
         <v>0</v>
       </c>
       <c r="V65" s="9" t="s">
-        <v>455</v>
+        <v>459</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>456</v>
+        <v>460</v>
       </c>
       <c r="B66" s="9" t="str">
         <f aca="false">"#"&amp;_xlfn.MINIFS($D$6:$D$61,$O$6:$O$61,6)&amp;"~#"&amp;_xlfn.MAXIFS($D$6:$D$61,$O$6:$O$61,6)</f>
@@ -37834,7 +38091,7 @@
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>457</v>
+        <v>461</v>
       </c>
       <c r="B67" s="9" t="str">
         <f aca="false">"#"&amp;_xlfn.MINIFS($D$6:$D$61,$O$6:$O$61,7)&amp;"~#"&amp;_xlfn.MAXIFS($D$6:$D$61,$O$6:$O$61,7)</f>
@@ -37919,7 +38176,7 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>458</v>
+        <v>462</v>
       </c>
       <c r="B68" s="9" t="str">
         <f aca="false">"#"&amp;_xlfn.MINIFS($D$6:$D$61,$O$6:$O$61,8)&amp;"~#"&amp;_xlfn.MAXIFS($D$6:$D$61,$O$6:$O$61,8)</f>
@@ -38004,7 +38261,7 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>459</v>
+        <v>463</v>
       </c>
       <c r="B69" s="9" t="str">
         <f aca="false">"#"&amp;_xlfn.MINIFS($D$6:$D$61,$O$6:$O$61,9)&amp;"~#"&amp;_xlfn.MAXIFS($D$6:$D$61,$O$6:$O$61,9)</f>
@@ -38089,7 +38346,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
-        <v>460</v>
+        <v>464</v>
       </c>
       <c r="B70" s="9" t="str">
         <f aca="false">"#"&amp;_xlfn.MINIFS($D$6:$D$61,$O$6:$O$61,10)&amp;"~#"&amp;_xlfn.MAXIFS($D$6:$D$61,$O$6:$O$61,10)</f>
@@ -38174,7 +38431,7 @@
     </row>
     <row r="71" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="38" t="s">
-        <v>461</v>
+        <v>465</v>
       </c>
       <c r="B71" s="10" t="str">
         <f aca="false">"#"&amp;_xlfn.MINIFS($D$6:$D$61,$O$6:$O$61,"&gt;=6")&amp;"~#"&amp;_xlfn.MAXIFS($D$6:$D$61,$O$6:$O$61,"&lt;=10")</f>
@@ -38257,12 +38514,12 @@
         <v>4</v>
       </c>
       <c r="V71" s="38" t="s">
-        <v>462</v>
+        <v>466</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="13" t="s">
-        <v>463</v>
+        <v>467</v>
       </c>
       <c r="B73" s="13"/>
       <c r="C73" s="13"/>
@@ -38274,7 +38531,7 @@
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="13" t="s">
-        <v>464</v>
+        <v>468</v>
       </c>
       <c r="B74" s="13"/>
       <c r="C74" s="13"/>
@@ -38286,7 +38543,7 @@
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="13" t="s">
-        <v>465</v>
+        <v>469</v>
       </c>
       <c r="B75" s="13"/>
       <c r="C75" s="13"/>
@@ -38298,7 +38555,7 @@
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
-        <v>466</v>
+        <v>470</v>
       </c>
       <c r="B76" s="9"/>
       <c r="C76" s="9"/>
@@ -38310,7 +38567,7 @@
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="13" t="s">
-        <v>467</v>
+        <v>471</v>
       </c>
       <c r="B77" s="13"/>
       <c r="C77" s="13"/>
@@ -38322,22 +38579,22 @@
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="2" t="s">
-        <v>468</v>
+        <v>472</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="40" t="s">
-        <v>469</v>
+        <v>473</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="2" t="s">
-        <v>470</v>
+        <v>474</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="2" t="s">
-        <v>471</v>
+        <v>475</v>
       </c>
     </row>
   </sheetData>
@@ -38402,12 +38659,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>472</v>
+        <v>476</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>473</v>
+        <v>477</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38456,21 +38713,21 @@
     </row>
     <row r="6" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="49" t="s">
-        <v>474</v>
+        <v>478</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="11" t="s">
-        <v>475</v>
+        <v>479</v>
       </c>
       <c r="B7" s="33" t="s">
-        <v>476</v>
+        <v>480</v>
       </c>
       <c r="C7" s="11" t="s">
-        <v>477</v>
+        <v>481</v>
       </c>
       <c r="D7" s="11" t="s">
-        <v>478</v>
+        <v>482</v>
       </c>
       <c r="E7" s="11"/>
       <c r="F7" s="11"/>
@@ -38496,7 +38753,7 @@
         <v>2</v>
       </c>
       <c r="H8" s="51" t="s">
-        <v>479</v>
+        <v>483</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38516,7 +38773,7 @@
         <v>2</v>
       </c>
       <c r="H9" s="51" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38536,12 +38793,12 @@
         <v>45</v>
       </c>
       <c r="H10" s="51" t="s">
-        <v>480</v>
+        <v>484</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>481</v>
+        <v>485</v>
       </c>
       <c r="B11" s="50" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$17),01_Inputs!$B$17,"미확인")</f>
@@ -38556,7 +38813,7 @@
         <v>6</v>
       </c>
       <c r="H11" s="51" t="s">
-        <v>482</v>
+        <v>486</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -38576,12 +38833,12 @@
         <v>2</v>
       </c>
       <c r="H12" s="51" t="s">
-        <v>483</v>
+        <v>487</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="13" t="s">
-        <v>484</v>
+        <v>488</v>
       </c>
       <c r="B13" s="50" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$30),01_Inputs!$B$30,"미확인")</f>
@@ -38596,12 +38853,12 @@
         <v>미확인</v>
       </c>
       <c r="H13" s="51" t="s">
-        <v>485</v>
+        <v>489</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>486</v>
+        <v>490</v>
       </c>
       <c r="B14" s="50" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$32),01_Inputs!$B$32,"미확인")</f>
@@ -38616,12 +38873,12 @@
         <v>2</v>
       </c>
       <c r="H14" s="51" t="s">
-        <v>487</v>
+        <v>491</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="52" t="s">
-        <v>488</v>
+        <v>492</v>
       </c>
       <c r="B15" s="53" t="n">
         <f aca="false">SUM(B8:B12)</f>
@@ -38638,7 +38895,7 @@
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="52" t="s">
-        <v>489</v>
+        <v>493</v>
       </c>
       <c r="B16" s="53" t="n">
         <f aca="false">SUM(B8:B14)</f>
@@ -38653,22 +38910,22 @@
         <v>59 + 미확인</v>
       </c>
       <c r="H16" s="54" t="s">
-        <v>490</v>
+        <v>494</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>491</v>
+        <v>495</v>
       </c>
       <c r="B17" s="27" t="n">
         <f aca="false">01_Inputs!$B$30/01_Inputs!$B$39</f>
         <v>2.25</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D17" s="55" t="s">
-        <v>493</v>
+        <v>497</v>
       </c>
       <c r="E17" s="55"/>
       <c r="F17" s="55"/>
@@ -38677,7 +38934,7 @@
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>494</v>
+        <v>498</v>
       </c>
       <c r="B18" s="15" t="n">
         <f aca="false">ROUNDUP(03_Capacity_Model!$B$17,0)*24</f>
@@ -38687,7 +38944,7 @@
         <v>42</v>
       </c>
       <c r="D18" s="56" t="s">
-        <v>495</v>
+        <v>499</v>
       </c>
       <c r="E18" s="56"/>
       <c r="F18" s="56"/>
@@ -38696,12 +38953,12 @@
     </row>
     <row r="20" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="49" t="s">
-        <v>496</v>
+        <v>500</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>497</v>
+        <v>501</v>
       </c>
       <c r="B21" s="53" t="n">
         <f aca="false">01_Inputs!$B$15+01_Inputs!$B$16</f>
@@ -38711,7 +38968,7 @@
         <v>47</v>
       </c>
       <c r="D21" s="55" t="s">
-        <v>498</v>
+        <v>502</v>
       </c>
       <c r="E21" s="55"/>
       <c r="F21" s="55"/>
@@ -38720,7 +38977,7 @@
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="13" t="s">
-        <v>499</v>
+        <v>503</v>
       </c>
       <c r="B22" s="15" t="n">
         <f aca="false">03_Capacity_Model!$B$21+01_Inputs!$B$17</f>
@@ -38730,7 +38987,7 @@
         <v>47</v>
       </c>
       <c r="D22" s="56" t="s">
-        <v>500</v>
+        <v>504</v>
       </c>
       <c r="E22" s="56"/>
       <c r="F22" s="56"/>
@@ -38739,7 +38996,7 @@
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="13" t="s">
-        <v>501</v>
+        <v>505</v>
       </c>
       <c r="B23" s="15" t="n">
         <f aca="false">03_Capacity_Model!$B$21+N(01_Inputs!$B$22)</f>
@@ -38749,7 +39006,7 @@
         <v>47</v>
       </c>
       <c r="D23" s="56" t="s">
-        <v>502</v>
+        <v>506</v>
       </c>
       <c r="E23" s="56"/>
       <c r="F23" s="56"/>
@@ -38758,12 +39015,12 @@
     </row>
     <row r="25" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="49" t="s">
-        <v>503</v>
+        <v>507</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="13" t="s">
-        <v>504</v>
+        <v>508</v>
       </c>
       <c r="B26" s="50" t="n">
         <f aca="false">01_Inputs!$B$16</f>
@@ -38773,7 +39030,7 @@
         <v>47</v>
       </c>
       <c r="D26" s="55" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="E26" s="55"/>
       <c r="F26" s="55"/>
@@ -38782,7 +39039,7 @@
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>506</v>
+        <v>510</v>
       </c>
       <c r="B27" s="27" t="n">
         <f aca="false">01_Inputs!$B$11/03_Capacity_Model!$B$26</f>
@@ -38792,7 +39049,7 @@
         <v>201</v>
       </c>
       <c r="D27" s="56" t="s">
-        <v>507</v>
+        <v>511</v>
       </c>
       <c r="E27" s="56"/>
       <c r="F27" s="56"/>
@@ -38801,7 +39058,7 @@
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="13" t="s">
-        <v>508</v>
+        <v>512</v>
       </c>
       <c r="B28" s="48" t="n">
         <f aca="false">INT(03_Capacity_Model!$B$27)</f>
@@ -38818,7 +39075,7 @@
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="13" t="s">
-        <v>509</v>
+        <v>513</v>
       </c>
       <c r="B29" s="15" t="n">
         <f aca="false">01_Inputs!$B$11-03_Capacity_Model!$B$28*03_Capacity_Model!$B$26</f>
@@ -38835,7 +39092,7 @@
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="13" t="s">
-        <v>510</v>
+        <v>514</v>
       </c>
       <c r="B30" s="45" t="n">
         <f aca="false">03_Capacity_Model!$B$28*01_Inputs!$B$49</f>
@@ -38845,7 +39102,7 @@
         <v>292</v>
       </c>
       <c r="D30" s="55" t="s">
-        <v>511</v>
+        <v>515</v>
       </c>
       <c r="E30" s="55"/>
       <c r="F30" s="55"/>
@@ -38854,7 +39111,7 @@
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="13" t="s">
-        <v>512</v>
+        <v>516</v>
       </c>
       <c r="B31" s="27" t="n">
         <f aca="false">01_Inputs!$B$11/03_Capacity_Model!$B$21</f>
@@ -38864,7 +39121,7 @@
         <v>201</v>
       </c>
       <c r="D31" s="56" t="s">
-        <v>513</v>
+        <v>517</v>
       </c>
       <c r="E31" s="56"/>
       <c r="F31" s="56"/>
@@ -38873,17 +39130,17 @@
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="13" t="s">
-        <v>514</v>
+        <v>518</v>
       </c>
       <c r="B32" s="16" t="n">
         <f aca="false">INT(01_Inputs!$B$12/03_Capacity_Model!$B$26)</f>
         <v>194</v>
       </c>
       <c r="C32" s="9" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D32" s="56" t="s">
-        <v>516</v>
+        <v>520</v>
       </c>
       <c r="E32" s="56"/>
       <c r="F32" s="56"/>
@@ -38892,7 +39149,7 @@
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="13" t="s">
-        <v>517</v>
+        <v>521</v>
       </c>
       <c r="B33" s="22" t="n">
         <f aca="false">03_Capacity_Model!$B$32*01_Inputs!$B$49</f>
@@ -38909,12 +39166,12 @@
     </row>
     <row r="35" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="49" t="s">
-        <v>518</v>
+        <v>522</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="13" t="s">
-        <v>519</v>
+        <v>523</v>
       </c>
       <c r="B36" s="57" t="n">
         <f aca="false">01_Inputs!$B$70</f>
@@ -38931,7 +39188,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="13" t="s">
-        <v>520</v>
+        <v>524</v>
       </c>
       <c r="B37" s="15" t="n">
         <f aca="false">03_Capacity_Model!$B$36*03_Capacity_Model!$B$26</f>
@@ -38948,7 +39205,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>521</v>
+        <v>525</v>
       </c>
       <c r="B38" s="53" t="n">
         <f aca="false">01_Inputs!$B$11-03_Capacity_Model!$B$37</f>
@@ -38958,7 +39215,7 @@
         <v>33</v>
       </c>
       <c r="D38" s="56" t="s">
-        <v>522</v>
+        <v>526</v>
       </c>
       <c r="E38" s="56"/>
       <c r="F38" s="56"/>
@@ -38967,7 +39224,7 @@
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="13" t="s">
-        <v>523</v>
+        <v>527</v>
       </c>
       <c r="B39" s="15" t="n">
         <f aca="false">03_Capacity_Model!$B$36*03_Capacity_Model!$B$21</f>
@@ -38984,7 +39241,7 @@
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>524</v>
+        <v>528</v>
       </c>
       <c r="B40" s="27" t="n">
         <f aca="false">01_Inputs!$B$11/03_Capacity_Model!$B$36</f>
@@ -38994,7 +39251,7 @@
         <v>47</v>
       </c>
       <c r="D40" s="55" t="s">
-        <v>525</v>
+        <v>529</v>
       </c>
       <c r="E40" s="55"/>
       <c r="F40" s="55"/>
@@ -39003,7 +39260,7 @@
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="13" t="s">
-        <v>526</v>
+        <v>530</v>
       </c>
       <c r="B41" s="45" t="n">
         <f aca="false">03_Capacity_Model!$B$36*01_Inputs!$B$49</f>
@@ -39020,7 +39277,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="13" t="s">
-        <v>527</v>
+        <v>531</v>
       </c>
       <c r="B42" s="45" t="n">
         <f aca="false">03_Capacity_Model!$B$41*12</f>
@@ -39030,7 +39287,7 @@
         <v>289</v>
       </c>
       <c r="D42" s="55" t="s">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="E42" s="55"/>
       <c r="F42" s="55"/>
@@ -39039,7 +39296,7 @@
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="13" t="s">
-        <v>529</v>
+        <v>533</v>
       </c>
       <c r="B43" s="22" t="n">
         <f aca="false">INT(01_Inputs!$B$12/03_Capacity_Model!$B$40)*01_Inputs!$B$49</f>
@@ -39056,12 +39313,12 @@
     </row>
     <row r="45" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="49" t="s">
-        <v>530</v>
+        <v>534</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="13" t="s">
-        <v>531</v>
+        <v>535</v>
       </c>
       <c r="B46" s="58" t="n">
         <f aca="false">INDEX(02_Batch_Raw!$E$6:$E$61,MATCH(01_Inputs!$B$97,02_Batch_Raw!$D$6:$D$61,0))</f>
@@ -39071,7 +39328,7 @@
         <v>134</v>
       </c>
       <c r="D46" s="55" t="s">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="E46" s="55"/>
       <c r="F46" s="55"/>
@@ -39080,7 +39337,7 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="B47" s="58" t="n">
         <f aca="false">INDEX(02_Batch_Raw!$E$6:$E$61,MATCH(01_Inputs!$B$98,02_Batch_Raw!$D$6:$D$61,0))</f>
@@ -39090,7 +39347,7 @@
         <v>134</v>
       </c>
       <c r="D47" s="55" t="s">
-        <v>534</v>
+        <v>538</v>
       </c>
       <c r="E47" s="55"/>
       <c r="F47" s="55"/>
@@ -39099,17 +39356,17 @@
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="13" t="s">
-        <v>535</v>
+        <v>539</v>
       </c>
       <c r="B48" s="16" t="n">
         <f aca="false">01_Inputs!$B$98-01_Inputs!$B$97+1</f>
         <v>54</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>536</v>
+        <v>540</v>
       </c>
       <c r="D48" s="55" t="s">
-        <v>537</v>
+        <v>541</v>
       </c>
       <c r="E48" s="55"/>
       <c r="F48" s="55"/>
@@ -39118,7 +39375,7 @@
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="13" t="s">
-        <v>538</v>
+        <v>542</v>
       </c>
       <c r="B49" s="16" t="n">
         <f aca="false">03_Capacity_Model!$B$47-03_Capacity_Model!$B$46</f>
@@ -39135,7 +39392,7 @@
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="13" t="s">
-        <v>442</v>
+        <v>446</v>
       </c>
       <c r="B50" s="16" t="n">
         <f aca="false">SUM(02_Batch_Raw!$P$6:$P$61)</f>
@@ -39145,7 +39402,7 @@
         <v>260</v>
       </c>
       <c r="D50" s="55" t="s">
-        <v>539</v>
+        <v>543</v>
       </c>
       <c r="E50" s="55"/>
       <c r="F50" s="55"/>
@@ -39154,7 +39411,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="13" t="s">
-        <v>540</v>
+        <v>544</v>
       </c>
       <c r="B51" s="47" t="n">
         <f aca="false">03_Capacity_Model!$B$49*24/03_Capacity_Model!$B$50</f>
@@ -39164,7 +39421,7 @@
         <v>47</v>
       </c>
       <c r="D51" s="56" t="s">
-        <v>541</v>
+        <v>545</v>
       </c>
       <c r="E51" s="56"/>
       <c r="F51" s="56"/>
@@ -39173,7 +39430,7 @@
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="13" t="s">
-        <v>542</v>
+        <v>546</v>
       </c>
       <c r="B52" s="27" t="n">
         <f aca="false">(03_Capacity_Model!$B$49-1)*24/03_Capacity_Model!$B$50</f>
@@ -39190,7 +39447,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="13" t="s">
-        <v>543</v>
+        <v>547</v>
       </c>
       <c r="B53" s="27" t="n">
         <f aca="false">(03_Capacity_Model!$B$49+1)*24/03_Capacity_Model!$B$50</f>
@@ -39207,7 +39464,7 @@
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="13" t="s">
-        <v>544</v>
+        <v>548</v>
       </c>
       <c r="B54" s="50" t="n">
         <f aca="false">02_Batch_Raw!$L$71*24</f>
@@ -39217,7 +39474,7 @@
         <v>42</v>
       </c>
       <c r="D54" s="55" t="s">
-        <v>545</v>
+        <v>549</v>
       </c>
       <c r="E54" s="55"/>
       <c r="F54" s="55"/>
@@ -39226,7 +39483,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>546</v>
+        <v>550</v>
       </c>
       <c r="B55" s="59" t="n">
         <f aca="false">02_Batch_Raw!$Q$71/02_Batch_Raw!$J$71</f>
@@ -39243,7 +39500,7 @@
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="13" t="s">
-        <v>547</v>
+        <v>551</v>
       </c>
       <c r="B56" s="27" t="n">
         <f aca="false">03_Capacity_Model!$B$51-03_Capacity_Model!$B$26</f>
@@ -39253,7 +39510,7 @@
         <v>47</v>
       </c>
       <c r="D56" s="56" t="s">
-        <v>548</v>
+        <v>552</v>
       </c>
       <c r="E56" s="56"/>
       <c r="F56" s="56"/>
@@ -39262,7 +39519,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="13" t="s">
-        <v>549</v>
+        <v>553</v>
       </c>
       <c r="B57" s="47" t="n">
         <f aca="false">03_Capacity_Model!$B$51-03_Capacity_Model!$B$21</f>
@@ -39279,7 +39536,7 @@
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="13" t="s">
-        <v>550</v>
+        <v>554</v>
       </c>
       <c r="B58" s="27" t="n">
         <f aca="false">30*24/03_Capacity_Model!$B$51</f>
@@ -39296,7 +39553,7 @@
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="13" t="s">
-        <v>551</v>
+        <v>555</v>
       </c>
       <c r="B59" s="27" t="n">
         <f aca="false">31*24/03_Capacity_Model!$B$51</f>
@@ -39306,7 +39563,7 @@
         <v>201</v>
       </c>
       <c r="D59" s="55" t="s">
-        <v>552</v>
+        <v>556</v>
       </c>
       <c r="E59" s="55"/>
       <c r="F59" s="55"/>
@@ -39315,7 +39572,7 @@
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="13" t="s">
-        <v>553</v>
+        <v>557</v>
       </c>
       <c r="B60" s="22" t="n">
         <f aca="false">03_Capacity_Model!$B$58*01_Inputs!$B$49</f>
@@ -39332,14 +39589,14 @@
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="13" t="s">
-        <v>554</v>
+        <v>558</v>
       </c>
       <c r="B61" s="16" t="n">
         <f aca="false">INT(01_Inputs!$B$12/03_Capacity_Model!$B$51)</f>
         <v>129</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D61" s="56"/>
       <c r="E61" s="56"/>
@@ -39349,7 +39606,7 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="13" t="s">
-        <v>555</v>
+        <v>559</v>
       </c>
       <c r="B62" s="45" t="n">
         <f aca="false">03_Capacity_Model!$B$61*01_Inputs!$B$49</f>
@@ -39359,7 +39616,7 @@
         <v>289</v>
       </c>
       <c r="D62" s="56" t="s">
-        <v>556</v>
+        <v>560</v>
       </c>
       <c r="E62" s="56"/>
       <c r="F62" s="56"/>
@@ -39368,7 +39625,7 @@
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="13" t="s">
-        <v>557</v>
+        <v>561</v>
       </c>
       <c r="B63" s="27" t="n">
         <f aca="false">(02_Batch_Raw!$E$61-02_Batch_Raw!$E$6)*24/(02_Batch_Raw!$D$61-02_Batch_Raw!$D$6)</f>
@@ -39378,7 +39635,7 @@
         <v>47</v>
       </c>
       <c r="D63" s="55" t="s">
-        <v>558</v>
+        <v>562</v>
       </c>
       <c r="E63" s="55"/>
       <c r="F63" s="55"/>
@@ -39387,17 +39644,17 @@
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="13" t="s">
-        <v>559</v>
+        <v>563</v>
       </c>
       <c r="B64" s="57" t="n">
         <f aca="false">02_Batch_Raw!$E$77</f>
         <v>0</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>560</v>
+        <v>564</v>
       </c>
       <c r="D64" s="55" t="s">
-        <v>561</v>
+        <v>565</v>
       </c>
       <c r="E64" s="55"/>
       <c r="F64" s="55"/>
@@ -39406,12 +39663,12 @@
     </row>
     <row r="66" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="49" t="s">
-        <v>562</v>
+        <v>566</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="13" t="s">
-        <v>563</v>
+        <v>567</v>
       </c>
       <c r="B67" s="60" t="n">
         <f aca="false">01_Inputs!$B$63*1000</f>
@@ -39428,17 +39685,17 @@
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>564</v>
+        <v>568</v>
       </c>
       <c r="B68" s="61" t="n">
         <f aca="false">03_Capacity_Model!$B$67/01_Inputs!$B$49</f>
         <v>137.894736842105</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D68" s="55" t="s">
-        <v>565</v>
+        <v>569</v>
       </c>
       <c r="E68" s="55"/>
       <c r="F68" s="55"/>
@@ -39447,14 +39704,14 @@
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="13" t="s">
-        <v>566</v>
+        <v>570</v>
       </c>
       <c r="B69" s="16" t="n">
         <f aca="false">ROUND(03_Capacity_Model!$B$68,0)</f>
         <v>138</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D69" s="56"/>
       <c r="E69" s="56"/>
@@ -39464,7 +39721,7 @@
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="13" t="s">
-        <v>567</v>
+        <v>571</v>
       </c>
       <c r="B70" s="22" t="n">
         <f aca="false">03_Capacity_Model!$B$69*01_Inputs!$B$49</f>
@@ -39474,7 +39731,7 @@
         <v>289</v>
       </c>
       <c r="D70" s="55" t="s">
-        <v>568</v>
+        <v>572</v>
       </c>
       <c r="E70" s="55"/>
       <c r="F70" s="55"/>
@@ -39483,7 +39740,7 @@
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="13" t="s">
-        <v>569</v>
+        <v>573</v>
       </c>
       <c r="B71" s="27" t="n">
         <f aca="false">03_Capacity_Model!$B$68/12</f>
@@ -39500,7 +39757,7 @@
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="13" t="s">
-        <v>570</v>
+        <v>574</v>
       </c>
       <c r="B72" s="47" t="n">
         <f aca="false">01_Inputs!$B$12/03_Capacity_Model!$B$68</f>
@@ -39510,7 +39767,7 @@
         <v>47</v>
       </c>
       <c r="D72" s="56" t="s">
-        <v>571</v>
+        <v>575</v>
       </c>
       <c r="E72" s="56"/>
       <c r="F72" s="56"/>
@@ -39519,7 +39776,7 @@
     </row>
     <row r="74" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="49" t="s">
-        <v>572</v>
+        <v>576</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -39527,28 +39784,28 @@
         <v>14</v>
       </c>
       <c r="B75" s="33" t="s">
-        <v>573</v>
+        <v>577</v>
       </c>
       <c r="C75" s="11" t="s">
-        <v>574</v>
+        <v>578</v>
       </c>
       <c r="D75" s="11" t="s">
-        <v>575</v>
+        <v>579</v>
       </c>
       <c r="E75" s="11" t="s">
-        <v>576</v>
+        <v>580</v>
       </c>
       <c r="F75" s="33" t="s">
-        <v>577</v>
+        <v>581</v>
       </c>
       <c r="G75" s="11"/>
       <c r="H75" s="11" t="s">
-        <v>578</v>
+        <v>582</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="52" t="s">
-        <v>579</v>
+        <v>583</v>
       </c>
       <c r="B76" s="27" t="n">
         <f aca="false">03_Capacity_Model!$B$26</f>
@@ -39571,12 +39828,12 @@
         <v>10.28</v>
       </c>
       <c r="H76" s="54" t="s">
-        <v>580</v>
+        <v>584</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="52" t="s">
-        <v>581</v>
+        <v>585</v>
       </c>
       <c r="B77" s="27" t="n">
         <f aca="false">03_Capacity_Model!$B$40</f>
@@ -39599,12 +39856,12 @@
         <v>-1.12</v>
       </c>
       <c r="H77" s="51" t="s">
-        <v>582</v>
+        <v>586</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="52" t="s">
-        <v>583</v>
+        <v>587</v>
       </c>
       <c r="B78" s="27" t="n">
         <f aca="false">03_Capacity_Model!$B$51</f>
@@ -39627,12 +39884,12 @@
         <v>-1.69</v>
       </c>
       <c r="H78" s="54" t="s">
-        <v>584</v>
+        <v>588</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="52" t="s">
-        <v>585</v>
+        <v>589</v>
       </c>
       <c r="B79" s="27" t="n">
         <f aca="false">03_Capacity_Model!$B$72</f>
@@ -39655,12 +39912,12 @@
         <v>0</v>
       </c>
       <c r="H79" s="54" t="s">
-        <v>586</v>
+        <v>590</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
-        <v>587</v>
+        <v>591</v>
       </c>
       <c r="B80" s="47" t="n">
         <f aca="false">CHOOSE(01_Inputs!$B$100,03_Capacity_Model!$B$26,03_Capacity_Model!$B$40,03_Capacity_Model!$B$51,03_Capacity_Model!$B$72)</f>
@@ -39670,7 +39927,7 @@
         <v>47</v>
       </c>
       <c r="D80" s="56" t="s">
-        <v>588</v>
+        <v>592</v>
       </c>
       <c r="E80" s="56"/>
       <c r="F80" s="56"/>
@@ -39679,12 +39936,12 @@
     </row>
     <row r="82" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="49" t="s">
-        <v>589</v>
+        <v>593</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="13" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="B83" s="62" t="n">
         <f aca="false">01_Inputs!$B$66</f>
@@ -39694,7 +39951,7 @@
         <v>181</v>
       </c>
       <c r="D83" s="56" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="E83" s="56"/>
       <c r="F83" s="56"/>
@@ -39703,7 +39960,7 @@
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="13" t="s">
-        <v>592</v>
+        <v>596</v>
       </c>
       <c r="B84" s="47" t="n">
         <f aca="false">03_Capacity_Model!$B$83-01_Inputs!$B$65</f>
@@ -39713,7 +39970,7 @@
         <v>181</v>
       </c>
       <c r="D84" s="55" t="s">
-        <v>593</v>
+        <v>597</v>
       </c>
       <c r="E84" s="55"/>
       <c r="F84" s="55"/>
@@ -39722,7 +39979,7 @@
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="s">
-        <v>594</v>
+        <v>598</v>
       </c>
       <c r="B85" s="63" t="n">
         <f aca="false">01_Inputs!$B$65/03_Capacity_Model!$B$83</f>
@@ -39739,14 +39996,14 @@
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>595</v>
+        <v>599</v>
       </c>
       <c r="B86" s="64" t="n">
         <f aca="false">01_Inputs!$B$65*1000/01_Inputs!$B$49</f>
         <v>248.421052631579</v>
       </c>
       <c r="C86" s="9" t="s">
-        <v>515</v>
+        <v>519</v>
       </c>
       <c r="D86" s="56"/>
       <c r="E86" s="56"/>
@@ -39756,7 +40013,7 @@
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>596</v>
+        <v>600</v>
       </c>
       <c r="B87" s="27" t="n">
         <f aca="false">01_Inputs!$B$12/03_Capacity_Model!$B$86</f>
@@ -39766,7 +40023,7 @@
         <v>47</v>
       </c>
       <c r="D87" s="56" t="s">
-        <v>597</v>
+        <v>601</v>
       </c>
       <c r="E87" s="56"/>
       <c r="F87" s="56"/>
@@ -39775,7 +40032,7 @@
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="13" t="s">
-        <v>598</v>
+        <v>602</v>
       </c>
       <c r="B88" s="47" t="n">
         <f aca="false">01_Inputs!$B$8*01_Inputs!$B$12/03_Capacity_Model!$B$86</f>
@@ -39785,7 +40042,7 @@
         <v>47</v>
       </c>
       <c r="D88" s="56" t="s">
-        <v>599</v>
+        <v>603</v>
       </c>
       <c r="E88" s="56"/>
       <c r="F88" s="56"/>
@@ -39794,7 +40051,7 @@
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="13" t="s">
-        <v>600</v>
+        <v>604</v>
       </c>
       <c r="B89" s="27" t="n">
         <f aca="false">03_Capacity_Model!$B$88-03_Capacity_Model!$B$72</f>
@@ -39804,7 +40061,7 @@
         <v>47</v>
       </c>
       <c r="D89" s="56" t="s">
-        <v>601</v>
+        <v>605</v>
       </c>
       <c r="E89" s="56"/>
       <c r="F89" s="56"/>
@@ -39813,7 +40070,7 @@
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="13" t="s">
-        <v>602</v>
+        <v>606</v>
       </c>
       <c r="B90" s="50" t="n">
         <f aca="false">01_Inputs!$B$84</f>
@@ -39823,7 +40080,7 @@
         <v>42</v>
       </c>
       <c r="D90" s="56" t="s">
-        <v>603</v>
+        <v>607</v>
       </c>
       <c r="E90" s="56"/>
       <c r="F90" s="56"/>
@@ -39832,7 +40089,7 @@
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>604</v>
+        <v>608</v>
       </c>
       <c r="B91" s="19" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$83),01_Inputs!$B$83,ROUND(03_Capacity_Model!$B$88,1))</f>
@@ -39842,7 +40099,7 @@
         <v>47</v>
       </c>
       <c r="D91" s="56" t="s">
-        <v>605</v>
+        <v>609</v>
       </c>
       <c r="E91" s="56"/>
       <c r="F91" s="56"/>
@@ -39851,16 +40108,16 @@
     </row>
     <row r="92" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="33" t="s">
-        <v>606</v>
+        <v>610</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C92" s="11" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D92" s="11" t="s">
-        <v>609</v>
+        <v>613</v>
       </c>
       <c r="E92" s="11"/>
       <c r="F92" s="11"/>
@@ -39994,7 +40251,7 @@
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="13" t="s">
-        <v>610</v>
+        <v>614</v>
       </c>
       <c r="B93" s="15" t="n">
         <f aca="false">(0+0*03_Capacity_Model!$B$91)+01_Inputs!$B$14</f>
@@ -40005,7 +40262,7 @@
         <v>4</v>
       </c>
       <c r="D93" s="13" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="H93" s="51"/>
       <c r="J93" s="66" t="n">
@@ -40175,7 +40432,7 @@
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="13" t="s">
-        <v>612</v>
+        <v>616</v>
       </c>
       <c r="B94" s="15" t="n">
         <f aca="false">C93</f>
@@ -40186,10 +40443,10 @@
         <v>49</v>
       </c>
       <c r="D94" s="13" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="H94" s="54" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="J94" s="66" t="n">
         <f aca="false">IF(AND(J$92+6&gt;$B94,J$92&lt;$C94),1,"")</f>
@@ -40358,7 +40615,7 @@
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="13" t="s">
-        <v>613</v>
+        <v>617</v>
       </c>
       <c r="B95" s="15" t="n">
         <f aca="false">C94</f>
@@ -40369,10 +40626,10 @@
         <v>57</v>
       </c>
       <c r="D95" s="13" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="H95" s="54" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="J95" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B95,J$92&lt;$C95),1,"")</f>
@@ -40541,7 +40798,7 @@
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="13" t="s">
-        <v>616</v>
+        <v>620</v>
       </c>
       <c r="B96" s="15" t="n">
         <f aca="false">C95</f>
@@ -40552,10 +40809,10 @@
         <v>75</v>
       </c>
       <c r="D96" s="13" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="H96" s="51" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J96" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B96,J$92&lt;$C96),1,"")</f>
@@ -40724,7 +40981,7 @@
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="13" t="s">
-        <v>619</v>
+        <v>623</v>
       </c>
       <c r="B97" s="15" t="n">
         <f aca="false">(03_Capacity_Model!$B$90+0*03_Capacity_Model!$B$91)+01_Inputs!$B$14</f>
@@ -40735,7 +40992,7 @@
         <v>34</v>
       </c>
       <c r="D97" s="13" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H97" s="51"/>
       <c r="J97" s="66" t="str">
@@ -40905,7 +41162,7 @@
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="13" t="s">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="B98" s="15" t="n">
         <f aca="false">C97</f>
@@ -40916,10 +41173,10 @@
         <v>79</v>
       </c>
       <c r="D98" s="13" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H98" s="54" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="J98" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B98,J$92&lt;$C98),1,"")</f>
@@ -41088,7 +41345,7 @@
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="13" t="s">
-        <v>622</v>
+        <v>626</v>
       </c>
       <c r="B99" s="15" t="n">
         <f aca="false">C98</f>
@@ -41099,10 +41356,10 @@
         <v>87</v>
       </c>
       <c r="D99" s="13" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="H99" s="54" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="J99" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B99,J$92&lt;$C99),1,"")</f>
@@ -41271,7 +41528,7 @@
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="13" t="s">
-        <v>623</v>
+        <v>627</v>
       </c>
       <c r="B100" s="15" t="n">
         <f aca="false">C99</f>
@@ -41282,10 +41539,10 @@
         <v>105</v>
       </c>
       <c r="D100" s="13" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="H100" s="51" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J100" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B100,J$92&lt;$C100),1,"")</f>
@@ -41454,7 +41711,7 @@
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="13" t="s">
-        <v>624</v>
+        <v>628</v>
       </c>
       <c r="B101" s="15" t="n">
         <f aca="false">(0+1*03_Capacity_Model!$B$91)+01_Inputs!$B$14</f>
@@ -41465,7 +41722,7 @@
         <v>74.5</v>
       </c>
       <c r="D101" s="13" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="H101" s="51"/>
       <c r="J101" s="66" t="str">
@@ -41635,7 +41892,7 @@
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="13" t="s">
-        <v>625</v>
+        <v>629</v>
       </c>
       <c r="B102" s="15" t="n">
         <f aca="false">C101</f>
@@ -41646,10 +41903,10 @@
         <v>119.5</v>
       </c>
       <c r="D102" s="13" t="s">
-        <v>611</v>
+        <v>615</v>
       </c>
       <c r="H102" s="54" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="J102" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B102,J$92&lt;$C102),1,"")</f>
@@ -41818,7 +42075,7 @@
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="13" t="s">
-        <v>626</v>
+        <v>630</v>
       </c>
       <c r="B103" s="15" t="n">
         <f aca="false">C102</f>
@@ -41829,10 +42086,10 @@
         <v>127.5</v>
       </c>
       <c r="D103" s="13" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="H103" s="54" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="J103" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B103,J$92&lt;$C103),1,"")</f>
@@ -42001,7 +42258,7 @@
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="13" t="s">
-        <v>627</v>
+        <v>631</v>
       </c>
       <c r="B104" s="15" t="n">
         <f aca="false">C103</f>
@@ -42012,10 +42269,10 @@
         <v>145.5</v>
       </c>
       <c r="D104" s="13" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="H104" s="51" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J104" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B104,J$92&lt;$C104),1,"")</f>
@@ -42184,7 +42441,7 @@
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="13" t="s">
-        <v>628</v>
+        <v>632</v>
       </c>
       <c r="B105" s="15" t="n">
         <f aca="false">(03_Capacity_Model!$B$90+1*03_Capacity_Model!$B$91)+01_Inputs!$B$14</f>
@@ -42195,7 +42452,7 @@
         <v>104.5</v>
       </c>
       <c r="D105" s="13" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H105" s="51"/>
       <c r="J105" s="66" t="str">
@@ -42365,7 +42622,7 @@
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="13" t="s">
-        <v>629</v>
+        <v>633</v>
       </c>
       <c r="B106" s="15" t="n">
         <f aca="false">C105</f>
@@ -42376,10 +42633,10 @@
         <v>149.5</v>
       </c>
       <c r="D106" s="13" t="s">
-        <v>620</v>
+        <v>624</v>
       </c>
       <c r="H106" s="54" t="s">
-        <v>505</v>
+        <v>509</v>
       </c>
       <c r="J106" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B106,J$92&lt;$C106),1,"")</f>
@@ -42548,7 +42805,7 @@
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="13" t="s">
-        <v>630</v>
+        <v>634</v>
       </c>
       <c r="B107" s="15" t="n">
         <f aca="false">C106</f>
@@ -42559,10 +42816,10 @@
         <v>157.5</v>
       </c>
       <c r="D107" s="13" t="s">
-        <v>614</v>
+        <v>618</v>
       </c>
       <c r="H107" s="54" t="s">
-        <v>615</v>
+        <v>619</v>
       </c>
       <c r="J107" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B107,J$92&lt;$C107),1,"")</f>
@@ -42731,7 +42988,7 @@
     </row>
     <row r="108" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A108" s="13" t="s">
-        <v>631</v>
+        <v>635</v>
       </c>
       <c r="B108" s="15" t="n">
         <f aca="false">C107</f>
@@ -42742,10 +42999,10 @@
         <v>175.5</v>
       </c>
       <c r="D108" s="13" t="s">
-        <v>617</v>
+        <v>621</v>
       </c>
       <c r="H108" s="51" t="s">
-        <v>618</v>
+        <v>622</v>
       </c>
       <c r="J108" s="66" t="str">
         <f aca="false">IF(AND(J$92+6&gt;$B108,J$92&lt;$C108),1,"")</f>
@@ -42914,7 +43171,7 @@
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="13" t="s">
-        <v>632</v>
+        <v>636</v>
       </c>
       <c r="B109" s="15" t="n">
         <f aca="false">MIN(03_Capacity_Model!$B$90,03_Capacity_Model!$B$91-03_Capacity_Model!$B$90)</f>
@@ -42924,7 +43181,7 @@
         <v>42</v>
       </c>
       <c r="D109" s="56" t="s">
-        <v>633</v>
+        <v>637</v>
       </c>
       <c r="E109" s="56"/>
       <c r="F109" s="56"/>
@@ -42933,12 +43190,12 @@
     </row>
     <row r="111" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A111" s="49" t="s">
-        <v>634</v>
+        <v>638</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="9" t="s">
-        <v>635</v>
+        <v>639</v>
       </c>
       <c r="B112" s="50" t="n">
         <f aca="false">SUM(04_Monthly_2026_2028!AB18:AB29)</f>
@@ -42948,7 +43205,7 @@
         <v>37</v>
       </c>
       <c r="D112" s="55" t="s">
-        <v>636</v>
+        <v>640</v>
       </c>
       <c r="E112" s="55"/>
       <c r="F112" s="55"/>
@@ -42957,7 +43214,7 @@
     </row>
     <row r="113" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A113" s="9" t="s">
-        <v>637</v>
+        <v>641</v>
       </c>
       <c r="B113" s="50" t="n">
         <f aca="false">SUM(04_Monthly_2026_2028!AB30:AB41)</f>
@@ -42974,7 +43231,7 @@
     </row>
     <row r="114" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A114" s="9" t="s">
-        <v>638</v>
+        <v>642</v>
       </c>
       <c r="B114" s="50" t="n">
         <f aca="false">MAX(04_Monthly_2026_2028!AB18:AB41)</f>
@@ -42991,14 +43248,14 @@
     </row>
     <row r="115" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A115" s="9" t="s">
-        <v>639</v>
+        <v>643</v>
       </c>
       <c r="B115" s="57" t="n">
         <f aca="false">SUM(04_Monthly_2026_2028!AD18:AE29)</f>
         <v>96</v>
       </c>
       <c r="C115" s="13" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D115" s="56"/>
       <c r="E115" s="56"/>
@@ -43008,14 +43265,14 @@
     </row>
     <row r="116" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A116" s="9" t="s">
-        <v>641</v>
+        <v>645</v>
       </c>
       <c r="B116" s="57" t="n">
         <f aca="false">SUM(04_Monthly_2026_2028!AD30:AE41)</f>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C116" s="13" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D116" s="56"/>
       <c r="E116" s="56"/>
@@ -43025,22 +43282,22 @@
     </row>
     <row r="117" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="11" t="s">
-        <v>642</v>
+        <v>646</v>
       </c>
       <c r="B117" s="11" t="s">
-        <v>643</v>
+        <v>647</v>
       </c>
       <c r="C117" s="11" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D117" s="11" t="s">
-        <v>644</v>
+        <v>648</v>
       </c>
       <c r="E117" s="33" t="s">
-        <v>645</v>
+        <v>649</v>
       </c>
       <c r="F117" s="33" t="s">
-        <v>646</v>
+        <v>650</v>
       </c>
       <c r="G117" s="11"/>
       <c r="H117" s="11" t="s">
@@ -43049,7 +43306,7 @@
     </row>
     <row r="118" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A118" s="52" t="s">
-        <v>647</v>
+        <v>651</v>
       </c>
       <c r="B118" s="15" t="s">
         <v>69</v>
@@ -43070,12 +43327,12 @@
         <v>미확인</v>
       </c>
       <c r="H118" s="54" t="s">
-        <v>648</v>
+        <v>652</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A119" s="52" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B119" s="15" t="n">
         <f aca="false">01_Inputs!$B$93</f>
@@ -43103,7 +43360,7 @@
     </row>
     <row r="120" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A120" s="52" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B120" s="15" t="n">
         <f aca="false">01_Inputs!$B$94</f>
@@ -43131,7 +43388,7 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="52" t="s">
-        <v>651</v>
+        <v>655</v>
       </c>
       <c r="B121" s="15" t="n">
         <f aca="false">01_Inputs!$B$95</f>
@@ -43159,36 +43416,36 @@
     </row>
     <row r="123" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A123" s="49" t="s">
-        <v>652</v>
+        <v>656</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="33" t="s">
-        <v>653</v>
+        <v>657</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>654</v>
+        <v>658</v>
       </c>
       <c r="C124" s="11" t="s">
-        <v>655</v>
+        <v>659</v>
       </c>
       <c r="D124" s="33" t="s">
-        <v>656</v>
+        <v>660</v>
       </c>
       <c r="E124" s="11" t="s">
-        <v>657</v>
+        <v>661</v>
       </c>
       <c r="F124" s="11" t="s">
-        <v>658</v>
+        <v>662</v>
       </c>
       <c r="G124" s="11"/>
       <c r="H124" s="11" t="s">
-        <v>659</v>
+        <v>663</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A125" s="52" t="s">
-        <v>649</v>
+        <v>653</v>
       </c>
       <c r="B125" s="15" t="n">
         <f aca="false">01_Inputs!$B$93</f>
@@ -43217,7 +43474,7 @@
     </row>
     <row r="126" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A126" s="52" t="s">
-        <v>650</v>
+        <v>654</v>
       </c>
       <c r="B126" s="15" t="n">
         <f aca="false">01_Inputs!$B$94</f>
@@ -43246,7 +43503,7 @@
     </row>
     <row r="127" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A127" s="52" t="s">
-        <v>660</v>
+        <v>664</v>
       </c>
       <c r="B127" s="15" t="n">
         <f aca="false">01_Inputs!$B$95</f>
@@ -43275,12 +43532,12 @@
     </row>
     <row r="129" customFormat="false" ht="17.15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A129" s="49" t="s">
-        <v>661</v>
+        <v>665</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="9" t="s">
-        <v>662</v>
+        <v>666</v>
       </c>
       <c r="B130" s="60" t="n">
         <f aca="false">01_Inputs!$B$51</f>
@@ -43290,7 +43547,7 @@
         <v>147</v>
       </c>
       <c r="D130" s="56" t="s">
-        <v>663</v>
+        <v>667</v>
       </c>
       <c r="E130" s="56"/>
       <c r="F130" s="56"/>
@@ -43299,7 +43556,7 @@
     </row>
     <row r="131" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="13" t="s">
-        <v>664</v>
+        <v>668</v>
       </c>
       <c r="B131" s="22" t="n">
         <f aca="false">01_Inputs!$B$49-01_Inputs!$B$43</f>
@@ -43309,7 +43566,7 @@
         <v>151</v>
       </c>
       <c r="D131" s="55" t="s">
-        <v>665</v>
+        <v>669</v>
       </c>
       <c r="E131" s="55"/>
       <c r="F131" s="55"/>
@@ -43318,7 +43575,7 @@
     </row>
     <row r="132" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="13" t="s">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="B132" s="22" t="n">
         <f aca="false">01_Inputs!$B$49-01_Inputs!$B$44</f>
@@ -43328,7 +43585,7 @@
         <v>151</v>
       </c>
       <c r="D132" s="55" t="s">
-        <v>667</v>
+        <v>671</v>
       </c>
       <c r="E132" s="55"/>
       <c r="F132" s="55"/>
@@ -43337,7 +43594,7 @@
     </row>
     <row r="133" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="13" t="s">
-        <v>668</v>
+        <v>672</v>
       </c>
       <c r="B133" s="23" t="n">
         <f aca="false">01_Inputs!$B$52*01_Inputs!$B$53</f>
@@ -43347,7 +43604,7 @@
         <v>151</v>
       </c>
       <c r="D133" s="56" t="s">
-        <v>669</v>
+        <v>673</v>
       </c>
       <c r="E133" s="56"/>
       <c r="F133" s="56"/>
@@ -43356,7 +43613,7 @@
     </row>
     <row r="134" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A134" s="13" t="s">
-        <v>670</v>
+        <v>674</v>
       </c>
       <c r="B134" s="23" t="n">
         <f aca="false">01_Inputs!$B$52*01_Inputs!$B$54</f>
@@ -43373,7 +43630,7 @@
     </row>
     <row r="135" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="13" t="s">
-        <v>671</v>
+        <v>675</v>
       </c>
       <c r="B135" s="63" t="str">
         <f aca="false">IF(AND(ISNUMBER(01_Inputs!$B$60),ISNUMBER(01_Inputs!$B$58)),01_Inputs!$B$60/01_Inputs!$B$58,"보류")</f>
@@ -43383,7 +43640,7 @@
         <v>159</v>
       </c>
       <c r="D135" s="56" t="s">
-        <v>672</v>
+        <v>676</v>
       </c>
       <c r="E135" s="56"/>
       <c r="F135" s="56"/>
@@ -43392,7 +43649,7 @@
     </row>
     <row r="136" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A136" s="13" t="s">
-        <v>673</v>
+        <v>677</v>
       </c>
       <c r="B136" s="63" t="str">
         <f aca="false">IF(AND(ISNUMBER(01_Inputs!$B$60),ISNUMBER(01_Inputs!$B$58),ISNUMBER(01_Inputs!$B$59)),01_Inputs!$B$60/(01_Inputs!$B$58+01_Inputs!$B$59),"보류")</f>
@@ -43526,12 +43783,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>674</v>
+        <v>678</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>675</v>
+        <v>679</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -43580,175 +43837,175 @@
     </row>
     <row r="5" customFormat="false" ht="54" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="11" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B5" s="11" t="s">
-        <v>311</v>
+        <v>314</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>677</v>
+        <v>681</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="E5" s="11" t="s">
-        <v>679</v>
+        <v>683</v>
       </c>
       <c r="F5" s="11" t="s">
-        <v>680</v>
+        <v>684</v>
       </c>
       <c r="G5" s="11" t="s">
-        <v>681</v>
+        <v>685</v>
       </c>
       <c r="H5" s="11" t="s">
-        <v>682</v>
+        <v>686</v>
       </c>
       <c r="I5" s="11" t="s">
-        <v>683</v>
+        <v>687</v>
       </c>
       <c r="J5" s="11" t="s">
-        <v>684</v>
+        <v>688</v>
       </c>
       <c r="K5" s="11" t="s">
-        <v>685</v>
+        <v>689</v>
       </c>
       <c r="L5" s="11" t="s">
-        <v>686</v>
+        <v>690</v>
       </c>
       <c r="M5" s="11" t="s">
-        <v>687</v>
+        <v>691</v>
       </c>
       <c r="N5" s="11" t="s">
-        <v>688</v>
+        <v>692</v>
       </c>
       <c r="O5" s="11" t="s">
-        <v>689</v>
+        <v>693</v>
       </c>
       <c r="P5" s="11" t="s">
-        <v>690</v>
+        <v>694</v>
       </c>
       <c r="Q5" s="33" t="s">
-        <v>691</v>
+        <v>695</v>
       </c>
       <c r="R5" s="11" t="s">
-        <v>692</v>
+        <v>696</v>
       </c>
       <c r="S5" s="11" t="s">
-        <v>693</v>
+        <v>697</v>
       </c>
       <c r="T5" s="11" t="s">
-        <v>694</v>
+        <v>698</v>
       </c>
       <c r="U5" s="11" t="s">
-        <v>695</v>
+        <v>699</v>
       </c>
       <c r="V5" s="33" t="s">
-        <v>696</v>
+        <v>700</v>
       </c>
       <c r="W5" s="11" t="s">
-        <v>697</v>
+        <v>701</v>
       </c>
       <c r="X5" s="11" t="s">
-        <v>698</v>
+        <v>702</v>
       </c>
       <c r="Y5" s="11" t="s">
-        <v>699</v>
+        <v>703</v>
       </c>
       <c r="Z5" s="11" t="s">
-        <v>700</v>
+        <v>704</v>
       </c>
       <c r="AA5" s="33" t="s">
-        <v>701</v>
+        <v>705</v>
       </c>
       <c r="AB5" s="33" t="s">
-        <v>702</v>
+        <v>706</v>
       </c>
       <c r="AC5" s="33" t="s">
-        <v>703</v>
+        <v>707</v>
       </c>
       <c r="AD5" s="11" t="s">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="AE5" s="11" t="s">
-        <v>705</v>
+        <v>709</v>
       </c>
       <c r="AF5" s="11" t="s">
-        <v>706</v>
+        <v>710</v>
       </c>
       <c r="AG5" s="11" t="s">
-        <v>707</v>
+        <v>711</v>
       </c>
       <c r="AH5" s="11" t="s">
-        <v>708</v>
+        <v>712</v>
       </c>
       <c r="AI5" s="11" t="s">
-        <v>709</v>
+        <v>713</v>
       </c>
       <c r="AJ5" s="33" t="s">
-        <v>710</v>
+        <v>714</v>
       </c>
       <c r="AK5" s="33" t="s">
-        <v>711</v>
+        <v>715</v>
       </c>
       <c r="AL5" s="33" t="s">
-        <v>712</v>
+        <v>716</v>
       </c>
       <c r="AM5" s="11" t="s">
-        <v>713</v>
+        <v>717</v>
       </c>
       <c r="AN5" s="11" t="s">
-        <v>714</v>
+        <v>718</v>
       </c>
       <c r="AO5" s="11" t="s">
-        <v>715</v>
+        <v>719</v>
       </c>
       <c r="AP5" s="11" t="s">
-        <v>716</v>
+        <v>720</v>
       </c>
       <c r="AQ5" s="11" t="s">
-        <v>717</v>
+        <v>721</v>
       </c>
       <c r="AR5" s="11" t="s">
-        <v>718</v>
+        <v>722</v>
       </c>
       <c r="AS5" s="11" t="s">
-        <v>719</v>
+        <v>723</v>
       </c>
       <c r="AT5" s="11" t="s">
-        <v>720</v>
+        <v>724</v>
       </c>
       <c r="AU5" s="11" t="s">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="AV5" s="33" t="s">
-        <v>722</v>
+        <v>726</v>
       </c>
       <c r="AW5" s="11" t="s">
-        <v>723</v>
+        <v>727</v>
       </c>
       <c r="AX5" s="11" t="s">
-        <v>724</v>
+        <v>728</v>
       </c>
       <c r="AY5" s="11" t="s">
-        <v>725</v>
+        <v>729</v>
       </c>
       <c r="AZ5" s="11" t="s">
-        <v>726</v>
+        <v>730</v>
       </c>
       <c r="BA5" s="11" t="s">
-        <v>727</v>
+        <v>731</v>
       </c>
       <c r="BB5" s="11" t="s">
-        <v>728</v>
+        <v>732</v>
       </c>
       <c r="BC5" s="11" t="s">
-        <v>729</v>
+        <v>733</v>
       </c>
       <c r="BD5" s="11" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
       <c r="BE5" s="11" t="s">
-        <v>731</v>
+        <v>735</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -49187,7 +49444,7 @@
       </c>
       <c r="W30" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$C$136),01_Inputs!$C$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X30" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$C$137),01_Inputs!$C$137,"미제시")</f>
@@ -49195,11 +49452,11 @@
       </c>
       <c r="Y30" s="35" t="n">
         <f aca="false">SUM(U30:X30)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z30" s="64" t="n">
         <f aca="false">Y30/Q30</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA30" s="64" t="n">
         <f aca="false">(N(U30)+N(V30))/01_Inputs!$B$42</f>
@@ -49215,7 +49472,7 @@
       </c>
       <c r="AD30" s="64" t="n">
         <f aca="false">N(W30)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE30" s="64" t="n">
         <f aca="false">N(X30)/01_Inputs!$B$44</f>
@@ -49243,11 +49500,11 @@
       </c>
       <c r="AK30" s="15" t="n">
         <f aca="false">(AD30+AE30)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL30" s="15" t="n">
         <f aca="false">(AD30+AE30)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM30" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -49259,7 +49516,7 @@
       </c>
       <c r="AO30" s="37" t="n">
         <f aca="false">T30-Y30</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP30" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S30),S30-Y30,"미확인")</f>
@@ -49410,7 +49667,7 @@
       </c>
       <c r="W31" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$D$136),01_Inputs!$D$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X31" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$D$137),01_Inputs!$D$137,"미제시")</f>
@@ -49418,11 +49675,11 @@
       </c>
       <c r="Y31" s="35" t="n">
         <f aca="false">SUM(U31:X31)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z31" s="64" t="n">
         <f aca="false">Y31/Q31</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA31" s="64" t="n">
         <f aca="false">(N(U31)+N(V31))/01_Inputs!$B$42</f>
@@ -49438,7 +49695,7 @@
       </c>
       <c r="AD31" s="64" t="n">
         <f aca="false">N(W31)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE31" s="64" t="n">
         <f aca="false">N(X31)/01_Inputs!$B$44</f>
@@ -49466,11 +49723,11 @@
       </c>
       <c r="AK31" s="15" t="n">
         <f aca="false">(AD31+AE31)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL31" s="15" t="n">
         <f aca="false">(AD31+AE31)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM31" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -49482,7 +49739,7 @@
       </c>
       <c r="AO31" s="37" t="n">
         <f aca="false">T31-Y31</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP31" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S31),S31-Y31,"미확인")</f>
@@ -49633,7 +49890,7 @@
       </c>
       <c r="W32" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$E$136),01_Inputs!$E$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X32" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$E$137),01_Inputs!$E$137,"미제시")</f>
@@ -49641,11 +49898,11 @@
       </c>
       <c r="Y32" s="35" t="n">
         <f aca="false">SUM(U32:X32)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z32" s="64" t="n">
         <f aca="false">Y32/Q32</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA32" s="64" t="n">
         <f aca="false">(N(U32)+N(V32))/01_Inputs!$B$42</f>
@@ -49661,7 +49918,7 @@
       </c>
       <c r="AD32" s="64" t="n">
         <f aca="false">N(W32)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE32" s="64" t="n">
         <f aca="false">N(X32)/01_Inputs!$B$44</f>
@@ -49689,11 +49946,11 @@
       </c>
       <c r="AK32" s="15" t="n">
         <f aca="false">(AD32+AE32)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL32" s="15" t="n">
         <f aca="false">(AD32+AE32)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM32" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -49705,7 +49962,7 @@
       </c>
       <c r="AO32" s="37" t="n">
         <f aca="false">T32-Y32</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP32" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S32),S32-Y32,"미확인")</f>
@@ -49856,7 +50113,7 @@
       </c>
       <c r="W33" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$F$136),01_Inputs!$F$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X33" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$F$137),01_Inputs!$F$137,"미제시")</f>
@@ -49864,11 +50121,11 @@
       </c>
       <c r="Y33" s="35" t="n">
         <f aca="false">SUM(U33:X33)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z33" s="64" t="n">
         <f aca="false">Y33/Q33</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA33" s="64" t="n">
         <f aca="false">(N(U33)+N(V33))/01_Inputs!$B$42</f>
@@ -49884,7 +50141,7 @@
       </c>
       <c r="AD33" s="64" t="n">
         <f aca="false">N(W33)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE33" s="64" t="n">
         <f aca="false">N(X33)/01_Inputs!$B$44</f>
@@ -49912,11 +50169,11 @@
       </c>
       <c r="AK33" s="15" t="n">
         <f aca="false">(AD33+AE33)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL33" s="15" t="n">
         <f aca="false">(AD33+AE33)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM33" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -49928,7 +50185,7 @@
       </c>
       <c r="AO33" s="37" t="n">
         <f aca="false">T33-Y33</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP33" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S33),S33-Y33,"미확인")</f>
@@ -50079,7 +50336,7 @@
       </c>
       <c r="W34" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$G$136),01_Inputs!$G$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X34" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$G$137),01_Inputs!$G$137,"미제시")</f>
@@ -50087,11 +50344,11 @@
       </c>
       <c r="Y34" s="35" t="n">
         <f aca="false">SUM(U34:X34)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z34" s="64" t="n">
         <f aca="false">Y34/Q34</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA34" s="64" t="n">
         <f aca="false">(N(U34)+N(V34))/01_Inputs!$B$42</f>
@@ -50107,7 +50364,7 @@
       </c>
       <c r="AD34" s="64" t="n">
         <f aca="false">N(W34)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE34" s="64" t="n">
         <f aca="false">N(X34)/01_Inputs!$B$44</f>
@@ -50135,11 +50392,11 @@
       </c>
       <c r="AK34" s="15" t="n">
         <f aca="false">(AD34+AE34)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL34" s="15" t="n">
         <f aca="false">(AD34+AE34)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM34" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -50151,7 +50408,7 @@
       </c>
       <c r="AO34" s="37" t="n">
         <f aca="false">T34-Y34</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP34" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S34),S34-Y34,"미확인")</f>
@@ -50302,7 +50559,7 @@
       </c>
       <c r="W35" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$H$136),01_Inputs!$H$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X35" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$H$137),01_Inputs!$H$137,"미제시")</f>
@@ -50310,11 +50567,11 @@
       </c>
       <c r="Y35" s="35" t="n">
         <f aca="false">SUM(U35:X35)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z35" s="64" t="n">
         <f aca="false">Y35/Q35</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA35" s="64" t="n">
         <f aca="false">(N(U35)+N(V35))/01_Inputs!$B$42</f>
@@ -50330,7 +50587,7 @@
       </c>
       <c r="AD35" s="64" t="n">
         <f aca="false">N(W35)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE35" s="64" t="n">
         <f aca="false">N(X35)/01_Inputs!$B$44</f>
@@ -50358,11 +50615,11 @@
       </c>
       <c r="AK35" s="15" t="n">
         <f aca="false">(AD35+AE35)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL35" s="15" t="n">
         <f aca="false">(AD35+AE35)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM35" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -50374,7 +50631,7 @@
       </c>
       <c r="AO35" s="37" t="n">
         <f aca="false">T35-Y35</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP35" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S35),S35-Y35,"미확인")</f>
@@ -50525,7 +50782,7 @@
       </c>
       <c r="W36" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$I$136),01_Inputs!$I$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X36" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$I$137),01_Inputs!$I$137,"미제시")</f>
@@ -50533,11 +50790,11 @@
       </c>
       <c r="Y36" s="35" t="n">
         <f aca="false">SUM(U36:X36)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z36" s="64" t="n">
         <f aca="false">Y36/Q36</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA36" s="64" t="n">
         <f aca="false">(N(U36)+N(V36))/01_Inputs!$B$42</f>
@@ -50553,7 +50810,7 @@
       </c>
       <c r="AD36" s="64" t="n">
         <f aca="false">N(W36)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE36" s="64" t="n">
         <f aca="false">N(X36)/01_Inputs!$B$44</f>
@@ -50581,11 +50838,11 @@
       </c>
       <c r="AK36" s="15" t="n">
         <f aca="false">(AD36+AE36)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL36" s="15" t="n">
         <f aca="false">(AD36+AE36)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM36" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -50597,7 +50854,7 @@
       </c>
       <c r="AO36" s="37" t="n">
         <f aca="false">T36-Y36</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP36" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S36),S36-Y36,"미확인")</f>
@@ -50748,7 +51005,7 @@
       </c>
       <c r="W37" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$J$136),01_Inputs!$J$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X37" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$J$137),01_Inputs!$J$137,"미제시")</f>
@@ -50756,11 +51013,11 @@
       </c>
       <c r="Y37" s="35" t="n">
         <f aca="false">SUM(U37:X37)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z37" s="64" t="n">
         <f aca="false">Y37/Q37</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA37" s="64" t="n">
         <f aca="false">(N(U37)+N(V37))/01_Inputs!$B$42</f>
@@ -50776,7 +51033,7 @@
       </c>
       <c r="AD37" s="64" t="n">
         <f aca="false">N(W37)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE37" s="64" t="n">
         <f aca="false">N(X37)/01_Inputs!$B$44</f>
@@ -50804,11 +51061,11 @@
       </c>
       <c r="AK37" s="15" t="n">
         <f aca="false">(AD37+AE37)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL37" s="15" t="n">
         <f aca="false">(AD37+AE37)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM37" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -50820,7 +51077,7 @@
       </c>
       <c r="AO37" s="37" t="n">
         <f aca="false">T37-Y37</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP37" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S37),S37-Y37,"미확인")</f>
@@ -50971,7 +51228,7 @@
       </c>
       <c r="W38" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$K$136),01_Inputs!$K$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X38" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$K$137),01_Inputs!$K$137,"미제시")</f>
@@ -50979,11 +51236,11 @@
       </c>
       <c r="Y38" s="35" t="n">
         <f aca="false">SUM(U38:X38)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z38" s="64" t="n">
         <f aca="false">Y38/Q38</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA38" s="64" t="n">
         <f aca="false">(N(U38)+N(V38))/01_Inputs!$B$42</f>
@@ -50999,7 +51256,7 @@
       </c>
       <c r="AD38" s="64" t="n">
         <f aca="false">N(W38)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE38" s="64" t="n">
         <f aca="false">N(X38)/01_Inputs!$B$44</f>
@@ -51027,11 +51284,11 @@
       </c>
       <c r="AK38" s="15" t="n">
         <f aca="false">(AD38+AE38)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL38" s="15" t="n">
         <f aca="false">(AD38+AE38)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM38" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -51043,7 +51300,7 @@
       </c>
       <c r="AO38" s="37" t="n">
         <f aca="false">T38-Y38</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP38" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S38),S38-Y38,"미확인")</f>
@@ -51194,7 +51451,7 @@
       </c>
       <c r="W39" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$L$136),01_Inputs!$L$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X39" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$L$137),01_Inputs!$L$137,"미제시")</f>
@@ -51202,11 +51459,11 @@
       </c>
       <c r="Y39" s="35" t="n">
         <f aca="false">SUM(U39:X39)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z39" s="64" t="n">
         <f aca="false">Y39/Q39</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA39" s="64" t="n">
         <f aca="false">(N(U39)+N(V39))/01_Inputs!$B$42</f>
@@ -51222,7 +51479,7 @@
       </c>
       <c r="AD39" s="64" t="n">
         <f aca="false">N(W39)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE39" s="64" t="n">
         <f aca="false">N(X39)/01_Inputs!$B$44</f>
@@ -51250,11 +51507,11 @@
       </c>
       <c r="AK39" s="15" t="n">
         <f aca="false">(AD39+AE39)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL39" s="15" t="n">
         <f aca="false">(AD39+AE39)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM39" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -51266,7 +51523,7 @@
       </c>
       <c r="AO39" s="37" t="n">
         <f aca="false">T39-Y39</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP39" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S39),S39-Y39,"미확인")</f>
@@ -51417,7 +51674,7 @@
       </c>
       <c r="W40" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$M$136),01_Inputs!$M$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X40" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$M$137),01_Inputs!$M$137,"미제시")</f>
@@ -51425,11 +51682,11 @@
       </c>
       <c r="Y40" s="35" t="n">
         <f aca="false">SUM(U40:X40)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z40" s="64" t="n">
         <f aca="false">Y40/Q40</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA40" s="64" t="n">
         <f aca="false">(N(U40)+N(V40))/01_Inputs!$B$42</f>
@@ -51445,7 +51702,7 @@
       </c>
       <c r="AD40" s="64" t="n">
         <f aca="false">N(W40)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE40" s="64" t="n">
         <f aca="false">N(X40)/01_Inputs!$B$44</f>
@@ -51473,11 +51730,11 @@
       </c>
       <c r="AK40" s="15" t="n">
         <f aca="false">(AD40+AE40)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL40" s="15" t="n">
         <f aca="false">(AD40+AE40)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM40" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -51489,7 +51746,7 @@
       </c>
       <c r="AO40" s="37" t="n">
         <f aca="false">T40-Y40</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP40" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S40),S40-Y40,"미확인")</f>
@@ -51640,7 +51897,7 @@
       </c>
       <c r="W41" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$N$136),01_Inputs!$N$136,"미제시")</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="X41" s="70" t="n">
         <f aca="false">IF(ISNUMBER(01_Inputs!$N$137),01_Inputs!$N$137,"미제시")</f>
@@ -51648,11 +51905,11 @@
       </c>
       <c r="Y41" s="35" t="n">
         <f aca="false">SUM(U41:X41)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z41" s="64" t="n">
         <f aca="false">Y41/Q41</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="AA41" s="64" t="n">
         <f aca="false">(N(U41)+N(V41))/01_Inputs!$B$42</f>
@@ -51668,7 +51925,7 @@
       </c>
       <c r="AD41" s="64" t="n">
         <f aca="false">N(W41)/01_Inputs!$B$43</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE41" s="64" t="n">
         <f aca="false">N(X41)/01_Inputs!$B$44</f>
@@ -51696,11 +51953,11 @@
       </c>
       <c r="AK41" s="15" t="n">
         <f aca="false">(AD41+AE41)*01_Inputs!$B$38</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL41" s="15" t="n">
         <f aca="false">(AD41+AE41)*01_Inputs!$B$33</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AM41" s="15" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$87),01_Inputs!$B$87,"미확인")</f>
@@ -51712,7 +51969,7 @@
       </c>
       <c r="AO41" s="37" t="n">
         <f aca="false">T41-Y41</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="AP41" s="37" t="str">
         <f aca="false">IF(ISNUMBER(S41),S41-Y41,"미확인")</f>
@@ -51781,7 +52038,7 @@
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="38" t="s">
-        <v>732</v>
+        <v>736</v>
       </c>
       <c r="J42" s="45" t="n">
         <f aca="false">IF(COUNT(J6:J17)=12,SUM(J6:J17),"부분합계 "&amp;TEXT(SUM(J6:J17),"#,##0")&amp;" ("&amp;COUNT(J6:J17)&amp;"/12개월)")</f>
@@ -51878,7 +52135,7 @@
     </row>
     <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="38" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="J43" s="45" t="str">
         <f aca="false">IF(COUNT(J18:J29)=12,SUM(J18:J29),"부분합계 "&amp;TEXT(SUM(J18:J29),"#,##0")&amp;" ("&amp;COUNT(J18:J29)&amp;"/12개월)")</f>
@@ -51967,7 +52224,7 @@
     </row>
     <row r="44" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="38" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="J44" s="45" t="str">
         <f aca="false">IF(COUNT(J30:J41)=12,SUM(J30:J41),"부분합계 "&amp;TEXT(SUM(J30:J41),"#,##0")&amp;" ("&amp;COUNT(J30:J41)&amp;"/12개월)")</f>
@@ -51999,7 +52256,7 @@
       </c>
       <c r="W44" s="35" t="n">
         <f aca="false">SUM(W30:W41)</f>
-        <v>13440</v>
+        <v>10080</v>
       </c>
       <c r="X44" s="35" t="n">
         <f aca="false">IF(COUNT(X30:X41)=0,"미제시",SUM(X30:X41))</f>
@@ -52007,11 +52264,11 @@
       </c>
       <c r="Y44" s="35" t="n">
         <f aca="false">SUM(Y30:Y41)</f>
-        <v>49120</v>
+        <v>45760</v>
       </c>
       <c r="Z44" s="71" t="n">
         <f aca="false">SUM(Z30:Z41)</f>
-        <v>258.526315789474</v>
+        <v>240.842105263158</v>
       </c>
       <c r="AA44" s="71" t="n">
         <f aca="false">SUM(AA30:AA41)</f>
@@ -52027,7 +52284,7 @@
       </c>
       <c r="AD44" s="71" t="n">
         <f aca="false">SUM(AD30:AD41)</f>
-        <v>96</v>
+        <v>72</v>
       </c>
       <c r="AE44" s="71" t="n">
         <f aca="false">SUM(AE30:AE41)</f>
@@ -52043,20 +52300,20 @@
       </c>
       <c r="AK44" s="53" t="n">
         <f aca="false">SUM(AK30:AK41)</f>
-        <v>960</v>
+        <v>768</v>
       </c>
       <c r="AL44" s="53" t="n">
         <f aca="false">SUM(AL30:AL41)</f>
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="AO44" s="35" t="n">
         <f aca="false">SUM(AO30:AO41)</f>
-        <v>-1919.99999999999</v>
+        <v>1440.00000000001</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="38" t="s">
-        <v>733</v>
+        <v>737</v>
       </c>
       <c r="Y45" s="37" t="n">
         <f aca="false">MAX(Y6:Y17)</f>
@@ -52093,7 +52350,7 @@
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="38" t="s">
-        <v>734</v>
+        <v>738</v>
       </c>
       <c r="Y46" s="37" t="n">
         <f aca="false">MAX(Y18:Y29)</f>
@@ -52130,11 +52387,11 @@
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="38" t="s">
-        <v>735</v>
+        <v>739</v>
       </c>
       <c r="Y47" s="37" t="n">
         <f aca="false">MAX(Y30:Y41)</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="AA47" s="64" t="n">
         <f aca="false">MAX(AA30:AA41)</f>
@@ -52150,7 +52407,7 @@
       </c>
       <c r="AD47" s="64" t="n">
         <f aca="false">MAX(AD30:AD41)</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AE47" s="64" t="n">
         <f aca="false">MAX(AE30:AE41)</f>
@@ -52158,41 +52415,41 @@
       </c>
       <c r="AK47" s="15" t="n">
         <f aca="false">MAX(AK30:AK41)</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="AL47" s="15" t="n">
         <f aca="false">MAX(AL30:AL41)</f>
-        <v>20</v>
+        <v>16</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="2" t="s">
-        <v>736</v>
+        <v>740</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="2" t="s">
-        <v>737</v>
+        <v>741</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="2" t="s">
-        <v>738</v>
+        <v>742</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="40" t="s">
-        <v>739</v>
+        <v>743</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="40" t="s">
-        <v>740</v>
+        <v>744</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="2" t="s">
-        <v>741</v>
+        <v>745</v>
       </c>
     </row>
   </sheetData>
@@ -52259,12 +52516,12 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>742</v>
+        <v>746</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>743</v>
+        <v>747</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -52313,7 +52570,7 @@
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="72" t="s">
-        <v>744</v>
+        <v>748</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -52321,30 +52578,30 @@
         <v>14</v>
       </c>
       <c r="B6" s="11" t="s">
-        <v>607</v>
+        <v>611</v>
       </c>
       <c r="C6" s="11" t="s">
-        <v>608</v>
+        <v>612</v>
       </c>
       <c r="D6" s="11" t="s">
-        <v>745</v>
+        <v>749</v>
       </c>
       <c r="E6" s="11" t="s">
-        <v>746</v>
+        <v>750</v>
       </c>
       <c r="F6" s="33" t="s">
-        <v>747</v>
+        <v>751</v>
       </c>
       <c r="G6" s="11" t="s">
-        <v>748</v>
+        <v>752</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="13" t="s">
-        <v>750</v>
+        <v>754</v>
       </c>
       <c r="B7" s="58" t="n">
         <v>46023</v>
@@ -52354,16 +52611,16 @@
         <v>46418</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E7" s="13" t="s">
-        <v>752</v>
+        <v>756</v>
       </c>
       <c r="F7" s="13" t="s">
-        <v>753</v>
+        <v>757</v>
       </c>
       <c r="G7" s="13" t="s">
-        <v>754</v>
+        <v>758</v>
       </c>
       <c r="H7" s="13" t="s">
         <v>21</v>
@@ -52371,7 +52628,7 @@
     </row>
     <row r="8" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="13" t="s">
-        <v>755</v>
+        <v>759</v>
       </c>
       <c r="B8" s="58" t="n">
         <f aca="false">01_Inputs!$B$75</f>
@@ -52382,10 +52639,10 @@
         <v>46538</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>751</v>
+        <v>755</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>756</v>
+        <v>760</v>
       </c>
       <c r="F8" s="9" t="s">
         <v>69</v>
@@ -52411,7 +52668,7 @@
         <v>46568</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>757</v>
+        <v>761</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>213</v>
@@ -52429,7 +52686,7 @@
     </row>
     <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
-        <v>758</v>
+        <v>762</v>
       </c>
       <c r="B10" s="58" t="n">
         <f aca="false">01_Inputs!$B$78</f>
@@ -52437,13 +52694,13 @@
       </c>
       <c r="C10" s="58"/>
       <c r="D10" s="9" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="E10" s="13" t="s">
-        <v>760</v>
+        <v>764</v>
       </c>
       <c r="F10" s="13" t="s">
-        <v>761</v>
+        <v>765</v>
       </c>
       <c r="G10" s="9" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$83),01_Inputs!$B$83&amp;" h/Batch","설비별 간격 미확인")</f>
@@ -52455,7 +52712,7 @@
     </row>
     <row r="11" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="13" t="s">
-        <v>762</v>
+        <v>766</v>
       </c>
       <c r="B11" s="58" t="n">
         <f aca="false">01_Inputs!$B$78</f>
@@ -52466,20 +52723,20 @@
         <v>46934</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="E11" s="9"/>
       <c r="F11" s="9"/>
       <c r="G11" s="9" t="s">
-        <v>763</v>
+        <v>767</v>
       </c>
       <c r="H11" s="13" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="12" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>764</v>
+        <v>768</v>
       </c>
       <c r="B12" s="58" t="n">
         <v>46753</v>
@@ -52488,14 +52745,14 @@
         <v>47118</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="E12" s="9"/>
       <c r="F12" s="9" t="s">
-        <v>765</v>
+        <v>769</v>
       </c>
       <c r="G12" s="9" t="s">
-        <v>766</v>
+        <v>770</v>
       </c>
       <c r="H12" s="13" t="s">
         <v>111</v>
@@ -52503,7 +52760,7 @@
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>767</v>
+        <v>771</v>
       </c>
       <c r="B13" s="58" t="str">
         <f aca="false">IF(ISNUMBER(01_Inputs!$B$72),01_Inputs!$B$72,"미정")</f>
@@ -52511,14 +52768,14 @@
       </c>
       <c r="C13" s="58"/>
       <c r="D13" s="9" t="s">
-        <v>759</v>
+        <v>763</v>
       </c>
       <c r="E13" s="9" t="s">
-        <v>768</v>
+        <v>772</v>
       </c>
       <c r="F13" s="9"/>
       <c r="G13" s="9" t="s">
-        <v>769</v>
+        <v>773</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>195</v>
@@ -52526,7 +52783,7 @@
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="72" t="s">
-        <v>770</v>
+        <v>774</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -52534,22 +52791,22 @@
         <v>14</v>
       </c>
       <c r="B16" s="11" t="s">
-        <v>771</v>
+        <v>775</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>772</v>
+        <v>776</v>
       </c>
       <c r="D16" s="11" t="s">
-        <v>773</v>
+        <v>777</v>
       </c>
       <c r="E16" s="33" t="s">
-        <v>774</v>
+        <v>778</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>775</v>
+        <v>779</v>
       </c>
       <c r="G16" s="11" t="s">
-        <v>749</v>
+        <v>753</v>
       </c>
       <c r="H16" s="11" t="s">
         <v>16</v>
@@ -52557,7 +52814,7 @@
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="13" t="s">
-        <v>776</v>
+        <v>780</v>
       </c>
       <c r="B17" s="47" t="n">
         <f aca="false">01_Inputs!$B$63</f>
@@ -52577,13 +52834,13 @@
         <v>63.5267175572519</v>
       </c>
       <c r="G17" s="13" t="s">
-        <v>777</v>
+        <v>781</v>
       </c>
       <c r="H17" s="9"/>
     </row>
     <row r="18" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="13" t="s">
-        <v>778</v>
+        <v>782</v>
       </c>
       <c r="B18" s="47" t="n">
         <f aca="false">01_Inputs!$B$66</f>
@@ -52603,15 +52860,15 @@
         <v>63.5267175572519</v>
       </c>
       <c r="G18" s="13" t="s">
-        <v>591</v>
+        <v>595</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>779</v>
+        <v>783</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="13" t="s">
-        <v>780</v>
+        <v>784</v>
       </c>
       <c r="B19" s="47" t="n">
         <f aca="false">01_Inputs!$B$65</f>
@@ -52634,15 +52891,15 @@
         <v>70.5254237288136</v>
       </c>
       <c r="G19" s="13" t="s">
-        <v>781</v>
+        <v>785</v>
       </c>
       <c r="H19" s="9" t="s">
-        <v>782</v>
+        <v>786</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="B20" s="47" t="n">
         <f aca="false">01_Inputs!$B$68</f>
@@ -52668,12 +52925,12 @@
         <v>195</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>784</v>
+        <v>788</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="13" t="s">
-        <v>785</v>
+        <v>789</v>
       </c>
       <c r="B21" s="47" t="n">
         <f aca="false">01_Inputs!$B$69</f>
@@ -52693,42 +52950,42 @@
         <v>66.576</v>
       </c>
       <c r="G21" s="13" t="s">
-        <v>786</v>
+        <v>790</v>
       </c>
       <c r="H21" s="9" t="s">
-        <v>787</v>
+        <v>791</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="72" t="s">
-        <v>788</v>
+        <v>792</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="11" t="s">
-        <v>789</v>
+        <v>793</v>
       </c>
       <c r="B24" s="11" t="s">
-        <v>790</v>
+        <v>794</v>
       </c>
       <c r="C24" s="11" t="s">
-        <v>791</v>
+        <v>795</v>
       </c>
       <c r="D24" s="33" t="s">
-        <v>792</v>
+        <v>796</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>793</v>
+        <v>797</v>
       </c>
       <c r="F24" s="11"/>
       <c r="G24" s="11"/>
       <c r="H24" s="11" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>795</v>
+        <v>799</v>
       </c>
       <c r="B25" s="62" t="n">
         <f aca="false">01_Inputs!$O$138/1000</f>
@@ -52749,12 +53006,12 @@
       <c r="F25" s="73"/>
       <c r="G25" s="73"/>
       <c r="H25" s="9" t="s">
-        <v>796</v>
+        <v>800</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>797</v>
+        <v>801</v>
       </c>
       <c r="B26" s="62" t="n">
         <f aca="false">01_Inputs!$O$139/1000</f>
@@ -52775,12 +53032,12 @@
       <c r="F26" s="73"/>
       <c r="G26" s="73"/>
       <c r="H26" s="9" t="s">
-        <v>798</v>
+        <v>802</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>799</v>
+        <v>803</v>
       </c>
       <c r="B27" s="62" t="n">
         <f aca="false">01_Inputs!$O$139/1000</f>
@@ -52801,12 +53058,12 @@
       <c r="F27" s="73"/>
       <c r="G27" s="73"/>
       <c r="H27" s="9" t="s">
-        <v>800</v>
+        <v>804</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>801</v>
+        <v>805</v>
       </c>
       <c r="B28" s="62" t="n">
         <f aca="false">SUM(01_Inputs!C139:H139)/1000</f>
@@ -52827,12 +53084,12 @@
       <c r="F28" s="73"/>
       <c r="G28" s="73"/>
       <c r="H28" s="13" t="s">
-        <v>802</v>
+        <v>806</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>803</v>
+        <v>807</v>
       </c>
       <c r="B29" s="62" t="n">
         <f aca="false">SUM(01_Inputs!I139:N139)/1000</f>
@@ -52853,16 +53110,16 @@
       <c r="F29" s="73"/>
       <c r="G29" s="73"/>
       <c r="H29" s="9" t="s">
-        <v>804</v>
-      </c>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>808</v>
+      </c>
+    </row>
+    <row r="30" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>805</v>
+        <v>809</v>
       </c>
       <c r="B30" s="62" t="n">
         <f aca="false">01_Inputs!$O$140/1000</f>
-        <v>49.12</v>
+        <v>45.76</v>
       </c>
       <c r="C30" s="62" t="n">
         <f aca="false">01_Inputs!$B$65</f>
@@ -52870,25 +53127,25 @@
       </c>
       <c r="D30" s="47" t="n">
         <f aca="false">C30-B30</f>
-        <v>-1.91999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="E30" s="9" t="str">
         <f aca="false">IF(D30&lt;0,"부족 방향","여유 방향")</f>
-        <v>부족 방향</v>
+        <v>여유 방향</v>
       </c>
       <c r="F30" s="73"/>
       <c r="G30" s="73"/>
-      <c r="H30" s="9" t="s">
-        <v>806</v>
-      </c>
-    </row>
-    <row r="31" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="H30" s="13" t="s">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>807</v>
+        <v>811</v>
       </c>
       <c r="B31" s="62" t="n">
         <f aca="false">01_Inputs!$O$140/1000</f>
-        <v>49.12</v>
+        <v>45.76</v>
       </c>
       <c r="C31" s="62" t="n">
         <f aca="false">01_Inputs!$B$68</f>
@@ -52896,7 +53153,7 @@
       </c>
       <c r="D31" s="47" t="n">
         <f aca="false">C31-B31</f>
-        <v>1.08000000000001</v>
+        <v>4.44000000000001</v>
       </c>
       <c r="E31" s="9" t="str">
         <f aca="false">IF(D31&lt;0,"부족 방향","여유 방향")</f>
@@ -52904,13 +53161,13 @@
       </c>
       <c r="F31" s="73"/>
       <c r="G31" s="73"/>
-      <c r="H31" s="9" t="s">
-        <v>808</v>
+      <c r="H31" s="13" t="s">
+        <v>812</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="72" t="s">
-        <v>809</v>
+        <v>813</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -52918,76 +53175,76 @@
         <v>14</v>
       </c>
       <c r="B34" s="33" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C34" s="33" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D34" s="33" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E34" s="33" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="F34" s="33" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="G34" s="33" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="H34" s="33" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="I34" s="33" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="J34" s="33" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K34" s="33" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="L34" s="33" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="M34" s="33" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="N34" s="33" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="O34" s="33" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="P34" s="33" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="Q34" s="33" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="R34" s="33" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="S34" s="33" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="T34" s="33" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="U34" s="33" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="V34" s="33" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="W34" s="33" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="X34" s="33" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="Y34" s="33" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="Z34" s="11" t="s">
         <v>16</v>
@@ -52995,7 +53252,7 @@
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="52" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="B35" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!D18</f>
@@ -53096,7 +53353,7 @@
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="52" t="s">
-        <v>834</v>
+        <v>838</v>
       </c>
       <c r="B36" s="57" t="n">
         <f aca="false">04_Monthly_2026_2028!O18</f>
@@ -53197,7 +53454,7 @@
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="52" t="s">
-        <v>835</v>
+        <v>839</v>
       </c>
       <c r="B37" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!S18</f>
@@ -53298,7 +53555,7 @@
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="52" t="s">
-        <v>836</v>
+        <v>840</v>
       </c>
       <c r="B38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y18</f>
@@ -53350,81 +53607,81 @@
       </c>
       <c r="N38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y30</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="O38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y31</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="P38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y32</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Q38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y33</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="R38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y34</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="S38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y35</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="T38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y36</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="U38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y37</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="V38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y38</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="W38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y39</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="X38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y40</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Y38" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y41</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="72" t="s">
-        <v>837</v>
+        <v>841</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>838</v>
+        <v>842</v>
       </c>
       <c r="B41" s="33" t="s">
-        <v>839</v>
+        <v>843</v>
       </c>
       <c r="C41" s="33" t="s">
-        <v>840</v>
+        <v>844</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>841</v>
+        <v>845</v>
       </c>
       <c r="E41" s="11"/>
       <c r="F41" s="11"/>
       <c r="G41" s="11"/>
       <c r="H41" s="11" t="s">
-        <v>794</v>
+        <v>798</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="52" t="s">
-        <v>842</v>
+        <v>846</v>
       </c>
       <c r="B42" s="74" t="n">
         <v>0</v>
@@ -53436,12 +53693,12 @@
         <v>0.5</v>
       </c>
       <c r="H42" s="54" t="s">
-        <v>843</v>
+        <v>847</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="52" t="s">
-        <v>844</v>
+        <v>848</v>
       </c>
       <c r="B43" s="31" t="n">
         <v>0</v>
@@ -53453,12 +53710,12 @@
         <v>0</v>
       </c>
       <c r="H43" s="54" t="s">
-        <v>845</v>
+        <v>849</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="52" t="s">
-        <v>846</v>
+        <v>850</v>
       </c>
       <c r="B44" s="30" t="n">
         <v>0</v>
@@ -53470,12 +53727,12 @@
         <v>3</v>
       </c>
       <c r="H44" s="54" t="s">
-        <v>847</v>
+        <v>851</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="52" t="s">
-        <v>848</v>
+        <v>852</v>
       </c>
       <c r="B45" s="31" t="n">
         <f aca="false">01_Inputs!$B$65*1000/12</f>
@@ -53490,12 +53747,12 @@
         <v>3933.33333333333</v>
       </c>
       <c r="H45" s="54" t="s">
-        <v>849</v>
+        <v>853</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="38" t="s">
-        <v>850</v>
+        <v>854</v>
       </c>
       <c r="B46" s="30" t="n">
         <v>0</v>
@@ -53507,12 +53764,12 @@
         <v>0</v>
       </c>
       <c r="H46" s="51" t="s">
-        <v>851</v>
+        <v>855</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="52" t="s">
-        <v>852</v>
+        <v>856</v>
       </c>
       <c r="B47" s="74" t="n">
         <v>1</v>
@@ -53524,92 +53781,92 @@
         <v>1</v>
       </c>
       <c r="H47" s="54" t="s">
-        <v>853</v>
+        <v>857</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="11" t="s">
-        <v>854</v>
+        <v>858</v>
       </c>
       <c r="B49" s="33" t="s">
-        <v>810</v>
+        <v>814</v>
       </c>
       <c r="C49" s="33" t="s">
-        <v>811</v>
+        <v>815</v>
       </c>
       <c r="D49" s="33" t="s">
-        <v>812</v>
+        <v>816</v>
       </c>
       <c r="E49" s="33" t="s">
-        <v>813</v>
+        <v>817</v>
       </c>
       <c r="F49" s="33" t="s">
-        <v>814</v>
+        <v>818</v>
       </c>
       <c r="G49" s="33" t="s">
-        <v>815</v>
+        <v>819</v>
       </c>
       <c r="H49" s="33" t="s">
-        <v>816</v>
+        <v>820</v>
       </c>
       <c r="I49" s="33" t="s">
-        <v>817</v>
+        <v>821</v>
       </c>
       <c r="J49" s="33" t="s">
-        <v>818</v>
+        <v>822</v>
       </c>
       <c r="K49" s="33" t="s">
-        <v>819</v>
+        <v>823</v>
       </c>
       <c r="L49" s="33" t="s">
-        <v>820</v>
+        <v>824</v>
       </c>
       <c r="M49" s="33" t="s">
-        <v>821</v>
+        <v>825</v>
       </c>
       <c r="N49" s="33" t="s">
-        <v>822</v>
+        <v>826</v>
       </c>
       <c r="O49" s="33" t="s">
-        <v>823</v>
+        <v>827</v>
       </c>
       <c r="P49" s="33" t="s">
-        <v>824</v>
+        <v>828</v>
       </c>
       <c r="Q49" s="33" t="s">
-        <v>825</v>
+        <v>829</v>
       </c>
       <c r="R49" s="33" t="s">
-        <v>826</v>
+        <v>830</v>
       </c>
       <c r="S49" s="33" t="s">
-        <v>827</v>
+        <v>831</v>
       </c>
       <c r="T49" s="33" t="s">
-        <v>828</v>
+        <v>832</v>
       </c>
       <c r="U49" s="33" t="s">
-        <v>829</v>
+        <v>833</v>
       </c>
       <c r="V49" s="33" t="s">
-        <v>830</v>
+        <v>834</v>
       </c>
       <c r="W49" s="33" t="s">
-        <v>831</v>
+        <v>835</v>
       </c>
       <c r="X49" s="33" t="s">
-        <v>832</v>
+        <v>836</v>
       </c>
       <c r="Y49" s="33" t="s">
-        <v>833</v>
+        <v>837</v>
       </c>
       <c r="Z49" s="11" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="52" t="s">
-        <v>855</v>
+        <v>859</v>
       </c>
       <c r="B50" s="22" t="n">
         <f aca="false">04_Monthly_2026_2028!C18*24/03_Capacity_Model!$B$80*01_Inputs!$B$49</f>
@@ -53710,7 +53967,7 @@
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="52" t="s">
-        <v>856</v>
+        <v>860</v>
       </c>
       <c r="B51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y18</f>
@@ -53762,60 +54019,60 @@
       </c>
       <c r="N51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y30</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="O51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y31</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="P51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y32</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Q51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y33</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="R51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y34</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="S51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y35</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="T51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y36</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="U51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y37</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="V51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y38</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="W51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y39</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="X51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y40</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Y51" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!Y41</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="Z51" s="45" t="n">
         <f aca="false">SUM(B51:Y51)</f>
-        <v>92520</v>
+        <v>89160</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="38" t="s">
-        <v>857</v>
+        <v>861</v>
       </c>
       <c r="B52" s="22" t="n">
         <f aca="false">IF(1=1,B50,IF(1&lt;=5,B50*$B$42,IF(1=6,$B$43,IF(1-6&lt;=$B$44,B50,IF(AND(1&gt;12,$B$46=1),01_Inputs!$B$68*1000/12,$B$45)))))*$B$47</f>
@@ -53920,7 +54177,7 @@
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>858</v>
+        <v>862</v>
       </c>
       <c r="B53" s="22" t="n">
         <f aca="false">B52-B51</f>
@@ -53972,56 +54229,56 @@
       </c>
       <c r="N53" s="22" t="n">
         <f aca="false">M53+N52-N51</f>
-        <v>-17864.8993288591</v>
+        <v>-17584.8993288591</v>
       </c>
       <c r="O53" s="22" t="n">
         <f aca="false">N53+O52-O51</f>
-        <v>-18024.8993288591</v>
+        <v>-17464.8993288591</v>
       </c>
       <c r="P53" s="22" t="n">
         <f aca="false">O53+P52-P51</f>
-        <v>-18184.8993288591</v>
+        <v>-17344.8993288591</v>
       </c>
       <c r="Q53" s="22" t="n">
         <f aca="false">P53+Q52-Q51</f>
-        <v>-18344.8993288591</v>
+        <v>-17224.8993288591</v>
       </c>
       <c r="R53" s="22" t="n">
         <f aca="false">Q53+R52-R51</f>
-        <v>-18504.8993288591</v>
+        <v>-17104.8993288591</v>
       </c>
       <c r="S53" s="22" t="n">
         <f aca="false">R53+S52-S51</f>
-        <v>-18664.8993288591</v>
+        <v>-16984.8993288591</v>
       </c>
       <c r="T53" s="22" t="n">
         <f aca="false">S53+T52-T51</f>
-        <v>-18824.8993288591</v>
+        <v>-16864.8993288591</v>
       </c>
       <c r="U53" s="22" t="n">
         <f aca="false">T53+U52-U51</f>
-        <v>-18984.8993288591</v>
+        <v>-16744.8993288591</v>
       </c>
       <c r="V53" s="22" t="n">
         <f aca="false">U53+V52-V51</f>
-        <v>-19144.8993288591</v>
+        <v>-16624.8993288591</v>
       </c>
       <c r="W53" s="22" t="n">
         <f aca="false">V53+W52-W51</f>
-        <v>-19304.8993288591</v>
+        <v>-16504.8993288591</v>
       </c>
       <c r="X53" s="22" t="n">
         <f aca="false">W53+X52-X51</f>
-        <v>-19464.8993288591</v>
+        <v>-16384.8993288591</v>
       </c>
       <c r="Y53" s="22" t="n">
         <f aca="false">X53+Y52-Y51</f>
-        <v>-19624.8993288591</v>
+        <v>-16264.8993288591</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="38" t="s">
-        <v>859</v>
+        <v>863</v>
       </c>
       <c r="B54" s="22" t="n">
         <f aca="false">IF(1=1,B50,IF(1&lt;=5,B50*$C$42,IF(1=6,$C$43,IF(1-6&lt;=$C$44,B50,IF(AND(1&gt;12,$C$46=1),01_Inputs!$B$68*1000/12,$C$45)))))*$C$47</f>
@@ -54126,7 +54383,7 @@
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>860</v>
+        <v>864</v>
       </c>
       <c r="B55" s="22" t="n">
         <f aca="false">B54-B51</f>
@@ -54178,56 +54435,56 @@
       </c>
       <c r="N55" s="22" t="n">
         <f aca="false">M55+N54-N51</f>
-        <v>-9754.8322147651</v>
+        <v>-9474.8322147651</v>
       </c>
       <c r="O55" s="22" t="n">
         <f aca="false">N55+O54-O51</f>
-        <v>-9914.8322147651</v>
+        <v>-9354.8322147651</v>
       </c>
       <c r="P55" s="22" t="n">
         <f aca="false">O55+P54-P51</f>
-        <v>-10074.8322147651</v>
+        <v>-9234.8322147651</v>
       </c>
       <c r="Q55" s="22" t="n">
         <f aca="false">P55+Q54-Q51</f>
-        <v>-10234.8322147651</v>
+        <v>-9114.8322147651</v>
       </c>
       <c r="R55" s="22" t="n">
         <f aca="false">Q55+R54-R51</f>
-        <v>-10394.8322147651</v>
+        <v>-8994.8322147651</v>
       </c>
       <c r="S55" s="22" t="n">
         <f aca="false">R55+S54-S51</f>
-        <v>-10554.8322147651</v>
+        <v>-8874.8322147651</v>
       </c>
       <c r="T55" s="22" t="n">
         <f aca="false">S55+T54-T51</f>
-        <v>-10714.8322147651</v>
+        <v>-8754.8322147651</v>
       </c>
       <c r="U55" s="22" t="n">
         <f aca="false">T55+U54-U51</f>
-        <v>-10874.8322147651</v>
+        <v>-8634.8322147651</v>
       </c>
       <c r="V55" s="22" t="n">
         <f aca="false">U55+V54-V51</f>
-        <v>-11034.8322147651</v>
+        <v>-8514.8322147651</v>
       </c>
       <c r="W55" s="22" t="n">
         <f aca="false">V55+W54-W51</f>
-        <v>-11194.8322147651</v>
+        <v>-8394.8322147651</v>
       </c>
       <c r="X55" s="22" t="n">
         <f aca="false">W55+X54-X51</f>
-        <v>-11354.8322147651</v>
+        <v>-8274.8322147651</v>
       </c>
       <c r="Y55" s="22" t="n">
         <f aca="false">X55+Y54-Y51</f>
-        <v>-11514.8322147651</v>
+        <v>-8154.8322147651</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="38" t="s">
-        <v>861</v>
+        <v>865</v>
       </c>
       <c r="B56" s="22" t="n">
         <f aca="false">IF(1=1,B50,IF(1&lt;=5,B50*$D$42,IF(1=6,$D$43,IF(1-6&lt;=$D$44,B50,IF(AND(1&gt;12,$D$46=1),01_Inputs!$B$68*1000/12,$D$45)))))*$D$47</f>
@@ -54332,7 +54589,7 @@
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>862</v>
+        <v>866</v>
       </c>
       <c r="B57" s="22" t="n">
         <f aca="false">B56-B51</f>
@@ -54384,76 +54641,76 @@
       </c>
       <c r="N57" s="22" t="n">
         <f aca="false">M57+N56-N51</f>
-        <v>-19392.1476510067</v>
+        <v>-19112.1476510067</v>
       </c>
       <c r="O57" s="22" t="n">
         <f aca="false">N57+O56-O51</f>
-        <v>-19552.1476510067</v>
+        <v>-18992.1476510067</v>
       </c>
       <c r="P57" s="22" t="n">
         <f aca="false">O57+P56-P51</f>
-        <v>-19712.1476510067</v>
+        <v>-18872.1476510067</v>
       </c>
       <c r="Q57" s="22" t="n">
         <f aca="false">P57+Q56-Q51</f>
-        <v>-19872.1476510067</v>
+        <v>-18752.1476510067</v>
       </c>
       <c r="R57" s="22" t="n">
         <f aca="false">Q57+R56-R51</f>
-        <v>-20032.1476510067</v>
+        <v>-18632.1476510067</v>
       </c>
       <c r="S57" s="22" t="n">
         <f aca="false">R57+S56-S51</f>
-        <v>-20192.1476510067</v>
+        <v>-18512.1476510067</v>
       </c>
       <c r="T57" s="22" t="n">
         <f aca="false">S57+T56-T51</f>
-        <v>-20352.1476510067</v>
+        <v>-18392.1476510067</v>
       </c>
       <c r="U57" s="22" t="n">
         <f aca="false">T57+U56-U51</f>
-        <v>-20512.1476510067</v>
+        <v>-18272.1476510067</v>
       </c>
       <c r="V57" s="22" t="n">
         <f aca="false">U57+V56-V51</f>
-        <v>-20672.1476510067</v>
+        <v>-18152.1476510067</v>
       </c>
       <c r="W57" s="22" t="n">
         <f aca="false">V57+W56-W51</f>
-        <v>-20832.1476510067</v>
+        <v>-18032.1476510067</v>
       </c>
       <c r="X57" s="22" t="n">
         <f aca="false">W57+X56-X51</f>
-        <v>-20992.1476510067</v>
+        <v>-17912.1476510067</v>
       </c>
       <c r="Y57" s="22" t="n">
         <f aca="false">X57+Y56-Y51</f>
-        <v>-21152.1476510067</v>
+        <v>-17792.1476510067</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>863</v>
+        <v>867</v>
       </c>
       <c r="B59" s="33" t="s">
-        <v>864</v>
+        <v>868</v>
       </c>
       <c r="C59" s="33" t="s">
-        <v>865</v>
+        <v>869</v>
       </c>
       <c r="D59" s="33" t="s">
-        <v>866</v>
+        <v>870</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="11"/>
       <c r="G59" s="11"/>
       <c r="H59" s="11" t="s">
-        <v>867</v>
+        <v>871</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="38" t="s">
-        <v>868</v>
+        <v>872</v>
       </c>
       <c r="B60" s="45" t="n">
         <f aca="false">SUM(B52:M52)</f>
@@ -54468,12 +54725,12 @@
         <v>24167.8523489933</v>
       </c>
       <c r="H60" s="51" t="s">
-        <v>869</v>
+        <v>873</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="38" t="s">
-        <v>870</v>
+        <v>874</v>
       </c>
       <c r="B61" s="45" t="n">
         <f aca="false">SUM(B52:M52)-SUM(B51:M51)</f>
@@ -54491,97 +54748,97 @@
     </row>
     <row r="62" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="38" t="s">
-        <v>871</v>
+        <v>875</v>
       </c>
       <c r="B62" s="45" t="n">
         <f aca="false">SUM(N52:Y52)-SUM(N51:Y51)</f>
-        <v>-1919.99999999999</v>
+        <v>1440.00000000001</v>
       </c>
       <c r="C62" s="45" t="n">
         <f aca="false">SUM(N54:Y54)-SUM(N51:Y51)</f>
-        <v>-1919.99999999999</v>
+        <v>1440.00000000001</v>
       </c>
       <c r="D62" s="45" t="n">
         <f aca="false">SUM(N56:Y56)-SUM(N51:Y51)</f>
-        <v>-1919.99999999999</v>
+        <v>1440.00000000001</v>
       </c>
       <c r="H62" s="54" t="s">
-        <v>872</v>
+        <v>876</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="39.55" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="52" t="s">
-        <v>873</v>
+        <v>877</v>
       </c>
       <c r="B63" s="45" t="n">
         <f aca="false">MAX(0,-MIN(B53:Y53))</f>
-        <v>19624.8993288591</v>
+        <v>17704.8993288591</v>
       </c>
       <c r="C63" s="45" t="n">
         <f aca="false">MAX(0,-MIN(B55:Y55))</f>
-        <v>11514.8322147651</v>
+        <v>9594.8322147651</v>
       </c>
       <c r="D63" s="45" t="n">
         <f aca="false">MAX(0,-MIN(B57:Y57))</f>
-        <v>21152.1476510067</v>
+        <v>19232.1476510067</v>
       </c>
       <c r="H63" s="54" t="s">
-        <v>874</v>
+        <v>878</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="52" t="s">
-        <v>875</v>
+        <v>879</v>
       </c>
       <c r="B64" s="10" t="str">
         <f aca="false">IF(MIN(B53:Y53)&lt;0,INDEX($B$49:$Y$49,MATCH(MIN(B53:Y53),B53:Y53,0)),"-")</f>
-        <v>28.12</v>
+        <v>27.12</v>
       </c>
       <c r="C64" s="10" t="str">
         <f aca="false">IF(MIN(B55:Y55)&lt;0,INDEX($B$49:$Y$49,MATCH(MIN(B55:Y55),B55:Y55,0)),"-")</f>
-        <v>28.12</v>
+        <v>27.12</v>
       </c>
       <c r="D64" s="10" t="str">
         <f aca="false">IF(MIN(B57:Y57)&lt;0,INDEX($B$49:$Y$49,MATCH(MIN(B57:Y57),B57:Y57,0)),"-")</f>
-        <v>28.12</v>
+        <v>27.12</v>
       </c>
       <c r="H64" s="51" t="s">
-        <v>876</v>
+        <v>880</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="72" t="s">
-        <v>877</v>
+        <v>881</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>878</v>
+        <v>882</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>879</v>
+        <v>883</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>880</v>
+        <v>884</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
-        <v>881</v>
+        <v>885</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
-        <v>882</v>
+        <v>886</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
     </row>
   </sheetData>
@@ -54623,17 +54880,17 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A1" s="1" t="s">
-        <v>884</v>
+        <v>888</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="40" t="s">
-        <v>885</v>
+        <v>889</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="72" t="s">
-        <v>886</v>
+        <v>890</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -54647,12 +54904,12 @@
         <v>12</v>
       </c>
       <c r="D5" s="11" t="s">
-        <v>887</v>
+        <v>891</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="9" t="s">
-        <v>888</v>
+        <v>892</v>
       </c>
       <c r="B6" s="50" t="n">
         <f aca="false">01_Inputs!$B$20</f>
@@ -54662,12 +54919,12 @@
         <v>42</v>
       </c>
       <c r="D6" s="9" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="9" t="s">
-        <v>890</v>
+        <v>894</v>
       </c>
       <c r="B7" s="50" t="n">
         <f aca="false">01_Inputs!$B$16</f>
@@ -54677,12 +54934,12 @@
         <v>42</v>
       </c>
       <c r="D7" s="9" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="9" t="s">
-        <v>891</v>
+        <v>895</v>
       </c>
       <c r="B8" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$16</f>
@@ -54692,12 +54949,12 @@
         <v>42</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="9" t="s">
-        <v>893</v>
+        <v>897</v>
       </c>
       <c r="B9" s="50" t="n">
         <f aca="false">03_Capacity_Model!$C$16</f>
@@ -54707,27 +54964,27 @@
         <v>42</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="9" t="s">
-        <v>894</v>
+        <v>898</v>
       </c>
       <c r="B10" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$17</f>
         <v>2.25</v>
       </c>
       <c r="C10" s="13" t="s">
-        <v>492</v>
+        <v>496</v>
       </c>
       <c r="D10" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="9" t="s">
-        <v>895</v>
+        <v>899</v>
       </c>
       <c r="B11" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$21</f>
@@ -54737,12 +54994,12 @@
         <v>42</v>
       </c>
       <c r="D11" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="9" t="s">
-        <v>896</v>
+        <v>900</v>
       </c>
       <c r="B12" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$27</f>
@@ -54752,12 +55009,12 @@
         <v>222</v>
       </c>
       <c r="D12" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="9" t="s">
-        <v>897</v>
+        <v>901</v>
       </c>
       <c r="B13" s="60" t="n">
         <f aca="false">03_Capacity_Model!$B$30</f>
@@ -54767,12 +55024,12 @@
         <v>151</v>
       </c>
       <c r="D13" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>898</v>
+        <v>902</v>
       </c>
       <c r="B14" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$37</f>
@@ -54782,12 +55039,12 @@
         <v>42</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="9" t="s">
-        <v>899</v>
+        <v>903</v>
       </c>
       <c r="B15" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$38</f>
@@ -54797,12 +55054,12 @@
         <v>42</v>
       </c>
       <c r="D15" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="9" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="B16" s="60" t="n">
         <f aca="false">03_Capacity_Model!$B$41</f>
@@ -54812,12 +55069,12 @@
         <v>151</v>
       </c>
       <c r="D16" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="9" t="s">
-        <v>901</v>
+        <v>905</v>
       </c>
       <c r="B17" s="60" t="n">
         <f aca="false">03_Capacity_Model!$B$42</f>
@@ -54827,12 +55084,12 @@
         <v>151</v>
       </c>
       <c r="D17" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="9" t="s">
-        <v>902</v>
+        <v>906</v>
       </c>
       <c r="B18" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$40</f>
@@ -54842,12 +55099,12 @@
         <v>42</v>
       </c>
       <c r="D18" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="9" t="s">
-        <v>903</v>
+        <v>907</v>
       </c>
       <c r="B19" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$51</f>
@@ -54857,12 +55114,12 @@
         <v>42</v>
       </c>
       <c r="D19" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="9" t="s">
-        <v>904</v>
+        <v>908</v>
       </c>
       <c r="B20" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$52</f>
@@ -54872,12 +55129,12 @@
         <v>42</v>
       </c>
       <c r="D20" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A21" s="9" t="s">
-        <v>905</v>
+        <v>909</v>
       </c>
       <c r="B21" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$53</f>
@@ -54887,12 +55144,12 @@
         <v>42</v>
       </c>
       <c r="D21" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>906</v>
+        <v>910</v>
       </c>
       <c r="B22" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$54</f>
@@ -54902,12 +55159,12 @@
         <v>42</v>
       </c>
       <c r="D22" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A23" s="9" t="s">
-        <v>907</v>
+        <v>911</v>
       </c>
       <c r="B23" s="57" t="n">
         <f aca="false">03_Capacity_Model!$B$50</f>
@@ -54915,12 +55172,12 @@
       </c>
       <c r="C23" s="9"/>
       <c r="D23" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A24" s="9" t="s">
-        <v>908</v>
+        <v>912</v>
       </c>
       <c r="B24" s="57" t="n">
         <f aca="false">03_Capacity_Model!$B$49</f>
@@ -54930,12 +55187,12 @@
         <v>120</v>
       </c>
       <c r="D24" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A25" s="9" t="s">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="B25" s="57" t="n">
         <f aca="false">03_Capacity_Model!$B$48</f>
@@ -54943,12 +55200,12 @@
       </c>
       <c r="C25" s="9"/>
       <c r="D25" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A26" s="9" t="s">
-        <v>910</v>
+        <v>914</v>
       </c>
       <c r="B26" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$57</f>
@@ -54958,12 +55215,12 @@
         <v>42</v>
       </c>
       <c r="D26" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A27" s="9" t="s">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="B27" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$56</f>
@@ -54973,12 +55230,12 @@
         <v>42</v>
       </c>
       <c r="D27" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A28" s="9" t="s">
-        <v>912</v>
+        <v>916</v>
       </c>
       <c r="B28" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$58</f>
@@ -54988,12 +55245,12 @@
         <v>222</v>
       </c>
       <c r="D28" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A29" s="9" t="s">
-        <v>913</v>
+        <v>917</v>
       </c>
       <c r="B29" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$59</f>
@@ -55003,12 +55260,12 @@
         <v>222</v>
       </c>
       <c r="D29" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A30" s="9" t="s">
-        <v>914</v>
+        <v>918</v>
       </c>
       <c r="B30" s="60" t="n">
         <f aca="false">03_Capacity_Model!$B$60</f>
@@ -55018,12 +55275,12 @@
         <v>151</v>
       </c>
       <c r="D30" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A31" s="9" t="s">
-        <v>915</v>
+        <v>919</v>
       </c>
       <c r="B31" s="60" t="n">
         <f aca="false">03_Capacity_Model!$B$62</f>
@@ -55033,12 +55290,12 @@
         <v>151</v>
       </c>
       <c r="D31" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>916</v>
+        <v>920</v>
       </c>
       <c r="B32" s="59" t="n">
         <f aca="false">03_Capacity_Model!$B$55</f>
@@ -55048,12 +55305,12 @@
         <v>159</v>
       </c>
       <c r="D32" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="9" t="s">
-        <v>917</v>
+        <v>921</v>
       </c>
       <c r="B33" s="57" t="n">
         <f aca="false">03_Capacity_Model!$B$64</f>
@@ -55061,27 +55318,27 @@
       </c>
       <c r="C33" s="9"/>
       <c r="D33" s="9" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="9" t="s">
-        <v>919</v>
+        <v>923</v>
       </c>
       <c r="B34" s="57" t="n">
         <f aca="false">02_Batch_Raw!$E$73</f>
         <v>0</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>920</v>
+        <v>924</v>
       </c>
       <c r="D34" s="9" t="s">
-        <v>918</v>
+        <v>922</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="9" t="s">
-        <v>921</v>
+        <v>925</v>
       </c>
       <c r="B35" s="75" t="n">
         <f aca="false">03_Capacity_Model!$B$68</f>
@@ -55091,12 +55348,12 @@
         <v>222</v>
       </c>
       <c r="D35" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="9" t="s">
-        <v>922</v>
+        <v>926</v>
       </c>
       <c r="B36" s="60" t="n">
         <f aca="false">03_Capacity_Model!$B$70</f>
@@ -55106,12 +55363,12 @@
         <v>151</v>
       </c>
       <c r="D36" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="9" t="s">
-        <v>923</v>
+        <v>927</v>
       </c>
       <c r="B37" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$72</f>
@@ -55121,12 +55378,12 @@
         <v>42</v>
       </c>
       <c r="D37" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="9" t="s">
-        <v>924</v>
+        <v>928</v>
       </c>
       <c r="B38" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$71</f>
@@ -55136,27 +55393,27 @@
         <v>222</v>
       </c>
       <c r="D38" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="9" t="s">
-        <v>925</v>
+        <v>929</v>
       </c>
       <c r="B39" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$84</f>
         <v>5.2</v>
       </c>
       <c r="C39" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D39" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="9" t="s">
-        <v>927</v>
+        <v>931</v>
       </c>
       <c r="B40" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$88</f>
@@ -55166,12 +55423,12 @@
         <v>42</v>
       </c>
       <c r="D40" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="9" t="s">
-        <v>928</v>
+        <v>932</v>
       </c>
       <c r="B41" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$87</f>
@@ -55181,12 +55438,12 @@
         <v>42</v>
       </c>
       <c r="D41" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A42" s="9" t="s">
-        <v>929</v>
+        <v>933</v>
       </c>
       <c r="B42" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$89</f>
@@ -55196,12 +55453,12 @@
         <v>42</v>
       </c>
       <c r="D42" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A43" s="9" t="s">
-        <v>930</v>
+        <v>934</v>
       </c>
       <c r="B43" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$90</f>
@@ -55211,12 +55468,12 @@
         <v>42</v>
       </c>
       <c r="D43" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>931</v>
+        <v>935</v>
       </c>
       <c r="B44" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$91</f>
@@ -55226,12 +55483,12 @@
         <v>42</v>
       </c>
       <c r="D44" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="9" t="s">
-        <v>932</v>
+        <v>936</v>
       </c>
       <c r="B45" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$109</f>
@@ -55241,12 +55498,12 @@
         <v>42</v>
       </c>
       <c r="D45" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="9" t="s">
-        <v>933</v>
+        <v>937</v>
       </c>
       <c r="B46" s="50" t="n">
         <f aca="false">03_Capacity_Model!$E$125</f>
@@ -55256,12 +55513,12 @@
         <v>42</v>
       </c>
       <c r="D46" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="9" t="s">
-        <v>934</v>
+        <v>938</v>
       </c>
       <c r="B47" s="50" t="n">
         <f aca="false">03_Capacity_Model!$F$125</f>
@@ -55271,12 +55528,12 @@
         <v>42</v>
       </c>
       <c r="D47" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="9" t="s">
-        <v>935</v>
+        <v>939</v>
       </c>
       <c r="B48" s="50" t="n">
         <f aca="false">03_Capacity_Model!$F$126</f>
@@ -55286,12 +55543,12 @@
         <v>42</v>
       </c>
       <c r="D48" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A49" s="9" t="s">
-        <v>936</v>
+        <v>940</v>
       </c>
       <c r="B49" s="50" t="n">
         <f aca="false">03_Capacity_Model!$D$125</f>
@@ -55301,12 +55558,12 @@
         <v>42</v>
       </c>
       <c r="D49" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>937</v>
+        <v>941</v>
       </c>
       <c r="B50" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$112</f>
@@ -55316,12 +55573,12 @@
         <v>42</v>
       </c>
       <c r="D50" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="9" t="s">
-        <v>938</v>
+        <v>942</v>
       </c>
       <c r="B51" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$113</f>
@@ -55331,12 +55588,12 @@
         <v>42</v>
       </c>
       <c r="D51" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="9" t="s">
-        <v>939</v>
+        <v>943</v>
       </c>
       <c r="B52" s="50" t="n">
         <f aca="false">03_Capacity_Model!$B$114</f>
@@ -55346,12 +55603,12 @@
         <v>42</v>
       </c>
       <c r="D52" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="9" t="s">
-        <v>940</v>
+        <v>944</v>
       </c>
       <c r="B53" s="59" t="n">
         <f aca="false">03_Capacity_Model!$E$119</f>
@@ -55361,12 +55618,12 @@
         <v>159</v>
       </c>
       <c r="D53" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="9" t="s">
-        <v>941</v>
+        <v>945</v>
       </c>
       <c r="B54" s="59" t="n">
         <f aca="false">03_Capacity_Model!$E$120</f>
@@ -55376,252 +55633,252 @@
         <v>159</v>
       </c>
       <c r="D54" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="9" t="s">
-        <v>942</v>
+        <v>946</v>
       </c>
       <c r="B55" s="57" t="n">
         <f aca="false">03_Capacity_Model!$B$115</f>
         <v>96</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D55" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="9" t="s">
-        <v>943</v>
+        <v>947</v>
       </c>
       <c r="B56" s="57" t="n">
         <f aca="false">03_Capacity_Model!$B$116</f>
-        <v>120</v>
+        <v>96</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>640</v>
+        <v>644</v>
       </c>
       <c r="D56" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="9" t="s">
-        <v>944</v>
+        <v>948</v>
       </c>
       <c r="B57" s="62" t="n">
         <f aca="false">01_Inputs!$O$138/1000</f>
         <v>19.22</v>
       </c>
       <c r="C57" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D57" s="9" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A58" s="9" t="s">
-        <v>945</v>
+        <v>949</v>
       </c>
       <c r="B58" s="62" t="n">
         <f aca="false">01_Inputs!$O$139/1000</f>
         <v>43.4</v>
       </c>
       <c r="C58" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D58" s="9" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="9" t="s">
-        <v>946</v>
+        <v>950</v>
       </c>
       <c r="B59" s="62" t="n">
         <f aca="false">01_Inputs!$O$140/1000</f>
-        <v>49.12</v>
+        <v>45.76</v>
       </c>
       <c r="C59" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D59" s="9" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A60" s="9" t="s">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="B60" s="62" t="n">
         <f aca="false">SUM(01_Inputs!C139:H139)/1000</f>
         <v>18.84</v>
       </c>
       <c r="C60" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D60" s="9" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
-        <v>948</v>
+        <v>952</v>
       </c>
       <c r="B61" s="62" t="n">
         <f aca="false">SUM(01_Inputs!I139:N139)/1000</f>
         <v>24.56</v>
       </c>
       <c r="C61" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D61" s="9" t="s">
-        <v>889</v>
+        <v>893</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="9" t="s">
-        <v>949</v>
+        <v>953</v>
       </c>
       <c r="B62" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$25</f>
         <v>6.98</v>
       </c>
       <c r="C62" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D62" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="9" t="s">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="B63" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$26</f>
         <v>-17.2</v>
       </c>
       <c r="C63" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D63" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A64" s="9" t="s">
-        <v>952</v>
+        <v>956</v>
       </c>
       <c r="B64" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$27</f>
         <v>3.8</v>
       </c>
       <c r="C64" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D64" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A65" s="9" t="s">
-        <v>953</v>
+        <v>957</v>
       </c>
       <c r="B65" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$28</f>
         <v>-5.74</v>
       </c>
       <c r="C65" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D65" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>954</v>
+        <v>958</v>
       </c>
       <c r="B66" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$29</f>
         <v>-0.95999999999999</v>
       </c>
       <c r="C66" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D66" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A67" s="9" t="s">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="B67" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$30</f>
-        <v>-1.91999999999999</v>
+        <v>1.44</v>
       </c>
       <c r="C67" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D67" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A68" s="9" t="s">
-        <v>956</v>
+        <v>960</v>
       </c>
       <c r="B68" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$31</f>
-        <v>1.08000000000001</v>
+        <v>4.44000000000001</v>
       </c>
       <c r="C68" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D68" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A69" s="9" t="s">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="B69" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$C$29</f>
         <v>23.6</v>
       </c>
       <c r="C69" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D69" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A70" s="9" t="s">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="B70" s="62" t="n">
         <f aca="false">05_Reflux_Scenarios!$C$28</f>
         <v>13.1</v>
       </c>
       <c r="C70" s="9" t="s">
-        <v>926</v>
+        <v>930</v>
       </c>
       <c r="D70" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A71" s="9" t="s">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="B71" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!$S$42</f>
@@ -55631,12 +55888,12 @@
         <v>151</v>
       </c>
       <c r="D71" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A72" s="9" t="s">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="B72" s="57" t="n">
         <f aca="false">04_Monthly_2026_2028!$O$42</f>
@@ -55646,12 +55903,12 @@
         <v>222</v>
       </c>
       <c r="D72" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A73" s="9" t="s">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="B73" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!$S$43</f>
@@ -55661,12 +55918,12 @@
         <v>151</v>
       </c>
       <c r="D73" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A74" s="9" t="s">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="B74" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!$S$44</f>
@@ -55676,12 +55933,12 @@
         <v>151</v>
       </c>
       <c r="D74" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A75" s="9" t="s">
-        <v>964</v>
+        <v>968</v>
       </c>
       <c r="B75" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!$S$18</f>
@@ -55691,12 +55948,12 @@
         <v>151</v>
       </c>
       <c r="D75" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A76" s="9" t="s">
-        <v>965</v>
+        <v>969</v>
       </c>
       <c r="B76" s="57" t="n">
         <f aca="false">04_Monthly_2026_2028!$O$18</f>
@@ -55706,12 +55963,12 @@
         <v>222</v>
       </c>
       <c r="D76" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
-        <v>966</v>
+        <v>970</v>
       </c>
       <c r="B77" s="62" t="n">
         <f aca="false">03_Capacity_Model!$B$80</f>
@@ -55721,12 +55978,12 @@
         <v>42</v>
       </c>
       <c r="D77" s="9" t="s">
-        <v>892</v>
+        <v>896</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A78" s="9" t="s">
-        <v>967</v>
+        <v>971</v>
       </c>
       <c r="B78" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!$Z$43</f>
@@ -55736,27 +55993,27 @@
         <v>222</v>
       </c>
       <c r="D78" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A79" s="9" t="s">
-        <v>968</v>
+        <v>972</v>
       </c>
       <c r="B79" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!$Z$44</f>
-        <v>258.526315789474</v>
+        <v>240.842105263158</v>
       </c>
       <c r="C79" s="9" t="s">
         <v>222</v>
       </c>
       <c r="D79" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A80" s="9" t="s">
-        <v>969</v>
+        <v>973</v>
       </c>
       <c r="B80" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!$W$43</f>
@@ -55766,12 +56023,12 @@
         <v>151</v>
       </c>
       <c r="D80" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A81" s="9" t="s">
-        <v>970</v>
+        <v>974</v>
       </c>
       <c r="B81" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!$X$43</f>
@@ -55781,12 +56038,12 @@
         <v>151</v>
       </c>
       <c r="D81" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A82" s="9" t="s">
-        <v>971</v>
+        <v>975</v>
       </c>
       <c r="B82" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!$V$43</f>
@@ -55796,27 +56053,27 @@
         <v>151</v>
       </c>
       <c r="D82" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A83" s="9" t="s">
-        <v>972</v>
+        <v>976</v>
       </c>
       <c r="B83" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!$W$44</f>
-        <v>13440</v>
+        <v>10080</v>
       </c>
       <c r="C83" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D83" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="9" t="s">
-        <v>973</v>
+        <v>977</v>
       </c>
       <c r="B84" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!$V$44</f>
@@ -55826,12 +56083,12 @@
         <v>151</v>
       </c>
       <c r="D84" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A85" s="9" t="s">
-        <v>974</v>
+        <v>978</v>
       </c>
       <c r="B85" s="60" t="n">
         <f aca="false">04_Monthly_2026_2028!$X$44</f>
@@ -55841,12 +56098,12 @@
         <v>151</v>
       </c>
       <c r="D85" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="B86" s="50" t="n">
         <f aca="false">04_Monthly_2026_2028!$AK$43</f>
@@ -55856,27 +56113,27 @@
         <v>42</v>
       </c>
       <c r="D86" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="9" t="s">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="B87" s="50" t="n">
         <f aca="false">04_Monthly_2026_2028!$AK$44</f>
-        <v>960</v>
+        <v>768</v>
       </c>
       <c r="C87" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D87" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="9" t="s">
-        <v>977</v>
+        <v>981</v>
       </c>
       <c r="B88" s="50" t="str">
         <f aca="false">04_Monthly_2026_2028!$AH$43</f>
@@ -55886,12 +56143,12 @@
         <v>42</v>
       </c>
       <c r="D88" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="9" t="s">
-        <v>978</v>
+        <v>982</v>
       </c>
       <c r="B89" s="50" t="n">
         <f aca="false">04_Monthly_2026_2028!$AL$43</f>
@@ -55901,12 +56158,12 @@
         <v>42</v>
       </c>
       <c r="D89" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="9" t="s">
-        <v>979</v>
+        <v>983</v>
       </c>
       <c r="B90" s="50" t="n">
         <f aca="false">04_Monthly_2026_2028!$AC$43</f>
@@ -55916,27 +56173,27 @@
         <v>42</v>
       </c>
       <c r="D90" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="9" t="s">
-        <v>980</v>
+        <v>984</v>
       </c>
       <c r="B91" s="50" t="n">
         <f aca="false">04_Monthly_2026_2028!$AL$44</f>
-        <v>240</v>
+        <v>192</v>
       </c>
       <c r="C91" s="9" t="s">
         <v>42</v>
       </c>
       <c r="D91" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="9" t="s">
-        <v>981</v>
+        <v>985</v>
       </c>
       <c r="B92" s="50" t="n">
         <f aca="false">04_Monthly_2026_2028!$AC$44</f>
@@ -55946,12 +56203,12 @@
         <v>42</v>
       </c>
       <c r="D92" s="9" t="s">
-        <v>960</v>
+        <v>964</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="9" t="s">
-        <v>982</v>
+        <v>986</v>
       </c>
       <c r="B93" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$B$60</f>
@@ -55961,12 +56218,12 @@
         <v>151</v>
       </c>
       <c r="D93" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A94" s="9" t="s">
-        <v>983</v>
+        <v>987</v>
       </c>
       <c r="B94" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$B$61</f>
@@ -55976,57 +56233,57 @@
         <v>151</v>
       </c>
       <c r="D94" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A95" s="9" t="s">
-        <v>984</v>
+        <v>988</v>
       </c>
       <c r="B95" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$B$62</f>
-        <v>-1919.99999999999</v>
+        <v>1440.00000000001</v>
       </c>
       <c r="C95" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D95" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A96" s="9" t="s">
-        <v>985</v>
+        <v>989</v>
       </c>
       <c r="B96" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$B$63</f>
-        <v>19624.8993288591</v>
+        <v>17704.8993288591</v>
       </c>
       <c r="C96" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D96" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A97" s="9" t="s">
-        <v>986</v>
+        <v>990</v>
       </c>
       <c r="B97" s="73" t="str">
         <f aca="false">05_Reflux_Scenarios!$B$64</f>
-        <v>28.12</v>
+        <v>27.12</v>
       </c>
       <c r="C97" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D97" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A98" s="9" t="s">
-        <v>987</v>
+        <v>991</v>
       </c>
       <c r="B98" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$C$60</f>
@@ -56036,12 +56293,12 @@
         <v>151</v>
       </c>
       <c r="D98" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A99" s="9" t="s">
-        <v>988</v>
+        <v>992</v>
       </c>
       <c r="B99" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$C$61</f>
@@ -56051,57 +56308,57 @@
         <v>151</v>
       </c>
       <c r="D99" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A100" s="9" t="s">
-        <v>989</v>
+        <v>993</v>
       </c>
       <c r="B100" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$C$62</f>
-        <v>-1919.99999999999</v>
+        <v>1440.00000000001</v>
       </c>
       <c r="C100" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D100" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A101" s="9" t="s">
-        <v>990</v>
+        <v>994</v>
       </c>
       <c r="B101" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$C$63</f>
-        <v>11514.8322147651</v>
+        <v>9594.8322147651</v>
       </c>
       <c r="C101" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D101" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A102" s="9" t="s">
-        <v>991</v>
+        <v>995</v>
       </c>
       <c r="B102" s="73" t="str">
         <f aca="false">05_Reflux_Scenarios!$C$64</f>
-        <v>28.12</v>
+        <v>27.12</v>
       </c>
       <c r="C102" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D102" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A103" s="9" t="s">
-        <v>992</v>
+        <v>996</v>
       </c>
       <c r="B103" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$60</f>
@@ -56111,12 +56368,12 @@
         <v>151</v>
       </c>
       <c r="D103" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A104" s="9" t="s">
-        <v>993</v>
+        <v>997</v>
       </c>
       <c r="B104" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$61</f>
@@ -56126,57 +56383,57 @@
         <v>151</v>
       </c>
       <c r="D104" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A105" s="9" t="s">
-        <v>994</v>
+        <v>998</v>
       </c>
       <c r="B105" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$62</f>
-        <v>-1919.99999999999</v>
+        <v>1440.00000000001</v>
       </c>
       <c r="C105" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D105" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A106" s="9" t="s">
-        <v>995</v>
+        <v>999</v>
       </c>
       <c r="B106" s="60" t="n">
         <f aca="false">05_Reflux_Scenarios!$D$63</f>
-        <v>21152.1476510067</v>
+        <v>19232.1476510067</v>
       </c>
       <c r="C106" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D106" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A107" s="9" t="s">
-        <v>996</v>
+        <v>1000</v>
       </c>
       <c r="B107" s="73" t="str">
         <f aca="false">05_Reflux_Scenarios!$D$64</f>
-        <v>28.12</v>
+        <v>27.12</v>
       </c>
       <c r="C107" s="9" t="s">
         <v>151</v>
       </c>
       <c r="D107" s="9" t="s">
-        <v>950</v>
+        <v>954</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A109" s="72" t="s">
-        <v>997</v>
+        <v>1001</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -56184,19 +56441,19 @@
         <v>14</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>998</v>
+        <v>1002</v>
       </c>
       <c r="C110" s="11" t="s">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="D110" s="11" t="s">
-        <v>1000</v>
+        <v>1004</v>
       </c>
       <c r="E110" s="11" t="s">
-        <v>1001</v>
+        <v>1005</v>
       </c>
       <c r="F110" s="33" t="s">
-        <v>1002</v>
+        <v>1006</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -56305,21 +56562,21 @@
     </row>
     <row r="121" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A121" s="72" t="s">
-        <v>1003</v>
+        <v>1007</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="11" t="s">
-        <v>676</v>
+        <v>680</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>678</v>
+        <v>682</v>
       </c>
       <c r="C122" s="11" t="s">
-        <v>326</v>
+        <v>329</v>
       </c>
       <c r="D122" s="33" t="s">
-        <v>328</v>
+        <v>331</v>
       </c>
       <c r="E122" s="11" t="s">
         <v>142</v>
@@ -56328,28 +56585,28 @@
         <v>139</v>
       </c>
       <c r="G122" s="11" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
       <c r="H122" s="11" t="s">
-        <v>1005</v>
+        <v>1009</v>
       </c>
       <c r="I122" s="11" t="s">
-        <v>1006</v>
+        <v>1010</v>
       </c>
       <c r="J122" s="11" t="s">
-        <v>1007</v>
+        <v>1011</v>
       </c>
       <c r="K122" s="11" t="s">
-        <v>1008</v>
+        <v>1012</v>
       </c>
       <c r="L122" s="33" t="s">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="M122" s="33" t="s">
-        <v>1010</v>
+        <v>1014</v>
       </c>
       <c r="N122" s="11" t="s">
-        <v>730</v>
+        <v>734</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -57763,7 +58020,7 @@
       </c>
       <c r="E147" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W30</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F147" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X30</f>
@@ -57771,7 +58028,7 @@
       </c>
       <c r="G147" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y30</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H147" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T30</f>
@@ -57779,7 +58036,7 @@
       </c>
       <c r="I147" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO30</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J147" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O30</f>
@@ -57795,7 +58052,7 @@
       </c>
       <c r="M147" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD30+04_Monthly_2026_2028!AE30</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N147" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD30</f>
@@ -57821,7 +58078,7 @@
       </c>
       <c r="E148" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W31</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F148" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X31</f>
@@ -57829,7 +58086,7 @@
       </c>
       <c r="G148" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y31</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H148" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T31</f>
@@ -57837,7 +58094,7 @@
       </c>
       <c r="I148" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO31</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J148" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O31</f>
@@ -57853,7 +58110,7 @@
       </c>
       <c r="M148" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD31+04_Monthly_2026_2028!AE31</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N148" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD31</f>
@@ -57879,7 +58136,7 @@
       </c>
       <c r="E149" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W32</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F149" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X32</f>
@@ -57887,7 +58144,7 @@
       </c>
       <c r="G149" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y32</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H149" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T32</f>
@@ -57895,7 +58152,7 @@
       </c>
       <c r="I149" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO32</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J149" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O32</f>
@@ -57911,7 +58168,7 @@
       </c>
       <c r="M149" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD32+04_Monthly_2026_2028!AE32</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N149" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD32</f>
@@ -57937,7 +58194,7 @@
       </c>
       <c r="E150" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W33</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F150" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X33</f>
@@ -57945,7 +58202,7 @@
       </c>
       <c r="G150" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y33</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H150" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T33</f>
@@ -57953,7 +58210,7 @@
       </c>
       <c r="I150" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO33</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J150" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O33</f>
@@ -57969,7 +58226,7 @@
       </c>
       <c r="M150" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD33+04_Monthly_2026_2028!AE33</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N150" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD33</f>
@@ -57995,7 +58252,7 @@
       </c>
       <c r="E151" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W34</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F151" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X34</f>
@@ -58003,7 +58260,7 @@
       </c>
       <c r="G151" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y34</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H151" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T34</f>
@@ -58011,7 +58268,7 @@
       </c>
       <c r="I151" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO34</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J151" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O34</f>
@@ -58027,7 +58284,7 @@
       </c>
       <c r="M151" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD34+04_Monthly_2026_2028!AE34</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N151" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD34</f>
@@ -58053,7 +58310,7 @@
       </c>
       <c r="E152" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W35</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F152" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X35</f>
@@ -58061,7 +58318,7 @@
       </c>
       <c r="G152" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y35</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H152" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T35</f>
@@ -58069,7 +58326,7 @@
       </c>
       <c r="I152" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO35</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J152" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O35</f>
@@ -58085,7 +58342,7 @@
       </c>
       <c r="M152" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD35+04_Monthly_2026_2028!AE35</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N152" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD35</f>
@@ -58111,7 +58368,7 @@
       </c>
       <c r="E153" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W36</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F153" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X36</f>
@@ -58119,7 +58376,7 @@
       </c>
       <c r="G153" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y36</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H153" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T36</f>
@@ -58127,7 +58384,7 @@
       </c>
       <c r="I153" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO36</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J153" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O36</f>
@@ -58143,7 +58400,7 @@
       </c>
       <c r="M153" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD36+04_Monthly_2026_2028!AE36</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N153" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD36</f>
@@ -58169,7 +58426,7 @@
       </c>
       <c r="E154" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W37</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F154" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X37</f>
@@ -58177,7 +58434,7 @@
       </c>
       <c r="G154" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y37</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H154" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T37</f>
@@ -58185,7 +58442,7 @@
       </c>
       <c r="I154" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO37</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J154" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O37</f>
@@ -58201,7 +58458,7 @@
       </c>
       <c r="M154" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD37+04_Monthly_2026_2028!AE37</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N154" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD37</f>
@@ -58227,7 +58484,7 @@
       </c>
       <c r="E155" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W38</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F155" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X38</f>
@@ -58235,7 +58492,7 @@
       </c>
       <c r="G155" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y38</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H155" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T38</f>
@@ -58243,7 +58500,7 @@
       </c>
       <c r="I155" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO38</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J155" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O38</f>
@@ -58259,7 +58516,7 @@
       </c>
       <c r="M155" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD38+04_Monthly_2026_2028!AE38</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N155" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD38</f>
@@ -58285,7 +58542,7 @@
       </c>
       <c r="E156" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W39</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F156" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X39</f>
@@ -58293,7 +58550,7 @@
       </c>
       <c r="G156" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y39</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H156" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T39</f>
@@ -58301,7 +58558,7 @@
       </c>
       <c r="I156" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO39</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J156" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O39</f>
@@ -58317,7 +58574,7 @@
       </c>
       <c r="M156" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD39+04_Monthly_2026_2028!AE39</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N156" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD39</f>
@@ -58343,7 +58600,7 @@
       </c>
       <c r="E157" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W40</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F157" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X40</f>
@@ -58351,7 +58608,7 @@
       </c>
       <c r="G157" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y40</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H157" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T40</f>
@@ -58359,7 +58616,7 @@
       </c>
       <c r="I157" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO40</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J157" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O40</f>
@@ -58375,7 +58632,7 @@
       </c>
       <c r="M157" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD40+04_Monthly_2026_2028!AE40</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N157" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD40</f>
@@ -58401,7 +58658,7 @@
       </c>
       <c r="E158" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!W41</f>
-        <v>1120</v>
+        <v>840</v>
       </c>
       <c r="F158" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!X41</f>
@@ -58409,7 +58666,7 @@
       </c>
       <c r="G158" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!Y41</f>
-        <v>4093.33333333333</v>
+        <v>3813.33333333333</v>
       </c>
       <c r="H158" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!T41</f>
@@ -58417,7 +58674,7 @@
       </c>
       <c r="I158" s="70" t="n">
         <f aca="false">04_Monthly_2026_2028!AO41</f>
-        <v>-160</v>
+        <v>120</v>
       </c>
       <c r="J158" s="57" t="str">
         <f aca="false">04_Monthly_2026_2028!O41</f>
@@ -58433,7 +58690,7 @@
       </c>
       <c r="M158" s="76" t="n">
         <f aca="false">04_Monthly_2026_2028!AD41+04_Monthly_2026_2028!AE41</f>
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="N158" s="73" t="str">
         <f aca="false">04_Monthly_2026_2028!BD41</f>
@@ -58442,7 +58699,7 @@
     </row>
     <row r="160" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A160" s="72" t="s">
-        <v>1011</v>
+        <v>1015</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -58450,12 +58707,12 @@
         <v>260</v>
       </c>
       <c r="B161" s="11" t="s">
-        <v>1012</v>
+        <v>1016</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A162" s="9" t="s">
-        <v>1013</v>
+        <v>1017</v>
       </c>
       <c r="B162" s="57" t="n">
         <f aca="false">02_Batch_Raw!O71</f>
@@ -58464,7 +58721,7 @@
     </row>
     <row r="163" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A163" s="9" t="s">
-        <v>1014</v>
+        <v>1018</v>
       </c>
       <c r="B163" s="57" t="n">
         <f aca="false">02_Batch_Raw!P71</f>
@@ -58473,7 +58730,7 @@
     </row>
     <row r="164" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A164" s="9" t="s">
-        <v>1015</v>
+        <v>1019</v>
       </c>
       <c r="B164" s="57" t="n">
         <f aca="false">02_Batch_Raw!Q71</f>
@@ -58482,7 +58739,7 @@
     </row>
     <row r="165" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A165" s="9" t="s">
-        <v>1016</v>
+        <v>1020</v>
       </c>
       <c r="B165" s="57" t="n">
         <f aca="false">02_Batch_Raw!R71</f>
@@ -58491,7 +58748,7 @@
     </row>
     <row r="166" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A166" s="9" t="s">
-        <v>1017</v>
+        <v>1021</v>
       </c>
       <c r="B166" s="57" t="n">
         <f aca="false">02_Batch_Raw!S71</f>
@@ -58500,150 +58757,150 @@
     </row>
     <row r="168" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A168" s="72" t="s">
-        <v>1018</v>
+        <v>1022</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="11" t="s">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="B169" s="11" t="s">
-        <v>1020</v>
+        <v>1024</v>
       </c>
       <c r="C169" s="11" t="s">
-        <v>1021</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A170" s="13" t="s">
-        <v>1022</v>
+        <v>1026</v>
       </c>
       <c r="B170" s="13" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C170" s="13" t="s">
-        <v>1024</v>
+        <v>1028</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A171" s="13" t="s">
-        <v>1025</v>
+        <v>1029</v>
       </c>
       <c r="B171" s="13" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C171" s="13" t="s">
-        <v>1026</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A172" s="13" t="s">
-        <v>1027</v>
+        <v>1031</v>
       </c>
       <c r="B172" s="13" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C172" s="9" t="s">
-        <v>1029</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A173" s="13" t="s">
-        <v>1030</v>
+        <v>1034</v>
       </c>
       <c r="B173" s="13" t="s">
-        <v>1031</v>
+        <v>1035</v>
       </c>
       <c r="C173" s="9" t="s">
-        <v>1032</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A174" s="9" t="s">
-        <v>1033</v>
+        <v>1037</v>
       </c>
       <c r="B174" s="13" t="s">
-        <v>1034</v>
+        <v>1038</v>
       </c>
       <c r="C174" s="13" t="s">
-        <v>1035</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A175" s="13" t="s">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="B175" s="13" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C175" s="9" t="s">
-        <v>1037</v>
+        <v>1041</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A176" s="13" t="s">
-        <v>1038</v>
+        <v>1042</v>
       </c>
       <c r="B176" s="13" t="s">
-        <v>1039</v>
+        <v>1043</v>
       </c>
       <c r="C176" s="13" t="s">
-        <v>1040</v>
+        <v>1044</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A177" s="13" t="s">
-        <v>1041</v>
+        <v>1045</v>
       </c>
       <c r="B177" s="13" t="s">
-        <v>1028</v>
+        <v>1032</v>
       </c>
       <c r="C177" s="9" t="s">
-        <v>1042</v>
+        <v>1046</v>
       </c>
     </row>
     <row r="178" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A178" s="13" t="s">
-        <v>1043</v>
+        <v>1047</v>
       </c>
       <c r="B178" s="13" t="s">
-        <v>1023</v>
+        <v>1027</v>
       </c>
       <c r="C178" s="9" t="s">
-        <v>1044</v>
+        <v>1048</v>
       </c>
     </row>
     <row r="179" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A179" s="13" t="s">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="B179" s="13" t="s">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="C179" s="13" t="s">
-        <v>1047</v>
+        <v>1051</v>
       </c>
     </row>
     <row r="180" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A180" s="9" t="s">
-        <v>1048</v>
+        <v>1052</v>
       </c>
       <c r="B180" s="13" t="s">
-        <v>1049</v>
+        <v>1053</v>
       </c>
       <c r="C180" s="13" t="s">
-        <v>1004</v>
+        <v>1008</v>
       </c>
     </row>
     <row r="181" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A181" s="9" t="s">
-        <v>1050</v>
+        <v>1054</v>
       </c>
       <c r="B181" s="13" t="s">
-        <v>1051</v>
+        <v>1055</v>
       </c>
       <c r="C181" s="9" t="s">
-        <v>1052</v>
+        <v>1056</v>
       </c>
     </row>
   </sheetData>

--- a/SKTC_CpZr_Capacity_RawData_Calculation_2026_2028.xlsx
+++ b/SKTC_CpZr_Capacity_RawData_Calculation_2026_2028.xlsx
@@ -3780,7 +3780,64 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">2028</t>
+      <t xml:space="preserve">ARS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">운영 시점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">7</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">월 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· 2028</t>
     </r>
     <r>
       <rPr>
@@ -3843,142 +3900,45 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">첨부 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">PPT 2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">장 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'ARS 200 L </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">운영 계획 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">('26 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">설치 → </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'27~)'</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">근거는 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">'27~ </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">운영 계획뿐 — 전환 월 미확정</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">확인 필요 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한솔 </t>
+      <t xml:space="preserve">사용자 지시 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(ARS </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">운영 시점 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2027</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">년 </t>
     </r>
     <r>
       <rPr>
@@ -3997,7 +3957,7 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">월 전환 자동 적용 안 함</t>
+      <t xml:space="preserve">월</t>
     </r>
     <r>
       <rPr>
@@ -4008,6 +3968,55 @@
         <charset val="1"/>
       </rPr>
       <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이지켐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한솔 동일 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">'27.7~ ARS · '27.1~6 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">수동</t>
     </r>
   </si>
   <si>
@@ -21297,17 +21306,133 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">이지켐 수동 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">· </t>
+      <t xml:space="preserve">이지켐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한솔 수동 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(~'27.6)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">현재 조건 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">(03 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">선택 간격</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">)</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">공사</t>
+  </si>
+  <si>
+    <t xml:space="preserve">가동 여부 미확인</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1·2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">개선 적용 생산</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">대</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">시간차 병행</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이지켐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
     </r>
     <r>
       <rPr>
@@ -21326,151 +21451,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">'27.1~6 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">수동</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">현재 조건 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(03 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">선택 간격</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">공사</t>
-  </si>
-  <si>
-    <t xml:space="preserve">가동 여부 미확인</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1·2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">개선 적용 생산</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">대</t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">시간차 병행</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">한솔 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ARS · </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이지켐 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ARS(</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전환 월 확인</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">)</t>
+      <t xml:space="preserve">ARS ('27.7~)</t>
     </r>
   </si>
   <si>
@@ -26621,17 +26602,55 @@
         <rFont val="Noto Sans CJK SC"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve">한솔 수동</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·ARS </t>
+      <t xml:space="preserve">한솔 수동 충진시간 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">· </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">이지켐</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">·</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Noto Sans CJK SC"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">한솔 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="9"/>
+        <color rgb="FF000000"/>
+        <rFont val="Arial"/>
+        <family val="0"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">ARS </t>
     </r>
     <r>
       <rPr>
@@ -26650,54 +26669,7 @@
         <family val="0"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">· </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">이지켐 </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ARS </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">전환 월</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Arial"/>
-        <family val="0"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">·</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="9"/>
-        <color rgb="FF000000"/>
-        <rFont val="Noto Sans CJK SC"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">시간</t>
+      <t xml:space="preserve">('27.7~)</t>
     </r>
   </si>
   <si>
@@ -28208,11 +28180,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="96233383"/>
-        <c:axId val="20192760"/>
+        <c:axId val="39492676"/>
+        <c:axId val="19255739"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="96233383"/>
+        <c:axId val="39492676"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -28244,7 +28216,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="20192760"/>
+        <c:crossAx val="19255739"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -28252,7 +28224,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="20192760"/>
+        <c:axId val="19255739"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -28294,7 +28266,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="96233383"/>
+        <c:crossAx val="39492676"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -28939,11 +28911,11 @@
         </c:ser>
         <c:gapWidth val="150"/>
         <c:overlap val="0"/>
-        <c:axId val="83994883"/>
-        <c:axId val="32617448"/>
+        <c:axId val="38867338"/>
+        <c:axId val="50331020"/>
       </c:barChart>
       <c:catAx>
-        <c:axId val="83994883"/>
+        <c:axId val="38867338"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -28975,7 +28947,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="32617448"/>
+        <c:crossAx val="50331020"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblAlgn val="ctr"/>
@@ -28983,7 +28955,7 @@
         <c:noMultiLvlLbl val="0"/>
       </c:catAx>
       <c:valAx>
-        <c:axId val="32617448"/>
+        <c:axId val="50331020"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -29025,7 +28997,7 @@
             </a:pPr>
           </a:p>
         </c:txPr>
-        <c:crossAx val="83994883"/>
+        <c:crossAx val="38867338"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -30272,12 +30244,12 @@
         <v>140</v>
       </c>
     </row>
-    <row r="47" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="13" t="s">
         <v>141</v>
       </c>
       <c r="B47" s="21" t="n">
-        <v>46388</v>
+        <v>46569</v>
       </c>
       <c r="C47" s="13" t="s">
         <v>134</v>
@@ -46804,15 +46776,15 @@
       </c>
       <c r="AF18" s="13" t="str">
         <f aca="false">IF(AD18=0,"-",IF(A18&gt;=01_Inputs!$B$47,"ARS","수동"))</f>
-        <v>ARS</v>
+        <v>수동</v>
       </c>
       <c r="AG18" s="13" t="str">
         <f aca="false">IF(AE18=0,"-",IF(A18&gt;=01_Inputs!$B$46,"ARS","수동"))</f>
         <v>수동</v>
       </c>
-      <c r="AH18" s="15" t="str">
+      <c r="AH18" s="15" t="n">
         <f aca="false">IF(AD18=0,0,IF(AF18="수동",AD18*01_Inputs!$B$34,IF(ISNUMBER(01_Inputs!$B$36),AD18*01_Inputs!$B$36,"미확인")))</f>
-        <v>미확인</v>
+        <v>32</v>
       </c>
       <c r="AI18" s="15" t="str">
         <f aca="false">IF(AE18=0,0,IF(AG18="수동",IF(ISNUMBER(01_Inputs!$B$35),AE18*01_Inputs!$B$35,"미확인"),IF(ISNUMBER(01_Inputs!$B$37),AE18*01_Inputs!$B$37,"미확인")))</f>
@@ -46820,7 +46792,7 @@
       </c>
       <c r="AJ18" s="15" t="str">
         <f aca="false">IF(AND(ISNUMBER(AH18),ISNUMBER(AI18)),AH18+AI18,"부분 "&amp;TEXT(N(AH18)+N(AI18),"0")&amp;" h + 미확인")</f>
-        <v>부분 0 h + 미확인</v>
+        <v>부분 32 h + 미확인</v>
       </c>
       <c r="AK18" s="15" t="n">
         <f aca="false">(AD18+AE18)*01_Inputs!$B$38</f>
@@ -47027,15 +46999,15 @@
       </c>
       <c r="AF19" s="13" t="str">
         <f aca="false">IF(AD19=0,"-",IF(A19&gt;=01_Inputs!$B$47,"ARS","수동"))</f>
-        <v>ARS</v>
+        <v>수동</v>
       </c>
       <c r="AG19" s="13" t="str">
         <f aca="false">IF(AE19=0,"-",IF(A19&gt;=01_Inputs!$B$46,"ARS","수동"))</f>
         <v>수동</v>
       </c>
-      <c r="AH19" s="15" t="str">
+      <c r="AH19" s="15" t="n">
         <f aca="false">IF(AD19=0,0,IF(AF19="수동",AD19*01_Inputs!$B$34,IF(ISNUMBER(01_Inputs!$B$36),AD19*01_Inputs!$B$36,"미확인")))</f>
-        <v>미확인</v>
+        <v>32</v>
       </c>
       <c r="AI19" s="15" t="str">
         <f aca="false">IF(AE19=0,0,IF(AG19="수동",IF(ISNUMBER(01_Inputs!$B$35),AE19*01_Inputs!$B$35,"미확인"),IF(ISNUMBER(01_Inputs!$B$37),AE19*01_Inputs!$B$37,"미확인")))</f>
@@ -47043,7 +47015,7 @@
       </c>
       <c r="AJ19" s="15" t="str">
         <f aca="false">IF(AND(ISNUMBER(AH19),ISNUMBER(AI19)),AH19+AI19,"부분 "&amp;TEXT(N(AH19)+N(AI19),"0")&amp;" h + 미확인")</f>
-        <v>부분 0 h + 미확인</v>
+        <v>부분 32 h + 미확인</v>
       </c>
       <c r="AK19" s="15" t="n">
         <f aca="false">(AD19+AE19)*01_Inputs!$B$38</f>
@@ -47250,15 +47222,15 @@
       </c>
       <c r="AF20" s="13" t="str">
         <f aca="false">IF(AD20=0,"-",IF(A20&gt;=01_Inputs!$B$47,"ARS","수동"))</f>
-        <v>ARS</v>
+        <v>수동</v>
       </c>
       <c r="AG20" s="13" t="str">
         <f aca="false">IF(AE20=0,"-",IF(A20&gt;=01_Inputs!$B$46,"ARS","수동"))</f>
         <v>수동</v>
       </c>
-      <c r="AH20" s="15" t="str">
+      <c r="AH20" s="15" t="n">
         <f aca="false">IF(AD20=0,0,IF(AF20="수동",AD20*01_Inputs!$B$34,IF(ISNUMBER(01_Inputs!$B$36),AD20*01_Inputs!$B$36,"미확인")))</f>
-        <v>미확인</v>
+        <v>32</v>
       </c>
       <c r="AI20" s="15" t="str">
         <f aca="false">IF(AE20=0,0,IF(AG20="수동",IF(ISNUMBER(01_Inputs!$B$35),AE20*01_Inputs!$B$35,"미확인"),IF(ISNUMBER(01_Inputs!$B$37),AE20*01_Inputs!$B$37,"미확인")))</f>
@@ -47266,7 +47238,7 @@
       </c>
       <c r="AJ20" s="15" t="str">
         <f aca="false">IF(AND(ISNUMBER(AH20),ISNUMBER(AI20)),AH20+AI20,"부분 "&amp;TEXT(N(AH20)+N(AI20),"0")&amp;" h + 미확인")</f>
-        <v>부분 0 h + 미확인</v>
+        <v>부분 32 h + 미확인</v>
       </c>
       <c r="AK20" s="15" t="n">
         <f aca="false">(AD20+AE20)*01_Inputs!$B$38</f>
@@ -47473,15 +47445,15 @@
       </c>
       <c r="AF21" s="13" t="str">
         <f aca="false">IF(AD21=0,"-",IF(A21&gt;=01_Inputs!$B$47,"ARS","수동"))</f>
-        <v>ARS</v>
+        <v>수동</v>
       </c>
       <c r="AG21" s="13" t="str">
         <f aca="false">IF(AE21=0,"-",IF(A21&gt;=01_Inputs!$B$46,"ARS","수동"))</f>
         <v>수동</v>
       </c>
-      <c r="AH21" s="15" t="str">
+      <c r="AH21" s="15" t="n">
         <f aca="false">IF(AD21=0,0,IF(AF21="수동",AD21*01_Inputs!$B$34,IF(ISNUMBER(01_Inputs!$B$36),AD21*01_Inputs!$B$36,"미확인")))</f>
-        <v>미확인</v>
+        <v>32</v>
       </c>
       <c r="AI21" s="15" t="str">
         <f aca="false">IF(AE21=0,0,IF(AG21="수동",IF(ISNUMBER(01_Inputs!$B$35),AE21*01_Inputs!$B$35,"미확인"),IF(ISNUMBER(01_Inputs!$B$37),AE21*01_Inputs!$B$37,"미확인")))</f>
@@ -47489,7 +47461,7 @@
       </c>
       <c r="AJ21" s="15" t="str">
         <f aca="false">IF(AND(ISNUMBER(AH21),ISNUMBER(AI21)),AH21+AI21,"부분 "&amp;TEXT(N(AH21)+N(AI21),"0")&amp;" h + 미확인")</f>
-        <v>부분 0 h + 미확인</v>
+        <v>부분 32 h + 미확인</v>
       </c>
       <c r="AK21" s="15" t="n">
         <f aca="false">(AD21+AE21)*01_Inputs!$B$38</f>
@@ -47696,15 +47668,15 @@
       </c>
       <c r="AF22" s="13" t="str">
         <f aca="false">IF(AD22=0,"-",IF(A22&gt;=01_Inputs!$B$47,"ARS","수동"))</f>
-        <v>ARS</v>
+        <v>수동</v>
       </c>
       <c r="AG22" s="13" t="str">
         <f aca="false">IF(AE22=0,"-",IF(A22&gt;=01_Inputs!$B$46,"ARS","수동"))</f>
         <v>수동</v>
       </c>
-      <c r="AH22" s="15" t="str">
+      <c r="AH22" s="15" t="n">
         <f aca="false">IF(AD22=0,0,IF(AF22="수동",AD22*01_Inputs!$B$34,IF(ISNUMBER(01_Inputs!$B$36),AD22*01_Inputs!$B$36,"미확인")))</f>
-        <v>미확인</v>
+        <v>32</v>
       </c>
       <c r="AI22" s="15" t="str">
         <f aca="false">IF(AE22=0,0,IF(AG22="수동",IF(ISNUMBER(01_Inputs!$B$35),AE22*01_Inputs!$B$35,"미확인"),IF(ISNUMBER(01_Inputs!$B$37),AE22*01_Inputs!$B$37,"미확인")))</f>
@@ -47712,7 +47684,7 @@
       </c>
       <c r="AJ22" s="15" t="str">
         <f aca="false">IF(AND(ISNUMBER(AH22),ISNUMBER(AI22)),AH22+AI22,"부분 "&amp;TEXT(N(AH22)+N(AI22),"0")&amp;" h + 미확인")</f>
-        <v>부분 0 h + 미확인</v>
+        <v>부분 32 h + 미확인</v>
       </c>
       <c r="AK22" s="15" t="n">
         <f aca="false">(AD22+AE22)*01_Inputs!$B$38</f>
@@ -47919,15 +47891,15 @@
       </c>
       <c r="AF23" s="13" t="str">
         <f aca="false">IF(AD23=0,"-",IF(A23&gt;=01_Inputs!$B$47,"ARS","수동"))</f>
-        <v>ARS</v>
+        <v>수동</v>
       </c>
       <c r="AG23" s="13" t="str">
         <f aca="false">IF(AE23=0,"-",IF(A23&gt;=01_Inputs!$B$46,"ARS","수동"))</f>
         <v>수동</v>
       </c>
-      <c r="AH23" s="15" t="str">
+      <c r="AH23" s="15" t="n">
         <f aca="false">IF(AD23=0,0,IF(AF23="수동",AD23*01_Inputs!$B$34,IF(ISNUMBER(01_Inputs!$B$36),AD23*01_Inputs!$B$36,"미확인")))</f>
-        <v>미확인</v>
+        <v>32</v>
       </c>
       <c r="AI23" s="15" t="str">
         <f aca="false">IF(AE23=0,0,IF(AG23="수동",IF(ISNUMBER(01_Inputs!$B$35),AE23*01_Inputs!$B$35,"미확인"),IF(ISNUMBER(01_Inputs!$B$37),AE23*01_Inputs!$B$37,"미확인")))</f>
@@ -47935,7 +47907,7 @@
       </c>
       <c r="AJ23" s="15" t="str">
         <f aca="false">IF(AND(ISNUMBER(AH23),ISNUMBER(AI23)),AH23+AI23,"부분 "&amp;TEXT(N(AH23)+N(AI23),"0")&amp;" h + 미확인")</f>
-        <v>부분 0 h + 미확인</v>
+        <v>부분 32 h + 미확인</v>
       </c>
       <c r="AK23" s="15" t="n">
         <f aca="false">(AD23+AE23)*01_Inputs!$B$38</f>
@@ -52203,7 +52175,7 @@
       </c>
       <c r="AH43" s="53" t="str">
         <f aca="false">IF(COUNTIF(AH18:AH29,"미확인")&gt;0,"부분 "&amp;TEXT(SUM(AH18:AH29),"0")&amp;" h + 미확인",SUM(AH18:AH29))</f>
-        <v>부분 0 h + 미확인</v>
+        <v>부분 192 h + 미확인</v>
       </c>
       <c r="AI43" s="53" t="str">
         <f aca="false">IF(COUNTIF(AI18:AI29,"미확인")&gt;0,"부분 "&amp;TEXT(SUM(AI18:AI29),"0")&amp;" h + 미확인",SUM(AI18:AI29))</f>
@@ -52684,7 +52656,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="26.85" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="24.6" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="13" t="s">
         <v>762</v>
       </c>
@@ -56137,7 +56109,7 @@
       </c>
       <c r="B88" s="50" t="str">
         <f aca="false">04_Monthly_2026_2028!$AH$43</f>
-        <v>부분 0 h + 미확인</v>
+        <v>부분 192 h + 미확인</v>
       </c>
       <c r="C88" s="9" t="s">
         <v>42</v>

--- a/SKTC_CpZr_Capacity_RawData_Calculation_2026_2028.xlsx
+++ b/SKTC_CpZr_Capacity_RawData_Calculation_2026_2028.xlsx
@@ -297,7 +297,7 @@
     <xf numFmtId="167" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -306,13 +306,13 @@
     <xf numFmtId="168" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="166" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="167" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="166" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -344,10 +344,10 @@
     <xf numFmtId="167" fontId="5" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="170" fontId="5" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="167" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="171" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -474,342 +474,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>누적 (생산 − 출하)</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'07_버전비교'!B14</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'07_버전비교'!$C$10:$Z$10</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'07_버전비교'!$C$14:$Z$14</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'07_버전비교'!B15</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'07_버전비교'!$C$10:$Z$10</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'07_버전비교'!$C$15:$Z$15</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <title>
-          <tx>
-            <rich>
-              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:pPr>
-                  <a:defRPr/>
-                </a:pPr>
-                <a:r>
-                  <a:t>kg</a:t>
-                </a:r>
-              </a:p>
-            </rich>
-          </tx>
-        </title>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
-  <chart>
-    <title>
-      <tx>
-        <rich>
-          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
-          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-            <a:pPr>
-              <a:defRPr/>
-            </a:pPr>
-            <a:r>
-              <a:t>월 생산 vs 출하</a:t>
-            </a:r>
-          </a:p>
-        </rich>
-      </tx>
-    </title>
-    <plotArea>
-      <lineChart>
-        <grouping val="standard"/>
-        <ser>
-          <idx val="0"/>
-          <order val="0"/>
-          <tx>
-            <strRef>
-              <f>'07_버전비교'!B11</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'07_버전비교'!$C$10:$Z$10</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'07_버전비교'!$C$11:$Z$11</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="1"/>
-          <order val="1"/>
-          <tx>
-            <strRef>
-              <f>'07_버전비교'!B12</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'07_버전비교'!$C$10:$Z$10</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'07_버전비교'!$C$12:$Z$12</f>
-            </numRef>
-          </val>
-        </ser>
-        <ser>
-          <idx val="2"/>
-          <order val="2"/>
-          <tx>
-            <strRef>
-              <f>'07_버전비교'!B13</f>
-            </strRef>
-          </tx>
-          <spPr>
-            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-              <a:prstDash val="solid"/>
-            </a:ln>
-          </spPr>
-          <marker>
-            <symbol val="none"/>
-            <spPr>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </marker>
-          <cat>
-            <numRef>
-              <f>'07_버전비교'!$C$10:$Z$10</f>
-            </numRef>
-          </cat>
-          <val>
-            <numRef>
-              <f>'07_버전비교'!$C$13:$Z$13</f>
-            </numRef>
-          </val>
-        </ser>
-        <axId val="10"/>
-        <axId val="100"/>
-      </lineChart>
-      <catAx>
-        <axId val="10"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="100"/>
-        <lblOffset val="100"/>
-      </catAx>
-      <valAx>
-        <axId val="100"/>
-        <scaling>
-          <orientation val="minMax"/>
-        </scaling>
-        <axPos val="l"/>
-        <majorGridlines/>
-        <majorTickMark val="none"/>
-        <minorTickMark val="none"/>
-        <crossAx val="10"/>
-      </valAx>
-    </plotArea>
-    <legend>
-      <legendPos val="r"/>
-    </legend>
-    <plotVisOnly val="1"/>
-    <dispBlanksAs val="gap"/>
-  </chart>
-</chartSpace>
-</file>
-
-<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
-  <oneCellAnchor>
-    <from>
-      <col>1</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7920000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="1" name="Chart 1"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>13</col>
-      <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="7920000" cy="2520000"/>
-    <graphicFrame>
-      <nvGraphicFramePr>
-        <cNvPr id="2" name="Chart 2"/>
-        <cNvGraphicFramePr/>
-      </nvGraphicFramePr>
-      <xfrm/>
-      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
-        </a:graphicData>
-      </a:graphic>
-    </graphicFrame>
-    <clientData/>
-  </oneCellAnchor>
-</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2106,12 +1770,12 @@
     <row r="70">
       <c r="B70" s="10" t="inlineStr">
         <is>
-          <t>월 Capa. (47.2톤 · 대정비 반영)</t>
+          <t>월 Capa. (47.2톤 ÷ 11)</t>
         </is>
       </c>
       <c r="C70" s="22">
-        <f>(CAPA_RF*1000-MAINT_KG)/11</f>
-        <v>4182.90909090909</v>
+        <f>CAPA_RF*1000/11</f>
+        <v>4290.90909090909</v>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
@@ -2120,19 +1784,19 @@
       </c>
       <c r="E70" s="12" t="inlineStr">
         <is>
-          <t>(47,200 − 대정비 월) ÷ 11</t>
+          <t>47,200 ÷ 11 · 대정비 월은 별도 (1,188 kg)</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="B71" s="10" t="inlineStr">
         <is>
-          <t>월 Capa. (50.2톤 · 대정비 반영)</t>
+          <t>월 Capa. (50.2톤 ÷ 11)</t>
         </is>
       </c>
       <c r="C71" s="22">
-        <f>(CAPA_105*1000-MAINT_KG)/11</f>
-        <v>4455.63636363636</v>
+        <f>CAPA_105*1000/11</f>
+        <v>4563.63636363636</v>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
@@ -2141,7 +1805,7 @@
       </c>
       <c r="E71" s="12" t="inlineStr">
         <is>
-          <t>(50,200 − 대정비 월) ÷ 11</t>
+          <t>50,200 ÷ 11 · 대정비 월은 별도 (1,188 kg)</t>
         </is>
       </c>
     </row>
@@ -2180,7 +1844,9 @@
           <t>기초재고 (2027-01-01)</t>
         </is>
       </c>
-      <c r="C75" s="23" t="n"/>
+      <c r="C75" s="23" t="n">
+        <v>2882</v>
+      </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
           <t>kg</t>
@@ -2188,14 +1854,14 @@
       </c>
       <c r="E75" s="12" t="inlineStr">
         <is>
-          <t>입력 시 월별 기말재고 계산</t>
+          <t>재고 = 전월 재고 + 생산 − 출하</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="B76" s="10" t="inlineStr">
         <is>
-          <t>양품률 (출하 가능)</t>
+          <t>양품률 (입력 시 재고에 반영)</t>
         </is>
       </c>
       <c r="C76" s="24" t="n"/>
@@ -2206,7 +1872,7 @@
       </c>
       <c r="E76" s="12" t="inlineStr">
         <is>
-          <t>입력 전에는 100%로 대체하지 않음</t>
+          <t>공란이면 생산계획 그대로 재고 계산</t>
         </is>
       </c>
     </row>
@@ -2271,43 +1937,43 @@
           <t>기존 생산계획 (1~4월 확정)</t>
         </is>
       </c>
-      <c r="C80" s="26" t="n">
+      <c r="C80" s="23" t="n">
         <v>2178</v>
       </c>
-      <c r="D80" s="26" t="n">
+      <c r="D80" s="23" t="n">
         <v>2178</v>
       </c>
-      <c r="E80" s="26" t="n">
+      <c r="E80" s="23" t="n">
         <v>3168</v>
       </c>
-      <c r="F80" s="26" t="n">
+      <c r="F80" s="23" t="n">
         <v>1188</v>
       </c>
-      <c r="G80" s="26" t="n">
+      <c r="G80" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="H80" s="26" t="n">
+      <c r="H80" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="I80" s="26" t="n">
+      <c r="I80" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="J80" s="26" t="n">
+      <c r="J80" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="K80" s="26" t="n">
+      <c r="K80" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="L80" s="26" t="n">
+      <c r="L80" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="M80" s="26" t="n">
+      <c r="M80" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="N80" s="26" t="n">
+      <c r="N80" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="O80" s="27">
+      <c r="O80" s="26">
         <f>SUM(C80:N80)</f>
         <v>37224</v>
       </c>
@@ -2366,43 +2032,43 @@
           <t>기존 생산계획</t>
         </is>
       </c>
-      <c r="C83" s="26" t="n">
+      <c r="C83" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="D83" s="26" t="n">
+      <c r="D83" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="E83" s="26" t="n">
+      <c r="E83" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="F83" s="26" t="n">
+      <c r="F83" s="23" t="n">
         <v>1188</v>
       </c>
-      <c r="G83" s="26" t="n">
+      <c r="G83" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="H83" s="26" t="n">
+      <c r="H83" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="I83" s="26" t="n">
+      <c r="I83" s="23" t="n">
         <v>3564</v>
       </c>
-      <c r="J83" s="26" t="n">
+      <c r="J83" s="23" t="n">
         <v>3168</v>
       </c>
-      <c r="K83" s="26" t="n">
+      <c r="K83" s="23" t="n">
         <v>3168</v>
       </c>
-      <c r="L83" s="26" t="n">
+      <c r="L83" s="23" t="n">
         <v>3168</v>
       </c>
-      <c r="M83" s="26" t="n">
+      <c r="M83" s="23" t="n">
         <v>3168</v>
       </c>
-      <c r="N83" s="26" t="n">
+      <c r="N83" s="23" t="n">
         <v>3168</v>
       </c>
-      <c r="O83" s="27">
+      <c r="O83" s="26">
         <f>SUM(C83:N83)</f>
         <v>38412</v>
       </c>
@@ -2468,40 +2134,40 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C87" s="28" t="n">
+      <c r="C87" s="27" t="n">
         <v>1600</v>
       </c>
-      <c r="D87" s="28" t="n">
+      <c r="D87" s="27" t="n">
         <v>1420</v>
       </c>
-      <c r="E87" s="28" t="n">
+      <c r="E87" s="27" t="n">
         <v>1440</v>
       </c>
-      <c r="F87" s="28" t="n">
+      <c r="F87" s="27" t="n">
         <v>1580</v>
       </c>
-      <c r="G87" s="28" t="n">
+      <c r="G87" s="27" t="n">
         <v>1200</v>
       </c>
-      <c r="H87" s="28" t="n">
+      <c r="H87" s="27" t="n">
         <v>1200</v>
       </c>
-      <c r="I87" s="28" t="n">
+      <c r="I87" s="27" t="n">
         <v>1360</v>
       </c>
-      <c r="J87" s="28" t="n">
+      <c r="J87" s="27" t="n">
         <v>1420</v>
       </c>
-      <c r="K87" s="28" t="n">
+      <c r="K87" s="27" t="n">
         <v>1380</v>
       </c>
-      <c r="L87" s="28" t="n">
+      <c r="L87" s="27" t="n">
         <v>1480</v>
       </c>
-      <c r="M87" s="28" t="n">
+      <c r="M87" s="27" t="n">
         <v>1480</v>
       </c>
-      <c r="N87" s="28" t="n">
+      <c r="N87" s="27" t="n">
         <v>1420</v>
       </c>
       <c r="O87" s="21">
@@ -2515,18 +2181,18 @@
           <t>CXMT</t>
         </is>
       </c>
-      <c r="C88" s="23" t="n"/>
-      <c r="D88" s="23" t="n"/>
-      <c r="E88" s="23" t="n"/>
-      <c r="F88" s="23" t="n"/>
-      <c r="G88" s="23" t="n"/>
-      <c r="H88" s="23" t="n"/>
-      <c r="I88" s="23" t="n"/>
-      <c r="J88" s="23" t="n"/>
-      <c r="K88" s="23" t="n"/>
-      <c r="L88" s="23" t="n"/>
-      <c r="M88" s="23" t="n"/>
-      <c r="N88" s="23" t="n"/>
+      <c r="C88" s="28" t="n"/>
+      <c r="D88" s="28" t="n"/>
+      <c r="E88" s="28" t="n"/>
+      <c r="F88" s="28" t="n"/>
+      <c r="G88" s="28" t="n"/>
+      <c r="H88" s="28" t="n"/>
+      <c r="I88" s="28" t="n"/>
+      <c r="J88" s="28" t="n"/>
+      <c r="K88" s="28" t="n"/>
+      <c r="L88" s="28" t="n"/>
+      <c r="M88" s="28" t="n"/>
+      <c r="N88" s="28" t="n"/>
       <c r="O88" s="21" t="str">
         <f>IF(COUNT(C88:N88)=0,"미제시",SUM(C88:N88))</f>
         <v>미제시</v>
@@ -2538,40 +2204,40 @@
           <t>이지켐</t>
         </is>
       </c>
-      <c r="C89" s="26" t="n">
+      <c r="C89" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D89" s="26" t="n">
+      <c r="D89" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E89" s="26" t="n">
+      <c r="E89" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="F89" s="26" t="n">
+      <c r="F89" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="G89" s="26" t="n">
+      <c r="G89" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="H89" s="26" t="n">
+      <c r="H89" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="I89" s="26" t="n">
+      <c r="I89" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="J89" s="26" t="n">
+      <c r="J89" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="K89" s="26" t="n">
+      <c r="K89" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="L89" s="26" t="n">
+      <c r="L89" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="M89" s="26" t="n">
+      <c r="M89" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="N89" s="26" t="n">
+      <c r="N89" s="23" t="n">
         <v>560</v>
       </c>
       <c r="O89" s="21">
@@ -2585,18 +2251,18 @@
           <t>한솔</t>
         </is>
       </c>
-      <c r="C90" s="23" t="n"/>
-      <c r="D90" s="23" t="n"/>
-      <c r="E90" s="23" t="n"/>
-      <c r="F90" s="23" t="n"/>
-      <c r="G90" s="23" t="n"/>
-      <c r="H90" s="23" t="n"/>
-      <c r="I90" s="23" t="n"/>
-      <c r="J90" s="23" t="n"/>
-      <c r="K90" s="23" t="n"/>
-      <c r="L90" s="23" t="n"/>
-      <c r="M90" s="23" t="n"/>
-      <c r="N90" s="23" t="n"/>
+      <c r="C90" s="28" t="n"/>
+      <c r="D90" s="28" t="n"/>
+      <c r="E90" s="28" t="n"/>
+      <c r="F90" s="28" t="n"/>
+      <c r="G90" s="28" t="n"/>
+      <c r="H90" s="28" t="n"/>
+      <c r="I90" s="28" t="n"/>
+      <c r="J90" s="28" t="n"/>
+      <c r="K90" s="28" t="n"/>
+      <c r="L90" s="28" t="n"/>
+      <c r="M90" s="28" t="n"/>
+      <c r="N90" s="28" t="n"/>
       <c r="O90" s="21" t="str">
         <f>IF(COUNT(C90:N90)=0,"미제시",SUM(C90:N90))</f>
         <v>미제시</v>
@@ -2608,55 +2274,55 @@
           <t>합계</t>
         </is>
       </c>
-      <c r="C91" s="27">
+      <c r="C91" s="26">
         <f>SUM(C87:C90)</f>
         <v>1600</v>
       </c>
-      <c r="D91" s="27">
+      <c r="D91" s="26">
         <f>SUM(D87:D90)</f>
         <v>1420</v>
       </c>
-      <c r="E91" s="27">
+      <c r="E91" s="26">
         <f>SUM(E87:E90)</f>
         <v>1440</v>
       </c>
-      <c r="F91" s="27">
+      <c r="F91" s="26">
         <f>SUM(F87:F90)</f>
         <v>1580</v>
       </c>
-      <c r="G91" s="27">
+      <c r="G91" s="26">
         <f>SUM(G87:G90)</f>
         <v>1200</v>
       </c>
-      <c r="H91" s="27">
+      <c r="H91" s="26">
         <f>SUM(H87:H90)</f>
         <v>1200</v>
       </c>
-      <c r="I91" s="27">
+      <c r="I91" s="26">
         <f>SUM(I87:I90)</f>
         <v>1360</v>
       </c>
-      <c r="J91" s="27">
+      <c r="J91" s="26">
         <f>SUM(J87:J90)</f>
         <v>1420</v>
       </c>
-      <c r="K91" s="27">
+      <c r="K91" s="26">
         <f>SUM(K87:K90)</f>
         <v>1940</v>
       </c>
-      <c r="L91" s="27">
+      <c r="L91" s="26">
         <f>SUM(L87:L90)</f>
         <v>2040</v>
       </c>
-      <c r="M91" s="27">
+      <c r="M91" s="26">
         <f>SUM(M87:M90)</f>
         <v>2040</v>
       </c>
-      <c r="N91" s="27">
+      <c r="N91" s="26">
         <f>SUM(N87:N90)</f>
         <v>1980</v>
       </c>
-      <c r="O91" s="27">
+      <c r="O91" s="26">
         <f>SUM(O87:O90)</f>
         <v>19220</v>
       </c>
@@ -2715,51 +2381,51 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C94" s="28">
+      <c r="C94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="D94" s="28">
+      <c r="D94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="E94" s="28">
+      <c r="E94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="F94" s="28">
+      <c r="F94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="G94" s="28">
+      <c r="G94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="H94" s="28">
+      <c r="H94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="I94" s="28">
+      <c r="I94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="J94" s="28">
+      <c r="J94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="K94" s="28">
+      <c r="K94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="L94" s="28">
+      <c r="L94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="M94" s="28">
+      <c r="M94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="N94" s="28">
+      <c r="N94" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
@@ -2774,40 +2440,40 @@
           <t>CXMT</t>
         </is>
       </c>
-      <c r="C95" s="26" t="n">
+      <c r="C95" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="D95" s="26" t="n">
+      <c r="D95" s="23" t="n">
         <v>0</v>
       </c>
-      <c r="E95" s="26" t="n">
+      <c r="E95" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="F95" s="26" t="n">
+      <c r="F95" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="G95" s="26" t="n">
+      <c r="G95" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="H95" s="26" t="n">
+      <c r="H95" s="23" t="n">
         <v>580</v>
       </c>
-      <c r="I95" s="26" t="n">
+      <c r="I95" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="J95" s="26" t="n">
+      <c r="J95" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="K95" s="26" t="n">
+      <c r="K95" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="L95" s="26" t="n">
+      <c r="L95" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="M95" s="26" t="n">
+      <c r="M95" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="N95" s="26" t="n">
+      <c r="N95" s="23" t="n">
         <v>780</v>
       </c>
       <c r="O95" s="21">
@@ -2821,45 +2487,45 @@
           <t>이지켐</t>
         </is>
       </c>
-      <c r="C96" s="26" t="n">
+      <c r="C96" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="D96" s="26" t="n">
+      <c r="D96" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="E96" s="26" t="n">
+      <c r="E96" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="F96" s="26" t="n">
+      <c r="F96" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="G96" s="26" t="n">
+      <c r="G96" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="H96" s="26" t="n">
+      <c r="H96" s="23" t="n">
         <v>560</v>
       </c>
-      <c r="I96" s="26" t="n">
-        <v>1120</v>
-      </c>
-      <c r="J96" s="26" t="n">
-        <v>1120</v>
-      </c>
-      <c r="K96" s="26" t="n">
-        <v>1120</v>
-      </c>
-      <c r="L96" s="26" t="n">
-        <v>1120</v>
-      </c>
-      <c r="M96" s="26" t="n">
-        <v>1120</v>
-      </c>
-      <c r="N96" s="26" t="n">
-        <v>1120</v>
+      <c r="I96" s="23" t="n">
+        <v>840</v>
+      </c>
+      <c r="J96" s="23" t="n">
+        <v>840</v>
+      </c>
+      <c r="K96" s="23" t="n">
+        <v>840</v>
+      </c>
+      <c r="L96" s="23" t="n">
+        <v>840</v>
+      </c>
+      <c r="M96" s="23" t="n">
+        <v>840</v>
+      </c>
+      <c r="N96" s="23" t="n">
+        <v>840</v>
       </c>
       <c r="O96" s="21">
         <f>IF(COUNT(C96:N96)=0,"미제시",SUM(C96:N96))</f>
-        <v>10080</v>
+        <v>8400</v>
       </c>
     </row>
     <row r="97">
@@ -2868,40 +2534,40 @@
           <t>한솔</t>
         </is>
       </c>
-      <c r="C97" s="26" t="n">
+      <c r="C97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="D97" s="26" t="n">
+      <c r="D97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="E97" s="26" t="n">
+      <c r="E97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="F97" s="26" t="n">
+      <c r="F97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="G97" s="26" t="n">
+      <c r="G97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="H97" s="26" t="n">
+      <c r="H97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="I97" s="26" t="n">
+      <c r="I97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="J97" s="26" t="n">
+      <c r="J97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="K97" s="26" t="n">
+      <c r="K97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="L97" s="26" t="n">
+      <c r="L97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="M97" s="26" t="n">
+      <c r="M97" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="N97" s="26" t="n">
+      <c r="N97" s="23" t="n">
         <v>300</v>
       </c>
       <c r="O97" s="21">
@@ -2915,57 +2581,57 @@
           <t>합계</t>
         </is>
       </c>
-      <c r="C98" s="27">
+      <c r="C98" s="26">
         <f>SUM(C94:C97)</f>
         <v>2753.33333333333</v>
       </c>
-      <c r="D98" s="27">
+      <c r="D98" s="26">
         <f>SUM(D94:D97)</f>
         <v>2753.33333333333</v>
       </c>
-      <c r="E98" s="27">
+      <c r="E98" s="26">
         <f>SUM(E94:E97)</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="F98" s="27">
+      <c r="F98" s="26">
         <f>SUM(F94:F97)</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="G98" s="27">
+      <c r="G98" s="26">
         <f>SUM(G94:G97)</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="H98" s="27">
+      <c r="H98" s="26">
         <f>SUM(H94:H97)</f>
         <v>3333.33333333333</v>
       </c>
-      <c r="I98" s="27">
+      <c r="I98" s="26">
         <f>SUM(I94:I97)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="J98" s="27">
+        <v>3813.33333333333</v>
+      </c>
+      <c r="J98" s="26">
         <f>SUM(J94:J97)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="K98" s="27">
+        <v>3813.33333333333</v>
+      </c>
+      <c r="K98" s="26">
         <f>SUM(K94:K97)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="L98" s="27">
+        <v>3813.33333333333</v>
+      </c>
+      <c r="L98" s="26">
         <f>SUM(L94:L97)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="M98" s="27">
+        <v>3813.33333333333</v>
+      </c>
+      <c r="M98" s="26">
         <f>SUM(M94:M97)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="N98" s="27">
+        <v>3813.33333333333</v>
+      </c>
+      <c r="N98" s="26">
         <f>SUM(N94:N97)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="O98" s="27">
+        <v>3813.33333333333</v>
+      </c>
+      <c r="O98" s="26">
         <f>SUM(O94:O97)</f>
-        <v>43400</v>
+        <v>41720</v>
       </c>
     </row>
     <row r="100">
@@ -3022,51 +2688,51 @@
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C101" s="28">
+      <c r="C101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="D101" s="28">
+      <c r="D101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="E101" s="28">
+      <c r="E101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="F101" s="28">
+      <c r="F101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="G101" s="28">
+      <c r="G101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="H101" s="28">
+      <c r="H101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="I101" s="28">
+      <c r="I101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="J101" s="28">
+      <c r="J101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="K101" s="28">
+      <c r="K101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="L101" s="28">
+      <c r="L101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="M101" s="28">
+      <c r="M101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="N101" s="28">
+      <c r="N101" s="27">
         <f>22720/12</f>
         <v>1893.33333333333</v>
       </c>
@@ -3081,40 +2747,40 @@
           <t>CXMT</t>
         </is>
       </c>
-      <c r="C102" s="26" t="n">
+      <c r="C102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="D102" s="26" t="n">
+      <c r="D102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="E102" s="26" t="n">
+      <c r="E102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="F102" s="26" t="n">
+      <c r="F102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="G102" s="26" t="n">
+      <c r="G102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="H102" s="26" t="n">
+      <c r="H102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="I102" s="26" t="n">
+      <c r="I102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="J102" s="26" t="n">
+      <c r="J102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="K102" s="26" t="n">
+      <c r="K102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="L102" s="26" t="n">
+      <c r="L102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="M102" s="26" t="n">
+      <c r="M102" s="23" t="n">
         <v>780</v>
       </c>
-      <c r="N102" s="26" t="n">
+      <c r="N102" s="23" t="n">
         <v>780</v>
       </c>
       <c r="O102" s="21">
@@ -3128,40 +2794,40 @@
           <t>이지켐</t>
         </is>
       </c>
-      <c r="C103" s="26" t="n">
+      <c r="C103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="D103" s="26" t="n">
+      <c r="D103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="E103" s="26" t="n">
+      <c r="E103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="F103" s="26" t="n">
+      <c r="F103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="G103" s="26" t="n">
+      <c r="G103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="H103" s="26" t="n">
+      <c r="H103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="I103" s="26" t="n">
+      <c r="I103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="J103" s="26" t="n">
+      <c r="J103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="K103" s="26" t="n">
+      <c r="K103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="L103" s="26" t="n">
+      <c r="L103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="M103" s="26" t="n">
+      <c r="M103" s="23" t="n">
         <v>840</v>
       </c>
-      <c r="N103" s="26" t="n">
+      <c r="N103" s="23" t="n">
         <v>840</v>
       </c>
       <c r="O103" s="21">
@@ -3175,40 +2841,40 @@
           <t>한솔</t>
         </is>
       </c>
-      <c r="C104" s="26" t="n">
+      <c r="C104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="D104" s="26" t="n">
+      <c r="D104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="E104" s="26" t="n">
+      <c r="E104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="F104" s="26" t="n">
+      <c r="F104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="G104" s="26" t="n">
+      <c r="G104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="H104" s="26" t="n">
+      <c r="H104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="I104" s="26" t="n">
+      <c r="I104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="J104" s="26" t="n">
+      <c r="J104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="K104" s="26" t="n">
+      <c r="K104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="L104" s="26" t="n">
+      <c r="L104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="M104" s="26" t="n">
+      <c r="M104" s="23" t="n">
         <v>300</v>
       </c>
-      <c r="N104" s="26" t="n">
+      <c r="N104" s="23" t="n">
         <v>300</v>
       </c>
       <c r="O104" s="21">
@@ -3222,55 +2888,55 @@
           <t>합계</t>
         </is>
       </c>
-      <c r="C105" s="27">
+      <c r="C105" s="26">
         <f>SUM(C101:C104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="D105" s="27">
+      <c r="D105" s="26">
         <f>SUM(D101:D104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="E105" s="27">
+      <c r="E105" s="26">
         <f>SUM(E101:E104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="F105" s="27">
+      <c r="F105" s="26">
         <f>SUM(F101:F104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="G105" s="27">
+      <c r="G105" s="26">
         <f>SUM(G101:G104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="H105" s="27">
+      <c r="H105" s="26">
         <f>SUM(H101:H104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="I105" s="27">
+      <c r="I105" s="26">
         <f>SUM(I101:I104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="J105" s="27">
+      <c r="J105" s="26">
         <f>SUM(J101:J104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="K105" s="27">
+      <c r="K105" s="26">
         <f>SUM(K101:K104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="L105" s="27">
+      <c r="L105" s="26">
         <f>SUM(L101:L104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="M105" s="27">
+      <c r="M105" s="26">
         <f>SUM(M101:M104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="N105" s="27">
+      <c r="N105" s="26">
         <f>SUM(N101:N104)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="O105" s="27">
+      <c r="O105" s="26">
         <f>SUM(O101:O104)</f>
         <v>45760</v>
       </c>
@@ -3278,7 +2944,7 @@
     <row r="107">
       <c r="B107" s="18" t="inlineStr">
         <is>
-          <t>2026 CXMT·한솔 미제시 칸은 0이 아니라 공란 · 하이닉스 22,720 ÷ 12 균등 · 2028 이지켐 840 kg/월</t>
+          <t>2026 CXMT·한솔 미제시 칸은 0이 아니라 공란 · 하이닉스 22,720 ÷ 12 균등 · 이지켐 2027.7~ 840 kg/월</t>
         </is>
       </c>
     </row>
@@ -4986,7 +4652,7 @@
         <f>SUM(F7:F18)</f>
         <v>11</v>
       </c>
-      <c r="D19" s="27">
+      <c r="D19" s="26">
         <f>C19*KG_B</f>
         <v>2090</v>
       </c>
@@ -5006,7 +4672,7 @@
       </c>
       <c r="C22" s="13">
         <f>IF(ISNUMBER(INT_NEXT),INT_NEXT,N_NEW*(8760/12)/(CAPA_M/KG_B))</f>
-        <v>66.3174823958967</v>
+        <v>64.6483050847458</v>
       </c>
       <c r="D22" s="18" t="inlineStr">
         <is>
@@ -5068,11 +4734,11 @@
       </c>
       <c r="C25" s="17">
         <f>B25*INT_RF</f>
-        <v>-66.3174823958967</v>
+        <v>-64.6483050847458</v>
       </c>
       <c r="D25" s="17">
         <f>C25+T_57</f>
-        <v>-9.31748239589672</v>
+        <v>-7.64830508474577</v>
       </c>
       <c r="E25" s="33">
         <f>IF(AND(D25&gt;=0,D25&lt;MH),1,0)</f>
@@ -5080,11 +4746,11 @@
       </c>
       <c r="F25" s="17">
         <f>OFFSET_H+B25*INT_RF</f>
-        <v>-36.3174823958967</v>
+        <v>-34.6483050847458</v>
       </c>
       <c r="G25" s="17">
         <f>F25+T_57</f>
-        <v>20.6825176041033</v>
+        <v>22.3516949152542</v>
       </c>
       <c r="H25" s="33">
         <f>IF(AND(G25&gt;=0,G25&lt;MH),1,0)</f>
@@ -5126,11 +4792,11 @@
       </c>
       <c r="C27" s="17">
         <f>B27*INT_RF</f>
-        <v>66.3174823958967</v>
+        <v>64.6483050847458</v>
       </c>
       <c r="D27" s="17">
         <f>C27+T_57</f>
-        <v>123.317482395897</v>
+        <v>121.648305084746</v>
       </c>
       <c r="E27" s="33">
         <f>IF(AND(D27&gt;=0,D27&lt;MH),1,0)</f>
@@ -5138,11 +4804,11 @@
       </c>
       <c r="F27" s="17">
         <f>OFFSET_H+B27*INT_RF</f>
-        <v>96.3174823958967</v>
+        <v>94.6483050847458</v>
       </c>
       <c r="G27" s="17">
         <f>F27+T_57</f>
-        <v>153.317482395897</v>
+        <v>151.648305084746</v>
       </c>
       <c r="H27" s="33">
         <f>IF(AND(G27&gt;=0,G27&lt;MH),1,0)</f>
@@ -5155,11 +4821,11 @@
       </c>
       <c r="C28" s="17">
         <f>B28*INT_RF</f>
-        <v>132.634964791793</v>
+        <v>129.296610169492</v>
       </c>
       <c r="D28" s="17">
         <f>C28+T_57</f>
-        <v>189.634964791793</v>
+        <v>186.296610169492</v>
       </c>
       <c r="E28" s="33">
         <f>IF(AND(D28&gt;=0,D28&lt;MH),1,0)</f>
@@ -5167,11 +4833,11 @@
       </c>
       <c r="F28" s="17">
         <f>OFFSET_H+B28*INT_RF</f>
-        <v>162.634964791793</v>
+        <v>159.296610169492</v>
       </c>
       <c r="G28" s="17">
         <f>F28+T_57</f>
-        <v>219.634964791793</v>
+        <v>216.296610169492</v>
       </c>
       <c r="H28" s="33">
         <f>IF(AND(G28&gt;=0,G28&lt;MH),1,0)</f>
@@ -5184,11 +4850,11 @@
       </c>
       <c r="C29" s="17">
         <f>B29*INT_RF</f>
-        <v>198.95244718769</v>
+        <v>193.944915254237</v>
       </c>
       <c r="D29" s="17">
         <f>C29+T_57</f>
-        <v>255.95244718769</v>
+        <v>250.944915254237</v>
       </c>
       <c r="E29" s="33">
         <f>IF(AND(D29&gt;=0,D29&lt;MH),1,0)</f>
@@ -5196,11 +4862,11 @@
       </c>
       <c r="F29" s="17">
         <f>OFFSET_H+B29*INT_RF</f>
-        <v>228.95244718769</v>
+        <v>223.944915254237</v>
       </c>
       <c r="G29" s="17">
         <f>F29+T_57</f>
-        <v>285.95244718769</v>
+        <v>280.944915254237</v>
       </c>
       <c r="H29" s="33">
         <f>IF(AND(G29&gt;=0,G29&lt;MH),1,0)</f>
@@ -5213,11 +4879,11 @@
       </c>
       <c r="C30" s="17">
         <f>B30*INT_RF</f>
-        <v>265.269929583587</v>
+        <v>258.593220338983</v>
       </c>
       <c r="D30" s="17">
         <f>C30+T_57</f>
-        <v>322.269929583587</v>
+        <v>315.593220338983</v>
       </c>
       <c r="E30" s="33">
         <f>IF(AND(D30&gt;=0,D30&lt;MH),1,0)</f>
@@ -5225,11 +4891,11 @@
       </c>
       <c r="F30" s="17">
         <f>OFFSET_H+B30*INT_RF</f>
-        <v>295.269929583587</v>
+        <v>288.593220338983</v>
       </c>
       <c r="G30" s="17">
         <f>F30+T_57</f>
-        <v>352.269929583587</v>
+        <v>345.593220338983</v>
       </c>
       <c r="H30" s="33">
         <f>IF(AND(G30&gt;=0,G30&lt;MH),1,0)</f>
@@ -5242,11 +4908,11 @@
       </c>
       <c r="C31" s="17">
         <f>B31*INT_RF</f>
-        <v>331.587411979484</v>
+        <v>323.241525423729</v>
       </c>
       <c r="D31" s="17">
         <f>C31+T_57</f>
-        <v>388.587411979484</v>
+        <v>380.241525423729</v>
       </c>
       <c r="E31" s="33">
         <f>IF(AND(D31&gt;=0,D31&lt;MH),1,0)</f>
@@ -5254,11 +4920,11 @@
       </c>
       <c r="F31" s="17">
         <f>OFFSET_H+B31*INT_RF</f>
-        <v>361.587411979484</v>
+        <v>353.241525423729</v>
       </c>
       <c r="G31" s="17">
         <f>F31+T_57</f>
-        <v>418.587411979484</v>
+        <v>410.241525423729</v>
       </c>
       <c r="H31" s="33">
         <f>IF(AND(G31&gt;=0,G31&lt;MH),1,0)</f>
@@ -5271,11 +4937,11 @@
       </c>
       <c r="C32" s="17">
         <f>B32*INT_RF</f>
-        <v>397.90489437538</v>
+        <v>387.889830508475</v>
       </c>
       <c r="D32" s="17">
         <f>C32+T_57</f>
-        <v>454.90489437538</v>
+        <v>444.889830508475</v>
       </c>
       <c r="E32" s="33">
         <f>IF(AND(D32&gt;=0,D32&lt;MH),1,0)</f>
@@ -5283,11 +4949,11 @@
       </c>
       <c r="F32" s="17">
         <f>OFFSET_H+B32*INT_RF</f>
-        <v>427.90489437538</v>
+        <v>417.889830508475</v>
       </c>
       <c r="G32" s="17">
         <f>F32+T_57</f>
-        <v>484.90489437538</v>
+        <v>474.889830508475</v>
       </c>
       <c r="H32" s="33">
         <f>IF(AND(G32&gt;=0,G32&lt;MH),1,0)</f>
@@ -5300,11 +4966,11 @@
       </c>
       <c r="C33" s="17">
         <f>B33*INT_RF</f>
-        <v>464.222376771277</v>
+        <v>452.53813559322</v>
       </c>
       <c r="D33" s="17">
         <f>C33+T_57</f>
-        <v>521.222376771277</v>
+        <v>509.53813559322</v>
       </c>
       <c r="E33" s="33">
         <f>IF(AND(D33&gt;=0,D33&lt;MH),1,0)</f>
@@ -5312,11 +4978,11 @@
       </c>
       <c r="F33" s="17">
         <f>OFFSET_H+B33*INT_RF</f>
-        <v>494.222376771277</v>
+        <v>482.53813559322</v>
       </c>
       <c r="G33" s="17">
         <f>F33+T_57</f>
-        <v>551.222376771277</v>
+        <v>539.53813559322</v>
       </c>
       <c r="H33" s="33">
         <f>IF(AND(G33&gt;=0,G33&lt;MH),1,0)</f>
@@ -5329,11 +4995,11 @@
       </c>
       <c r="C34" s="17">
         <f>B34*INT_RF</f>
-        <v>530.539859167174</v>
+        <v>517.186440677966</v>
       </c>
       <c r="D34" s="17">
         <f>C34+T_57</f>
-        <v>587.539859167174</v>
+        <v>574.186440677966</v>
       </c>
       <c r="E34" s="33">
         <f>IF(AND(D34&gt;=0,D34&lt;MH),1,0)</f>
@@ -5341,11 +5007,11 @@
       </c>
       <c r="F34" s="17">
         <f>OFFSET_H+B34*INT_RF</f>
-        <v>560.539859167174</v>
+        <v>547.186440677966</v>
       </c>
       <c r="G34" s="17">
         <f>F34+T_57</f>
-        <v>617.539859167174</v>
+        <v>604.186440677966</v>
       </c>
       <c r="H34" s="33">
         <f>IF(AND(G34&gt;=0,G34&lt;MH),1,0)</f>
@@ -5358,11 +5024,11 @@
       </c>
       <c r="C35" s="17">
         <f>B35*INT_RF</f>
-        <v>596.857341563071</v>
+        <v>581.834745762712</v>
       </c>
       <c r="D35" s="17">
         <f>C35+T_57</f>
-        <v>653.857341563071</v>
+        <v>638.834745762712</v>
       </c>
       <c r="E35" s="33">
         <f>IF(AND(D35&gt;=0,D35&lt;MH),1,0)</f>
@@ -5370,11 +5036,11 @@
       </c>
       <c r="F35" s="17">
         <f>OFFSET_H+B35*INT_RF</f>
-        <v>626.857341563071</v>
+        <v>611.834745762712</v>
       </c>
       <c r="G35" s="17">
         <f>F35+T_57</f>
-        <v>683.857341563071</v>
+        <v>668.834745762712</v>
       </c>
       <c r="H35" s="33">
         <f>IF(AND(G35&gt;=0,G35&lt;MH),1,0)</f>
@@ -5387,23 +5053,23 @@
       </c>
       <c r="C36" s="17">
         <f>B36*INT_RF</f>
-        <v>663.174823958967</v>
+        <v>646.483050847458</v>
       </c>
       <c r="D36" s="17">
         <f>C36+T_57</f>
-        <v>720.174823958967</v>
+        <v>703.483050847458</v>
       </c>
       <c r="E36" s="33">
         <f>IF(AND(D36&gt;=0,D36&lt;MH),1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F36" s="17">
         <f>OFFSET_H+B36*INT_RF</f>
-        <v>693.174823958967</v>
+        <v>676.483050847458</v>
       </c>
       <c r="G36" s="17">
         <f>F36+T_57</f>
-        <v>750.174823958967</v>
+        <v>733.483050847458</v>
       </c>
       <c r="H36" s="33">
         <f>IF(AND(G36&gt;=0,G36&lt;MH),1,0)</f>
@@ -5418,11 +5084,11 @@
       </c>
       <c r="C37" s="34">
         <f>SUM(E25:E36)+SUM(H25:H36)</f>
-        <v>21</v>
-      </c>
-      <c r="D37" s="27">
+        <v>22</v>
+      </c>
+      <c r="D37" s="26">
         <f>C37*KG_B</f>
-        <v>3990</v>
+        <v>4180</v>
       </c>
     </row>
     <row r="38">
@@ -5433,7 +5099,7 @@
       </c>
       <c r="C38" s="35">
         <f>CAPA_M/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
     </row>
     <row r="40" ht="20" customHeight="1">
@@ -5494,7 +5160,7 @@
         <f>INT(MH/T_REF)</f>
         <v>16</v>
       </c>
-      <c r="E42" s="27">
+      <c r="E42" s="26">
         <f>D42*KG_B</f>
         <v>3040</v>
       </c>
@@ -5526,7 +5192,7 @@
         <f>MAX_B</f>
         <v>11</v>
       </c>
-      <c r="E43" s="27">
+      <c r="E43" s="26">
         <f>D43*KG_B</f>
         <v>2090</v>
       </c>
@@ -5558,7 +5224,7 @@
         <f>E44/KG_B</f>
         <v>11.4912280701754</v>
       </c>
-      <c r="E44" s="27">
+      <c r="E44" s="26">
         <f>CAPA_NOW*1000/12</f>
         <v>2183.33333333333</v>
       </c>
@@ -5590,7 +5256,7 @@
         <f>E45/KG_B</f>
         <v>18.7578947368421</v>
       </c>
-      <c r="E45" s="27">
+      <c r="E45" s="26">
         <f>'01_입력'!$G$80</f>
         <v>3564</v>
       </c>
@@ -5621,11 +5287,11 @@
       </c>
       <c r="D46" s="32">
         <f>E46/KG_B</f>
-        <v>22.0153110047847</v>
-      </c>
-      <c r="E46" s="27">
+        <v>22.5837320574163</v>
+      </c>
+      <c r="E46" s="26">
         <f>CAPA_M</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="F46" s="36">
         <f>CAPA_RF</f>
@@ -5633,11 +5299,11 @@
       </c>
       <c r="G46" s="17">
         <f>N_NEW*730/D46</f>
-        <v>66.3174823958967</v>
+        <v>64.6483050847458</v>
       </c>
       <c r="H46" s="12" t="inlineStr">
         <is>
-          <t>(47,200 − 1,188) ÷ 11</t>
+          <t>47,200 ÷ 11 (대정비 월 별도)</t>
         </is>
       </c>
     </row>
@@ -5653,11 +5319,11 @@
       </c>
       <c r="D47" s="32">
         <f>E47/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="E47" s="27">
+        <v>24.0191387559809</v>
+      </c>
+      <c r="E47" s="26">
         <f>CAPA_M105</f>
-        <v>4455.63636363636</v>
+        <v>4563.63636363636</v>
       </c>
       <c r="F47" s="36">
         <f>CAPA_105</f>
@@ -5665,11 +5331,11 @@
       </c>
       <c r="G47" s="17">
         <f>N_NEW*730/D47</f>
-        <v>62.2582224761283</v>
+        <v>60.7848605577689</v>
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>(50,200 − 1,188) ÷ 11</t>
+          <t>50,200 ÷ 11 (대정비 월 별도)</t>
         </is>
       </c>
     </row>
@@ -5799,11 +5465,11 @@
       </c>
       <c r="D7" s="22">
         <f>CAPA_M</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="E7" s="32">
         <f>D7/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
@@ -5812,7 +5478,7 @@
       </c>
       <c r="G7" s="18" t="inlineStr">
         <is>
-          <t>(47,200 − 대정비) ÷ 11</t>
+          <t>47,200 ÷ 11 · 대정비 월 1,188 kg 별도</t>
         </is>
       </c>
     </row>
@@ -5828,11 +5494,11 @@
       </c>
       <c r="D8" s="22">
         <f>CAPA_M105</f>
-        <v>4455.63636363636</v>
+        <v>4563.63636363636</v>
       </c>
       <c r="E8" s="32">
         <f>D8/KG_B</f>
-        <v>23.4507177033493</v>
+        <v>24.0191387559809</v>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
@@ -5841,7 +5507,7 @@
       </c>
       <c r="G8" s="18" t="inlineStr">
         <is>
-          <t>(50,200 − 대정비) ÷ 11</t>
+          <t>50,200 ÷ 11 · 대정비 월 1,188 kg 별도</t>
         </is>
       </c>
     </row>
@@ -5884,7 +5550,7 @@
         <f>MAINT_KG/1000</f>
         <v>1.188</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="26">
         <f>MAINT_KG</f>
         <v>1188</v>
       </c>
@@ -6137,7 +5803,7 @@
         <f>'01_입력'!N91</f>
         <v>1980</v>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="26">
         <f>SUM(C23:N23)</f>
         <v>19220</v>
       </c>
@@ -6196,7 +5862,7 @@
         <f>CAPA_NOW*1000/12</f>
         <v>2183.33333333333</v>
       </c>
-      <c r="O24" s="27">
+      <c r="O24" s="26">
         <f>SUM(C24:N24)</f>
         <v>26200</v>
       </c>
@@ -6279,7 +5945,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O42"/>
+  <dimension ref="B1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -6309,7 +5975,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>PPT 연도별 표. 생산 = 1~4월 확정 + 월 Capa. (대정비 반영) · 출하·충진은 01_입력 · 08_후공정부하 연결.</t>
+          <t>PPT 연도별 표. 생산 = 1~4월 확정 + 월 Capa. (연간 ÷ 11) · 출하·충진은 01_입력 · 08_후공정부하 연결.</t>
         </is>
       </c>
     </row>
@@ -6415,7 +6081,7 @@
         <f>IF(MONTH(N$4)=MAINT_M,"대정비",IF(N$4&lt;RF_START,"정제기 1대",IF(N$4&gt;=T_105,"2대·105℃","정제기 2대")))</f>
         <v>정제기 2대</v>
       </c>
-      <c r="O5" s="27" t="inlineStr"/>
+      <c r="O5" s="26" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="29" t="inlineStr">
@@ -6441,39 +6107,39 @@
       </c>
       <c r="G6" s="22">
         <f>IF(MONTH(G$4)=MAINT_M,MAINT_KG,IF(G$4&gt;=T_105,CAPA_M105,IF(G$4&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="H6" s="22">
         <f>IF(MONTH(H$4)=MAINT_M,MAINT_KG,IF(H$4&gt;=T_105,CAPA_M105,IF(H$4&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="I6" s="22">
         <f>IF(MONTH(I$4)=MAINT_M,MAINT_KG,IF(I$4&gt;=T_105,CAPA_M105,IF(I$4&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="J6" s="22">
         <f>IF(MONTH(J$4)=MAINT_M,MAINT_KG,IF(J$4&gt;=T_105,CAPA_M105,IF(J$4&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="K6" s="22">
         <f>IF(MONTH(K$4)=MAINT_M,MAINT_KG,IF(K$4&gt;=T_105,CAPA_M105,IF(K$4&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="L6" s="22">
         <f>IF(MONTH(L$4)=MAINT_M,MAINT_KG,IF(L$4&gt;=T_105,CAPA_M105,IF(L$4&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="M6" s="22">
         <f>IF(MONTH(M$4)=MAINT_M,MAINT_KG,IF(M$4&gt;=T_105,CAPA_M105,IF(M$4&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4182.90909090909</v>
+        <v>4290.90909090909</v>
       </c>
       <c r="N6" s="22">
         <f>IF(MONTH(N$4)=MAINT_M,MAINT_KG,IF(N$4&gt;=T_105,CAPA_M105,IF(N$4&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="O6" s="27">
+        <v>4290.90909090909</v>
+      </c>
+      <c r="O6" s="26">
         <f>SUM(C6:N6)</f>
-        <v>42175.2727272727</v>
+        <v>43039.2727272727</v>
       </c>
     </row>
     <row r="7">
@@ -6500,452 +6166,452 @@
       </c>
       <c r="G7" s="32">
         <f>G6/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="H7" s="32">
         <f>H6/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="I7" s="32">
         <f>I6/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="J7" s="32">
         <f>J6/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="K7" s="32">
         <f>K6/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="L7" s="32">
         <f>L6/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="M7" s="32">
         <f>M6/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="N7" s="32">
         <f>N6/KG_B</f>
-        <v>22.0153110047847</v>
+        <v>22.5837320574163</v>
       </c>
       <c r="O7" s="35">
         <f>SUM(C7:N7)</f>
-        <v>221.975119617225</v>
+        <v>226.522488038278</v>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="10" t="inlineStr">
         <is>
+          <t>생산 − 출하</t>
+        </is>
+      </c>
+      <c r="C8" s="38">
+        <f>C6-C14</f>
+        <v>-575.333333333333</v>
+      </c>
+      <c r="D8" s="38">
+        <f>D6-D14</f>
+        <v>-575.333333333333</v>
+      </c>
+      <c r="E8" s="38">
+        <f>E6-E14</f>
+        <v>-165.333333333333</v>
+      </c>
+      <c r="F8" s="38">
+        <f>F6-F14</f>
+        <v>-2145.33333333333</v>
+      </c>
+      <c r="G8" s="38">
+        <f>G6-G14</f>
+        <v>957.575757575758</v>
+      </c>
+      <c r="H8" s="38">
+        <f>H6-H14</f>
+        <v>957.575757575758</v>
+      </c>
+      <c r="I8" s="38">
+        <f>I6-I14</f>
+        <v>477.575757575758</v>
+      </c>
+      <c r="J8" s="38">
+        <f>J6-J14</f>
+        <v>477.575757575758</v>
+      </c>
+      <c r="K8" s="38">
+        <f>K6-K14</f>
+        <v>477.575757575758</v>
+      </c>
+      <c r="L8" s="38">
+        <f>L6-L14</f>
+        <v>477.575757575758</v>
+      </c>
+      <c r="M8" s="38">
+        <f>M6-M14</f>
+        <v>477.575757575758</v>
+      </c>
+      <c r="N8" s="38">
+        <f>N6-N14</f>
+        <v>477.575757575758</v>
+      </c>
+      <c r="O8" s="40">
+        <f>SUM(C8:N8)</f>
+        <v>1319.27272727273</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>재고 (전월 재고 + 생산 − 출하)</t>
+        </is>
+      </c>
+      <c r="C9" s="40">
+        <f>N(INV_0)+C6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-C14</f>
+        <v>2306.66666666667</v>
+      </c>
+      <c r="D9" s="40">
+        <f>C9+D6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-D14</f>
+        <v>1731.33333333333</v>
+      </c>
+      <c r="E9" s="40">
+        <f>D9+E6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-E14</f>
+        <v>1566</v>
+      </c>
+      <c r="F9" s="40">
+        <f>E9+F6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-F14</f>
+        <v>-579.333333333332</v>
+      </c>
+      <c r="G9" s="40">
+        <f>F9+G6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-G14</f>
+        <v>378.242424242426</v>
+      </c>
+      <c r="H9" s="40">
+        <f>G9+H6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-H14</f>
+        <v>1335.81818181818</v>
+      </c>
+      <c r="I9" s="40">
+        <f>H9+I6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-I14</f>
+        <v>1813.39393939394</v>
+      </c>
+      <c r="J9" s="40">
+        <f>I9+J6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-J14</f>
+        <v>2290.9696969697</v>
+      </c>
+      <c r="K9" s="40">
+        <f>J9+K6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-K14</f>
+        <v>2768.54545454546</v>
+      </c>
+      <c r="L9" s="40">
+        <f>K9+L6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-L14</f>
+        <v>3246.12121212122</v>
+      </c>
+      <c r="M9" s="40">
+        <f>L9+M6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-M14</f>
+        <v>3723.69696969697</v>
+      </c>
+      <c r="N9" s="40">
+        <f>M9+N6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-N14</f>
+        <v>4201.27272727273</v>
+      </c>
+      <c r="O9" s="40">
+        <f>N9</f>
+        <v>4201.27272727273</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C8" s="40">
+      <c r="C10" s="41">
         <f>'01_입력'!$C$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D10" s="41">
         <f>'01_입력'!$D$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E10" s="41">
         <f>'01_입력'!$E$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F10" s="41">
         <f>'01_입력'!$F$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G10" s="41">
         <f>'01_입력'!$G$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="H8" s="40">
+      <c r="H10" s="41">
         <f>'01_입력'!$H$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="I8" s="40">
+      <c r="I10" s="41">
         <f>'01_입력'!$I$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="J8" s="40">
+      <c r="J10" s="41">
         <f>'01_입력'!$J$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="K8" s="40">
+      <c r="K10" s="41">
         <f>'01_입력'!$K$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="L8" s="40">
+      <c r="L10" s="41">
         <f>'01_입력'!$L$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="M8" s="40">
+      <c r="M10" s="41">
         <f>'01_입력'!$M$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N10" s="41">
         <f>'01_입력'!$N$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="O8" s="27">
-        <f>SUM(C8:N8)</f>
+      <c r="O10" s="26">
+        <f>SUM(C10:N10)</f>
         <v>22720</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="10" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>CXMT</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C11" s="21">
         <f>'01_입력'!$C$95</f>
         <v>0</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D11" s="21">
         <f>'01_입력'!$D$95</f>
         <v>0</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E11" s="21">
         <f>'01_입력'!$E$95</f>
         <v>580</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F11" s="21">
         <f>'01_입력'!$F$95</f>
         <v>580</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G11" s="21">
         <f>'01_입력'!$G$95</f>
         <v>580</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H11" s="21">
         <f>'01_입력'!$H$95</f>
         <v>580</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I11" s="21">
         <f>'01_입력'!$I$95</f>
         <v>780</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J11" s="21">
         <f>'01_입력'!$J$95</f>
         <v>780</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K11" s="21">
         <f>'01_입력'!$K$95</f>
         <v>780</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L11" s="21">
         <f>'01_입력'!$L$95</f>
         <v>780</v>
       </c>
-      <c r="M9" s="21">
+      <c r="M11" s="21">
         <f>'01_입력'!$M$95</f>
         <v>780</v>
       </c>
-      <c r="N9" s="21">
+      <c r="N11" s="21">
         <f>'01_입력'!$N$95</f>
         <v>780</v>
       </c>
-      <c r="O9" s="27">
-        <f>SUM(C9:N9)</f>
+      <c r="O11" s="26">
+        <f>SUM(C11:N11)</f>
         <v>7000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="10" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>이지켐</t>
         </is>
       </c>
-      <c r="C10" s="21">
+      <c r="C12" s="21">
         <f>'01_입력'!$C$96</f>
         <v>560</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D12" s="21">
         <f>'01_입력'!$D$96</f>
         <v>560</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E12" s="21">
         <f>'01_입력'!$E$96</f>
         <v>560</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F12" s="21">
         <f>'01_입력'!$F$96</f>
         <v>560</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G12" s="21">
         <f>'01_입력'!$G$96</f>
         <v>560</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H12" s="21">
         <f>'01_입력'!$H$96</f>
         <v>560</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I12" s="21">
         <f>'01_입력'!$I$96</f>
-        <v>1120</v>
-      </c>
-      <c r="J10" s="21">
+        <v>840</v>
+      </c>
+      <c r="J12" s="21">
         <f>'01_입력'!$J$96</f>
-        <v>1120</v>
-      </c>
-      <c r="K10" s="21">
+        <v>840</v>
+      </c>
+      <c r="K12" s="21">
         <f>'01_입력'!$K$96</f>
-        <v>1120</v>
-      </c>
-      <c r="L10" s="21">
+        <v>840</v>
+      </c>
+      <c r="L12" s="21">
         <f>'01_입력'!$L$96</f>
-        <v>1120</v>
-      </c>
-      <c r="M10" s="21">
+        <v>840</v>
+      </c>
+      <c r="M12" s="21">
         <f>'01_입력'!$M$96</f>
-        <v>1120</v>
-      </c>
-      <c r="N10" s="21">
+        <v>840</v>
+      </c>
+      <c r="N12" s="21">
         <f>'01_입력'!$N$96</f>
-        <v>1120</v>
-      </c>
-      <c r="O10" s="27">
-        <f>SUM(C10:N10)</f>
-        <v>10080</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="10" t="inlineStr">
+        <v>840</v>
+      </c>
+      <c r="O12" s="26">
+        <f>SUM(C12:N12)</f>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>한솔</t>
         </is>
       </c>
-      <c r="C11" s="21">
+      <c r="C13" s="21">
         <f>'01_입력'!$C$97</f>
         <v>300</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D13" s="21">
         <f>'01_입력'!$D$97</f>
         <v>300</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E13" s="21">
         <f>'01_입력'!$E$97</f>
         <v>300</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F13" s="21">
         <f>'01_입력'!$F$97</f>
         <v>300</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G13" s="21">
         <f>'01_입력'!$G$97</f>
         <v>300</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H13" s="21">
         <f>'01_입력'!$H$97</f>
         <v>300</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I13" s="21">
         <f>'01_입력'!$I$97</f>
         <v>300</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J13" s="21">
         <f>'01_입력'!$J$97</f>
         <v>300</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K13" s="21">
         <f>'01_입력'!$K$97</f>
         <v>300</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L13" s="21">
         <f>'01_입력'!$L$97</f>
         <v>300</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M13" s="21">
         <f>'01_입력'!$M$97</f>
         <v>300</v>
       </c>
-      <c r="N11" s="21">
+      <c r="N13" s="21">
         <f>'01_입력'!$N$97</f>
         <v>300</v>
       </c>
-      <c r="O11" s="27">
-        <f>SUM(C11:N11)</f>
+      <c r="O13" s="26">
+        <f>SUM(C13:N13)</f>
         <v>3600</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>출하 합계</t>
-        </is>
-      </c>
-      <c r="C12" s="40">
-        <f>SUM(C8:C11)</f>
-        <v>2753.33333333333</v>
-      </c>
-      <c r="D12" s="40">
-        <f>SUM(D8:D11)</f>
-        <v>2753.33333333333</v>
-      </c>
-      <c r="E12" s="40">
-        <f>SUM(E8:E11)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="F12" s="40">
-        <f>SUM(F8:F11)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="G12" s="40">
-        <f>SUM(G8:G11)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="H12" s="40">
-        <f>SUM(H8:H11)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="I12" s="40">
-        <f>SUM(I8:I11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="J12" s="40">
-        <f>SUM(J8:J11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="K12" s="40">
-        <f>SUM(K8:K11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="L12" s="40">
-        <f>SUM(L8:L11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="M12" s="40">
-        <f>SUM(M8:M11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="N12" s="40">
-        <f>SUM(N8:N11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="O12" s="27">
-        <f>SUM(C12:N12)</f>
-        <v>43400</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>생산 − 출하</t>
-        </is>
-      </c>
-      <c r="C13" s="38">
-        <f>C6-C12</f>
-        <v>-575.333333333333</v>
-      </c>
-      <c r="D13" s="38">
-        <f>D6-D12</f>
-        <v>-575.333333333333</v>
-      </c>
-      <c r="E13" s="38">
-        <f>E6-E12</f>
-        <v>-165.333333333333</v>
-      </c>
-      <c r="F13" s="38">
-        <f>F6-F12</f>
-        <v>-2145.33333333333</v>
-      </c>
-      <c r="G13" s="38">
-        <f>G6-G12</f>
-        <v>849.575757575758</v>
-      </c>
-      <c r="H13" s="38">
-        <f>H6-H12</f>
-        <v>849.575757575758</v>
-      </c>
-      <c r="I13" s="38">
-        <f>I6-I12</f>
-        <v>89.575757575758</v>
-      </c>
-      <c r="J13" s="38">
-        <f>J6-J12</f>
-        <v>89.575757575758</v>
-      </c>
-      <c r="K13" s="38">
-        <f>K6-K12</f>
-        <v>89.575757575758</v>
-      </c>
-      <c r="L13" s="38">
-        <f>L6-L12</f>
-        <v>89.575757575758</v>
-      </c>
-      <c r="M13" s="38">
-        <f>M6-M12</f>
-        <v>89.575757575758</v>
-      </c>
-      <c r="N13" s="38">
-        <f>N6-N12</f>
-        <v>89.575757575758</v>
-      </c>
-      <c r="O13" s="41">
-        <f>SUM(C13:N13)</f>
-        <v>-1224.72727272727</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>누적 (생산 − 출하)</t>
+          <t>출하 합계</t>
         </is>
       </c>
       <c r="C14" s="41">
-        <f>C13</f>
-        <v>-575.333333333333</v>
+        <f>SUM(C10:C13)</f>
+        <v>2753.33333333333</v>
       </c>
       <c r="D14" s="41">
-        <f>D13+C14</f>
-        <v>-1150.66666666667</v>
+        <f>SUM(D10:D13)</f>
+        <v>2753.33333333333</v>
       </c>
       <c r="E14" s="41">
-        <f>E13+D14</f>
-        <v>-1316</v>
+        <f>SUM(E10:E13)</f>
+        <v>3333.33333333333</v>
       </c>
       <c r="F14" s="41">
-        <f>F13+E14</f>
-        <v>-3461.33333333333</v>
+        <f>SUM(F10:F13)</f>
+        <v>3333.33333333333</v>
       </c>
       <c r="G14" s="41">
-        <f>G13+F14</f>
-        <v>-2611.75757575757</v>
+        <f>SUM(G10:G13)</f>
+        <v>3333.33333333333</v>
       </c>
       <c r="H14" s="41">
-        <f>H13+G14</f>
-        <v>-1762.18181818182</v>
+        <f>SUM(H10:H13)</f>
+        <v>3333.33333333333</v>
       </c>
       <c r="I14" s="41">
-        <f>I13+H14</f>
-        <v>-1672.60606060606</v>
+        <f>SUM(I10:I13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="J14" s="41">
-        <f>J13+I14</f>
-        <v>-1583.0303030303</v>
+        <f>SUM(J10:J13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="K14" s="41">
-        <f>K13+J14</f>
-        <v>-1493.45454545454</v>
+        <f>SUM(K10:K13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="L14" s="41">
-        <f>L13+K14</f>
-        <v>-1403.87878787878</v>
+        <f>SUM(L10:L13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="M14" s="41">
-        <f>M13+L14</f>
-        <v>-1314.30303030303</v>
+        <f>SUM(M10:M13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="N14" s="41">
-        <f>N13+M14</f>
-        <v>-1224.72727272727</v>
-      </c>
-      <c r="O14" s="41">
-        <f>N14</f>
-        <v>-1224.72727272727</v>
+        <f>SUM(N10:N13)</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="O14" s="26">
+        <f>SUM(C14:N14)</f>
+        <v>41720</v>
       </c>
     </row>
     <row r="15">
@@ -6955,1104 +6621,1106 @@
         </is>
       </c>
       <c r="C15" s="32">
-        <f>C12/KG_B</f>
+        <f>C14/KG_B</f>
         <v>14.4912280701754</v>
       </c>
       <c r="D15" s="32">
-        <f>D12/KG_B</f>
+        <f>D14/KG_B</f>
         <v>14.4912280701754</v>
       </c>
       <c r="E15" s="32">
-        <f>E12/KG_B</f>
+        <f>E14/KG_B</f>
         <v>17.5438596491228</v>
       </c>
       <c r="F15" s="32">
-        <f>F12/KG_B</f>
+        <f>F14/KG_B</f>
         <v>17.5438596491228</v>
       </c>
       <c r="G15" s="32">
-        <f>G12/KG_B</f>
+        <f>G14/KG_B</f>
         <v>17.5438596491228</v>
       </c>
       <c r="H15" s="32">
-        <f>H12/KG_B</f>
+        <f>H14/KG_B</f>
         <v>17.5438596491228</v>
       </c>
       <c r="I15" s="32">
-        <f>I12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>I14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="J15" s="32">
-        <f>J12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>J14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="K15" s="32">
-        <f>K12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>K14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="L15" s="32">
-        <f>L12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>L14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="M15" s="32">
-        <f>M12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>M14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="N15" s="32">
-        <f>N12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>N14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="O15" s="35">
         <f>SUM(C15:N15)</f>
-        <v>228.421052631579</v>
+        <v>219.578947368421</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="10" t="inlineStr">
         <is>
+          <t>200 L 충진 방식 (이지켐/한솔)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="str">
+        <f>'08_후공정부하'!C30&amp;"/"&amp;'08_후공정부하'!C33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="D16" s="5" t="str">
+        <f>'08_후공정부하'!D30&amp;"/"&amp;'08_후공정부하'!D33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="E16" s="5" t="str">
+        <f>'08_후공정부하'!E30&amp;"/"&amp;'08_후공정부하'!E33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="F16" s="5" t="str">
+        <f>'08_후공정부하'!F30&amp;"/"&amp;'08_후공정부하'!F33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="G16" s="5" t="str">
+        <f>'08_후공정부하'!G30&amp;"/"&amp;'08_후공정부하'!G33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="H16" s="5" t="str">
+        <f>'08_후공정부하'!H30&amp;"/"&amp;'08_후공정부하'!H33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="I16" s="5" t="str">
+        <f>'08_후공정부하'!I30&amp;"/"&amp;'08_후공정부하'!I33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="J16" s="5" t="str">
+        <f>'08_후공정부하'!J30&amp;"/"&amp;'08_후공정부하'!J33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="K16" s="5" t="str">
+        <f>'08_후공정부하'!K30&amp;"/"&amp;'08_후공정부하'!K33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="L16" s="5" t="str">
+        <f>'08_후공정부하'!L30&amp;"/"&amp;'08_후공정부하'!L33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="M16" s="5" t="str">
+        <f>'08_후공정부하'!M30&amp;"/"&amp;'08_후공정부하'!M33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="N16" s="5" t="str">
+        <f>'08_후공정부하'!N30&amp;"/"&amp;'08_후공정부하'!N33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="O16" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
           <t>5 Gal 충진 h</t>
         </is>
       </c>
-      <c r="C16" s="17">
+      <c r="C17" s="17">
         <f>'08_후공정부하'!C25</f>
         <v>189.333333333333</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D17" s="17">
         <f>'08_후공정부하'!D25</f>
         <v>189.333333333333</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E17" s="17">
         <f>'08_후공정부하'!E25</f>
         <v>247.333333333333</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F17" s="17">
         <f>'08_후공정부하'!F25</f>
         <v>247.333333333333</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G17" s="17">
         <f>'08_후공정부하'!G25</f>
         <v>247.333333333333</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H17" s="17">
         <f>'08_후공정부하'!H25</f>
         <v>247.333333333333</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I17" s="17">
         <f>'08_후공정부하'!I25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J17" s="17">
         <f>'08_후공정부하'!J25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K17" s="17">
         <f>'08_후공정부하'!K25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L17" s="17">
         <f>'08_후공정부하'!L25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M17" s="17">
         <f>'08_후공정부하'!M25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N17" s="17">
         <f>'08_후공정부하'!N25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="O16" s="13">
-        <f>SUM(C16:N16)</f>
+      <c r="O17" s="13">
+        <f>SUM(C17:N17)</f>
         <v>2972</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="10" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>200 L 충진 h</t>
         </is>
       </c>
-      <c r="C17" s="17">
+      <c r="C18" s="17">
         <f>'08_후공정부하'!C35</f>
         <v>48</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D18" s="17">
         <f>'08_후공정부하'!D35</f>
         <v>48</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E18" s="17">
         <f>'08_후공정부하'!E35</f>
         <v>48</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F18" s="17">
         <f>'08_후공정부하'!F35</f>
         <v>48</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G18" s="17">
         <f>'08_후공정부하'!G35</f>
         <v>48</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H18" s="17">
         <f>'08_후공정부하'!H35</f>
         <v>48</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I18" s="17">
         <f>'08_후공정부하'!I35</f>
-        <v>80</v>
-      </c>
-      <c r="J17" s="17">
+        <v>64</v>
+      </c>
+      <c r="J18" s="17">
         <f>'08_후공정부하'!J35</f>
-        <v>80</v>
-      </c>
-      <c r="K17" s="17">
+        <v>64</v>
+      </c>
+      <c r="K18" s="17">
         <f>'08_후공정부하'!K35</f>
-        <v>80</v>
-      </c>
-      <c r="L17" s="17">
+        <v>64</v>
+      </c>
+      <c r="L18" s="17">
         <f>'08_후공정부하'!L35</f>
-        <v>80</v>
-      </c>
-      <c r="M17" s="17">
+        <v>64</v>
+      </c>
+      <c r="M18" s="17">
         <f>'08_후공정부하'!M35</f>
-        <v>80</v>
-      </c>
-      <c r="N17" s="17">
+        <v>64</v>
+      </c>
+      <c r="N18" s="17">
         <f>'08_후공정부하'!N35</f>
-        <v>80</v>
-      </c>
-      <c r="O17" s="13">
-        <f>SUM(C17:N17)</f>
-        <v>768</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="10" t="inlineStr">
+        <v>64</v>
+      </c>
+      <c r="O18" s="13">
+        <f>SUM(C18:N18)</f>
+        <v>672</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>이지켐 용기</t>
         </is>
       </c>
-      <c r="C18" s="32">
+      <c r="C19" s="32">
         <f>'08_후공정부하'!C29</f>
         <v>4</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D19" s="32">
         <f>'08_후공정부하'!D29</f>
         <v>4</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E19" s="32">
         <f>'08_후공정부하'!E29</f>
         <v>4</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F19" s="32">
         <f>'08_후공정부하'!F29</f>
         <v>4</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G19" s="32">
         <f>'08_후공정부하'!G29</f>
         <v>4</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H19" s="32">
         <f>'08_후공정부하'!H29</f>
         <v>4</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I19" s="32">
         <f>'08_후공정부하'!I29</f>
-        <v>8</v>
-      </c>
-      <c r="J18" s="32">
+        <v>6</v>
+      </c>
+      <c r="J19" s="32">
         <f>'08_후공정부하'!J29</f>
-        <v>8</v>
-      </c>
-      <c r="K18" s="32">
+        <v>6</v>
+      </c>
+      <c r="K19" s="32">
         <f>'08_후공정부하'!K29</f>
-        <v>8</v>
-      </c>
-      <c r="L18" s="32">
+        <v>6</v>
+      </c>
+      <c r="L19" s="32">
         <f>'08_후공정부하'!L29</f>
-        <v>8</v>
-      </c>
-      <c r="M18" s="32">
+        <v>6</v>
+      </c>
+      <c r="M19" s="32">
         <f>'08_후공정부하'!M29</f>
-        <v>8</v>
-      </c>
-      <c r="N18" s="32">
+        <v>6</v>
+      </c>
+      <c r="N19" s="32">
         <f>'08_후공정부하'!N29</f>
-        <v>8</v>
-      </c>
-      <c r="O18" s="35">
-        <f>SUM(C18:N18)</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="O19" s="35">
+        <f>SUM(C19:N19)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>한솔 용기</t>
         </is>
       </c>
-      <c r="C19" s="32">
+      <c r="C20" s="32">
         <f>'08_후공정부하'!C32</f>
         <v>2</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D20" s="32">
         <f>'08_후공정부하'!D32</f>
         <v>2</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E20" s="32">
         <f>'08_후공정부하'!E32</f>
         <v>2</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F20" s="32">
         <f>'08_후공정부하'!F32</f>
         <v>2</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G20" s="32">
         <f>'08_후공정부하'!G32</f>
         <v>2</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H20" s="32">
         <f>'08_후공정부하'!H32</f>
         <v>2</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I20" s="32">
         <f>'08_후공정부하'!I32</f>
         <v>2</v>
       </c>
-      <c r="J19" s="32">
+      <c r="J20" s="32">
         <f>'08_후공정부하'!J32</f>
         <v>2</v>
       </c>
-      <c r="K19" s="32">
+      <c r="K20" s="32">
         <f>'08_후공정부하'!K32</f>
         <v>2</v>
       </c>
-      <c r="L19" s="32">
+      <c r="L20" s="32">
         <f>'08_후공정부하'!L32</f>
         <v>2</v>
       </c>
-      <c r="M19" s="32">
+      <c r="M20" s="32">
         <f>'08_후공정부하'!M32</f>
         <v>2</v>
       </c>
-      <c r="N19" s="32">
+      <c r="N20" s="32">
         <f>'08_후공정부하'!N32</f>
         <v>2</v>
       </c>
-      <c r="O19" s="35">
-        <f>SUM(C19:N19)</f>
+      <c r="O20" s="35">
+        <f>SUM(C20:N20)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>양품 생산 (양품률 입력 시)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),C6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),D6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),E6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),F6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),G6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),H6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),I6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),J6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),K6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),L6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="M20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),M6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),N6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="O20" s="27" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),SUM(C20:N20),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>기말재고 (기초재고·양품률 입력 시)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(INV_0),ISNUMBER(C20)),INV_0+C20-C12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(C21),ISNUMBER(D20)),C21+D20-D12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(D21),ISNUMBER(E20)),D21+E20-E12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(E21),ISNUMBER(F20)),E21+F20-F12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(F21),ISNUMBER(G20)),F21+G20-G12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(G21),ISNUMBER(H20)),G21+H20-H12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(H21),ISNUMBER(I20)),H21+I20-I12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(I21),ISNUMBER(J20)),I21+J20-J12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(J21),ISNUMBER(K20)),J21+K20-K12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(K21),ISNUMBER(L20)),K21+L20-L12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="M21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(L21),ISNUMBER(M20)),L21+M20-M12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(M21),ISNUMBER(N20)),M21+N20-N12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="O21" s="27" t="str">
-        <f>N21</f>
-        <v>-</v>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>46753</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>46784</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>46813</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <v>46844</v>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>46874</v>
+      </c>
+      <c r="H22" s="25" t="n">
+        <v>46905</v>
+      </c>
+      <c r="I22" s="25" t="n">
+        <v>46935</v>
+      </c>
+      <c r="J22" s="25" t="n">
+        <v>46966</v>
+      </c>
+      <c r="K22" s="25" t="n">
+        <v>46997</v>
+      </c>
+      <c r="L22" s="25" t="n">
+        <v>47027</v>
+      </c>
+      <c r="M22" s="25" t="n">
+        <v>47058</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>47088</v>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>연간</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="n">
-        <v>46753</v>
-      </c>
-      <c r="D23" s="25" t="n">
-        <v>46784</v>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>46813</v>
-      </c>
-      <c r="F23" s="25" t="n">
-        <v>46844</v>
-      </c>
-      <c r="G23" s="25" t="n">
-        <v>46874</v>
-      </c>
-      <c r="H23" s="25" t="n">
-        <v>46905</v>
-      </c>
-      <c r="I23" s="25" t="n">
-        <v>46935</v>
-      </c>
-      <c r="J23" s="25" t="n">
-        <v>46966</v>
-      </c>
-      <c r="K23" s="25" t="n">
-        <v>46997</v>
-      </c>
-      <c r="L23" s="25" t="n">
-        <v>47027</v>
-      </c>
-      <c r="M23" s="25" t="n">
-        <v>47058</v>
-      </c>
-      <c r="N23" s="25" t="n">
-        <v>47088</v>
-      </c>
-      <c r="O23" s="9" t="inlineStr">
-        <is>
-          <t>연간</t>
-        </is>
-      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>운전 조건</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="str">
+        <f>IF(MONTH(C$22)=MAINT_M,"대정비",IF(C$22&lt;RF_START,"정제기 1대",IF(C$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="D23" s="5" t="str">
+        <f>IF(MONTH(D$22)=MAINT_M,"대정비",IF(D$22&lt;RF_START,"정제기 1대",IF(D$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="E23" s="5" t="str">
+        <f>IF(MONTH(E$22)=MAINT_M,"대정비",IF(E$22&lt;RF_START,"정제기 1대",IF(E$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="F23" s="5" t="str">
+        <f>IF(MONTH(F$22)=MAINT_M,"대정비",IF(F$22&lt;RF_START,"정제기 1대",IF(F$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>대정비</v>
+      </c>
+      <c r="G23" s="5" t="str">
+        <f>IF(MONTH(G$22)=MAINT_M,"대정비",IF(G$22&lt;RF_START,"정제기 1대",IF(G$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="H23" s="5" t="str">
+        <f>IF(MONTH(H$22)=MAINT_M,"대정비",IF(H$22&lt;RF_START,"정제기 1대",IF(H$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="I23" s="5" t="str">
+        <f>IF(MONTH(I$22)=MAINT_M,"대정비",IF(I$22&lt;RF_START,"정제기 1대",IF(I$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="J23" s="5" t="str">
+        <f>IF(MONTH(J$22)=MAINT_M,"대정비",IF(J$22&lt;RF_START,"정제기 1대",IF(J$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="K23" s="5" t="str">
+        <f>IF(MONTH(K$22)=MAINT_M,"대정비",IF(K$22&lt;RF_START,"정제기 1대",IF(K$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="L23" s="5" t="str">
+        <f>IF(MONTH(L$22)=MAINT_M,"대정비",IF(L$22&lt;RF_START,"정제기 1대",IF(L$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="M23" s="5" t="str">
+        <f>IF(MONTH(M$22)=MAINT_M,"대정비",IF(M$22&lt;RF_START,"정제기 1대",IF(M$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="N23" s="5" t="str">
+        <f>IF(MONTH(N$22)=MAINT_M,"대정비",IF(N$22&lt;RF_START,"정제기 1대",IF(N$22&gt;=T_105,"2대·105℃","정제기 2대")))</f>
+        <v>2대·105℃</v>
+      </c>
+      <c r="O23" s="26" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>운전 조건</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="str">
-        <f>IF(MONTH(C$23)=MAINT_M,"대정비",IF(C$23&lt;RF_START,"정제기 1대",IF(C$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="D24" s="5" t="str">
-        <f>IF(MONTH(D$23)=MAINT_M,"대정비",IF(D$23&lt;RF_START,"정제기 1대",IF(D$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="E24" s="5" t="str">
-        <f>IF(MONTH(E$23)=MAINT_M,"대정비",IF(E$23&lt;RF_START,"정제기 1대",IF(E$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="F24" s="5" t="str">
-        <f>IF(MONTH(F$23)=MAINT_M,"대정비",IF(F$23&lt;RF_START,"정제기 1대",IF(F$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>대정비</v>
-      </c>
-      <c r="G24" s="5" t="str">
-        <f>IF(MONTH(G$23)=MAINT_M,"대정비",IF(G$23&lt;RF_START,"정제기 1대",IF(G$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="H24" s="5" t="str">
-        <f>IF(MONTH(H$23)=MAINT_M,"대정비",IF(H$23&lt;RF_START,"정제기 1대",IF(H$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="I24" s="5" t="str">
-        <f>IF(MONTH(I$23)=MAINT_M,"대정비",IF(I$23&lt;RF_START,"정제기 1대",IF(I$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="J24" s="5" t="str">
-        <f>IF(MONTH(J$23)=MAINT_M,"대정비",IF(J$23&lt;RF_START,"정제기 1대",IF(J$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="K24" s="5" t="str">
-        <f>IF(MONTH(K$23)=MAINT_M,"대정비",IF(K$23&lt;RF_START,"정제기 1대",IF(K$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="L24" s="5" t="str">
-        <f>IF(MONTH(L$23)=MAINT_M,"대정비",IF(L$23&lt;RF_START,"정제기 1대",IF(L$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="M24" s="5" t="str">
-        <f>IF(MONTH(M$23)=MAINT_M,"대정비",IF(M$23&lt;RF_START,"정제기 1대",IF(M$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="N24" s="5" t="str">
-        <f>IF(MONTH(N$23)=MAINT_M,"대정비",IF(N$23&lt;RF_START,"정제기 1대",IF(N$23&gt;=T_105,"2대·105℃","정제기 2대")))</f>
-        <v>2대·105℃</v>
-      </c>
-      <c r="O24" s="27" t="inlineStr"/>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>생산 (kg)</t>
+        </is>
+      </c>
+      <c r="C24" s="22">
+        <f>IF(MONTH(C$22)=MAINT_M,MAINT_KG,IF(C$22&gt;=T_105,CAPA_M105,IF(C$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="D24" s="22">
+        <f>IF(MONTH(D$22)=MAINT_M,MAINT_KG,IF(D$22&gt;=T_105,CAPA_M105,IF(D$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="E24" s="22">
+        <f>IF(MONTH(E$22)=MAINT_M,MAINT_KG,IF(E$22&gt;=T_105,CAPA_M105,IF(E$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="F24" s="22">
+        <f>IF(MONTH(F$22)=MAINT_M,MAINT_KG,IF(F$22&gt;=T_105,CAPA_M105,IF(F$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>1188</v>
+      </c>
+      <c r="G24" s="22">
+        <f>IF(MONTH(G$22)=MAINT_M,MAINT_KG,IF(G$22&gt;=T_105,CAPA_M105,IF(G$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="H24" s="22">
+        <f>IF(MONTH(H$22)=MAINT_M,MAINT_KG,IF(H$22&gt;=T_105,CAPA_M105,IF(H$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="I24" s="22">
+        <f>IF(MONTH(I$22)=MAINT_M,MAINT_KG,IF(I$22&gt;=T_105,CAPA_M105,IF(I$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="J24" s="22">
+        <f>IF(MONTH(J$22)=MAINT_M,MAINT_KG,IF(J$22&gt;=T_105,CAPA_M105,IF(J$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="K24" s="22">
+        <f>IF(MONTH(K$22)=MAINT_M,MAINT_KG,IF(K$22&gt;=T_105,CAPA_M105,IF(K$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="L24" s="22">
+        <f>IF(MONTH(L$22)=MAINT_M,MAINT_KG,IF(L$22&gt;=T_105,CAPA_M105,IF(L$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="M24" s="22">
+        <f>IF(MONTH(M$22)=MAINT_M,MAINT_KG,IF(M$22&gt;=T_105,CAPA_M105,IF(M$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="N24" s="22">
+        <f>IF(MONTH(N$22)=MAINT_M,MAINT_KG,IF(N$22&gt;=T_105,CAPA_M105,IF(N$22&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="O24" s="26">
+        <f>SUM(C24:N24)</f>
+        <v>51388</v>
+      </c>
     </row>
     <row r="25">
-      <c r="B25" s="29" t="inlineStr">
-        <is>
-          <t>생산 (kg)</t>
-        </is>
-      </c>
-      <c r="C25" s="22">
-        <f>IF(MONTH(C$23)=MAINT_M,MAINT_KG,IF(C$23&gt;=T_105,CAPA_M105,IF(C$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="D25" s="22">
-        <f>IF(MONTH(D$23)=MAINT_M,MAINT_KG,IF(D$23&gt;=T_105,CAPA_M105,IF(D$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="E25" s="22">
-        <f>IF(MONTH(E$23)=MAINT_M,MAINT_KG,IF(E$23&gt;=T_105,CAPA_M105,IF(E$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="F25" s="22">
-        <f>IF(MONTH(F$23)=MAINT_M,MAINT_KG,IF(F$23&gt;=T_105,CAPA_M105,IF(F$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>1188</v>
-      </c>
-      <c r="G25" s="22">
-        <f>IF(MONTH(G$23)=MAINT_M,MAINT_KG,IF(G$23&gt;=T_105,CAPA_M105,IF(G$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="H25" s="22">
-        <f>IF(MONTH(H$23)=MAINT_M,MAINT_KG,IF(H$23&gt;=T_105,CAPA_M105,IF(H$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="I25" s="22">
-        <f>IF(MONTH(I$23)=MAINT_M,MAINT_KG,IF(I$23&gt;=T_105,CAPA_M105,IF(I$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="J25" s="22">
-        <f>IF(MONTH(J$23)=MAINT_M,MAINT_KG,IF(J$23&gt;=T_105,CAPA_M105,IF(J$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="K25" s="22">
-        <f>IF(MONTH(K$23)=MAINT_M,MAINT_KG,IF(K$23&gt;=T_105,CAPA_M105,IF(K$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="L25" s="22">
-        <f>IF(MONTH(L$23)=MAINT_M,MAINT_KG,IF(L$23&gt;=T_105,CAPA_M105,IF(L$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="M25" s="22">
-        <f>IF(MONTH(M$23)=MAINT_M,MAINT_KG,IF(M$23&gt;=T_105,CAPA_M105,IF(M$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="N25" s="22">
-        <f>IF(MONTH(N$23)=MAINT_M,MAINT_KG,IF(N$23&gt;=T_105,CAPA_M105,IF(N$23&gt;=RF_START,CAPA_M,CAPA_NOW*1000/12)))</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="O25" s="27">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Batch 환산 (÷190)</t>
+        </is>
+      </c>
+      <c r="C25" s="32">
+        <f>C24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="D25" s="32">
+        <f>D24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="E25" s="32">
+        <f>E24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="F25" s="32">
+        <f>F24/KG_B</f>
+        <v>6.25263157894737</v>
+      </c>
+      <c r="G25" s="32">
+        <f>G24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="H25" s="32">
+        <f>H24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="I25" s="32">
+        <f>I24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="J25" s="32">
+        <f>J24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="K25" s="32">
+        <f>K24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="L25" s="32">
+        <f>L24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="M25" s="32">
+        <f>M24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="N25" s="32">
+        <f>N24/KG_B</f>
+        <v>24.0191387559809</v>
+      </c>
+      <c r="O25" s="35">
         <f>SUM(C25:N25)</f>
-        <v>50200</v>
+        <v>270.463157894737</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Batch 환산 (÷190)</t>
-        </is>
-      </c>
-      <c r="C26" s="32">
-        <f>C25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="D26" s="32">
-        <f>D25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="E26" s="32">
-        <f>E25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="F26" s="32">
-        <f>F25/KG_B</f>
-        <v>6.25263157894737</v>
-      </c>
-      <c r="G26" s="32">
-        <f>G25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="H26" s="32">
-        <f>H25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="I26" s="32">
-        <f>I25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="J26" s="32">
-        <f>J25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="K26" s="32">
-        <f>K25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="L26" s="32">
-        <f>L25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="M26" s="32">
-        <f>M25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="N26" s="32">
-        <f>N25/KG_B</f>
-        <v>23.4507177033493</v>
-      </c>
-      <c r="O26" s="35">
+          <t>생산 − 출하</t>
+        </is>
+      </c>
+      <c r="C26" s="38">
+        <f>C24-C32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="D26" s="38">
+        <f>D24-D32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="E26" s="38">
+        <f>E24-E32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="F26" s="38">
+        <f>F24-F32</f>
+        <v>-2625.33333333333</v>
+      </c>
+      <c r="G26" s="38">
+        <f>G24-G32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="H26" s="38">
+        <f>H24-H32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="I26" s="38">
+        <f>I24-I32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="J26" s="38">
+        <f>J24-J32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="K26" s="38">
+        <f>K24-K32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="L26" s="38">
+        <f>L24-L32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="M26" s="38">
+        <f>M24-M32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="N26" s="38">
+        <f>N24-N32</f>
+        <v>750.303030303031</v>
+      </c>
+      <c r="O26" s="40">
         <f>SUM(C26:N26)</f>
-        <v>264.21052631579</v>
+        <v>5628.00000000001</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>재고 (전월 재고 + 생산 − 출하)</t>
+        </is>
+      </c>
+      <c r="C27" s="40">
+        <f>N9+C24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-C32</f>
+        <v>4951.57575757576</v>
+      </c>
+      <c r="D27" s="40">
+        <f>C27+D24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-D32</f>
+        <v>5701.87878787879</v>
+      </c>
+      <c r="E27" s="40">
+        <f>D27+E24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-E32</f>
+        <v>6452.18181818183</v>
+      </c>
+      <c r="F27" s="40">
+        <f>E27+F24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-F32</f>
+        <v>3826.84848484849</v>
+      </c>
+      <c r="G27" s="40">
+        <f>F27+G24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-G32</f>
+        <v>4577.15151515152</v>
+      </c>
+      <c r="H27" s="40">
+        <f>G27+H24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-H32</f>
+        <v>5327.45454545455</v>
+      </c>
+      <c r="I27" s="40">
+        <f>H27+I24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-I32</f>
+        <v>6077.75757575759</v>
+      </c>
+      <c r="J27" s="40">
+        <f>I27+J24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-J32</f>
+        <v>6828.06060606062</v>
+      </c>
+      <c r="K27" s="40">
+        <f>J27+K24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-K32</f>
+        <v>7578.36363636365</v>
+      </c>
+      <c r="L27" s="40">
+        <f>K27+L24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-L32</f>
+        <v>8328.66666666668</v>
+      </c>
+      <c r="M27" s="40">
+        <f>L27+M24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-M32</f>
+        <v>9078.96969696971</v>
+      </c>
+      <c r="N27" s="40">
+        <f>M27+N24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-N32</f>
+        <v>9829.27272727275</v>
+      </c>
+      <c r="O27" s="40">
+        <f>N27</f>
+        <v>9829.27272727275</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C27" s="40">
+      <c r="C28" s="41">
         <f>'01_입력'!$C$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D28" s="41">
         <f>'01_입력'!$D$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="E27" s="40">
+      <c r="E28" s="41">
         <f>'01_입력'!$E$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="F27" s="40">
+      <c r="F28" s="41">
         <f>'01_입력'!$F$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="G27" s="40">
+      <c r="G28" s="41">
         <f>'01_입력'!$G$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="H27" s="40">
+      <c r="H28" s="41">
         <f>'01_입력'!$H$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I28" s="41">
         <f>'01_입력'!$I$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="J27" s="40">
+      <c r="J28" s="41">
         <f>'01_입력'!$J$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="K27" s="40">
+      <c r="K28" s="41">
         <f>'01_입력'!$K$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="L27" s="40">
+      <c r="L28" s="41">
         <f>'01_입력'!$L$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="M27" s="40">
+      <c r="M28" s="41">
         <f>'01_입력'!$M$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="N27" s="40">
+      <c r="N28" s="41">
         <f>'01_입력'!$N$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="O27" s="27">
-        <f>SUM(C27:N27)</f>
+      <c r="O28" s="26">
+        <f>SUM(C28:N28)</f>
         <v>22720</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="10" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>CXMT</t>
         </is>
       </c>
-      <c r="C28" s="21">
+      <c r="C29" s="21">
         <f>'01_입력'!$C$102</f>
         <v>780</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D29" s="21">
         <f>'01_입력'!$D$102</f>
         <v>780</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E29" s="21">
         <f>'01_입력'!$E$102</f>
         <v>780</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F29" s="21">
         <f>'01_입력'!$F$102</f>
         <v>780</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G29" s="21">
         <f>'01_입력'!$G$102</f>
         <v>780</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H29" s="21">
         <f>'01_입력'!$H$102</f>
         <v>780</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I29" s="21">
         <f>'01_입력'!$I$102</f>
         <v>780</v>
       </c>
-      <c r="J28" s="21">
+      <c r="J29" s="21">
         <f>'01_입력'!$J$102</f>
         <v>780</v>
       </c>
-      <c r="K28" s="21">
+      <c r="K29" s="21">
         <f>'01_입력'!$K$102</f>
         <v>780</v>
       </c>
-      <c r="L28" s="21">
+      <c r="L29" s="21">
         <f>'01_입력'!$L$102</f>
         <v>780</v>
       </c>
-      <c r="M28" s="21">
+      <c r="M29" s="21">
         <f>'01_입력'!$M$102</f>
         <v>780</v>
       </c>
-      <c r="N28" s="21">
+      <c r="N29" s="21">
         <f>'01_입력'!$N$102</f>
         <v>780</v>
       </c>
-      <c r="O28" s="27">
-        <f>SUM(C28:N28)</f>
+      <c r="O29" s="26">
+        <f>SUM(C29:N29)</f>
         <v>9360</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="10" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>이지켐</t>
         </is>
       </c>
-      <c r="C29" s="21">
+      <c r="C30" s="21">
         <f>'01_입력'!$C$103</f>
         <v>840</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D30" s="21">
         <f>'01_입력'!$D$103</f>
         <v>840</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E30" s="21">
         <f>'01_입력'!$E$103</f>
         <v>840</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F30" s="21">
         <f>'01_입력'!$F$103</f>
         <v>840</v>
       </c>
-      <c r="G29" s="21">
+      <c r="G30" s="21">
         <f>'01_입력'!$G$103</f>
         <v>840</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H30" s="21">
         <f>'01_입력'!$H$103</f>
         <v>840</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I30" s="21">
         <f>'01_입력'!$I$103</f>
         <v>840</v>
       </c>
-      <c r="J29" s="21">
+      <c r="J30" s="21">
         <f>'01_입력'!$J$103</f>
         <v>840</v>
       </c>
-      <c r="K29" s="21">
+      <c r="K30" s="21">
         <f>'01_입력'!$K$103</f>
         <v>840</v>
       </c>
-      <c r="L29" s="21">
+      <c r="L30" s="21">
         <f>'01_입력'!$L$103</f>
         <v>840</v>
       </c>
-      <c r="M29" s="21">
+      <c r="M30" s="21">
         <f>'01_입력'!$M$103</f>
         <v>840</v>
       </c>
-      <c r="N29" s="21">
+      <c r="N30" s="21">
         <f>'01_입력'!$N$103</f>
         <v>840</v>
       </c>
-      <c r="O29" s="27">
-        <f>SUM(C29:N29)</f>
+      <c r="O30" s="26">
+        <f>SUM(C30:N30)</f>
         <v>10080</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="10" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>한솔</t>
         </is>
       </c>
-      <c r="C30" s="21">
+      <c r="C31" s="21">
         <f>'01_입력'!$C$104</f>
         <v>300</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D31" s="21">
         <f>'01_입력'!$D$104</f>
         <v>300</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E31" s="21">
         <f>'01_입력'!$E$104</f>
         <v>300</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F31" s="21">
         <f>'01_입력'!$F$104</f>
         <v>300</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G31" s="21">
         <f>'01_입력'!$G$104</f>
         <v>300</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H31" s="21">
         <f>'01_입력'!$H$104</f>
         <v>300</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I31" s="21">
         <f>'01_입력'!$I$104</f>
         <v>300</v>
       </c>
-      <c r="J30" s="21">
+      <c r="J31" s="21">
         <f>'01_입력'!$J$104</f>
         <v>300</v>
       </c>
-      <c r="K30" s="21">
+      <c r="K31" s="21">
         <f>'01_입력'!$K$104</f>
         <v>300</v>
       </c>
-      <c r="L30" s="21">
+      <c r="L31" s="21">
         <f>'01_입력'!$L$104</f>
         <v>300</v>
       </c>
-      <c r="M30" s="21">
+      <c r="M31" s="21">
         <f>'01_입력'!$M$104</f>
         <v>300</v>
       </c>
-      <c r="N30" s="21">
+      <c r="N31" s="21">
         <f>'01_입력'!$N$104</f>
         <v>300</v>
       </c>
-      <c r="O30" s="27">
-        <f>SUM(C30:N30)</f>
+      <c r="O31" s="26">
+        <f>SUM(C31:N31)</f>
         <v>3600</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="29" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>출하 합계</t>
         </is>
       </c>
-      <c r="C31" s="40">
-        <f>SUM(C27:C30)</f>
+      <c r="C32" s="41">
+        <f>SUM(C28:C31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="D31" s="40">
-        <f>SUM(D27:D30)</f>
+      <c r="D32" s="41">
+        <f>SUM(D28:D31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="E31" s="40">
-        <f>SUM(E27:E30)</f>
+      <c r="E32" s="41">
+        <f>SUM(E28:E31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="F31" s="40">
-        <f>SUM(F27:F30)</f>
+      <c r="F32" s="41">
+        <f>SUM(F28:F31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="G31" s="40">
-        <f>SUM(G27:G30)</f>
+      <c r="G32" s="41">
+        <f>SUM(G28:G31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="H31" s="40">
-        <f>SUM(H27:H30)</f>
+      <c r="H32" s="41">
+        <f>SUM(H28:H31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="I31" s="40">
-        <f>SUM(I27:I30)</f>
+      <c r="I32" s="41">
+        <f>SUM(I28:I31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="J31" s="40">
-        <f>SUM(J27:J30)</f>
+      <c r="J32" s="41">
+        <f>SUM(J28:J31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="K31" s="40">
-        <f>SUM(K27:K30)</f>
+      <c r="K32" s="41">
+        <f>SUM(K28:K31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="L31" s="40">
-        <f>SUM(L27:L30)</f>
+      <c r="L32" s="41">
+        <f>SUM(L28:L31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="M31" s="40">
-        <f>SUM(M27:M30)</f>
+      <c r="M32" s="41">
+        <f>SUM(M28:M31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="N31" s="40">
-        <f>SUM(N27:N30)</f>
+      <c r="N32" s="41">
+        <f>SUM(N28:N31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="O31" s="27">
-        <f>SUM(C31:N31)</f>
+      <c r="O32" s="26">
+        <f>SUM(C32:N32)</f>
         <v>45760</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>생산 − 출하</t>
-        </is>
-      </c>
-      <c r="C32" s="38">
-        <f>C25-C31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="D32" s="38">
-        <f>D25-D31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="E32" s="38">
-        <f>E25-E31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="F32" s="38">
-        <f>F25-F31</f>
-        <v>-2625.33333333333</v>
-      </c>
-      <c r="G32" s="38">
-        <f>G25-G31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="H32" s="38">
-        <f>H25-H31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="I32" s="38">
-        <f>I25-I31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="J32" s="38">
-        <f>J25-J31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="K32" s="38">
-        <f>K25-K31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="L32" s="38">
-        <f>L25-L31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="M32" s="38">
-        <f>M25-M31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="N32" s="38">
-        <f>N25-N31</f>
-        <v>642.303030303031</v>
-      </c>
-      <c r="O32" s="41">
-        <f>SUM(C32:N32)</f>
-        <v>4440.00000000001</v>
-      </c>
-    </row>
     <row r="33">
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>누적 (생산 − 출하)</t>
-        </is>
-      </c>
-      <c r="C33" s="41">
-        <f>C32+N14</f>
-        <v>-582.424242424238</v>
-      </c>
-      <c r="D33" s="41">
-        <f>D32+C33</f>
-        <v>59.8787878787934</v>
-      </c>
-      <c r="E33" s="41">
-        <f>E32+D33</f>
-        <v>702.181818181824</v>
-      </c>
-      <c r="F33" s="41">
-        <f>F32+E33</f>
-        <v>-1923.15151515151</v>
-      </c>
-      <c r="G33" s="41">
-        <f>G32+F33</f>
-        <v>-1280.84848484848</v>
-      </c>
-      <c r="H33" s="41">
-        <f>H32+G33</f>
-        <v>-638.545454545447</v>
-      </c>
-      <c r="I33" s="41">
-        <f>I32+H33</f>
-        <v>3.75757575758416</v>
-      </c>
-      <c r="J33" s="41">
-        <f>J32+I33</f>
-        <v>646.060606060615</v>
-      </c>
-      <c r="K33" s="41">
-        <f>K32+J33</f>
-        <v>1288.36363636365</v>
-      </c>
-      <c r="L33" s="41">
-        <f>L32+K33</f>
-        <v>1930.66666666668</v>
-      </c>
-      <c r="M33" s="41">
-        <f>M32+L33</f>
-        <v>2572.96969696971</v>
-      </c>
-      <c r="N33" s="41">
-        <f>N32+M33</f>
-        <v>3215.27272727274</v>
-      </c>
-      <c r="O33" s="41">
-        <f>N33</f>
-        <v>3215.27272727274</v>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>필요 Batch (출하÷190)</t>
+        </is>
+      </c>
+      <c r="C33" s="32">
+        <f>C32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="D33" s="32">
+        <f>D32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="E33" s="32">
+        <f>E32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="F33" s="32">
+        <f>F32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="G33" s="32">
+        <f>G32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="H33" s="32">
+        <f>H32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="I33" s="32">
+        <f>I32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="J33" s="32">
+        <f>J32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="K33" s="32">
+        <f>K32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="L33" s="32">
+        <f>L32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="M33" s="32">
+        <f>M32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="N33" s="32">
+        <f>N32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="O33" s="35">
+        <f>SUM(C33:N33)</f>
+        <v>240.842105263158</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>필요 Batch (출하÷190)</t>
-        </is>
-      </c>
-      <c r="C34" s="32">
-        <f>C31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="D34" s="32">
-        <f>D31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="E34" s="32">
-        <f>E31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="F34" s="32">
-        <f>F31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="G34" s="32">
-        <f>G31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="H34" s="32">
-        <f>H31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="I34" s="32">
-        <f>I31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="J34" s="32">
-        <f>J31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="K34" s="32">
-        <f>K31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="L34" s="32">
-        <f>L31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="M34" s="32">
-        <f>M31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="N34" s="32">
-        <f>N31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="O34" s="35">
-        <f>SUM(C34:N34)</f>
-        <v>240.842105263158</v>
+          <t>200 L 충진 방식 (이지켐/한솔)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="str">
+        <f>'08_후공정부하'!C48&amp;"/"&amp;'08_후공정부하'!C51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="D34" s="5" t="str">
+        <f>'08_후공정부하'!D48&amp;"/"&amp;'08_후공정부하'!D51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="E34" s="5" t="str">
+        <f>'08_후공정부하'!E48&amp;"/"&amp;'08_후공정부하'!E51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="F34" s="5" t="str">
+        <f>'08_후공정부하'!F48&amp;"/"&amp;'08_후공정부하'!F51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="G34" s="5" t="str">
+        <f>'08_후공정부하'!G48&amp;"/"&amp;'08_후공정부하'!G51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="H34" s="5" t="str">
+        <f>'08_후공정부하'!H48&amp;"/"&amp;'08_후공정부하'!H51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="I34" s="5" t="str">
+        <f>'08_후공정부하'!I48&amp;"/"&amp;'08_후공정부하'!I51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="J34" s="5" t="str">
+        <f>'08_후공정부하'!J48&amp;"/"&amp;'08_후공정부하'!J51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="K34" s="5" t="str">
+        <f>'08_후공정부하'!K48&amp;"/"&amp;'08_후공정부하'!K51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="L34" s="5" t="str">
+        <f>'08_후공정부하'!L48&amp;"/"&amp;'08_후공정부하'!L51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="M34" s="5" t="str">
+        <f>'08_후공정부하'!M48&amp;"/"&amp;'08_후공정부하'!M51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="N34" s="5" t="str">
+        <f>'08_후공정부하'!N48&amp;"/"&amp;'08_후공정부하'!N51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="O34" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -8291,128 +7959,10 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>양품 생산 (양품률 입력 시)</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),C25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),D25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),E25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),F25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),G25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),H25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),I25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),J25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),K25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),L25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="M39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),M25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),N25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="O39" s="27" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),SUM(C39:N39),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
     <row r="40">
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>기말재고 (기초재고·양품률 입력 시)</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(N21),ISNUMBER(C39)),N21+C39-C31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(C40),ISNUMBER(D39)),C40+D39-D31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(D40),ISNUMBER(E39)),D40+E39-E31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(E40),ISNUMBER(F39)),E40+F39-F31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(F40),ISNUMBER(G39)),F40+G39-G31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(G40),ISNUMBER(H39)),G40+H39-H31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(H40),ISNUMBER(I39)),H40+I39-I31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(I40),ISNUMBER(J39)),I40+J39-J31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(J40),ISNUMBER(K39)),J40+K39-K31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(K40),ISNUMBER(L39)),K40+L39-L31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="M40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(L40),ISNUMBER(M39)),L40+M39-M31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(M40),ISNUMBER(N39)),M40+N39-N31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="O40" s="27" t="str">
-        <f>N40</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="inlineStr">
-        <is>
-          <t>2027년 1~4월은 확정 생산 (01_입력 G), 5월부터 월 Capa. · 2028년 105℃ 50.2톤 · 4월 대정비</t>
+      <c r="B40" s="18" t="inlineStr">
+        <is>
+          <t>2027년 1~4월은 확정 생산 (01_입력 G), 5월부터 47,200 ÷ 11 · 2028년 50,200 ÷ 11 · 4월 대정비 1,188 kg · 재고는 기초재고 2,882 kg부터</t>
         </is>
       </c>
     </row>
@@ -8427,14 +7977,14 @@
       <formula>C5="대정비"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:N24">
+  <conditionalFormatting sqref="C23:N23">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>C24="대정비"</formula>
+      <formula>C23="대정비"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:N25">
+  <conditionalFormatting sqref="C24:N24">
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>C24="대정비"</formula>
+      <formula>C23="대정비"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -8448,7 +7998,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:O42"/>
+  <dimension ref="B1:O40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -8584,7 +8134,7 @@
         <f>IF(MONTH(N$4)=MAINT_M,"대정비",IF(N$4&lt;RF_START,"정제기 1대","정제기 2대"))</f>
         <v>정제기 2대</v>
       </c>
-      <c r="O5" s="27" t="inlineStr"/>
+      <c r="O5" s="26" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="B6" s="29" t="inlineStr">
@@ -8640,7 +8190,7 @@
         <f>'01_입력'!$N$80</f>
         <v>3564</v>
       </c>
-      <c r="O6" s="27">
+      <c r="O6" s="26">
         <f>SUM(C6:N6)</f>
         <v>37224</v>
       </c>
@@ -8707,414 +8257,414 @@
     <row r="8">
       <c r="B8" s="10" t="inlineStr">
         <is>
+          <t>생산 − 출하</t>
+        </is>
+      </c>
+      <c r="C8" s="38">
+        <f>C6-C14</f>
+        <v>-575.333333333333</v>
+      </c>
+      <c r="D8" s="38">
+        <f>D6-D14</f>
+        <v>-575.333333333333</v>
+      </c>
+      <c r="E8" s="38">
+        <f>E6-E14</f>
+        <v>-165.333333333333</v>
+      </c>
+      <c r="F8" s="38">
+        <f>F6-F14</f>
+        <v>-2145.33333333333</v>
+      </c>
+      <c r="G8" s="38">
+        <f>G6-G14</f>
+        <v>230.666666666667</v>
+      </c>
+      <c r="H8" s="38">
+        <f>H6-H14</f>
+        <v>230.666666666667</v>
+      </c>
+      <c r="I8" s="38">
+        <f>I6-I14</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="J8" s="38">
+        <f>J6-J14</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="K8" s="38">
+        <f>K6-K14</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="L8" s="38">
+        <f>L6-L14</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="M8" s="38">
+        <f>M6-M14</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="N8" s="38">
+        <f>N6-N14</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="O8" s="40">
+        <f>SUM(C8:N8)</f>
+        <v>-4496</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="29" t="inlineStr">
+        <is>
+          <t>재고 (전월 재고 + 생산 − 출하)</t>
+        </is>
+      </c>
+      <c r="C9" s="40">
+        <f>N(INV_0)+C6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-C14</f>
+        <v>2306.66666666667</v>
+      </c>
+      <c r="D9" s="40">
+        <f>C9+D6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-D14</f>
+        <v>1731.33333333333</v>
+      </c>
+      <c r="E9" s="40">
+        <f>D9+E6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-E14</f>
+        <v>1566</v>
+      </c>
+      <c r="F9" s="40">
+        <f>E9+F6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-F14</f>
+        <v>-579.333333333332</v>
+      </c>
+      <c r="G9" s="40">
+        <f>F9+G6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-G14</f>
+        <v>-348.666666666665</v>
+      </c>
+      <c r="H9" s="40">
+        <f>G9+H6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-H14</f>
+        <v>-117.999999999998</v>
+      </c>
+      <c r="I9" s="40">
+        <f>H9+I6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-I14</f>
+        <v>-367.333333333331</v>
+      </c>
+      <c r="J9" s="40">
+        <f>I9+J6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-J14</f>
+        <v>-616.666666666664</v>
+      </c>
+      <c r="K9" s="40">
+        <f>J9+K6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-K14</f>
+        <v>-865.999999999997</v>
+      </c>
+      <c r="L9" s="40">
+        <f>K9+L6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-L14</f>
+        <v>-1115.33333333333</v>
+      </c>
+      <c r="M9" s="40">
+        <f>L9+M6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-M14</f>
+        <v>-1364.66666666666</v>
+      </c>
+      <c r="N9" s="40">
+        <f>M9+N6*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-N14</f>
+        <v>-1614</v>
+      </c>
+      <c r="O9" s="40">
+        <f>N9</f>
+        <v>-1614</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="10" t="inlineStr">
+        <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C8" s="40">
+      <c r="C10" s="41">
         <f>'01_입력'!$C$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="D8" s="40">
+      <c r="D10" s="41">
         <f>'01_입력'!$D$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="E8" s="40">
+      <c r="E10" s="41">
         <f>'01_입력'!$E$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="F8" s="40">
+      <c r="F10" s="41">
         <f>'01_입력'!$F$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="G8" s="40">
+      <c r="G10" s="41">
         <f>'01_입력'!$G$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="H8" s="40">
+      <c r="H10" s="41">
         <f>'01_입력'!$H$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="I8" s="40">
+      <c r="I10" s="41">
         <f>'01_입력'!$I$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="J8" s="40">
+      <c r="J10" s="41">
         <f>'01_입력'!$J$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="K8" s="40">
+      <c r="K10" s="41">
         <f>'01_입력'!$K$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="L8" s="40">
+      <c r="L10" s="41">
         <f>'01_입력'!$L$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="M8" s="40">
+      <c r="M10" s="41">
         <f>'01_입력'!$M$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="N8" s="40">
+      <c r="N10" s="41">
         <f>'01_입력'!$N$94</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="O8" s="27">
-        <f>SUM(C8:N8)</f>
+      <c r="O10" s="26">
+        <f>SUM(C10:N10)</f>
         <v>22720</v>
       </c>
     </row>
-    <row r="9">
-      <c r="B9" s="10" t="inlineStr">
+    <row r="11">
+      <c r="B11" s="10" t="inlineStr">
         <is>
           <t>CXMT</t>
         </is>
       </c>
-      <c r="C9" s="21">
+      <c r="C11" s="21">
         <f>'01_입력'!$C$95</f>
         <v>0</v>
       </c>
-      <c r="D9" s="21">
+      <c r="D11" s="21">
         <f>'01_입력'!$D$95</f>
         <v>0</v>
       </c>
-      <c r="E9" s="21">
+      <c r="E11" s="21">
         <f>'01_입력'!$E$95</f>
         <v>580</v>
       </c>
-      <c r="F9" s="21">
+      <c r="F11" s="21">
         <f>'01_입력'!$F$95</f>
         <v>580</v>
       </c>
-      <c r="G9" s="21">
+      <c r="G11" s="21">
         <f>'01_입력'!$G$95</f>
         <v>580</v>
       </c>
-      <c r="H9" s="21">
+      <c r="H11" s="21">
         <f>'01_입력'!$H$95</f>
         <v>580</v>
       </c>
-      <c r="I9" s="21">
+      <c r="I11" s="21">
         <f>'01_입력'!$I$95</f>
         <v>780</v>
       </c>
-      <c r="J9" s="21">
+      <c r="J11" s="21">
         <f>'01_입력'!$J$95</f>
         <v>780</v>
       </c>
-      <c r="K9" s="21">
+      <c r="K11" s="21">
         <f>'01_입력'!$K$95</f>
         <v>780</v>
       </c>
-      <c r="L9" s="21">
+      <c r="L11" s="21">
         <f>'01_입력'!$L$95</f>
         <v>780</v>
       </c>
-      <c r="M9" s="21">
+      <c r="M11" s="21">
         <f>'01_입력'!$M$95</f>
         <v>780</v>
       </c>
-      <c r="N9" s="21">
+      <c r="N11" s="21">
         <f>'01_입력'!$N$95</f>
         <v>780</v>
       </c>
-      <c r="O9" s="27">
-        <f>SUM(C9:N9)</f>
+      <c r="O11" s="26">
+        <f>SUM(C11:N11)</f>
         <v>7000</v>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" s="10" t="inlineStr">
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
         <is>
           <t>이지켐</t>
         </is>
       </c>
-      <c r="C10" s="21">
+      <c r="C12" s="21">
         <f>'01_입력'!$C$96</f>
         <v>560</v>
       </c>
-      <c r="D10" s="21">
+      <c r="D12" s="21">
         <f>'01_입력'!$D$96</f>
         <v>560</v>
       </c>
-      <c r="E10" s="21">
+      <c r="E12" s="21">
         <f>'01_입력'!$E$96</f>
         <v>560</v>
       </c>
-      <c r="F10" s="21">
+      <c r="F12" s="21">
         <f>'01_입력'!$F$96</f>
         <v>560</v>
       </c>
-      <c r="G10" s="21">
+      <c r="G12" s="21">
         <f>'01_입력'!$G$96</f>
         <v>560</v>
       </c>
-      <c r="H10" s="21">
+      <c r="H12" s="21">
         <f>'01_입력'!$H$96</f>
         <v>560</v>
       </c>
-      <c r="I10" s="21">
+      <c r="I12" s="21">
         <f>'01_입력'!$I$96</f>
-        <v>1120</v>
-      </c>
-      <c r="J10" s="21">
+        <v>840</v>
+      </c>
+      <c r="J12" s="21">
         <f>'01_입력'!$J$96</f>
-        <v>1120</v>
-      </c>
-      <c r="K10" s="21">
+        <v>840</v>
+      </c>
+      <c r="K12" s="21">
         <f>'01_입력'!$K$96</f>
-        <v>1120</v>
-      </c>
-      <c r="L10" s="21">
+        <v>840</v>
+      </c>
+      <c r="L12" s="21">
         <f>'01_입력'!$L$96</f>
-        <v>1120</v>
-      </c>
-      <c r="M10" s="21">
+        <v>840</v>
+      </c>
+      <c r="M12" s="21">
         <f>'01_입력'!$M$96</f>
-        <v>1120</v>
-      </c>
-      <c r="N10" s="21">
+        <v>840</v>
+      </c>
+      <c r="N12" s="21">
         <f>'01_입력'!$N$96</f>
-        <v>1120</v>
-      </c>
-      <c r="O10" s="27">
-        <f>SUM(C10:N10)</f>
-        <v>10080</v>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="10" t="inlineStr">
+        <v>840</v>
+      </c>
+      <c r="O12" s="26">
+        <f>SUM(C12:N12)</f>
+        <v>8400</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
         <is>
           <t>한솔</t>
         </is>
       </c>
-      <c r="C11" s="21">
+      <c r="C13" s="21">
         <f>'01_입력'!$C$97</f>
         <v>300</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D13" s="21">
         <f>'01_입력'!$D$97</f>
         <v>300</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E13" s="21">
         <f>'01_입력'!$E$97</f>
         <v>300</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F13" s="21">
         <f>'01_입력'!$F$97</f>
         <v>300</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G13" s="21">
         <f>'01_입력'!$G$97</f>
         <v>300</v>
       </c>
-      <c r="H11" s="21">
+      <c r="H13" s="21">
         <f>'01_입력'!$H$97</f>
         <v>300</v>
       </c>
-      <c r="I11" s="21">
+      <c r="I13" s="21">
         <f>'01_입력'!$I$97</f>
         <v>300</v>
       </c>
-      <c r="J11" s="21">
+      <c r="J13" s="21">
         <f>'01_입력'!$J$97</f>
         <v>300</v>
       </c>
-      <c r="K11" s="21">
+      <c r="K13" s="21">
         <f>'01_입력'!$K$97</f>
         <v>300</v>
       </c>
-      <c r="L11" s="21">
+      <c r="L13" s="21">
         <f>'01_입력'!$L$97</f>
         <v>300</v>
       </c>
-      <c r="M11" s="21">
+      <c r="M13" s="21">
         <f>'01_입력'!$M$97</f>
         <v>300</v>
       </c>
-      <c r="N11" s="21">
+      <c r="N13" s="21">
         <f>'01_입력'!$N$97</f>
         <v>300</v>
       </c>
-      <c r="O11" s="27">
-        <f>SUM(C11:N11)</f>
+      <c r="O13" s="26">
+        <f>SUM(C13:N13)</f>
         <v>3600</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>출하 합계</t>
-        </is>
-      </c>
-      <c r="C12" s="40">
-        <f>SUM(C8:C11)</f>
-        <v>2753.33333333333</v>
-      </c>
-      <c r="D12" s="40">
-        <f>SUM(D8:D11)</f>
-        <v>2753.33333333333</v>
-      </c>
-      <c r="E12" s="40">
-        <f>SUM(E8:E11)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="F12" s="40">
-        <f>SUM(F8:F11)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="G12" s="40">
-        <f>SUM(G8:G11)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="H12" s="40">
-        <f>SUM(H8:H11)</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="I12" s="40">
-        <f>SUM(I8:I11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="J12" s="40">
-        <f>SUM(J8:J11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="K12" s="40">
-        <f>SUM(K8:K11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="L12" s="40">
-        <f>SUM(L8:L11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="M12" s="40">
-        <f>SUM(M8:M11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="N12" s="40">
-        <f>SUM(N8:N11)</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="O12" s="27">
-        <f>SUM(C12:N12)</f>
-        <v>43400</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>생산 − 출하</t>
-        </is>
-      </c>
-      <c r="C13" s="38">
-        <f>C6-C12</f>
-        <v>-575.333333333333</v>
-      </c>
-      <c r="D13" s="38">
-        <f>D6-D12</f>
-        <v>-575.333333333333</v>
-      </c>
-      <c r="E13" s="38">
-        <f>E6-E12</f>
-        <v>-165.333333333333</v>
-      </c>
-      <c r="F13" s="38">
-        <f>F6-F12</f>
-        <v>-2145.33333333333</v>
-      </c>
-      <c r="G13" s="38">
-        <f>G6-G12</f>
-        <v>230.666666666667</v>
-      </c>
-      <c r="H13" s="38">
-        <f>H6-H12</f>
-        <v>230.666666666667</v>
-      </c>
-      <c r="I13" s="38">
-        <f>I6-I12</f>
-        <v>-529.333333333333</v>
-      </c>
-      <c r="J13" s="38">
-        <f>J6-J12</f>
-        <v>-529.333333333333</v>
-      </c>
-      <c r="K13" s="38">
-        <f>K6-K12</f>
-        <v>-529.333333333333</v>
-      </c>
-      <c r="L13" s="38">
-        <f>L6-L12</f>
-        <v>-529.333333333333</v>
-      </c>
-      <c r="M13" s="38">
-        <f>M6-M12</f>
-        <v>-529.333333333333</v>
-      </c>
-      <c r="N13" s="38">
-        <f>N6-N12</f>
-        <v>-529.333333333333</v>
-      </c>
-      <c r="O13" s="41">
-        <f>SUM(C13:N13)</f>
-        <v>-6176</v>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="29" t="inlineStr">
         <is>
-          <t>누적 (생산 − 출하)</t>
+          <t>출하 합계</t>
         </is>
       </c>
       <c r="C14" s="41">
-        <f>C13</f>
-        <v>-575.333333333333</v>
+        <f>SUM(C10:C13)</f>
+        <v>2753.33333333333</v>
       </c>
       <c r="D14" s="41">
-        <f>D13+C14</f>
-        <v>-1150.66666666667</v>
+        <f>SUM(D10:D13)</f>
+        <v>2753.33333333333</v>
       </c>
       <c r="E14" s="41">
-        <f>E13+D14</f>
-        <v>-1316</v>
+        <f>SUM(E10:E13)</f>
+        <v>3333.33333333333</v>
       </c>
       <c r="F14" s="41">
-        <f>F13+E14</f>
-        <v>-3461.33333333333</v>
+        <f>SUM(F10:F13)</f>
+        <v>3333.33333333333</v>
       </c>
       <c r="G14" s="41">
-        <f>G13+F14</f>
-        <v>-3230.66666666667</v>
+        <f>SUM(G10:G13)</f>
+        <v>3333.33333333333</v>
       </c>
       <c r="H14" s="41">
-        <f>H13+G14</f>
-        <v>-3000</v>
+        <f>SUM(H10:H13)</f>
+        <v>3333.33333333333</v>
       </c>
       <c r="I14" s="41">
-        <f>I13+H14</f>
-        <v>-3529.33333333333</v>
+        <f>SUM(I10:I13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="J14" s="41">
-        <f>J13+I14</f>
-        <v>-4058.66666666666</v>
+        <f>SUM(J10:J13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="K14" s="41">
-        <f>K13+J14</f>
-        <v>-4588</v>
+        <f>SUM(K10:K13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="L14" s="41">
-        <f>L13+K14</f>
-        <v>-5117.33333333333</v>
+        <f>SUM(L10:L13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="M14" s="41">
-        <f>M13+L14</f>
-        <v>-5646.66666666666</v>
+        <f>SUM(M10:M13)</f>
+        <v>3813.33333333333</v>
       </c>
       <c r="N14" s="41">
-        <f>N13+M14</f>
-        <v>-6176</v>
-      </c>
-      <c r="O14" s="41">
-        <f>N14</f>
-        <v>-6176</v>
+        <f>SUM(N10:N13)</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="O14" s="26">
+        <f>SUM(C14:N14)</f>
+        <v>41720</v>
       </c>
     </row>
     <row r="15">
@@ -9124,1104 +8674,1106 @@
         </is>
       </c>
       <c r="C15" s="32">
-        <f>C12/KG_B</f>
+        <f>C14/KG_B</f>
         <v>14.4912280701754</v>
       </c>
       <c r="D15" s="32">
-        <f>D12/KG_B</f>
+        <f>D14/KG_B</f>
         <v>14.4912280701754</v>
       </c>
       <c r="E15" s="32">
-        <f>E12/KG_B</f>
+        <f>E14/KG_B</f>
         <v>17.5438596491228</v>
       </c>
       <c r="F15" s="32">
-        <f>F12/KG_B</f>
+        <f>F14/KG_B</f>
         <v>17.5438596491228</v>
       </c>
       <c r="G15" s="32">
-        <f>G12/KG_B</f>
+        <f>G14/KG_B</f>
         <v>17.5438596491228</v>
       </c>
       <c r="H15" s="32">
-        <f>H12/KG_B</f>
+        <f>H14/KG_B</f>
         <v>17.5438596491228</v>
       </c>
       <c r="I15" s="32">
-        <f>I12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>I14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="J15" s="32">
-        <f>J12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>J14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="K15" s="32">
-        <f>K12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>K14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="L15" s="32">
-        <f>L12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>L14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="M15" s="32">
-        <f>M12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>M14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="N15" s="32">
-        <f>N12/KG_B</f>
-        <v>21.5438596491228</v>
+        <f>N14/KG_B</f>
+        <v>20.0701754385965</v>
       </c>
       <c r="O15" s="35">
         <f>SUM(C15:N15)</f>
-        <v>228.421052631579</v>
+        <v>219.578947368421</v>
       </c>
     </row>
     <row r="16">
       <c r="B16" s="10" t="inlineStr">
         <is>
+          <t>200 L 충진 방식 (이지켐/한솔)</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="str">
+        <f>'08_후공정부하'!C30&amp;"/"&amp;'08_후공정부하'!C33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="D16" s="5" t="str">
+        <f>'08_후공정부하'!D30&amp;"/"&amp;'08_후공정부하'!D33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="E16" s="5" t="str">
+        <f>'08_후공정부하'!E30&amp;"/"&amp;'08_후공정부하'!E33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="F16" s="5" t="str">
+        <f>'08_후공정부하'!F30&amp;"/"&amp;'08_후공정부하'!F33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="G16" s="5" t="str">
+        <f>'08_후공정부하'!G30&amp;"/"&amp;'08_후공정부하'!G33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="H16" s="5" t="str">
+        <f>'08_후공정부하'!H30&amp;"/"&amp;'08_후공정부하'!H33</f>
+        <v>수동/수동</v>
+      </c>
+      <c r="I16" s="5" t="str">
+        <f>'08_후공정부하'!I30&amp;"/"&amp;'08_후공정부하'!I33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="J16" s="5" t="str">
+        <f>'08_후공정부하'!J30&amp;"/"&amp;'08_후공정부하'!J33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="K16" s="5" t="str">
+        <f>'08_후공정부하'!K30&amp;"/"&amp;'08_후공정부하'!K33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="L16" s="5" t="str">
+        <f>'08_후공정부하'!L30&amp;"/"&amp;'08_후공정부하'!L33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="M16" s="5" t="str">
+        <f>'08_후공정부하'!M30&amp;"/"&amp;'08_후공정부하'!M33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="N16" s="5" t="str">
+        <f>'08_후공정부하'!N30&amp;"/"&amp;'08_후공정부하'!N33</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="O16" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="10" t="inlineStr">
+        <is>
           <t>5 Gal 충진 h</t>
         </is>
       </c>
-      <c r="C16" s="17">
+      <c r="C17" s="17">
         <f>'08_후공정부하'!C25</f>
         <v>189.333333333333</v>
       </c>
-      <c r="D16" s="17">
+      <c r="D17" s="17">
         <f>'08_후공정부하'!D25</f>
         <v>189.333333333333</v>
       </c>
-      <c r="E16" s="17">
+      <c r="E17" s="17">
         <f>'08_후공정부하'!E25</f>
         <v>247.333333333333</v>
       </c>
-      <c r="F16" s="17">
+      <c r="F17" s="17">
         <f>'08_후공정부하'!F25</f>
         <v>247.333333333333</v>
       </c>
-      <c r="G16" s="17">
+      <c r="G17" s="17">
         <f>'08_후공정부하'!G25</f>
         <v>247.333333333333</v>
       </c>
-      <c r="H16" s="17">
+      <c r="H17" s="17">
         <f>'08_후공정부하'!H25</f>
         <v>247.333333333333</v>
       </c>
-      <c r="I16" s="17">
+      <c r="I17" s="17">
         <f>'08_후공정부하'!I25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="J16" s="17">
+      <c r="J17" s="17">
         <f>'08_후공정부하'!J25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="K16" s="17">
+      <c r="K17" s="17">
         <f>'08_후공정부하'!K25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="L16" s="17">
+      <c r="L17" s="17">
         <f>'08_후공정부하'!L25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="M16" s="17">
+      <c r="M17" s="17">
         <f>'08_후공정부하'!M25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="N16" s="17">
+      <c r="N17" s="17">
         <f>'08_후공정부하'!N25</f>
         <v>267.333333333333</v>
       </c>
-      <c r="O16" s="13">
-        <f>SUM(C16:N16)</f>
+      <c r="O17" s="13">
+        <f>SUM(C17:N17)</f>
         <v>2972</v>
       </c>
     </row>
-    <row r="17">
-      <c r="B17" s="10" t="inlineStr">
+    <row r="18">
+      <c r="B18" s="10" t="inlineStr">
         <is>
           <t>200 L 충진 h</t>
         </is>
       </c>
-      <c r="C17" s="17">
+      <c r="C18" s="17">
         <f>'08_후공정부하'!C35</f>
         <v>48</v>
       </c>
-      <c r="D17" s="17">
+      <c r="D18" s="17">
         <f>'08_후공정부하'!D35</f>
         <v>48</v>
       </c>
-      <c r="E17" s="17">
+      <c r="E18" s="17">
         <f>'08_후공정부하'!E35</f>
         <v>48</v>
       </c>
-      <c r="F17" s="17">
+      <c r="F18" s="17">
         <f>'08_후공정부하'!F35</f>
         <v>48</v>
       </c>
-      <c r="G17" s="17">
+      <c r="G18" s="17">
         <f>'08_후공정부하'!G35</f>
         <v>48</v>
       </c>
-      <c r="H17" s="17">
+      <c r="H18" s="17">
         <f>'08_후공정부하'!H35</f>
         <v>48</v>
       </c>
-      <c r="I17" s="17">
+      <c r="I18" s="17">
         <f>'08_후공정부하'!I35</f>
-        <v>80</v>
-      </c>
-      <c r="J17" s="17">
+        <v>64</v>
+      </c>
+      <c r="J18" s="17">
         <f>'08_후공정부하'!J35</f>
-        <v>80</v>
-      </c>
-      <c r="K17" s="17">
+        <v>64</v>
+      </c>
+      <c r="K18" s="17">
         <f>'08_후공정부하'!K35</f>
-        <v>80</v>
-      </c>
-      <c r="L17" s="17">
+        <v>64</v>
+      </c>
+      <c r="L18" s="17">
         <f>'08_후공정부하'!L35</f>
-        <v>80</v>
-      </c>
-      <c r="M17" s="17">
+        <v>64</v>
+      </c>
+      <c r="M18" s="17">
         <f>'08_후공정부하'!M35</f>
-        <v>80</v>
-      </c>
-      <c r="N17" s="17">
+        <v>64</v>
+      </c>
+      <c r="N18" s="17">
         <f>'08_후공정부하'!N35</f>
-        <v>80</v>
-      </c>
-      <c r="O17" s="13">
-        <f>SUM(C17:N17)</f>
-        <v>768</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="10" t="inlineStr">
+        <v>64</v>
+      </c>
+      <c r="O18" s="13">
+        <f>SUM(C18:N18)</f>
+        <v>672</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="10" t="inlineStr">
         <is>
           <t>이지켐 용기</t>
         </is>
       </c>
-      <c r="C18" s="32">
+      <c r="C19" s="32">
         <f>'08_후공정부하'!C29</f>
         <v>4</v>
       </c>
-      <c r="D18" s="32">
+      <c r="D19" s="32">
         <f>'08_후공정부하'!D29</f>
         <v>4</v>
       </c>
-      <c r="E18" s="32">
+      <c r="E19" s="32">
         <f>'08_후공정부하'!E29</f>
         <v>4</v>
       </c>
-      <c r="F18" s="32">
+      <c r="F19" s="32">
         <f>'08_후공정부하'!F29</f>
         <v>4</v>
       </c>
-      <c r="G18" s="32">
+      <c r="G19" s="32">
         <f>'08_후공정부하'!G29</f>
         <v>4</v>
       </c>
-      <c r="H18" s="32">
+      <c r="H19" s="32">
         <f>'08_후공정부하'!H29</f>
         <v>4</v>
       </c>
-      <c r="I18" s="32">
+      <c r="I19" s="32">
         <f>'08_후공정부하'!I29</f>
-        <v>8</v>
-      </c>
-      <c r="J18" s="32">
+        <v>6</v>
+      </c>
+      <c r="J19" s="32">
         <f>'08_후공정부하'!J29</f>
-        <v>8</v>
-      </c>
-      <c r="K18" s="32">
+        <v>6</v>
+      </c>
+      <c r="K19" s="32">
         <f>'08_후공정부하'!K29</f>
-        <v>8</v>
-      </c>
-      <c r="L18" s="32">
+        <v>6</v>
+      </c>
+      <c r="L19" s="32">
         <f>'08_후공정부하'!L29</f>
-        <v>8</v>
-      </c>
-      <c r="M18" s="32">
+        <v>6</v>
+      </c>
+      <c r="M19" s="32">
         <f>'08_후공정부하'!M29</f>
-        <v>8</v>
-      </c>
-      <c r="N18" s="32">
+        <v>6</v>
+      </c>
+      <c r="N19" s="32">
         <f>'08_후공정부하'!N29</f>
-        <v>8</v>
-      </c>
-      <c r="O18" s="35">
-        <f>SUM(C18:N18)</f>
-        <v>72</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="10" t="inlineStr">
+        <v>6</v>
+      </c>
+      <c r="O19" s="35">
+        <f>SUM(C19:N19)</f>
+        <v>60</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="10" t="inlineStr">
         <is>
           <t>한솔 용기</t>
         </is>
       </c>
-      <c r="C19" s="32">
+      <c r="C20" s="32">
         <f>'08_후공정부하'!C32</f>
         <v>2</v>
       </c>
-      <c r="D19" s="32">
+      <c r="D20" s="32">
         <f>'08_후공정부하'!D32</f>
         <v>2</v>
       </c>
-      <c r="E19" s="32">
+      <c r="E20" s="32">
         <f>'08_후공정부하'!E32</f>
         <v>2</v>
       </c>
-      <c r="F19" s="32">
+      <c r="F20" s="32">
         <f>'08_후공정부하'!F32</f>
         <v>2</v>
       </c>
-      <c r="G19" s="32">
+      <c r="G20" s="32">
         <f>'08_후공정부하'!G32</f>
         <v>2</v>
       </c>
-      <c r="H19" s="32">
+      <c r="H20" s="32">
         <f>'08_후공정부하'!H32</f>
         <v>2</v>
       </c>
-      <c r="I19" s="32">
+      <c r="I20" s="32">
         <f>'08_후공정부하'!I32</f>
         <v>2</v>
       </c>
-      <c r="J19" s="32">
+      <c r="J20" s="32">
         <f>'08_후공정부하'!J32</f>
         <v>2</v>
       </c>
-      <c r="K19" s="32">
+      <c r="K20" s="32">
         <f>'08_후공정부하'!K32</f>
         <v>2</v>
       </c>
-      <c r="L19" s="32">
+      <c r="L20" s="32">
         <f>'08_후공정부하'!L32</f>
         <v>2</v>
       </c>
-      <c r="M19" s="32">
+      <c r="M20" s="32">
         <f>'08_후공정부하'!M32</f>
         <v>2</v>
       </c>
-      <c r="N19" s="32">
+      <c r="N20" s="32">
         <f>'08_후공정부하'!N32</f>
         <v>2</v>
       </c>
-      <c r="O19" s="35">
-        <f>SUM(C19:N19)</f>
+      <c r="O20" s="35">
+        <f>SUM(C20:N20)</f>
         <v>24</v>
       </c>
     </row>
-    <row r="20">
-      <c r="B20" s="10" t="inlineStr">
-        <is>
-          <t>양품 생산 (양품률 입력 시)</t>
-        </is>
-      </c>
-      <c r="C20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),C6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),D6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),E6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),F6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),G6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),H6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),I6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),J6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),K6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),L6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="M20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),M6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N20" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),N6*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="O20" s="27" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),SUM(C20:N20),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="10" t="inlineStr">
-        <is>
-          <t>기말재고 (기초재고·양품률 입력 시)</t>
-        </is>
-      </c>
-      <c r="C21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(INV_0),ISNUMBER(C20)),INV_0+C20-C12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(C21),ISNUMBER(D20)),C21+D20-D12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(D21),ISNUMBER(E20)),D21+E20-E12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(E21),ISNUMBER(F20)),E21+F20-F12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(F21),ISNUMBER(G20)),F21+G20-G12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(G21),ISNUMBER(H20)),G21+H20-H12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(H21),ISNUMBER(I20)),H21+I20-I12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(I21),ISNUMBER(J20)),I21+J20-J12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(J21),ISNUMBER(K20)),J21+K20-K12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(K21),ISNUMBER(L20)),K21+L20-L12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="M21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(L21),ISNUMBER(M20)),L21+M20-M12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N21" s="21" t="str">
-        <f>IF(AND(ISNUMBER(M21),ISNUMBER(N20)),M21+N20-N12,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="O21" s="27" t="str">
-        <f>N21</f>
-        <v>-</v>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>2028</t>
+        </is>
+      </c>
+      <c r="C22" s="25" t="n">
+        <v>46753</v>
+      </c>
+      <c r="D22" s="25" t="n">
+        <v>46784</v>
+      </c>
+      <c r="E22" s="25" t="n">
+        <v>46813</v>
+      </c>
+      <c r="F22" s="25" t="n">
+        <v>46844</v>
+      </c>
+      <c r="G22" s="25" t="n">
+        <v>46874</v>
+      </c>
+      <c r="H22" s="25" t="n">
+        <v>46905</v>
+      </c>
+      <c r="I22" s="25" t="n">
+        <v>46935</v>
+      </c>
+      <c r="J22" s="25" t="n">
+        <v>46966</v>
+      </c>
+      <c r="K22" s="25" t="n">
+        <v>46997</v>
+      </c>
+      <c r="L22" s="25" t="n">
+        <v>47027</v>
+      </c>
+      <c r="M22" s="25" t="n">
+        <v>47058</v>
+      </c>
+      <c r="N22" s="25" t="n">
+        <v>47088</v>
+      </c>
+      <c r="O22" s="9" t="inlineStr">
+        <is>
+          <t>연간</t>
+        </is>
       </c>
     </row>
     <row r="23">
-      <c r="B23" s="8" t="inlineStr">
-        <is>
-          <t>2028</t>
-        </is>
-      </c>
-      <c r="C23" s="25" t="n">
-        <v>46753</v>
-      </c>
-      <c r="D23" s="25" t="n">
-        <v>46784</v>
-      </c>
-      <c r="E23" s="25" t="n">
-        <v>46813</v>
-      </c>
-      <c r="F23" s="25" t="n">
-        <v>46844</v>
-      </c>
-      <c r="G23" s="25" t="n">
-        <v>46874</v>
-      </c>
-      <c r="H23" s="25" t="n">
-        <v>46905</v>
-      </c>
-      <c r="I23" s="25" t="n">
-        <v>46935</v>
-      </c>
-      <c r="J23" s="25" t="n">
-        <v>46966</v>
-      </c>
-      <c r="K23" s="25" t="n">
-        <v>46997</v>
-      </c>
-      <c r="L23" s="25" t="n">
-        <v>47027</v>
-      </c>
-      <c r="M23" s="25" t="n">
-        <v>47058</v>
-      </c>
-      <c r="N23" s="25" t="n">
-        <v>47088</v>
-      </c>
-      <c r="O23" s="9" t="inlineStr">
-        <is>
-          <t>연간</t>
-        </is>
-      </c>
+      <c r="B23" s="10" t="inlineStr">
+        <is>
+          <t>운전 조건</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="str">
+        <f>IF(MONTH(C$22)=MAINT_M,"대정비",IF(C$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="D23" s="5" t="str">
+        <f>IF(MONTH(D$22)=MAINT_M,"대정비",IF(D$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="E23" s="5" t="str">
+        <f>IF(MONTH(E$22)=MAINT_M,"대정비",IF(E$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="F23" s="5" t="str">
+        <f>IF(MONTH(F$22)=MAINT_M,"대정비",IF(F$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>대정비</v>
+      </c>
+      <c r="G23" s="5" t="str">
+        <f>IF(MONTH(G$22)=MAINT_M,"대정비",IF(G$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="H23" s="5" t="str">
+        <f>IF(MONTH(H$22)=MAINT_M,"대정비",IF(H$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="I23" s="5" t="str">
+        <f>IF(MONTH(I$22)=MAINT_M,"대정비",IF(I$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="J23" s="5" t="str">
+        <f>IF(MONTH(J$22)=MAINT_M,"대정비",IF(J$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="K23" s="5" t="str">
+        <f>IF(MONTH(K$22)=MAINT_M,"대정비",IF(K$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="L23" s="5" t="str">
+        <f>IF(MONTH(L$22)=MAINT_M,"대정비",IF(L$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="M23" s="5" t="str">
+        <f>IF(MONTH(M$22)=MAINT_M,"대정비",IF(M$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="N23" s="5" t="str">
+        <f>IF(MONTH(N$22)=MAINT_M,"대정비",IF(N$22&lt;RF_START,"정제기 1대","정제기 2대"))</f>
+        <v>정제기 2대</v>
+      </c>
+      <c r="O23" s="26" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="B24" s="10" t="inlineStr">
-        <is>
-          <t>운전 조건</t>
-        </is>
-      </c>
-      <c r="C24" s="5" t="str">
-        <f>IF(MONTH(C$23)=MAINT_M,"대정비",IF(C$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="D24" s="5" t="str">
-        <f>IF(MONTH(D$23)=MAINT_M,"대정비",IF(D$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="E24" s="5" t="str">
-        <f>IF(MONTH(E$23)=MAINT_M,"대정비",IF(E$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="F24" s="5" t="str">
-        <f>IF(MONTH(F$23)=MAINT_M,"대정비",IF(F$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>대정비</v>
-      </c>
-      <c r="G24" s="5" t="str">
-        <f>IF(MONTH(G$23)=MAINT_M,"대정비",IF(G$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="H24" s="5" t="str">
-        <f>IF(MONTH(H$23)=MAINT_M,"대정비",IF(H$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="I24" s="5" t="str">
-        <f>IF(MONTH(I$23)=MAINT_M,"대정비",IF(I$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="J24" s="5" t="str">
-        <f>IF(MONTH(J$23)=MAINT_M,"대정비",IF(J$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="K24" s="5" t="str">
-        <f>IF(MONTH(K$23)=MAINT_M,"대정비",IF(K$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="L24" s="5" t="str">
-        <f>IF(MONTH(L$23)=MAINT_M,"대정비",IF(L$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="M24" s="5" t="str">
-        <f>IF(MONTH(M$23)=MAINT_M,"대정비",IF(M$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="N24" s="5" t="str">
-        <f>IF(MONTH(N$23)=MAINT_M,"대정비",IF(N$23&lt;RF_START,"정제기 1대","정제기 2대"))</f>
-        <v>정제기 2대</v>
-      </c>
-      <c r="O24" s="27" t="inlineStr"/>
-    </row>
-    <row r="25">
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B24" s="29" t="inlineStr">
         <is>
           <t>생산 (kg)</t>
         </is>
       </c>
-      <c r="C25" s="22">
+      <c r="C24" s="22">
         <f>'01_입력'!$C$83</f>
         <v>3564</v>
       </c>
-      <c r="D25" s="22">
+      <c r="D24" s="22">
         <f>'01_입력'!$D$83</f>
         <v>3564</v>
       </c>
-      <c r="E25" s="22">
+      <c r="E24" s="22">
         <f>'01_입력'!$E$83</f>
         <v>3564</v>
       </c>
-      <c r="F25" s="22">
+      <c r="F24" s="22">
         <f>'01_입력'!$F$83</f>
         <v>1188</v>
       </c>
-      <c r="G25" s="22">
+      <c r="G24" s="22">
         <f>'01_입력'!$G$83</f>
         <v>3564</v>
       </c>
-      <c r="H25" s="22">
+      <c r="H24" s="22">
         <f>'01_입력'!$H$83</f>
         <v>3564</v>
       </c>
-      <c r="I25" s="22">
+      <c r="I24" s="22">
         <f>'01_입력'!$I$83</f>
         <v>3564</v>
       </c>
-      <c r="J25" s="22">
+      <c r="J24" s="22">
         <f>'01_입력'!$J$83</f>
         <v>3168</v>
       </c>
-      <c r="K25" s="22">
+      <c r="K24" s="22">
         <f>'01_입력'!$K$83</f>
         <v>3168</v>
       </c>
-      <c r="L25" s="22">
+      <c r="L24" s="22">
         <f>'01_입력'!$L$83</f>
         <v>3168</v>
       </c>
-      <c r="M25" s="22">
+      <c r="M24" s="22">
         <f>'01_입력'!$M$83</f>
         <v>3168</v>
       </c>
-      <c r="N25" s="22">
+      <c r="N24" s="22">
         <f>'01_입력'!$N$83</f>
         <v>3168</v>
       </c>
-      <c r="O25" s="27">
+      <c r="O24" s="26">
+        <f>SUM(C24:N24)</f>
+        <v>38412</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="10" t="inlineStr">
+        <is>
+          <t>Batch 환산 (÷190)</t>
+        </is>
+      </c>
+      <c r="C25" s="32">
+        <f>C24/KG_B</f>
+        <v>18.7578947368421</v>
+      </c>
+      <c r="D25" s="32">
+        <f>D24/KG_B</f>
+        <v>18.7578947368421</v>
+      </c>
+      <c r="E25" s="32">
+        <f>E24/KG_B</f>
+        <v>18.7578947368421</v>
+      </c>
+      <c r="F25" s="32">
+        <f>F24/KG_B</f>
+        <v>6.25263157894737</v>
+      </c>
+      <c r="G25" s="32">
+        <f>G24/KG_B</f>
+        <v>18.7578947368421</v>
+      </c>
+      <c r="H25" s="32">
+        <f>H24/KG_B</f>
+        <v>18.7578947368421</v>
+      </c>
+      <c r="I25" s="32">
+        <f>I24/KG_B</f>
+        <v>18.7578947368421</v>
+      </c>
+      <c r="J25" s="32">
+        <f>J24/KG_B</f>
+        <v>16.6736842105263</v>
+      </c>
+      <c r="K25" s="32">
+        <f>K24/KG_B</f>
+        <v>16.6736842105263</v>
+      </c>
+      <c r="L25" s="32">
+        <f>L24/KG_B</f>
+        <v>16.6736842105263</v>
+      </c>
+      <c r="M25" s="32">
+        <f>M24/KG_B</f>
+        <v>16.6736842105263</v>
+      </c>
+      <c r="N25" s="32">
+        <f>N24/KG_B</f>
+        <v>16.6736842105263</v>
+      </c>
+      <c r="O25" s="35">
         <f>SUM(C25:N25)</f>
-        <v>38412</v>
+        <v>202.168421052632</v>
       </c>
     </row>
     <row r="26">
       <c r="B26" s="10" t="inlineStr">
         <is>
-          <t>Batch 환산 (÷190)</t>
-        </is>
-      </c>
-      <c r="C26" s="32">
-        <f>C25/KG_B</f>
-        <v>18.7578947368421</v>
-      </c>
-      <c r="D26" s="32">
-        <f>D25/KG_B</f>
-        <v>18.7578947368421</v>
-      </c>
-      <c r="E26" s="32">
-        <f>E25/KG_B</f>
-        <v>18.7578947368421</v>
-      </c>
-      <c r="F26" s="32">
-        <f>F25/KG_B</f>
-        <v>6.25263157894737</v>
-      </c>
-      <c r="G26" s="32">
-        <f>G25/KG_B</f>
-        <v>18.7578947368421</v>
-      </c>
-      <c r="H26" s="32">
-        <f>H25/KG_B</f>
-        <v>18.7578947368421</v>
-      </c>
-      <c r="I26" s="32">
-        <f>I25/KG_B</f>
-        <v>18.7578947368421</v>
-      </c>
-      <c r="J26" s="32">
-        <f>J25/KG_B</f>
-        <v>16.6736842105263</v>
-      </c>
-      <c r="K26" s="32">
-        <f>K25/KG_B</f>
-        <v>16.6736842105263</v>
-      </c>
-      <c r="L26" s="32">
-        <f>L25/KG_B</f>
-        <v>16.6736842105263</v>
-      </c>
-      <c r="M26" s="32">
-        <f>M25/KG_B</f>
-        <v>16.6736842105263</v>
-      </c>
-      <c r="N26" s="32">
-        <f>N25/KG_B</f>
-        <v>16.6736842105263</v>
-      </c>
-      <c r="O26" s="35">
+          <t>생산 − 출하</t>
+        </is>
+      </c>
+      <c r="C26" s="38">
+        <f>C24-C32</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="D26" s="38">
+        <f>D24-D32</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="E26" s="38">
+        <f>E24-E32</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="F26" s="38">
+        <f>F24-F32</f>
+        <v>-2625.33333333333</v>
+      </c>
+      <c r="G26" s="38">
+        <f>G24-G32</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="H26" s="38">
+        <f>H24-H32</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="I26" s="38">
+        <f>I24-I32</f>
+        <v>-249.333333333333</v>
+      </c>
+      <c r="J26" s="38">
+        <f>J24-J32</f>
+        <v>-645.333333333333</v>
+      </c>
+      <c r="K26" s="38">
+        <f>K24-K32</f>
+        <v>-645.333333333333</v>
+      </c>
+      <c r="L26" s="38">
+        <f>L24-L32</f>
+        <v>-645.333333333333</v>
+      </c>
+      <c r="M26" s="38">
+        <f>M24-M32</f>
+        <v>-645.333333333333</v>
+      </c>
+      <c r="N26" s="38">
+        <f>N24-N32</f>
+        <v>-645.333333333333</v>
+      </c>
+      <c r="O26" s="40">
         <f>SUM(C26:N26)</f>
-        <v>202.168421052632</v>
+        <v>-7348</v>
       </c>
     </row>
     <row r="27">
-      <c r="B27" s="10" t="inlineStr">
+      <c r="B27" s="29" t="inlineStr">
+        <is>
+          <t>재고 (전월 재고 + 생산 − 출하)</t>
+        </is>
+      </c>
+      <c r="C27" s="40">
+        <f>N9+C24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-C32</f>
+        <v>-1863.33333333333</v>
+      </c>
+      <c r="D27" s="40">
+        <f>C27+D24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-D32</f>
+        <v>-2112.66666666666</v>
+      </c>
+      <c r="E27" s="40">
+        <f>D27+E24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-E32</f>
+        <v>-2362</v>
+      </c>
+      <c r="F27" s="40">
+        <f>E27+F24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-F32</f>
+        <v>-4987.33333333333</v>
+      </c>
+      <c r="G27" s="40">
+        <f>F27+G24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-G32</f>
+        <v>-5236.66666666666</v>
+      </c>
+      <c r="H27" s="40">
+        <f>G27+H24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-H32</f>
+        <v>-5485.99999999999</v>
+      </c>
+      <c r="I27" s="40">
+        <f>H27+I24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-I32</f>
+        <v>-5735.33333333333</v>
+      </c>
+      <c r="J27" s="40">
+        <f>I27+J24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-J32</f>
+        <v>-6380.66666666666</v>
+      </c>
+      <c r="K27" s="40">
+        <f>J27+K24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-K32</f>
+        <v>-7025.99999999999</v>
+      </c>
+      <c r="L27" s="40">
+        <f>K27+L24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-L32</f>
+        <v>-7671.33333333333</v>
+      </c>
+      <c r="M27" s="40">
+        <f>L27+M24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-M32</f>
+        <v>-8316.66666666666</v>
+      </c>
+      <c r="N27" s="40">
+        <f>M27+N24*IF(ISNUMBER(YIELD_Q),YIELD_Q,1)-N32</f>
+        <v>-8961.99999999999</v>
+      </c>
+      <c r="O27" s="40">
+        <f>N27</f>
+        <v>-8961.99999999999</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="10" t="inlineStr">
         <is>
           <t>SK하이닉스</t>
         </is>
       </c>
-      <c r="C27" s="40">
+      <c r="C28" s="41">
         <f>'01_입력'!$C$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="D27" s="40">
+      <c r="D28" s="41">
         <f>'01_입력'!$D$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="E27" s="40">
+      <c r="E28" s="41">
         <f>'01_입력'!$E$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="F27" s="40">
+      <c r="F28" s="41">
         <f>'01_입력'!$F$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="G27" s="40">
+      <c r="G28" s="41">
         <f>'01_입력'!$G$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="H27" s="40">
+      <c r="H28" s="41">
         <f>'01_입력'!$H$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="I27" s="40">
+      <c r="I28" s="41">
         <f>'01_입력'!$I$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="J27" s="40">
+      <c r="J28" s="41">
         <f>'01_입력'!$J$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="K27" s="40">
+      <c r="K28" s="41">
         <f>'01_입력'!$K$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="L27" s="40">
+      <c r="L28" s="41">
         <f>'01_입력'!$L$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="M27" s="40">
+      <c r="M28" s="41">
         <f>'01_입력'!$M$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="N27" s="40">
+      <c r="N28" s="41">
         <f>'01_입력'!$N$101</f>
         <v>1893.33333333333</v>
       </c>
-      <c r="O27" s="27">
-        <f>SUM(C27:N27)</f>
+      <c r="O28" s="26">
+        <f>SUM(C28:N28)</f>
         <v>22720</v>
       </c>
     </row>
-    <row r="28">
-      <c r="B28" s="10" t="inlineStr">
+    <row r="29">
+      <c r="B29" s="10" t="inlineStr">
         <is>
           <t>CXMT</t>
         </is>
       </c>
-      <c r="C28" s="21">
+      <c r="C29" s="21">
         <f>'01_입력'!$C$102</f>
         <v>780</v>
       </c>
-      <c r="D28" s="21">
+      <c r="D29" s="21">
         <f>'01_입력'!$D$102</f>
         <v>780</v>
       </c>
-      <c r="E28" s="21">
+      <c r="E29" s="21">
         <f>'01_입력'!$E$102</f>
         <v>780</v>
       </c>
-      <c r="F28" s="21">
+      <c r="F29" s="21">
         <f>'01_입력'!$F$102</f>
         <v>780</v>
       </c>
-      <c r="G28" s="21">
+      <c r="G29" s="21">
         <f>'01_입력'!$G$102</f>
         <v>780</v>
       </c>
-      <c r="H28" s="21">
+      <c r="H29" s="21">
         <f>'01_입력'!$H$102</f>
         <v>780</v>
       </c>
-      <c r="I28" s="21">
+      <c r="I29" s="21">
         <f>'01_입력'!$I$102</f>
         <v>780</v>
       </c>
-      <c r="J28" s="21">
+      <c r="J29" s="21">
         <f>'01_입력'!$J$102</f>
         <v>780</v>
       </c>
-      <c r="K28" s="21">
+      <c r="K29" s="21">
         <f>'01_입력'!$K$102</f>
         <v>780</v>
       </c>
-      <c r="L28" s="21">
+      <c r="L29" s="21">
         <f>'01_입력'!$L$102</f>
         <v>780</v>
       </c>
-      <c r="M28" s="21">
+      <c r="M29" s="21">
         <f>'01_입력'!$M$102</f>
         <v>780</v>
       </c>
-      <c r="N28" s="21">
+      <c r="N29" s="21">
         <f>'01_입력'!$N$102</f>
         <v>780</v>
       </c>
-      <c r="O28" s="27">
-        <f>SUM(C28:N28)</f>
+      <c r="O29" s="26">
+        <f>SUM(C29:N29)</f>
         <v>9360</v>
       </c>
     </row>
-    <row r="29">
-      <c r="B29" s="10" t="inlineStr">
+    <row r="30">
+      <c r="B30" s="10" t="inlineStr">
         <is>
           <t>이지켐</t>
         </is>
       </c>
-      <c r="C29" s="21">
+      <c r="C30" s="21">
         <f>'01_입력'!$C$103</f>
         <v>840</v>
       </c>
-      <c r="D29" s="21">
+      <c r="D30" s="21">
         <f>'01_입력'!$D$103</f>
         <v>840</v>
       </c>
-      <c r="E29" s="21">
+      <c r="E30" s="21">
         <f>'01_입력'!$E$103</f>
         <v>840</v>
       </c>
-      <c r="F29" s="21">
+      <c r="F30" s="21">
         <f>'01_입력'!$F$103</f>
         <v>840</v>
       </c>
-      <c r="G29" s="21">
+      <c r="G30" s="21">
         <f>'01_입력'!$G$103</f>
         <v>840</v>
       </c>
-      <c r="H29" s="21">
+      <c r="H30" s="21">
         <f>'01_입력'!$H$103</f>
         <v>840</v>
       </c>
-      <c r="I29" s="21">
+      <c r="I30" s="21">
         <f>'01_입력'!$I$103</f>
         <v>840</v>
       </c>
-      <c r="J29" s="21">
+      <c r="J30" s="21">
         <f>'01_입력'!$J$103</f>
         <v>840</v>
       </c>
-      <c r="K29" s="21">
+      <c r="K30" s="21">
         <f>'01_입력'!$K$103</f>
         <v>840</v>
       </c>
-      <c r="L29" s="21">
+      <c r="L30" s="21">
         <f>'01_입력'!$L$103</f>
         <v>840</v>
       </c>
-      <c r="M29" s="21">
+      <c r="M30" s="21">
         <f>'01_입력'!$M$103</f>
         <v>840</v>
       </c>
-      <c r="N29" s="21">
+      <c r="N30" s="21">
         <f>'01_입력'!$N$103</f>
         <v>840</v>
       </c>
-      <c r="O29" s="27">
-        <f>SUM(C29:N29)</f>
+      <c r="O30" s="26">
+        <f>SUM(C30:N30)</f>
         <v>10080</v>
       </c>
     </row>
-    <row r="30">
-      <c r="B30" s="10" t="inlineStr">
+    <row r="31">
+      <c r="B31" s="10" t="inlineStr">
         <is>
           <t>한솔</t>
         </is>
       </c>
-      <c r="C30" s="21">
+      <c r="C31" s="21">
         <f>'01_입력'!$C$104</f>
         <v>300</v>
       </c>
-      <c r="D30" s="21">
+      <c r="D31" s="21">
         <f>'01_입력'!$D$104</f>
         <v>300</v>
       </c>
-      <c r="E30" s="21">
+      <c r="E31" s="21">
         <f>'01_입력'!$E$104</f>
         <v>300</v>
       </c>
-      <c r="F30" s="21">
+      <c r="F31" s="21">
         <f>'01_입력'!$F$104</f>
         <v>300</v>
       </c>
-      <c r="G30" s="21">
+      <c r="G31" s="21">
         <f>'01_입력'!$G$104</f>
         <v>300</v>
       </c>
-      <c r="H30" s="21">
+      <c r="H31" s="21">
         <f>'01_입력'!$H$104</f>
         <v>300</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I31" s="21">
         <f>'01_입력'!$I$104</f>
         <v>300</v>
       </c>
-      <c r="J30" s="21">
+      <c r="J31" s="21">
         <f>'01_입력'!$J$104</f>
         <v>300</v>
       </c>
-      <c r="K30" s="21">
+      <c r="K31" s="21">
         <f>'01_입력'!$K$104</f>
         <v>300</v>
       </c>
-      <c r="L30" s="21">
+      <c r="L31" s="21">
         <f>'01_입력'!$L$104</f>
         <v>300</v>
       </c>
-      <c r="M30" s="21">
+      <c r="M31" s="21">
         <f>'01_입력'!$M$104</f>
         <v>300</v>
       </c>
-      <c r="N30" s="21">
+      <c r="N31" s="21">
         <f>'01_입력'!$N$104</f>
         <v>300</v>
       </c>
-      <c r="O30" s="27">
-        <f>SUM(C30:N30)</f>
+      <c r="O31" s="26">
+        <f>SUM(C31:N31)</f>
         <v>3600</v>
       </c>
     </row>
-    <row r="31">
-      <c r="B31" s="29" t="inlineStr">
+    <row r="32">
+      <c r="B32" s="29" t="inlineStr">
         <is>
           <t>출하 합계</t>
         </is>
       </c>
-      <c r="C31" s="40">
-        <f>SUM(C27:C30)</f>
+      <c r="C32" s="41">
+        <f>SUM(C28:C31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="D31" s="40">
-        <f>SUM(D27:D30)</f>
+      <c r="D32" s="41">
+        <f>SUM(D28:D31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="E31" s="40">
-        <f>SUM(E27:E30)</f>
+      <c r="E32" s="41">
+        <f>SUM(E28:E31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="F31" s="40">
-        <f>SUM(F27:F30)</f>
+      <c r="F32" s="41">
+        <f>SUM(F28:F31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="G31" s="40">
-        <f>SUM(G27:G30)</f>
+      <c r="G32" s="41">
+        <f>SUM(G28:G31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="H31" s="40">
-        <f>SUM(H27:H30)</f>
+      <c r="H32" s="41">
+        <f>SUM(H28:H31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="I31" s="40">
-        <f>SUM(I27:I30)</f>
+      <c r="I32" s="41">
+        <f>SUM(I28:I31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="J31" s="40">
-        <f>SUM(J27:J30)</f>
+      <c r="J32" s="41">
+        <f>SUM(J28:J31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="K31" s="40">
-        <f>SUM(K27:K30)</f>
+      <c r="K32" s="41">
+        <f>SUM(K28:K31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="L31" s="40">
-        <f>SUM(L27:L30)</f>
+      <c r="L32" s="41">
+        <f>SUM(L28:L31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="M31" s="40">
-        <f>SUM(M27:M30)</f>
+      <c r="M32" s="41">
+        <f>SUM(M28:M31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="N31" s="40">
-        <f>SUM(N27:N30)</f>
+      <c r="N32" s="41">
+        <f>SUM(N28:N31)</f>
         <v>3813.33333333333</v>
       </c>
-      <c r="O31" s="27">
-        <f>SUM(C31:N31)</f>
+      <c r="O32" s="26">
+        <f>SUM(C32:N32)</f>
         <v>45760</v>
       </c>
     </row>
-    <row r="32">
-      <c r="B32" s="10" t="inlineStr">
-        <is>
-          <t>생산 − 출하</t>
-        </is>
-      </c>
-      <c r="C32" s="38">
-        <f>C25-C31</f>
-        <v>-249.333333333333</v>
-      </c>
-      <c r="D32" s="38">
-        <f>D25-D31</f>
-        <v>-249.333333333333</v>
-      </c>
-      <c r="E32" s="38">
-        <f>E25-E31</f>
-        <v>-249.333333333333</v>
-      </c>
-      <c r="F32" s="38">
-        <f>F25-F31</f>
-        <v>-2625.33333333333</v>
-      </c>
-      <c r="G32" s="38">
-        <f>G25-G31</f>
-        <v>-249.333333333333</v>
-      </c>
-      <c r="H32" s="38">
-        <f>H25-H31</f>
-        <v>-249.333333333333</v>
-      </c>
-      <c r="I32" s="38">
-        <f>I25-I31</f>
-        <v>-249.333333333333</v>
-      </c>
-      <c r="J32" s="38">
-        <f>J25-J31</f>
-        <v>-645.333333333333</v>
-      </c>
-      <c r="K32" s="38">
-        <f>K25-K31</f>
-        <v>-645.333333333333</v>
-      </c>
-      <c r="L32" s="38">
-        <f>L25-L31</f>
-        <v>-645.333333333333</v>
-      </c>
-      <c r="M32" s="38">
-        <f>M25-M31</f>
-        <v>-645.333333333333</v>
-      </c>
-      <c r="N32" s="38">
-        <f>N25-N31</f>
-        <v>-645.333333333333</v>
-      </c>
-      <c r="O32" s="41">
-        <f>SUM(C32:N32)</f>
-        <v>-7348</v>
-      </c>
-    </row>
     <row r="33">
-      <c r="B33" s="29" t="inlineStr">
-        <is>
-          <t>누적 (생산 − 출하)</t>
-        </is>
-      </c>
-      <c r="C33" s="41">
-        <f>C32+N14</f>
-        <v>-6425.33333333333</v>
-      </c>
-      <c r="D33" s="41">
-        <f>D32+C33</f>
-        <v>-6674.66666666666</v>
-      </c>
-      <c r="E33" s="41">
-        <f>E32+D33</f>
-        <v>-6924</v>
-      </c>
-      <c r="F33" s="41">
-        <f>F32+E33</f>
-        <v>-9549.33333333333</v>
-      </c>
-      <c r="G33" s="41">
-        <f>G32+F33</f>
-        <v>-9798.66666666666</v>
-      </c>
-      <c r="H33" s="41">
-        <f>H32+G33</f>
-        <v>-10048</v>
-      </c>
-      <c r="I33" s="41">
-        <f>I32+H33</f>
-        <v>-10297.3333333333</v>
-      </c>
-      <c r="J33" s="41">
-        <f>J32+I33</f>
-        <v>-10942.6666666667</v>
-      </c>
-      <c r="K33" s="41">
-        <f>K32+J33</f>
-        <v>-11588</v>
-      </c>
-      <c r="L33" s="41">
-        <f>L32+K33</f>
-        <v>-12233.3333333333</v>
-      </c>
-      <c r="M33" s="41">
-        <f>M32+L33</f>
-        <v>-12878.6666666667</v>
-      </c>
-      <c r="N33" s="41">
-        <f>N32+M33</f>
-        <v>-13524</v>
-      </c>
-      <c r="O33" s="41">
-        <f>N33</f>
-        <v>-13524</v>
+      <c r="B33" s="10" t="inlineStr">
+        <is>
+          <t>필요 Batch (출하÷190)</t>
+        </is>
+      </c>
+      <c r="C33" s="32">
+        <f>C32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="D33" s="32">
+        <f>D32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="E33" s="32">
+        <f>E32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="F33" s="32">
+        <f>F32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="G33" s="32">
+        <f>G32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="H33" s="32">
+        <f>H32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="I33" s="32">
+        <f>I32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="J33" s="32">
+        <f>J32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="K33" s="32">
+        <f>K32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="L33" s="32">
+        <f>L32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="M33" s="32">
+        <f>M32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="N33" s="32">
+        <f>N32/KG_B</f>
+        <v>20.0701754385965</v>
+      </c>
+      <c r="O33" s="35">
+        <f>SUM(C33:N33)</f>
+        <v>240.842105263158</v>
       </c>
     </row>
     <row r="34">
       <c r="B34" s="10" t="inlineStr">
         <is>
-          <t>필요 Batch (출하÷190)</t>
-        </is>
-      </c>
-      <c r="C34" s="32">
-        <f>C31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="D34" s="32">
-        <f>D31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="E34" s="32">
-        <f>E31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="F34" s="32">
-        <f>F31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="G34" s="32">
-        <f>G31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="H34" s="32">
-        <f>H31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="I34" s="32">
-        <f>I31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="J34" s="32">
-        <f>J31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="K34" s="32">
-        <f>K31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="L34" s="32">
-        <f>L31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="M34" s="32">
-        <f>M31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="N34" s="32">
-        <f>N31/KG_B</f>
-        <v>20.0701754385965</v>
-      </c>
-      <c r="O34" s="35">
-        <f>SUM(C34:N34)</f>
-        <v>240.842105263158</v>
+          <t>200 L 충진 방식 (이지켐/한솔)</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="str">
+        <f>'08_후공정부하'!C48&amp;"/"&amp;'08_후공정부하'!C51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="D34" s="5" t="str">
+        <f>'08_후공정부하'!D48&amp;"/"&amp;'08_후공정부하'!D51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="E34" s="5" t="str">
+        <f>'08_후공정부하'!E48&amp;"/"&amp;'08_후공정부하'!E51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="F34" s="5" t="str">
+        <f>'08_후공정부하'!F48&amp;"/"&amp;'08_후공정부하'!F51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="G34" s="5" t="str">
+        <f>'08_후공정부하'!G48&amp;"/"&amp;'08_후공정부하'!G51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="H34" s="5" t="str">
+        <f>'08_후공정부하'!H48&amp;"/"&amp;'08_후공정부하'!H51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="I34" s="5" t="str">
+        <f>'08_후공정부하'!I48&amp;"/"&amp;'08_후공정부하'!I51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="J34" s="5" t="str">
+        <f>'08_후공정부하'!J48&amp;"/"&amp;'08_후공정부하'!J51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="K34" s="5" t="str">
+        <f>'08_후공정부하'!K48&amp;"/"&amp;'08_후공정부하'!K51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="L34" s="5" t="str">
+        <f>'08_후공정부하'!L48&amp;"/"&amp;'08_후공정부하'!L51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="M34" s="5" t="str">
+        <f>'08_후공정부하'!M48&amp;"/"&amp;'08_후공정부하'!M51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="N34" s="5" t="str">
+        <f>'08_후공정부하'!N48&amp;"/"&amp;'08_후공정부하'!N51</f>
+        <v>ARS/ARS</v>
+      </c>
+      <c r="O34" s="26" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -10460,126 +10012,8 @@
         <v>24</v>
       </c>
     </row>
-    <row r="39">
-      <c r="B39" s="10" t="inlineStr">
-        <is>
-          <t>양품 생산 (양품률 입력 시)</t>
-        </is>
-      </c>
-      <c r="C39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),C25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),D25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),E25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),F25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),G25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),H25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),I25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),J25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),K25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),L25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="M39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),M25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N39" s="21" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),N25*YIELD_Q,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="O39" s="27" t="str">
-        <f>IF(ISNUMBER(YIELD_Q),SUM(C39:N39),"-")</f>
-        <v>-</v>
-      </c>
-    </row>
     <row r="40">
-      <c r="B40" s="10" t="inlineStr">
-        <is>
-          <t>기말재고 (기초재고·양품률 입력 시)</t>
-        </is>
-      </c>
-      <c r="C40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(N21),ISNUMBER(C39)),N21+C39-C31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="D40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(C40),ISNUMBER(D39)),C40+D39-D31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="E40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(D40),ISNUMBER(E39)),D40+E39-E31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="F40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(E40),ISNUMBER(F39)),E40+F39-F31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="G40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(F40),ISNUMBER(G39)),F40+G39-G31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="H40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(G40),ISNUMBER(H39)),G40+H39-H31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="I40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(H40),ISNUMBER(I39)),H40+I39-I31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="J40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(I40),ISNUMBER(J39)),I40+J39-J31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="K40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(J40),ISNUMBER(K39)),J40+K39-K31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="L40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(K40),ISNUMBER(L39)),K40+L39-L31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="M40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(L40),ISNUMBER(M39)),L40+M39-M31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="N40" s="21" t="str">
-        <f>IF(AND(ISNUMBER(M40),ISNUMBER(N39)),M40+N39-N31,"-")</f>
-        <v>-</v>
-      </c>
-      <c r="O40" s="27" t="str">
-        <f>N40</f>
-        <v>-</v>
-      </c>
-    </row>
-    <row r="42">
-      <c r="B42" s="18" t="inlineStr">
+      <c r="B40" s="18" t="inlineStr">
         <is>
           <t>01_입력 G 기존 생산계획 · 2027년 1~4월 확정 · 2028년 생산계획 38,412 kg</t>
         </is>
@@ -10596,14 +10030,14 @@
       <formula>C5="대정비"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C24:N24">
+  <conditionalFormatting sqref="C23:N23">
     <cfRule type="expression" priority="3" dxfId="0">
-      <formula>C24="대정비"</formula>
+      <formula>C23="대정비"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="C25:N25">
+  <conditionalFormatting sqref="C24:N24">
     <cfRule type="expression" priority="4" dxfId="1">
-      <formula>C24="대정비"</formula>
+      <formula>C23="대정비"</formula>
     </cfRule>
   </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10617,7 +10051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:Z15"/>
+  <dimension ref="B1:Z16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -10658,7 +10092,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>필요 선행재고 = 2027.1부터 누적 (생산 − 출하)의 최저값 (양품률 100% 기준 최소치).</t>
+          <t>재고 = 기초재고 (2027-01-01) + 생산 − 출하 · 2028년은 2027년 말 재고에서 이어짐.</t>
         </is>
       </c>
     </row>
@@ -10707,10 +10141,20 @@
       </c>
       <c r="I5" s="9" t="inlineStr">
         <is>
-          <t>누적 최저</t>
+          <t>'27 말 재고</t>
         </is>
       </c>
       <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>'28 말 재고</t>
+        </is>
+      </c>
+      <c r="K5" s="9" t="inlineStr">
+        <is>
+          <t>최저 재고</t>
+        </is>
+      </c>
+      <c r="L5" s="9" t="inlineStr">
         <is>
           <t>최저 시점</t>
         </is>
@@ -10724,34 +10168,42 @@
       </c>
       <c r="C6" s="21">
         <f>'05_월별_Capa기준'!O6</f>
-        <v>42175.2727272727</v>
+        <v>43039.2727272727</v>
       </c>
       <c r="D6" s="21">
-        <f>'05_월별_Capa기준'!O12</f>
-        <v>43400</v>
-      </c>
-      <c r="E6" s="41">
+        <f>'05_월별_Capa기준'!O14</f>
+        <v>41720</v>
+      </c>
+      <c r="E6" s="40">
         <f>C6-D6</f>
-        <v>-1224.72727272727</v>
+        <v>1319.27272727273</v>
       </c>
       <c r="F6" s="21">
-        <f>'05_월별_Capa기준'!O25</f>
-        <v>50200</v>
+        <f>'05_월별_Capa기준'!O24</f>
+        <v>51388</v>
       </c>
       <c r="G6" s="21">
-        <f>'05_월별_Capa기준'!O31</f>
+        <f>'05_월별_Capa기준'!O32</f>
         <v>45760</v>
       </c>
-      <c r="H6" s="41">
+      <c r="H6" s="40">
         <f>F6-G6</f>
-        <v>4440</v>
-      </c>
-      <c r="I6" s="41">
-        <f>MIN('05_월별_Capa기준'!$C$14:$N$14,'05_월별_Capa기준'!$C$33:$N$33)</f>
-        <v>-3461.33333333333</v>
-      </c>
-      <c r="J6" s="42">
-        <f>IF(MIN('05_월별_Capa기준'!$C$14:$N$14)&lt;=MIN('05_월별_Capa기준'!$C$33:$N$33),INDEX('05_월별_Capa기준'!$C$4:$N$4,MATCH(MIN('05_월별_Capa기준'!$C$14:$N$14),'05_월별_Capa기준'!$C$14:$N$14,0)),INDEX('05_월별_Capa기준'!$C$23:$N$23,MATCH(MIN('05_월별_Capa기준'!$C$33:$N$33),'05_월별_Capa기준'!$C$33:$N$33,0)))</f>
+        <v>5628</v>
+      </c>
+      <c r="I6" s="40">
+        <f>'05_월별_Capa기준'!N9</f>
+        <v>4201.27272727273</v>
+      </c>
+      <c r="J6" s="40">
+        <f>'05_월별_Capa기준'!N27</f>
+        <v>9829.27272727275</v>
+      </c>
+      <c r="K6" s="40">
+        <f>MIN('05_월별_Capa기준'!$C$9:$N$9,'05_월별_Capa기준'!$C$27:$N$27)</f>
+        <v>-579.333333333332</v>
+      </c>
+      <c r="L6" s="42">
+        <f>IF(MIN('05_월별_Capa기준'!$C$9:$N$9)&lt;=MIN('05_월별_Capa기준'!$C$27:$N$27),INDEX('05_월별_Capa기준'!$C$4:$N$4,MATCH(MIN('05_월별_Capa기준'!$C$9:$N$9),'05_월별_Capa기준'!$C$9:$N$9,0)),INDEX('05_월별_Capa기준'!$C$22:$N$22,MATCH(MIN('05_월별_Capa기준'!$C$27:$N$27),'05_월별_Capa기준'!$C$27:$N$27,0)))</f>
         <v>46478.0</v>
       </c>
     </row>
@@ -10766,638 +10218,656 @@
         <v>37224</v>
       </c>
       <c r="D7" s="21">
-        <f>'06_월별_생산계획'!O12</f>
-        <v>43400</v>
-      </c>
-      <c r="E7" s="41">
+        <f>'06_월별_생산계획'!O14</f>
+        <v>41720</v>
+      </c>
+      <c r="E7" s="40">
         <f>C7-D7</f>
-        <v>-6176</v>
+        <v>-4496</v>
       </c>
       <c r="F7" s="21">
-        <f>'06_월별_생산계획'!O25</f>
+        <f>'06_월별_생산계획'!O24</f>
         <v>38412</v>
       </c>
       <c r="G7" s="21">
-        <f>'06_월별_생산계획'!O31</f>
+        <f>'06_월별_생산계획'!O32</f>
         <v>45760</v>
       </c>
-      <c r="H7" s="41">
+      <c r="H7" s="40">
         <f>F7-G7</f>
         <v>-7348</v>
       </c>
-      <c r="I7" s="41">
-        <f>MIN('06_월별_생산계획'!$C$14:$N$14,'06_월별_생산계획'!$C$33:$N$33)</f>
-        <v>-13524</v>
-      </c>
-      <c r="J7" s="42">
-        <f>IF(MIN('06_월별_생산계획'!$C$14:$N$14)&lt;=MIN('06_월별_생산계획'!$C$33:$N$33),INDEX('06_월별_생산계획'!$C$4:$N$4,MATCH(MIN('06_월별_생산계획'!$C$14:$N$14),'06_월별_생산계획'!$C$14:$N$14,0)),INDEX('06_월별_생산계획'!$C$23:$N$23,MATCH(MIN('06_월별_생산계획'!$C$33:$N$33),'06_월별_생산계획'!$C$33:$N$33,0)))</f>
+      <c r="I7" s="40">
+        <f>'06_월별_생산계획'!N9</f>
+        <v>-1614</v>
+      </c>
+      <c r="J7" s="40">
+        <f>'06_월별_생산계획'!N27</f>
+        <v>-8961.99999999999</v>
+      </c>
+      <c r="K7" s="40">
+        <f>MIN('06_월별_생산계획'!$C$9:$N$9,'06_월별_생산계획'!$C$27:$N$27)</f>
+        <v>-8961.99999999999</v>
+      </c>
+      <c r="L7" s="42">
+        <f>IF(MIN('06_월별_생산계획'!$C$9:$N$9)&lt;=MIN('06_월별_생산계획'!$C$27:$N$27),INDEX('06_월별_생산계획'!$C$4:$N$4,MATCH(MIN('06_월별_생산계획'!$C$9:$N$9),'06_월별_생산계획'!$C$9:$N$9,0)),INDEX('06_월별_생산계획'!$C$22:$N$22,MATCH(MIN('06_월별_생산계획'!$C$27:$N$27),'06_월별_생산계획'!$C$27:$N$27,0)))</f>
         <v>47088.0</v>
       </c>
     </row>
-    <row r="9" ht="20" customHeight="1">
-      <c r="B9" s="7" t="inlineStr">
-        <is>
-          <t>② 월별 추이 (kg)</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="8" t="inlineStr">
+    <row r="8">
+      <c r="B8" s="10" t="inlineStr">
+        <is>
+          <t>기초재고 (2027-01-01)</t>
+        </is>
+      </c>
+      <c r="C8" s="21">
+        <f>INV_0</f>
+        <v>2882</v>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>② 월별 생산 · 출하 · 재고 (kg)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>월</t>
         </is>
       </c>
-      <c r="C10" s="43" t="n">
+      <c r="C11" s="43" t="n">
         <v>46388</v>
       </c>
-      <c r="D10" s="43" t="n">
+      <c r="D11" s="43" t="n">
         <v>46419</v>
       </c>
-      <c r="E10" s="43" t="n">
+      <c r="E11" s="43" t="n">
         <v>46447</v>
       </c>
-      <c r="F10" s="43" t="n">
+      <c r="F11" s="43" t="n">
         <v>46478</v>
       </c>
-      <c r="G10" s="43" t="n">
+      <c r="G11" s="43" t="n">
         <v>46508</v>
       </c>
-      <c r="H10" s="43" t="n">
+      <c r="H11" s="43" t="n">
         <v>46539</v>
       </c>
-      <c r="I10" s="43" t="n">
+      <c r="I11" s="43" t="n">
         <v>46569</v>
       </c>
-      <c r="J10" s="43" t="n">
+      <c r="J11" s="43" t="n">
         <v>46600</v>
       </c>
-      <c r="K10" s="43" t="n">
+      <c r="K11" s="43" t="n">
         <v>46631</v>
       </c>
-      <c r="L10" s="43" t="n">
+      <c r="L11" s="43" t="n">
         <v>46661</v>
       </c>
-      <c r="M10" s="43" t="n">
+      <c r="M11" s="43" t="n">
         <v>46692</v>
       </c>
-      <c r="N10" s="43" t="n">
+      <c r="N11" s="43" t="n">
         <v>46722</v>
       </c>
-      <c r="O10" s="43" t="n">
+      <c r="O11" s="43" t="n">
         <v>46753</v>
       </c>
-      <c r="P10" s="43" t="n">
+      <c r="P11" s="43" t="n">
         <v>46784</v>
       </c>
-      <c r="Q10" s="43" t="n">
+      <c r="Q11" s="43" t="n">
         <v>46813</v>
       </c>
-      <c r="R10" s="43" t="n">
+      <c r="R11" s="43" t="n">
         <v>46844</v>
       </c>
-      <c r="S10" s="43" t="n">
+      <c r="S11" s="43" t="n">
         <v>46874</v>
       </c>
-      <c r="T10" s="43" t="n">
+      <c r="T11" s="43" t="n">
         <v>46905</v>
       </c>
-      <c r="U10" s="43" t="n">
+      <c r="U11" s="43" t="n">
         <v>46935</v>
       </c>
-      <c r="V10" s="43" t="n">
+      <c r="V11" s="43" t="n">
         <v>46966</v>
       </c>
-      <c r="W10" s="43" t="n">
+      <c r="W11" s="43" t="n">
         <v>46997</v>
       </c>
-      <c r="X10" s="43" t="n">
+      <c r="X11" s="43" t="n">
         <v>47027</v>
       </c>
-      <c r="Y10" s="43" t="n">
+      <c r="Y11" s="43" t="n">
         <v>47058</v>
       </c>
-      <c r="Z10" s="43" t="n">
+      <c r="Z11" s="43" t="n">
         <v>47088</v>
       </c>
     </row>
-    <row r="11">
-      <c r="B11" s="10" t="inlineStr">
-        <is>
-          <t>Capa. 기준 생산</t>
-        </is>
-      </c>
-      <c r="C11" s="21">
+    <row r="12">
+      <c r="B12" s="10" t="inlineStr">
+        <is>
+          <t>출하</t>
+        </is>
+      </c>
+      <c r="C12" s="21">
+        <f>'05_월별_Capa기준'!C14</f>
+        <v>2753.33333333333</v>
+      </c>
+      <c r="D12" s="21">
+        <f>'05_월별_Capa기준'!D14</f>
+        <v>2753.33333333333</v>
+      </c>
+      <c r="E12" s="21">
+        <f>'05_월별_Capa기준'!E14</f>
+        <v>3333.33333333333</v>
+      </c>
+      <c r="F12" s="21">
+        <f>'05_월별_Capa기준'!F14</f>
+        <v>3333.33333333333</v>
+      </c>
+      <c r="G12" s="21">
+        <f>'05_월별_Capa기준'!G14</f>
+        <v>3333.33333333333</v>
+      </c>
+      <c r="H12" s="21">
+        <f>'05_월별_Capa기준'!H14</f>
+        <v>3333.33333333333</v>
+      </c>
+      <c r="I12" s="21">
+        <f>'05_월별_Capa기준'!I14</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="J12" s="21">
+        <f>'05_월별_Capa기준'!J14</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="K12" s="21">
+        <f>'05_월별_Capa기준'!K14</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="L12" s="21">
+        <f>'05_월별_Capa기준'!L14</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="M12" s="21">
+        <f>'05_월별_Capa기준'!M14</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="N12" s="21">
+        <f>'05_월별_Capa기준'!N14</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="O12" s="21">
+        <f>'05_월별_Capa기준'!C32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="P12" s="21">
+        <f>'05_월별_Capa기준'!D32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="Q12" s="21">
+        <f>'05_월별_Capa기준'!E32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="R12" s="21">
+        <f>'05_월별_Capa기준'!F32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="S12" s="21">
+        <f>'05_월별_Capa기준'!G32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="T12" s="21">
+        <f>'05_월별_Capa기준'!H32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="U12" s="21">
+        <f>'05_월별_Capa기준'!I32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="V12" s="21">
+        <f>'05_월별_Capa기준'!J32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="W12" s="21">
+        <f>'05_월별_Capa기준'!K32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="X12" s="21">
+        <f>'05_월별_Capa기준'!L32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="Y12" s="21">
+        <f>'05_월별_Capa기준'!M32</f>
+        <v>3813.33333333333</v>
+      </c>
+      <c r="Z12" s="21">
+        <f>'05_월별_Capa기준'!N32</f>
+        <v>3813.33333333333</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" s="10" t="inlineStr">
+        <is>
+          <t>① 생산 (Capa. 기준)</t>
+        </is>
+      </c>
+      <c r="C13" s="21">
         <f>'05_월별_Capa기준'!C6</f>
         <v>2178</v>
       </c>
-      <c r="D11" s="21">
+      <c r="D13" s="21">
         <f>'05_월별_Capa기준'!D6</f>
         <v>2178</v>
       </c>
-      <c r="E11" s="21">
+      <c r="E13" s="21">
         <f>'05_월별_Capa기준'!E6</f>
         <v>3168</v>
       </c>
-      <c r="F11" s="21">
+      <c r="F13" s="21">
         <f>'05_월별_Capa기준'!F6</f>
         <v>1188</v>
       </c>
-      <c r="G11" s="21">
+      <c r="G13" s="21">
         <f>'05_월별_Capa기준'!G6</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="H11" s="21">
+        <v>4290.90909090909</v>
+      </c>
+      <c r="H13" s="21">
         <f>'05_월별_Capa기준'!H6</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="I11" s="21">
+        <v>4290.90909090909</v>
+      </c>
+      <c r="I13" s="21">
         <f>'05_월별_Capa기준'!I6</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="J11" s="21">
+        <v>4290.90909090909</v>
+      </c>
+      <c r="J13" s="21">
         <f>'05_월별_Capa기준'!J6</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="K11" s="21">
+        <v>4290.90909090909</v>
+      </c>
+      <c r="K13" s="21">
         <f>'05_월별_Capa기준'!K6</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="L11" s="21">
+        <v>4290.90909090909</v>
+      </c>
+      <c r="L13" s="21">
         <f>'05_월별_Capa기준'!L6</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="M11" s="21">
+        <v>4290.90909090909</v>
+      </c>
+      <c r="M13" s="21">
         <f>'05_월별_Capa기준'!M6</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="N11" s="21">
+        <v>4290.90909090909</v>
+      </c>
+      <c r="N13" s="21">
         <f>'05_월별_Capa기준'!N6</f>
-        <v>4182.90909090909</v>
-      </c>
-      <c r="O11" s="21">
-        <f>'05_월별_Capa기준'!C25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="P11" s="21">
-        <f>'05_월별_Capa기준'!D25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="Q11" s="21">
-        <f>'05_월별_Capa기준'!E25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="R11" s="21">
-        <f>'05_월별_Capa기준'!F25</f>
+        <v>4290.90909090909</v>
+      </c>
+      <c r="O13" s="21">
+        <f>'05_월별_Capa기준'!C24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="P13" s="21">
+        <f>'05_월별_Capa기준'!D24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="Q13" s="21">
+        <f>'05_월별_Capa기준'!E24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="R13" s="21">
+        <f>'05_월별_Capa기준'!F24</f>
         <v>1188</v>
       </c>
-      <c r="S11" s="21">
-        <f>'05_월별_Capa기준'!G25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="T11" s="21">
-        <f>'05_월별_Capa기준'!H25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="U11" s="21">
-        <f>'05_월별_Capa기준'!I25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="V11" s="21">
-        <f>'05_월별_Capa기준'!J25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="W11" s="21">
-        <f>'05_월별_Capa기준'!K25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="X11" s="21">
-        <f>'05_월별_Capa기준'!L25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="Y11" s="21">
-        <f>'05_월별_Capa기준'!M25</f>
-        <v>4455.63636363636</v>
-      </c>
-      <c r="Z11" s="21">
-        <f>'05_월별_Capa기준'!N25</f>
-        <v>4455.63636363636</v>
-      </c>
-    </row>
-    <row r="12">
-      <c r="B12" s="10" t="inlineStr">
-        <is>
-          <t>기존 생산계획</t>
-        </is>
-      </c>
-      <c r="C12" s="21">
+      <c r="S13" s="21">
+        <f>'05_월별_Capa기준'!G24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="T13" s="21">
+        <f>'05_월별_Capa기준'!H24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="U13" s="21">
+        <f>'05_월별_Capa기준'!I24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="V13" s="21">
+        <f>'05_월별_Capa기준'!J24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="W13" s="21">
+        <f>'05_월별_Capa기준'!K24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="X13" s="21">
+        <f>'05_월별_Capa기준'!L24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="Y13" s="21">
+        <f>'05_월별_Capa기준'!M24</f>
+        <v>4563.63636363636</v>
+      </c>
+      <c r="Z13" s="21">
+        <f>'05_월별_Capa기준'!N24</f>
+        <v>4563.63636363636</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>① 재고</t>
+        </is>
+      </c>
+      <c r="C14" s="40">
+        <f>'05_월별_Capa기준'!C9</f>
+        <v>2306.66666666667</v>
+      </c>
+      <c r="D14" s="40">
+        <f>'05_월별_Capa기준'!D9</f>
+        <v>1731.33333333333</v>
+      </c>
+      <c r="E14" s="40">
+        <f>'05_월별_Capa기준'!E9</f>
+        <v>1566</v>
+      </c>
+      <c r="F14" s="40">
+        <f>'05_월별_Capa기준'!F9</f>
+        <v>-579.333333333332</v>
+      </c>
+      <c r="G14" s="40">
+        <f>'05_월별_Capa기준'!G9</f>
+        <v>378.242424242426</v>
+      </c>
+      <c r="H14" s="40">
+        <f>'05_월별_Capa기준'!H9</f>
+        <v>1335.81818181818</v>
+      </c>
+      <c r="I14" s="40">
+        <f>'05_월별_Capa기준'!I9</f>
+        <v>1813.39393939394</v>
+      </c>
+      <c r="J14" s="40">
+        <f>'05_월별_Capa기준'!J9</f>
+        <v>2290.9696969697</v>
+      </c>
+      <c r="K14" s="40">
+        <f>'05_월별_Capa기준'!K9</f>
+        <v>2768.54545454546</v>
+      </c>
+      <c r="L14" s="40">
+        <f>'05_월별_Capa기준'!L9</f>
+        <v>3246.12121212122</v>
+      </c>
+      <c r="M14" s="40">
+        <f>'05_월별_Capa기준'!M9</f>
+        <v>3723.69696969697</v>
+      </c>
+      <c r="N14" s="40">
+        <f>'05_월별_Capa기준'!N9</f>
+        <v>4201.27272727273</v>
+      </c>
+      <c r="O14" s="40">
+        <f>'05_월별_Capa기준'!C27</f>
+        <v>4951.57575757576</v>
+      </c>
+      <c r="P14" s="40">
+        <f>'05_월별_Capa기준'!D27</f>
+        <v>5701.87878787879</v>
+      </c>
+      <c r="Q14" s="40">
+        <f>'05_월별_Capa기준'!E27</f>
+        <v>6452.18181818183</v>
+      </c>
+      <c r="R14" s="40">
+        <f>'05_월별_Capa기준'!F27</f>
+        <v>3826.84848484849</v>
+      </c>
+      <c r="S14" s="40">
+        <f>'05_월별_Capa기준'!G27</f>
+        <v>4577.15151515152</v>
+      </c>
+      <c r="T14" s="40">
+        <f>'05_월별_Capa기준'!H27</f>
+        <v>5327.45454545455</v>
+      </c>
+      <c r="U14" s="40">
+        <f>'05_월별_Capa기준'!I27</f>
+        <v>6077.75757575759</v>
+      </c>
+      <c r="V14" s="40">
+        <f>'05_월별_Capa기준'!J27</f>
+        <v>6828.06060606062</v>
+      </c>
+      <c r="W14" s="40">
+        <f>'05_월별_Capa기준'!K27</f>
+        <v>7578.36363636365</v>
+      </c>
+      <c r="X14" s="40">
+        <f>'05_월별_Capa기준'!L27</f>
+        <v>8328.66666666668</v>
+      </c>
+      <c r="Y14" s="40">
+        <f>'05_월별_Capa기준'!M27</f>
+        <v>9078.96969696971</v>
+      </c>
+      <c r="Z14" s="40">
+        <f>'05_월별_Capa기준'!N27</f>
+        <v>9829.27272727275</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="10" t="inlineStr">
+        <is>
+          <t>② 생산 (기존 생산계획)</t>
+        </is>
+      </c>
+      <c r="C15" s="21">
         <f>'06_월별_생산계획'!C6</f>
         <v>2178</v>
       </c>
-      <c r="D12" s="21">
+      <c r="D15" s="21">
         <f>'06_월별_생산계획'!D6</f>
         <v>2178</v>
       </c>
-      <c r="E12" s="21">
+      <c r="E15" s="21">
         <f>'06_월별_생산계획'!E6</f>
         <v>3168</v>
       </c>
-      <c r="F12" s="21">
+      <c r="F15" s="21">
         <f>'06_월별_생산계획'!F6</f>
         <v>1188</v>
       </c>
-      <c r="G12" s="21">
+      <c r="G15" s="21">
         <f>'06_월별_생산계획'!G6</f>
         <v>3564</v>
       </c>
-      <c r="H12" s="21">
+      <c r="H15" s="21">
         <f>'06_월별_생산계획'!H6</f>
         <v>3564</v>
       </c>
-      <c r="I12" s="21">
+      <c r="I15" s="21">
         <f>'06_월별_생산계획'!I6</f>
         <v>3564</v>
       </c>
-      <c r="J12" s="21">
+      <c r="J15" s="21">
         <f>'06_월별_생산계획'!J6</f>
         <v>3564</v>
       </c>
-      <c r="K12" s="21">
+      <c r="K15" s="21">
         <f>'06_월별_생산계획'!K6</f>
         <v>3564</v>
       </c>
-      <c r="L12" s="21">
+      <c r="L15" s="21">
         <f>'06_월별_생산계획'!L6</f>
         <v>3564</v>
       </c>
-      <c r="M12" s="21">
+      <c r="M15" s="21">
         <f>'06_월별_생산계획'!M6</f>
         <v>3564</v>
       </c>
-      <c r="N12" s="21">
+      <c r="N15" s="21">
         <f>'06_월별_생산계획'!N6</f>
         <v>3564</v>
       </c>
-      <c r="O12" s="21">
-        <f>'06_월별_생산계획'!C25</f>
+      <c r="O15" s="21">
+        <f>'06_월별_생산계획'!C24</f>
         <v>3564</v>
       </c>
-      <c r="P12" s="21">
-        <f>'06_월별_생산계획'!D25</f>
+      <c r="P15" s="21">
+        <f>'06_월별_생산계획'!D24</f>
         <v>3564</v>
       </c>
-      <c r="Q12" s="21">
-        <f>'06_월별_생산계획'!E25</f>
+      <c r="Q15" s="21">
+        <f>'06_월별_생산계획'!E24</f>
         <v>3564</v>
       </c>
-      <c r="R12" s="21">
-        <f>'06_월별_생산계획'!F25</f>
+      <c r="R15" s="21">
+        <f>'06_월별_생산계획'!F24</f>
         <v>1188</v>
       </c>
-      <c r="S12" s="21">
-        <f>'06_월별_생산계획'!G25</f>
+      <c r="S15" s="21">
+        <f>'06_월별_생산계획'!G24</f>
         <v>3564</v>
       </c>
-      <c r="T12" s="21">
-        <f>'06_월별_생산계획'!H25</f>
+      <c r="T15" s="21">
+        <f>'06_월별_생산계획'!H24</f>
         <v>3564</v>
       </c>
-      <c r="U12" s="21">
-        <f>'06_월별_생산계획'!I25</f>
+      <c r="U15" s="21">
+        <f>'06_월별_생산계획'!I24</f>
         <v>3564</v>
       </c>
-      <c r="V12" s="21">
-        <f>'06_월별_생산계획'!J25</f>
+      <c r="V15" s="21">
+        <f>'06_월별_생산계획'!J24</f>
         <v>3168</v>
       </c>
-      <c r="W12" s="21">
-        <f>'06_월별_생산계획'!K25</f>
+      <c r="W15" s="21">
+        <f>'06_월별_생산계획'!K24</f>
         <v>3168</v>
       </c>
-      <c r="X12" s="21">
-        <f>'06_월별_생산계획'!L25</f>
+      <c r="X15" s="21">
+        <f>'06_월별_생산계획'!L24</f>
         <v>3168</v>
       </c>
-      <c r="Y12" s="21">
-        <f>'06_월별_생산계획'!M25</f>
+      <c r="Y15" s="21">
+        <f>'06_월별_생산계획'!M24</f>
         <v>3168</v>
       </c>
-      <c r="Z12" s="21">
-        <f>'06_월별_생산계획'!N25</f>
+      <c r="Z15" s="21">
+        <f>'06_월별_생산계획'!N24</f>
         <v>3168</v>
       </c>
     </row>
-    <row r="13">
-      <c r="B13" s="10" t="inlineStr">
-        <is>
-          <t>출하</t>
-        </is>
-      </c>
-      <c r="C13" s="21">
-        <f>'05_월별_Capa기준'!C12</f>
-        <v>2753.33333333333</v>
-      </c>
-      <c r="D13" s="21">
-        <f>'05_월별_Capa기준'!D12</f>
-        <v>2753.33333333333</v>
-      </c>
-      <c r="E13" s="21">
-        <f>'05_월별_Capa기준'!E12</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="F13" s="21">
-        <f>'05_월별_Capa기준'!F12</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="G13" s="21">
-        <f>'05_월별_Capa기준'!G12</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="H13" s="21">
-        <f>'05_월별_Capa기준'!H12</f>
-        <v>3333.33333333333</v>
-      </c>
-      <c r="I13" s="21">
-        <f>'05_월별_Capa기준'!I12</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="J13" s="21">
-        <f>'05_월별_Capa기준'!J12</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="K13" s="21">
-        <f>'05_월별_Capa기준'!K12</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="L13" s="21">
-        <f>'05_월별_Capa기준'!L12</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="M13" s="21">
-        <f>'05_월별_Capa기준'!M12</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="N13" s="21">
-        <f>'05_월별_Capa기준'!N12</f>
-        <v>4093.33333333333</v>
-      </c>
-      <c r="O13" s="21">
-        <f>'05_월별_Capa기준'!C31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="P13" s="21">
-        <f>'05_월별_Capa기준'!D31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="Q13" s="21">
-        <f>'05_월별_Capa기준'!E31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="R13" s="21">
-        <f>'05_월별_Capa기준'!F31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="S13" s="21">
-        <f>'05_월별_Capa기준'!G31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="T13" s="21">
-        <f>'05_월별_Capa기준'!H31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="U13" s="21">
-        <f>'05_월별_Capa기준'!I31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="V13" s="21">
-        <f>'05_월별_Capa기준'!J31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="W13" s="21">
-        <f>'05_월별_Capa기준'!K31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="X13" s="21">
-        <f>'05_월별_Capa기준'!L31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="Y13" s="21">
-        <f>'05_월별_Capa기준'!M31</f>
-        <v>3813.33333333333</v>
-      </c>
-      <c r="Z13" s="21">
-        <f>'05_월별_Capa기준'!N31</f>
-        <v>3813.33333333333</v>
-      </c>
-    </row>
-    <row r="14">
-      <c r="B14" s="10" t="inlineStr">
-        <is>
-          <t>누적 — Capa. 기준</t>
-        </is>
-      </c>
-      <c r="C14" s="38">
-        <f>'05_월별_Capa기준'!C14</f>
-        <v>-575.333333333333</v>
-      </c>
-      <c r="D14" s="38">
-        <f>'05_월별_Capa기준'!D14</f>
-        <v>-1150.66666666667</v>
-      </c>
-      <c r="E14" s="38">
-        <f>'05_월별_Capa기준'!E14</f>
-        <v>-1316</v>
-      </c>
-      <c r="F14" s="38">
-        <f>'05_월별_Capa기준'!F14</f>
-        <v>-3461.33333333333</v>
-      </c>
-      <c r="G14" s="38">
-        <f>'05_월별_Capa기준'!G14</f>
-        <v>-2611.75757575757</v>
-      </c>
-      <c r="H14" s="38">
-        <f>'05_월별_Capa기준'!H14</f>
-        <v>-1762.18181818182</v>
-      </c>
-      <c r="I14" s="38">
-        <f>'05_월별_Capa기준'!I14</f>
-        <v>-1672.60606060606</v>
-      </c>
-      <c r="J14" s="38">
-        <f>'05_월별_Capa기준'!J14</f>
-        <v>-1583.0303030303</v>
-      </c>
-      <c r="K14" s="38">
-        <f>'05_월별_Capa기준'!K14</f>
-        <v>-1493.45454545454</v>
-      </c>
-      <c r="L14" s="38">
-        <f>'05_월별_Capa기준'!L14</f>
-        <v>-1403.87878787878</v>
-      </c>
-      <c r="M14" s="38">
-        <f>'05_월별_Capa기준'!M14</f>
-        <v>-1314.30303030303</v>
-      </c>
-      <c r="N14" s="38">
-        <f>'05_월별_Capa기준'!N14</f>
-        <v>-1224.72727272727</v>
-      </c>
-      <c r="O14" s="38">
-        <f>'05_월별_Capa기준'!C33</f>
-        <v>-582.424242424238</v>
-      </c>
-      <c r="P14" s="38">
-        <f>'05_월별_Capa기준'!D33</f>
-        <v>59.8787878787934</v>
-      </c>
-      <c r="Q14" s="38">
-        <f>'05_월별_Capa기준'!E33</f>
-        <v>702.181818181824</v>
-      </c>
-      <c r="R14" s="38">
-        <f>'05_월별_Capa기준'!F33</f>
-        <v>-1923.15151515151</v>
-      </c>
-      <c r="S14" s="38">
-        <f>'05_월별_Capa기준'!G33</f>
-        <v>-1280.84848484848</v>
-      </c>
-      <c r="T14" s="38">
-        <f>'05_월별_Capa기준'!H33</f>
-        <v>-638.545454545447</v>
-      </c>
-      <c r="U14" s="38">
-        <f>'05_월별_Capa기준'!I33</f>
-        <v>3.75757575758416</v>
-      </c>
-      <c r="V14" s="38">
-        <f>'05_월별_Capa기준'!J33</f>
-        <v>646.060606060615</v>
-      </c>
-      <c r="W14" s="38">
-        <f>'05_월별_Capa기준'!K33</f>
-        <v>1288.36363636365</v>
-      </c>
-      <c r="X14" s="38">
-        <f>'05_월별_Capa기준'!L33</f>
-        <v>1930.66666666668</v>
-      </c>
-      <c r="Y14" s="38">
-        <f>'05_월별_Capa기준'!M33</f>
-        <v>2572.96969696971</v>
-      </c>
-      <c r="Z14" s="38">
-        <f>'05_월별_Capa기준'!N33</f>
-        <v>3215.27272727274</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="B15" s="10" t="inlineStr">
-        <is>
-          <t>누적 — 기존 생산계획</t>
-        </is>
-      </c>
-      <c r="C15" s="38">
-        <f>'06_월별_생산계획'!C14</f>
-        <v>-575.333333333333</v>
-      </c>
-      <c r="D15" s="38">
-        <f>'06_월별_생산계획'!D14</f>
-        <v>-1150.66666666667</v>
-      </c>
-      <c r="E15" s="38">
-        <f>'06_월별_생산계획'!E14</f>
-        <v>-1316</v>
-      </c>
-      <c r="F15" s="38">
-        <f>'06_월별_생산계획'!F14</f>
-        <v>-3461.33333333333</v>
-      </c>
-      <c r="G15" s="38">
-        <f>'06_월별_생산계획'!G14</f>
-        <v>-3230.66666666667</v>
-      </c>
-      <c r="H15" s="38">
-        <f>'06_월별_생산계획'!H14</f>
-        <v>-3000</v>
-      </c>
-      <c r="I15" s="38">
-        <f>'06_월별_생산계획'!I14</f>
-        <v>-3529.33333333333</v>
-      </c>
-      <c r="J15" s="38">
-        <f>'06_월별_생산계획'!J14</f>
-        <v>-4058.66666666666</v>
-      </c>
-      <c r="K15" s="38">
-        <f>'06_월별_생산계획'!K14</f>
-        <v>-4588</v>
-      </c>
-      <c r="L15" s="38">
-        <f>'06_월별_생산계획'!L14</f>
-        <v>-5117.33333333333</v>
-      </c>
-      <c r="M15" s="38">
-        <f>'06_월별_생산계획'!M14</f>
-        <v>-5646.66666666666</v>
-      </c>
-      <c r="N15" s="38">
-        <f>'06_월별_생산계획'!N14</f>
-        <v>-6176</v>
-      </c>
-      <c r="O15" s="38">
-        <f>'06_월별_생산계획'!C33</f>
-        <v>-6425.33333333333</v>
-      </c>
-      <c r="P15" s="38">
-        <f>'06_월별_생산계획'!D33</f>
-        <v>-6674.66666666666</v>
-      </c>
-      <c r="Q15" s="38">
-        <f>'06_월별_생산계획'!E33</f>
-        <v>-6924</v>
-      </c>
-      <c r="R15" s="38">
-        <f>'06_월별_생산계획'!F33</f>
-        <v>-9549.33333333333</v>
-      </c>
-      <c r="S15" s="38">
-        <f>'06_월별_생산계획'!G33</f>
-        <v>-9798.66666666666</v>
-      </c>
-      <c r="T15" s="38">
-        <f>'06_월별_생산계획'!H33</f>
-        <v>-10048</v>
-      </c>
-      <c r="U15" s="38">
-        <f>'06_월별_생산계획'!I33</f>
-        <v>-10297.3333333333</v>
-      </c>
-      <c r="V15" s="38">
-        <f>'06_월별_생산계획'!J33</f>
-        <v>-10942.6666666667</v>
-      </c>
-      <c r="W15" s="38">
-        <f>'06_월별_생산계획'!K33</f>
-        <v>-11588</v>
-      </c>
-      <c r="X15" s="38">
-        <f>'06_월별_생산계획'!L33</f>
-        <v>-12233.3333333333</v>
-      </c>
-      <c r="Y15" s="38">
-        <f>'06_월별_생산계획'!M33</f>
-        <v>-12878.6666666667</v>
-      </c>
-      <c r="Z15" s="38">
-        <f>'06_월별_생산계획'!N33</f>
-        <v>-13524</v>
+    <row r="16">
+      <c r="B16" s="29" t="inlineStr">
+        <is>
+          <t>② 재고</t>
+        </is>
+      </c>
+      <c r="C16" s="40">
+        <f>'06_월별_생산계획'!C9</f>
+        <v>2306.66666666667</v>
+      </c>
+      <c r="D16" s="40">
+        <f>'06_월별_생산계획'!D9</f>
+        <v>1731.33333333333</v>
+      </c>
+      <c r="E16" s="40">
+        <f>'06_월별_생산계획'!E9</f>
+        <v>1566</v>
+      </c>
+      <c r="F16" s="40">
+        <f>'06_월별_생산계획'!F9</f>
+        <v>-579.333333333332</v>
+      </c>
+      <c r="G16" s="40">
+        <f>'06_월별_생산계획'!G9</f>
+        <v>-348.666666666665</v>
+      </c>
+      <c r="H16" s="40">
+        <f>'06_월별_생산계획'!H9</f>
+        <v>-117.999999999998</v>
+      </c>
+      <c r="I16" s="40">
+        <f>'06_월별_생산계획'!I9</f>
+        <v>-367.333333333331</v>
+      </c>
+      <c r="J16" s="40">
+        <f>'06_월별_생산계획'!J9</f>
+        <v>-616.666666666664</v>
+      </c>
+      <c r="K16" s="40">
+        <f>'06_월별_생산계획'!K9</f>
+        <v>-865.999999999997</v>
+      </c>
+      <c r="L16" s="40">
+        <f>'06_월별_생산계획'!L9</f>
+        <v>-1115.33333333333</v>
+      </c>
+      <c r="M16" s="40">
+        <f>'06_월별_생산계획'!M9</f>
+        <v>-1364.66666666666</v>
+      </c>
+      <c r="N16" s="40">
+        <f>'06_월별_생산계획'!N9</f>
+        <v>-1614</v>
+      </c>
+      <c r="O16" s="40">
+        <f>'06_월별_생산계획'!C27</f>
+        <v>-1863.33333333333</v>
+      </c>
+      <c r="P16" s="40">
+        <f>'06_월별_생산계획'!D27</f>
+        <v>-2112.66666666666</v>
+      </c>
+      <c r="Q16" s="40">
+        <f>'06_월별_생산계획'!E27</f>
+        <v>-2362</v>
+      </c>
+      <c r="R16" s="40">
+        <f>'06_월별_생산계획'!F27</f>
+        <v>-4987.33333333333</v>
+      </c>
+      <c r="S16" s="40">
+        <f>'06_월별_생산계획'!G27</f>
+        <v>-5236.66666666666</v>
+      </c>
+      <c r="T16" s="40">
+        <f>'06_월별_생산계획'!H27</f>
+        <v>-5485.99999999999</v>
+      </c>
+      <c r="U16" s="40">
+        <f>'06_월별_생산계획'!I27</f>
+        <v>-5735.33333333333</v>
+      </c>
+      <c r="V16" s="40">
+        <f>'06_월별_생산계획'!J27</f>
+        <v>-6380.66666666666</v>
+      </c>
+      <c r="W16" s="40">
+        <f>'06_월별_생산계획'!K27</f>
+        <v>-7025.99999999999</v>
+      </c>
+      <c r="X16" s="40">
+        <f>'06_월별_생산계획'!L27</f>
+        <v>-7671.33333333333</v>
+      </c>
+      <c r="Y16" s="40">
+        <f>'06_월별_생산계획'!M27</f>
+        <v>-8316.66666666666</v>
+      </c>
+      <c r="Z16" s="40">
+        <f>'06_월별_생산계획'!N27</f>
+        <v>-8961.99999999999</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -11544,7 +11014,7 @@
         <f>N('01_입력'!$N$87)+N('01_입력'!$N$88)</f>
         <v>1420</v>
       </c>
-      <c r="O5" s="27">
+      <c r="O5" s="26">
         <f>SUM(C5:N5)</f>
         <v>16980</v>
       </c>
@@ -12538,7 +12008,7 @@
         <f>N('01_입력'!$N$94)+N('01_입력'!$N$95)</f>
         <v>2673.33333333333</v>
       </c>
-      <c r="O23" s="27">
+      <c r="O23" s="26">
         <f>SUM(C23:N23)</f>
         <v>29720</v>
       </c>
@@ -12870,31 +12340,31 @@
       </c>
       <c r="I29" s="32">
         <f>N('01_입력'!$I$96)/KG_EZ</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J29" s="32">
         <f>N('01_입력'!$J$96)/KG_EZ</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="K29" s="32">
         <f>N('01_입력'!$K$96)/KG_EZ</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="L29" s="32">
         <f>N('01_입력'!$L$96)/KG_EZ</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="M29" s="32">
         <f>N('01_입력'!$M$96)/KG_EZ</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="N29" s="32">
         <f>N('01_입력'!$N$96)/KG_EZ</f>
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="O29" s="35">
         <f>SUM(C29:N29)</f>
-        <v>72</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30">
@@ -12989,31 +12459,31 @@
       </c>
       <c r="I31" s="17">
         <f>I29*IF(AND(I30="ARS",ISNUMBER(ARS_EZ_T)),ARS_EZ_T,FILL_EZ)</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="J31" s="17">
         <f>J29*IF(AND(J30="ARS",ISNUMBER(ARS_EZ_T)),ARS_EZ_T,FILL_EZ)</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="K31" s="17">
         <f>K29*IF(AND(K30="ARS",ISNUMBER(ARS_EZ_T)),ARS_EZ_T,FILL_EZ)</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="L31" s="17">
         <f>L29*IF(AND(L30="ARS",ISNUMBER(ARS_EZ_T)),ARS_EZ_T,FILL_EZ)</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="M31" s="17">
         <f>M29*IF(AND(M30="ARS",ISNUMBER(ARS_EZ_T)),ARS_EZ_T,FILL_EZ)</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="N31" s="17">
         <f>N29*IF(AND(N30="ARS",ISNUMBER(ARS_EZ_T)),ARS_EZ_T,FILL_EZ)</f>
-        <v>64</v>
+        <v>48</v>
       </c>
       <c r="O31" s="13">
         <f>SUM(C31:N31)</f>
-        <v>576</v>
+        <v>480</v>
       </c>
     </row>
     <row r="32">
@@ -13226,31 +12696,31 @@
       </c>
       <c r="I35" s="13">
         <f>I31+I34</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="J35" s="13">
         <f>J31+J34</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="K35" s="13">
         <f>K31+K34</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="L35" s="13">
         <f>L31+L34</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="M35" s="13">
         <f>M31+M34</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="N35" s="13">
         <f>N31+N34</f>
-        <v>80</v>
+        <v>64</v>
       </c>
       <c r="O35" s="13">
         <f>SUM(C35:N35)</f>
-        <v>768</v>
+        <v>672</v>
       </c>
     </row>
     <row r="36">
@@ -13285,31 +12755,31 @@
       </c>
       <c r="I36" s="17">
         <f>(I29+I32)*OQC_200</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="J36" s="17">
         <f>(J29+J32)*OQC_200</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="K36" s="17">
         <f>(K29+K32)*OQC_200</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="L36" s="17">
         <f>(L29+L32)*OQC_200</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="M36" s="17">
         <f>(M29+M32)*OQC_200</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="N36" s="17">
         <f>(N29+N32)*OQC_200</f>
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="O36" s="13">
         <f>SUM(C36:N36)</f>
-        <v>192</v>
+        <v>168</v>
       </c>
     </row>
     <row r="37">
@@ -13344,31 +12814,31 @@
       </c>
       <c r="I37" s="32">
         <f>(N('01_입력'!$I$94)+N('01_입력'!$I$95)+N('01_입력'!$I$96)+N('01_입력'!$I$97))/KG_B</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="J37" s="32">
         <f>(N('01_입력'!$J$94)+N('01_입력'!$J$95)+N('01_입력'!$J$96)+N('01_입력'!$J$97))/KG_B</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="K37" s="32">
         <f>(N('01_입력'!$K$94)+N('01_입력'!$K$95)+N('01_입력'!$K$96)+N('01_입력'!$K$97))/KG_B</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="L37" s="32">
         <f>(N('01_입력'!$L$94)+N('01_입력'!$L$95)+N('01_입력'!$L$96)+N('01_입력'!$L$97))/KG_B</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="M37" s="32">
         <f>(N('01_입력'!$M$94)+N('01_입력'!$M$95)+N('01_입력'!$M$96)+N('01_입력'!$M$97))/KG_B</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="N37" s="32">
         <f>(N('01_입력'!$N$94)+N('01_입력'!$N$95)+N('01_입력'!$N$96)+N('01_입력'!$N$97))/KG_B</f>
-        <v>21.5438596491228</v>
+        <v>20.0701754385965</v>
       </c>
       <c r="O37" s="35">
         <f>SUM(C37:N37)</f>
-        <v>228.421052631579</v>
+        <v>219.578947368421</v>
       </c>
     </row>
     <row r="38">
@@ -13403,31 +12873,31 @@
       </c>
       <c r="I38" s="17">
         <f>I37*(T_PQC+T_FQC)</f>
-        <v>172.350877192982</v>
+        <v>160.561403508772</v>
       </c>
       <c r="J38" s="17">
         <f>J37*(T_PQC+T_FQC)</f>
-        <v>172.350877192982</v>
+        <v>160.561403508772</v>
       </c>
       <c r="K38" s="17">
         <f>K37*(T_PQC+T_FQC)</f>
-        <v>172.350877192982</v>
+        <v>160.561403508772</v>
       </c>
       <c r="L38" s="17">
         <f>L37*(T_PQC+T_FQC)</f>
-        <v>172.350877192982</v>
+        <v>160.561403508772</v>
       </c>
       <c r="M38" s="17">
         <f>M37*(T_PQC+T_FQC)</f>
-        <v>172.350877192982</v>
+        <v>160.561403508772</v>
       </c>
       <c r="N38" s="17">
         <f>N37*(T_PQC+T_FQC)</f>
-        <v>172.350877192982</v>
+        <v>160.561403508772</v>
       </c>
       <c r="O38" s="13">
         <f>SUM(C38:N38)</f>
-        <v>1827.36842105263</v>
+        <v>1756.63157894737</v>
       </c>
     </row>
     <row r="40">
@@ -13532,7 +13002,7 @@
         <f>N('01_입력'!$N$101)+N('01_입력'!$N$102)</f>
         <v>2673.33333333333</v>
       </c>
-      <c r="O41" s="27">
+      <c r="O41" s="26">
         <f>SUM(C41:N41)</f>
         <v>32080</v>
       </c>
@@ -14815,7 +14285,7 @@
       </c>
       <c r="D19" s="47" t="inlineStr">
         <is>
-          <t>고객별 출하계획 (43.4 / 45.76톤) 유지</t>
+          <t>고객별 출하계획 (2027 41.72 / 2028 45.76톤) 유지</t>
         </is>
       </c>
       <c r="E19" s="47" t="inlineStr">
@@ -14889,14 +14359,14 @@
           <t>약 160~170 kg</t>
         </is>
       </c>
-      <c r="D23" s="23" t="n"/>
-      <c r="E23" s="23" t="n"/>
+      <c r="D23" s="28" t="n"/>
+      <c r="E23" s="28" t="n"/>
       <c r="F23" s="21">
         <f>IF(COUNT(D23:E23)=0,"",N(D23)+N(E23))</f>
       </c>
-      <c r="G23" s="23" t="n"/>
-      <c r="H23" s="23" t="n"/>
-      <c r="I23" s="23" t="n"/>
+      <c r="G23" s="28" t="n"/>
+      <c r="H23" s="28" t="n"/>
+      <c r="I23" s="28" t="n"/>
       <c r="J23" s="44">
         <f>IF(AND(ISNUMBER(F23),ISNUMBER(G23)),G23/F23,"")</f>
       </c>
@@ -14912,14 +14382,14 @@
           <t>약 220 kg</t>
         </is>
       </c>
-      <c r="D24" s="23" t="n"/>
-      <c r="E24" s="23" t="n"/>
+      <c r="D24" s="28" t="n"/>
+      <c r="E24" s="28" t="n"/>
       <c r="F24" s="21">
         <f>IF(COUNT(D24:E24)=0,"",N(D24)+N(E24))</f>
       </c>
-      <c r="G24" s="23" t="n"/>
-      <c r="H24" s="23" t="n"/>
-      <c r="I24" s="23" t="n"/>
+      <c r="G24" s="28" t="n"/>
+      <c r="H24" s="28" t="n"/>
+      <c r="I24" s="28" t="n"/>
       <c r="J24" s="44">
         <f>IF(AND(ISNUMBER(F24),ISNUMBER(G24)),G24/F24,"")</f>
       </c>
@@ -14935,14 +14405,14 @@
           <t>약 195~200 kg (197 kg)</t>
         </is>
       </c>
-      <c r="D25" s="23" t="n"/>
-      <c r="E25" s="23" t="n"/>
+      <c r="D25" s="28" t="n"/>
+      <c r="E25" s="28" t="n"/>
       <c r="F25" s="21">
         <f>IF(COUNT(D25:E25)=0,"",N(D25)+N(E25))</f>
       </c>
-      <c r="G25" s="23" t="n"/>
-      <c r="H25" s="23" t="n"/>
-      <c r="I25" s="23" t="n"/>
+      <c r="G25" s="28" t="n"/>
+      <c r="H25" s="28" t="n"/>
+      <c r="I25" s="28" t="n"/>
       <c r="J25" s="44">
         <f>IF(AND(ISNUMBER(F25),ISNUMBER(G25)),G25/F25,"")</f>
       </c>
@@ -14958,14 +14428,14 @@
           <t>200 kg × 75~80% ≈ 150~160 kg</t>
         </is>
       </c>
-      <c r="D26" s="23" t="n"/>
-      <c r="E26" s="23" t="n"/>
+      <c r="D26" s="28" t="n"/>
+      <c r="E26" s="28" t="n"/>
       <c r="F26" s="21">
         <f>IF(COUNT(D26:E26)=0,"",N(D26)+N(E26))</f>
       </c>
-      <c r="G26" s="23" t="n"/>
-      <c r="H26" s="23" t="n"/>
-      <c r="I26" s="23" t="n"/>
+      <c r="G26" s="28" t="n"/>
+      <c r="H26" s="28" t="n"/>
+      <c r="I26" s="28" t="n"/>
       <c r="J26" s="44">
         <f>IF(AND(ISNUMBER(F26),ISNUMBER(G26)),G26/F26,"")</f>
       </c>
@@ -14981,14 +14451,14 @@
           <t>추가 투입 제한</t>
         </is>
       </c>
-      <c r="D27" s="23" t="n"/>
-      <c r="E27" s="23" t="n"/>
+      <c r="D27" s="28" t="n"/>
+      <c r="E27" s="28" t="n"/>
       <c r="F27" s="21">
         <f>IF(COUNT(D27:E27)=0,"",N(D27)+N(E27))</f>
       </c>
-      <c r="G27" s="23" t="n"/>
-      <c r="H27" s="23" t="n"/>
-      <c r="I27" s="23" t="n"/>
+      <c r="G27" s="28" t="n"/>
+      <c r="H27" s="28" t="n"/>
+      <c r="I27" s="28" t="n"/>
       <c r="J27" s="44">
         <f>IF(AND(ISNUMBER(F27),ISNUMBER(G27)),G27/F27,"")</f>
       </c>

--- a/SKTC_CpZr_Capacity_RawData_Calculation_2026_2028.xlsx
+++ b/SKTC_CpZr_Capacity_RawData_Calculation_2026_2028.xlsx
@@ -49,21 +49,24 @@
     <definedName name="ARS_HS_S">'01_입력'!$C$40</definedName>
     <definedName name="ARS_EZ_T">'01_입력'!$C$41</definedName>
     <definedName name="ARS_HS_T">'01_입력'!$C$42</definedName>
-    <definedName name="WH_DAY">'01_입력'!$C$43</definedName>
-    <definedName name="WD_MON">'01_입력'!$C$44</definedName>
-    <definedName name="FILL_5G_EL">'01_입력'!$C$45</definedName>
-    <definedName name="B_SIZE">'01_입력'!$C$59</definedName>
-    <definedName name="B_YIELD">'01_입력'!$C$60</definedName>
-    <definedName name="KG_B">'01_입력'!$C$61</definedName>
-    <definedName name="B_TIME">'01_입력'!$C$62</definedName>
-    <definedName name="UNIT_RM">'01_입력'!$C$63</definedName>
-    <definedName name="MB_ONE">'01_입력'!$C$64</definedName>
-    <definedName name="MB_TWO">'01_입력'!$C$65</definedName>
-    <definedName name="MB_MAINT">'01_입력'!$C$66</definedName>
-    <definedName name="CAPA_NOW">'01_입력'!$C$70</definedName>
-    <definedName name="CAPA_ADD">'01_입력'!$C$71</definedName>
-    <definedName name="CAPA_RF">'01_입력'!$C$72</definedName>
-    <definedName name="CAPA_TWO">'01_입력'!$C$73</definedName>
+    <definedName name="SH_START">'01_입력'!$C$43</definedName>
+    <definedName name="SH_END">'01_입력'!$C$44</definedName>
+    <definedName name="SH_LUNCH">'01_입력'!$C$45</definedName>
+    <definedName name="WH_DAY">'01_입력'!$C$46</definedName>
+    <definedName name="WD_MON">'01_입력'!$C$47</definedName>
+    <definedName name="FILL_5G_EL">'01_입력'!$C$48</definedName>
+    <definedName name="B_SIZE">'01_입력'!$C$62</definedName>
+    <definedName name="B_YIELD">'01_입력'!$C$63</definedName>
+    <definedName name="KG_B">'01_입력'!$C$64</definedName>
+    <definedName name="B_TIME">'01_입력'!$C$65</definedName>
+    <definedName name="UNIT_RM">'01_입력'!$C$66</definedName>
+    <definedName name="MB_ONE">'01_입력'!$C$67</definedName>
+    <definedName name="MB_TWO">'01_입력'!$C$68</definedName>
+    <definedName name="MB_MAINT">'01_입력'!$C$69</definedName>
+    <definedName name="CAPA_NOW">'01_입력'!$C$73</definedName>
+    <definedName name="CAPA_ADD">'01_입력'!$C$74</definedName>
+    <definedName name="CAPA_RF">'01_입력'!$C$75</definedName>
+    <definedName name="CAPA_TWO">'01_입력'!$C$76</definedName>
     <definedName name="PL_B">'03_Batch주기'!$C$19</definedName>
     <definedName name="PL_KG">'03_Batch주기'!$C$20</definedName>
     <definedName name="CYC_ASIS">'03_Batch주기'!$C$21</definedName>
@@ -783,7 +786,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:M89"/>
+  <dimension ref="B1:M92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2" customWidth="1" min="1" max="1"/>
@@ -1396,7 +1399,7 @@
         </is>
       </c>
       <c r="C41" s="17">
-        <f>IF(COUNT(C48:C53)=0,"",SUM(C48:C53))</f>
+        <f>IF(COUNT(C51:C56)=0,"",SUM(C51:C56))</f>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
@@ -1416,7 +1419,7 @@
         </is>
       </c>
       <c r="C42" s="17">
-        <f>IF(COUNT(D48:D53)=0,"",SUM(D48:D53))</f>
+        <f>IF(COUNT(D51:D56)=0,"",SUM(D51:D56))</f>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
@@ -1432,35 +1435,35 @@
     <row r="43">
       <c r="B43" s="10" t="inlineStr">
         <is>
-          <t>글로브 박스 근무시간</t>
-        </is>
-      </c>
-      <c r="C43" s="11" t="n">
+          <t>충진 근무 시작 (상근조)</t>
+        </is>
+      </c>
+      <c r="C43" s="14" t="n">
         <v>8</v>
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>h/일</t>
+          <t>시</t>
         </is>
       </c>
       <c r="E43" s="12" t="inlineStr">
         <is>
-          <t>1교대 기준</t>
+          <t>충진은 보통 상근조만 진행</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="B44" s="10" t="inlineStr">
         <is>
-          <t>월 근무일</t>
+          <t>충진 근무 종료 (상근조)</t>
         </is>
       </c>
       <c r="C44" s="14" t="n">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>일/월</t>
+          <t>시</t>
         </is>
       </c>
       <c r="E44" s="12" t="inlineStr"/>
@@ -1468,11 +1471,11 @@
     <row r="45">
       <c r="B45" s="10" t="inlineStr">
         <is>
-          <t>5 Gal 9병 충진 경과 (근무시간 반영)</t>
+          <t>점심시간 (12:00~13:00)</t>
         </is>
       </c>
       <c r="C45" s="11" t="n">
-        <v>48</v>
+        <v>1</v>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
@@ -1481,66 +1484,93 @@
       </c>
       <c r="E45" s="12" t="inlineStr">
         <is>
-          <t>현장 설명 약 2일 (작업 18 h)</t>
+          <t>근무시간에서 제외</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="B46" s="10" t="inlineStr">
+        <is>
+          <t>충진 근무시간 (상근조)</t>
+        </is>
+      </c>
+      <c r="C46" s="17">
+        <f>SH_END-SH_START-SH_LUNCH</f>
+        <v>8</v>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>h/일</t>
+        </is>
+      </c>
+      <c r="E46" s="12" t="inlineStr">
+        <is>
+          <t>08:00~17:00 − 점심 1 h = 8 h/일</t>
         </is>
       </c>
     </row>
     <row r="47">
-      <c r="B47" s="8" t="inlineStr">
-        <is>
-          <t>ARS 작업 단계 (h/용기)</t>
-        </is>
-      </c>
-      <c r="C47" s="9" t="inlineStr">
-        <is>
-          <t>이지켐</t>
-        </is>
-      </c>
-      <c r="D47" s="9" t="inlineStr">
-        <is>
-          <t>한솔</t>
-        </is>
-      </c>
-      <c r="E47" s="8" t="inlineStr">
-        <is>
-          <t>수동과 ARS의 전체 시간 차이 확인용</t>
-        </is>
-      </c>
+      <c r="B47" s="10" t="inlineStr">
+        <is>
+          <t>월 근무일</t>
+        </is>
+      </c>
+      <c r="C47" s="14" t="n">
+        <v>22</v>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>일/월</t>
+        </is>
+      </c>
+      <c r="E47" s="12" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="B48" s="10" t="inlineStr">
         <is>
-          <t>용기 준비</t>
-        </is>
-      </c>
-      <c r="C48" s="16" t="n"/>
-      <c r="D48" s="16" t="n"/>
-      <c r="E48" s="18" t="inlineStr"/>
-    </row>
-    <row r="49">
-      <c r="B49" s="10" t="inlineStr">
-        <is>
-          <t>투입·반출</t>
-        </is>
-      </c>
-      <c r="C49" s="16" t="n"/>
-      <c r="D49" s="16" t="n"/>
-      <c r="E49" s="18" t="inlineStr"/>
+          <t>5 Gal 9병 충진 경과 (상근조 기준)</t>
+        </is>
+      </c>
+      <c r="C48" s="11" t="n">
+        <v>48</v>
+      </c>
+      <c r="D48" s="5" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E48" s="12" t="inlineStr">
+        <is>
+          <t>18 h ÷ 상근조 8 h/일 = 2.25 근무일 → 현장 설명 약 2일 (48 h)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
-      <c r="B50" s="10" t="inlineStr">
-        <is>
-          <t>퍼지</t>
-        </is>
-      </c>
-      <c r="C50" s="16" t="n"/>
-      <c r="D50" s="16" t="n"/>
-      <c r="E50" s="18" t="inlineStr"/>
+      <c r="B50" s="8" t="inlineStr">
+        <is>
+          <t>ARS 작업 단계 (h/용기)</t>
+        </is>
+      </c>
+      <c r="C50" s="9" t="inlineStr">
+        <is>
+          <t>이지켐</t>
+        </is>
+      </c>
+      <c r="D50" s="9" t="inlineStr">
+        <is>
+          <t>한솔</t>
+        </is>
+      </c>
+      <c r="E50" s="8" t="inlineStr">
+        <is>
+          <t>수동과 ARS의 전체 시간 차이 확인용</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="B51" s="10" t="inlineStr">
         <is>
-          <t>실제 충진</t>
+          <t>용기 준비</t>
         </is>
       </c>
       <c r="C51" s="16" t="n"/>
@@ -1550,7 +1580,7 @@
     <row r="52">
       <c r="B52" s="10" t="inlineStr">
         <is>
-          <t>설비 전환</t>
+          <t>투입·반출</t>
         </is>
       </c>
       <c r="C52" s="16" t="n"/>
@@ -1560,7 +1590,7 @@
     <row r="53">
       <c r="B53" s="10" t="inlineStr">
         <is>
-          <t>검사·OQC</t>
+          <t>퍼지</t>
         </is>
       </c>
       <c r="C53" s="16" t="n"/>
@@ -1570,7 +1600,7 @@
     <row r="54">
       <c r="B54" s="10" t="inlineStr">
         <is>
-          <t>작업자 투입시간</t>
+          <t>실제 충진</t>
         </is>
       </c>
       <c r="C54" s="16" t="n"/>
@@ -1580,456 +1610,486 @@
     <row r="55">
       <c r="B55" s="10" t="inlineStr">
         <is>
-          <t>설비 점유시간</t>
+          <t>설비 전환</t>
         </is>
       </c>
       <c r="C55" s="16" t="n"/>
       <c r="D55" s="16" t="n"/>
       <c r="E55" s="18" t="inlineStr"/>
     </row>
-    <row r="57" ht="20" customHeight="1">
-      <c r="B57" s="7" t="inlineStr">
+    <row r="56">
+      <c r="B56" s="10" t="inlineStr">
+        <is>
+          <t>검사·OQC</t>
+        </is>
+      </c>
+      <c r="C56" s="16" t="n"/>
+      <c r="D56" s="16" t="n"/>
+      <c r="E56" s="18" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="B57" s="10" t="inlineStr">
+        <is>
+          <t>작업자 투입시간</t>
+        </is>
+      </c>
+      <c r="C57" s="16" t="n"/>
+      <c r="D57" s="16" t="n"/>
+      <c r="E57" s="18" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="B58" s="10" t="inlineStr">
+        <is>
+          <t>설비 점유시간</t>
+        </is>
+      </c>
+      <c r="C58" s="16" t="n"/>
+      <c r="D58" s="16" t="n"/>
+      <c r="E58" s="18" t="inlineStr"/>
+    </row>
+    <row r="60" ht="20" customHeight="1">
+      <c r="B60" s="7" t="inlineStr">
         <is>
           <t>D. Batch 생산량 (생산팀 협의)</t>
         </is>
       </c>
     </row>
-    <row r="58">
-      <c r="B58" s="8" t="inlineStr">
+    <row r="61">
+      <c r="B61" s="8" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C58" s="9" t="inlineStr">
+      <c r="C61" s="9" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D58" s="9" t="inlineStr">
+      <c r="D61" s="9" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="E58" s="8" t="inlineStr">
+      <c r="E61" s="8" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
     </row>
-    <row r="59">
-      <c r="B59" s="10" t="inlineStr">
+    <row r="62">
+      <c r="B62" s="10" t="inlineStr">
         <is>
           <t>Batch size</t>
         </is>
       </c>
-      <c r="C59" s="14" t="n">
+      <c r="C62" s="14" t="n">
         <v>200</v>
       </c>
-      <c r="D59" s="5" t="inlineStr">
+      <c r="D62" s="5" t="inlineStr">
         <is>
           <t>kg</t>
         </is>
       </c>
-      <c r="E59" s="12" t="inlineStr">
+      <c r="E62" s="12" t="inlineStr">
         <is>
           <t>생산팀 협의</t>
         </is>
       </c>
     </row>
-    <row r="60">
-      <c r="B60" s="10" t="inlineStr">
+    <row r="63">
+      <c r="B63" s="10" t="inlineStr">
         <is>
           <t>Yield</t>
         </is>
       </c>
-      <c r="C60" s="19" t="n">
+      <c r="C63" s="19" t="n">
         <v>0.99</v>
       </c>
-      <c r="D60" s="5" t="inlineStr">
+      <c r="D63" s="5" t="inlineStr">
         <is>
           <t>%</t>
         </is>
       </c>
-      <c r="E60" s="12" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="B61" s="10" t="inlineStr">
+      <c r="E63" s="12" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="B64" s="10" t="inlineStr">
         <is>
           <t>kg/Batch (Batch size × Yield)</t>
         </is>
       </c>
-      <c r="C61" s="20">
+      <c r="C64" s="20">
         <f>B_SIZE*B_YIELD</f>
         <v>198</v>
       </c>
-      <c r="D61" s="5" t="inlineStr">
+      <c r="D64" s="5" t="inlineStr">
         <is>
           <t>kg/Batch</t>
         </is>
       </c>
-      <c r="E61" s="12" t="inlineStr">
+      <c r="E64" s="12" t="inlineStr">
         <is>
           <t>200 × 99% = 198 kg</t>
-        </is>
-      </c>
-    </row>
-    <row r="62">
-      <c r="B62" s="10" t="inlineStr">
-        <is>
-          <t>Batch time (협의)</t>
-        </is>
-      </c>
-      <c r="C62" s="11" t="n">
-        <v>55</v>
-      </c>
-      <c r="D62" s="5" t="inlineStr">
-        <is>
-          <t>h</t>
-        </is>
-      </c>
-      <c r="E62" s="12" t="inlineStr">
-        <is>
-          <t>준비·투입 ~ FQC (IQC~FQC 57 h − IQC 2 h)</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="B63" s="10" t="inlineStr">
-        <is>
-          <t>원단위</t>
-        </is>
-      </c>
-      <c r="C63" s="21" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="D63" s="5" t="inlineStr"/>
-      <c r="E63" s="12" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="B64" s="10" t="inlineStr">
-        <is>
-          <t>정제기 1대 월 Batch (계획)</t>
-        </is>
-      </c>
-      <c r="C64" s="14" t="n">
-        <v>12</v>
-      </c>
-      <c r="D64" s="5" t="inlineStr">
-        <is>
-          <t>Batch/월</t>
-        </is>
-      </c>
-      <c r="E64" s="12" t="inlineStr">
-        <is>
-          <t>12 × 198 = 2,376 kg</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="B65" s="10" t="inlineStr">
         <is>
-          <t>정제기 2대 월 Batch (계획)</t>
-        </is>
-      </c>
-      <c r="C65" s="14" t="n">
-        <v>20</v>
+          <t>Batch time (협의)</t>
+        </is>
+      </c>
+      <c r="C65" s="11" t="n">
+        <v>55</v>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>Batch/월</t>
+          <t>h</t>
         </is>
       </c>
       <c r="E65" s="12" t="inlineStr">
         <is>
-          <t>20 × 198 = 3,960 kg</t>
+          <t>준비·투입 ~ FQC (IQC~FQC 57 h − IQC 2 h)</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="B66" s="10" t="inlineStr">
         <is>
+          <t>원단위</t>
+        </is>
+      </c>
+      <c r="C66" s="21" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="D66" s="5" t="inlineStr"/>
+      <c r="E66" s="12" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="B67" s="10" t="inlineStr">
+        <is>
+          <t>정제기 1대 월 Batch (계획)</t>
+        </is>
+      </c>
+      <c r="C67" s="14" t="n">
+        <v>12</v>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>Batch/월</t>
+        </is>
+      </c>
+      <c r="E67" s="12" t="inlineStr">
+        <is>
+          <t>12 × 198 = 2,376 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="B68" s="10" t="inlineStr">
+        <is>
+          <t>정제기 2대 월 Batch (계획)</t>
+        </is>
+      </c>
+      <c r="C68" s="14" t="n">
+        <v>20</v>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>Batch/월</t>
+        </is>
+      </c>
+      <c r="E68" s="12" t="inlineStr">
+        <is>
+          <t>20 × 198 = 3,960 kg</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="B69" s="10" t="inlineStr">
+        <is>
           <t>대정비 월 Batch ('27.4)</t>
         </is>
       </c>
-      <c r="C66" s="14" t="n">
+      <c r="C69" s="14" t="n">
         <v>6</v>
       </c>
-      <c r="D66" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>Batch/월</t>
         </is>
       </c>
-      <c r="E66" s="12" t="inlineStr">
+      <c r="E69" s="12" t="inlineStr">
         <is>
           <t>6 × 198 = 1,188 kg</t>
         </is>
       </c>
     </row>
-    <row r="68" ht="20" customHeight="1">
-      <c r="B68" s="7" t="inlineStr">
+    <row r="71" ht="20" customHeight="1">
+      <c r="B71" s="7" t="inlineStr">
         <is>
           <t>E. Capa. 기준</t>
         </is>
       </c>
     </row>
-    <row r="69">
-      <c r="B69" s="8" t="inlineStr">
+    <row r="72">
+      <c r="B72" s="8" t="inlineStr">
         <is>
           <t>항목</t>
         </is>
       </c>
-      <c r="C69" s="9" t="inlineStr">
+      <c r="C72" s="9" t="inlineStr">
         <is>
           <t>값</t>
         </is>
       </c>
-      <c r="D69" s="9" t="inlineStr">
+      <c r="D72" s="9" t="inlineStr">
         <is>
           <t>단위</t>
         </is>
       </c>
-      <c r="E69" s="8" t="inlineStr">
+      <c r="E72" s="8" t="inlineStr">
         <is>
           <t>설명</t>
         </is>
       </c>
     </row>
-    <row r="70">
-      <c r="B70" s="10" t="inlineStr">
+    <row r="73">
+      <c r="B73" s="10" t="inlineStr">
         <is>
           <t>현재 연간 Capa.</t>
         </is>
       </c>
-      <c r="C70" s="22" t="n">
+      <c r="C73" s="22" t="n">
         <v>26.2</v>
       </c>
-      <c r="D70" s="5" t="inlineStr">
+      <c r="D73" s="5" t="inlineStr">
         <is>
           <t>t/년</t>
         </is>
       </c>
-      <c r="E70" s="12" t="inlineStr"/>
-    </row>
-    <row r="71">
-      <c r="B71" s="10" t="inlineStr">
+      <c r="E73" s="12" t="inlineStr"/>
+    </row>
+    <row r="74">
+      <c r="B74" s="10" t="inlineStr">
         <is>
           <t>리플럭스 증가분</t>
         </is>
       </c>
-      <c r="C71" s="22" t="n">
+      <c r="C74" s="22" t="n">
         <v>21</v>
       </c>
-      <c r="D71" s="5" t="inlineStr">
+      <c r="D74" s="5" t="inlineStr">
         <is>
           <t>t/년</t>
         </is>
       </c>
-      <c r="E71" s="12" t="inlineStr"/>
-    </row>
-    <row r="72">
-      <c r="B72" s="10" t="inlineStr">
+      <c r="E74" s="12" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="B75" s="10" t="inlineStr">
         <is>
           <t>개선 후 연간 Capa.</t>
         </is>
       </c>
-      <c r="C72" s="23">
+      <c r="C75" s="23">
         <f>CAPA_NOW+CAPA_ADD</f>
         <v>47.2</v>
       </c>
-      <c r="D72" s="5" t="inlineStr">
+      <c r="D75" s="5" t="inlineStr">
         <is>
           <t>t/년</t>
         </is>
       </c>
-      <c r="E72" s="12" t="inlineStr">
+      <c r="E75" s="12" t="inlineStr">
         <is>
           <t>현재의 2배(52.4) 아님 — Mix·Premix 준비 등</t>
         </is>
       </c>
     </row>
-    <row r="73">
-      <c r="B73" s="10" t="inlineStr">
+    <row r="76">
+      <c r="B76" s="10" t="inlineStr">
         <is>
           <t>정제기 2대 계획 연간 (20 Batch × 12)</t>
         </is>
       </c>
-      <c r="C73" s="23">
+      <c r="C76" s="23">
         <f>MB_TWO*KG_B*12/1000</f>
         <v>47.52</v>
       </c>
-      <c r="D73" s="5" t="inlineStr">
+      <c r="D76" s="5" t="inlineStr">
         <is>
           <t>t/년</t>
         </is>
       </c>
-      <c r="E73" s="12" t="inlineStr">
+      <c r="E76" s="12" t="inlineStr">
         <is>
           <t>47.2톤 계획 수준</t>
         </is>
       </c>
     </row>
-    <row r="75" ht="20" customHeight="1">
-      <c r="B75" s="7" t="inlineStr">
+    <row r="78" ht="20" customHeight="1">
+      <c r="B78" s="7" t="inlineStr">
         <is>
           <t>I. 생산계획 Batch 완료일 — 완료일 = 해당 Batch의 생산 및 충진 완료 예정일 (Batch마다 독립)</t>
         </is>
       </c>
     </row>
-    <row r="76">
-      <c r="B76" s="8" t="inlineStr">
+    <row r="79">
+      <c r="B79" s="8" t="inlineStr">
         <is>
           <t>Batch No.</t>
         </is>
       </c>
-      <c r="C76" s="9" t="inlineStr">
+      <c r="C79" s="9" t="inlineStr">
         <is>
           <t>완료일</t>
         </is>
       </c>
-      <c r="D76" s="8" t="inlineStr">
+      <c r="D79" s="8" t="inlineStr">
         <is>
           <t>비고</t>
         </is>
       </c>
-    </row>
-    <row r="77">
-      <c r="B77" s="24" t="inlineStr">
-        <is>
-          <t>#81</t>
-        </is>
-      </c>
-      <c r="C77" s="15" t="n">
-        <v>46293</v>
-      </c>
-      <c r="D77" s="18" t="inlineStr">
-        <is>
-          <t>9월 마지막 Batch (간격 기준점)</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="B78" s="24" t="inlineStr">
-        <is>
-          <t>#82</t>
-        </is>
-      </c>
-      <c r="C78" s="15" t="n">
-        <v>46296</v>
-      </c>
-      <c r="D78" s="18" t="inlineStr"/>
-    </row>
-    <row r="79">
-      <c r="B79" s="24" t="inlineStr">
-        <is>
-          <t>#83</t>
-        </is>
-      </c>
-      <c r="C79" s="15" t="n">
-        <v>46299</v>
-      </c>
-      <c r="D79" s="18" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="B80" s="24" t="inlineStr">
         <is>
-          <t>#84</t>
+          <t>#81</t>
         </is>
       </c>
       <c r="C80" s="15" t="n">
-        <v>46302</v>
-      </c>
-      <c r="D80" s="18" t="inlineStr"/>
+        <v>46293</v>
+      </c>
+      <c r="D80" s="18" t="inlineStr">
+        <is>
+          <t>9월 마지막 Batch (간격 기준점)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="B81" s="24" t="inlineStr">
         <is>
-          <t>#85</t>
+          <t>#82</t>
         </is>
       </c>
       <c r="C81" s="15" t="n">
-        <v>46305</v>
+        <v>46296</v>
       </c>
       <c r="D81" s="18" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="B82" s="24" t="inlineStr">
         <is>
-          <t>#86</t>
+          <t>#83</t>
         </is>
       </c>
       <c r="C82" s="15" t="n">
-        <v>46307</v>
+        <v>46299</v>
       </c>
       <c r="D82" s="18" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="B83" s="24" t="inlineStr">
         <is>
-          <t>#87</t>
+          <t>#84</t>
         </is>
       </c>
       <c r="C83" s="15" t="n">
-        <v>46310</v>
+        <v>46302</v>
       </c>
       <c r="D83" s="18" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="B84" s="24" t="inlineStr">
         <is>
-          <t>#88</t>
+          <t>#85</t>
         </is>
       </c>
       <c r="C84" s="15" t="n">
-        <v>46313</v>
+        <v>46305</v>
       </c>
       <c r="D84" s="18" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="B85" s="24" t="inlineStr">
         <is>
-          <t>#89</t>
+          <t>#86</t>
         </is>
       </c>
       <c r="C85" s="15" t="n">
-        <v>46315</v>
+        <v>46307</v>
       </c>
       <c r="D85" s="18" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="B86" s="24" t="inlineStr">
         <is>
-          <t>#90</t>
+          <t>#87</t>
         </is>
       </c>
       <c r="C86" s="15" t="n">
-        <v>46318</v>
+        <v>46310</v>
       </c>
       <c r="D86" s="18" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="B87" s="24" t="inlineStr">
         <is>
-          <t>#91</t>
+          <t>#88</t>
         </is>
       </c>
       <c r="C87" s="15" t="n">
-        <v>46321</v>
+        <v>46313</v>
       </c>
       <c r="D87" s="18" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="B88" s="24" t="inlineStr">
         <is>
+          <t>#89</t>
+        </is>
+      </c>
+      <c r="C88" s="15" t="n">
+        <v>46315</v>
+      </c>
+      <c r="D88" s="18" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="B89" s="24" t="inlineStr">
+        <is>
+          <t>#90</t>
+        </is>
+      </c>
+      <c r="C89" s="15" t="n">
+        <v>46318</v>
+      </c>
+      <c r="D89" s="18" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="B90" s="24" t="inlineStr">
+        <is>
+          <t>#91</t>
+        </is>
+      </c>
+      <c r="C90" s="15" t="n">
+        <v>46321</v>
+      </c>
+      <c r="D90" s="18" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="B91" s="24" t="inlineStr">
+        <is>
           <t>#92</t>
         </is>
       </c>
-      <c r="C88" s="15" t="n">
+      <c r="C91" s="15" t="n">
         <v>46324</v>
       </c>
-      <c r="D88" s="18" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="B89" s="18" t="inlineStr">
+      <c r="D91" s="18" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="B92" s="18" t="inlineStr">
         <is>
           <t>10월 완료 #82~#92 = 11 Batch · 행을 추가하면 03_Batch주기 계산 범위도 같이 조정</t>
         </is>
@@ -2333,17 +2393,17 @@
       </c>
       <c r="C16" s="50" t="inlineStr">
         <is>
-          <t>9병 18 h 작업, 근무시간 반영 시 약 2일 · 개선 방향 1~1.5일 · 18 h → 9 h 방안 검토</t>
+          <t>9병 18 h 작업 · 충진은 보통 상근조(08:00~17:00, 점심 12~13시 제외 = 8 h/일)만 진행 → 약 2일 · 개선 방향 1~1.5일 · 18 h → 9 h 방안 검토</t>
         </is>
       </c>
       <c r="D16" s="50" t="inlineStr">
         <is>
-          <t>2 h/병 · 18 h 유지 (개선은 미반영)</t>
+          <t>2 h/병 · 18 h 유지 · 상근조 8 h/일 기준 약 2일 (개선은 미반영)</t>
         </is>
       </c>
       <c r="E16" s="50" t="inlineStr">
         <is>
-          <t>교대·연장근무 · 충진 인원</t>
+          <t>18 h ÷ 8 h = 2.25일 → 9병째가 3일차로 넘어가는지 · 연장근무·교대 충진 가능 여부 · 인원</t>
         </is>
       </c>
     </row>
@@ -3904,7 +3964,7 @@
     <row r="22">
       <c r="B22" s="10" t="inlineStr">
         <is>
-          <t>5 Gal 9병 충진 경과 (근무시간 반영)</t>
+          <t>5 Gal 9병 충진 경과 (상근조 8 h/일)</t>
         </is>
       </c>
       <c r="C22" s="28">
@@ -3918,7 +3978,7 @@
       </c>
       <c r="E22" s="18" t="inlineStr">
         <is>
-          <t>현장 설명 약 2일 · 교대·연장근무 조건 확인</t>
+          <t>상근조 08~17시 · 점심 1 h 제외 → 현장 설명 약 2일</t>
         </is>
       </c>
     </row>
@@ -4041,11 +4101,11 @@
     </row>
     <row r="6">
       <c r="B6" s="5" t="str">
-        <f>'01_입력'!B77</f>
+        <f>'01_입력'!B80</f>
         <v>#81</v>
       </c>
       <c r="C6" s="29">
-        <f>'01_입력'!C77</f>
+        <f>'01_입력'!C80</f>
         <v>46293.0</v>
       </c>
       <c r="D6" s="5" t="str">
@@ -4065,11 +4125,11 @@
     </row>
     <row r="7">
       <c r="B7" s="5" t="str">
-        <f>'01_입력'!B78</f>
+        <f>'01_입력'!B81</f>
         <v>#82</v>
       </c>
       <c r="C7" s="29">
-        <f>'01_입력'!C78</f>
+        <f>'01_입력'!C81</f>
         <v>46296.0</v>
       </c>
       <c r="D7" s="5" t="str">
@@ -4095,11 +4155,11 @@
     </row>
     <row r="8">
       <c r="B8" s="5" t="str">
-        <f>'01_입력'!B79</f>
+        <f>'01_입력'!B82</f>
         <v>#83</v>
       </c>
       <c r="C8" s="29">
-        <f>'01_입력'!C79</f>
+        <f>'01_입력'!C82</f>
         <v>46299.0</v>
       </c>
       <c r="D8" s="5" t="str">
@@ -4125,11 +4185,11 @@
     </row>
     <row r="9">
       <c r="B9" s="5" t="str">
-        <f>'01_입력'!B80</f>
+        <f>'01_입력'!B83</f>
         <v>#84</v>
       </c>
       <c r="C9" s="29">
-        <f>'01_입력'!C80</f>
+        <f>'01_입력'!C83</f>
         <v>46302.0</v>
       </c>
       <c r="D9" s="5" t="str">
@@ -4155,11 +4215,11 @@
     </row>
     <row r="10">
       <c r="B10" s="5" t="str">
-        <f>'01_입력'!B81</f>
+        <f>'01_입력'!B84</f>
         <v>#85</v>
       </c>
       <c r="C10" s="29">
-        <f>'01_입력'!C81</f>
+        <f>'01_입력'!C84</f>
         <v>46305.0</v>
       </c>
       <c r="D10" s="5" t="str">
@@ -4185,11 +4245,11 @@
     </row>
     <row r="11">
       <c r="B11" s="5" t="str">
-        <f>'01_입력'!B82</f>
+        <f>'01_입력'!B85</f>
         <v>#86</v>
       </c>
       <c r="C11" s="29">
-        <f>'01_입력'!C82</f>
+        <f>'01_입력'!C85</f>
         <v>46307.0</v>
       </c>
       <c r="D11" s="5" t="str">
@@ -4215,11 +4275,11 @@
     </row>
     <row r="12">
       <c r="B12" s="5" t="str">
-        <f>'01_입력'!B83</f>
+        <f>'01_입력'!B86</f>
         <v>#87</v>
       </c>
       <c r="C12" s="29">
-        <f>'01_입력'!C83</f>
+        <f>'01_입력'!C86</f>
         <v>46310.0</v>
       </c>
       <c r="D12" s="5" t="str">
@@ -4245,11 +4305,11 @@
     </row>
     <row r="13">
       <c r="B13" s="5" t="str">
-        <f>'01_입력'!B84</f>
+        <f>'01_입력'!B87</f>
         <v>#88</v>
       </c>
       <c r="C13" s="29">
-        <f>'01_입력'!C84</f>
+        <f>'01_입력'!C87</f>
         <v>46313.0</v>
       </c>
       <c r="D13" s="5" t="str">
@@ -4275,11 +4335,11 @@
     </row>
     <row r="14">
       <c r="B14" s="5" t="str">
-        <f>'01_입력'!B85</f>
+        <f>'01_입력'!B88</f>
         <v>#89</v>
       </c>
       <c r="C14" s="29">
-        <f>'01_입력'!C85</f>
+        <f>'01_입력'!C88</f>
         <v>46315.0</v>
       </c>
       <c r="D14" s="5" t="str">
@@ -4305,11 +4365,11 @@
     </row>
     <row r="15">
       <c r="B15" s="5" t="str">
-        <f>'01_입력'!B86</f>
+        <f>'01_입력'!B89</f>
         <v>#90</v>
       </c>
       <c r="C15" s="29">
-        <f>'01_입력'!C86</f>
+        <f>'01_입력'!C89</f>
         <v>46318.0</v>
       </c>
       <c r="D15" s="5" t="str">
@@ -4335,11 +4395,11 @@
     </row>
     <row r="16">
       <c r="B16" s="5" t="str">
-        <f>'01_입력'!B87</f>
+        <f>'01_입력'!B90</f>
         <v>#91</v>
       </c>
       <c r="C16" s="29">
-        <f>'01_입력'!C87</f>
+        <f>'01_입력'!C90</f>
         <v>46321.0</v>
       </c>
       <c r="D16" s="5" t="str">
@@ -4365,11 +4425,11 @@
     </row>
     <row r="17">
       <c r="B17" s="5" t="str">
-        <f>'01_입력'!B88</f>
+        <f>'01_입력'!B91</f>
         <v>#92</v>
       </c>
       <c r="C17" s="29">
-        <f>'01_입력'!C88</f>
+        <f>'01_입력'!C91</f>
         <v>46324.0</v>
       </c>
       <c r="D17" s="5" t="str">
@@ -4602,7 +4662,7 @@
     <row r="32">
       <c r="B32" s="10" t="inlineStr">
         <is>
-          <t>5 Gal 9병 충진 (근무시간)</t>
+          <t>5 Gal 9병 충진 (상근조)</t>
         </is>
       </c>
       <c r="C32" s="17">
@@ -4627,7 +4687,7 @@
       </c>
       <c r="H32" s="12" t="inlineStr">
         <is>
-          <t>1교대 · 현장 설명 약 2일</t>
+          <t>상근조 8 h/일 · 현장 설명 약 2일</t>
         </is>
       </c>
     </row>
@@ -10324,7 +10384,7 @@
     <row r="9">
       <c r="B9" s="10" t="inlineStr">
         <is>
-          <t>글로브 박스 가용 h (1교대)</t>
+          <t>글로브 박스 가용 h (상근조)</t>
         </is>
       </c>
       <c r="C9" s="30">
